--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MUSAB EDER ÇİFTLİĞİ — KÜMES (A+B BLOK) VE MÜŞTEMİLAT — Kocaeli İli Karamürsel İlçesi İnebeyli Mahallesi 138 ada 17 parsel (7.966,67 m²)</t>
+          <t>MUSAB EDER ÇİFTLİĞİ KANATLI (ETLİK PİLİÇ) KÜMESİ — Kocaeli İli Karamürsel İlçesi İnebeyli Mahallesi 138 ada 17 parsel (7.966,67 m²)</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MUSAB EDER ÇİFTLİĞİ — KÜMES (A+B BLOK) VE MÜŞTEMİLAT — Kocaeli İli Karamürsel İlçesi İnebeyli Mahallesi 138 ada 17 parsel (7.966,67 m²)</t>
+          <t>MUSAB EDER ÇİFTLİĞİ KANATLI (ETLİK PİLİÇ) KÜMESİ — Kocaeli İli Karamürsel İlçesi İnebeyli Mahallesi 138 ada 17 parsel (7.966,67 m²)</t>
         </is>
       </c>
     </row>
@@ -16555,7 +16555,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MUSAB EDER ÇİFTLİĞİ — KÜMES (A+B BLOK) VE MÜŞTEMİLAT — Kocaeli İli Karamürsel İlçesi İnebeyli Mahallesi 138 ada 17 parsel (7.966,67 m²)</t>
+          <t>MUSAB EDER ÇİFTLİĞİ KANATLI (ETLİK PİLİÇ) KÜMESİ — Kocaeli İli Karamürsel İlçesi İnebeyli Mahallesi 138 ada 17 parsel (7.966,67 m²)</t>
         </is>
       </c>
     </row>
@@ -19703,7 +19703,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MUSAB EDER ÇİFTLİĞİ — KÜMES (A+B BLOK) VE MÜŞTEMİLAT — Kocaeli İli Karamürsel İlçesi İnebeyli Mahallesi 138 ada 17 parsel (7.966,67 m²)</t>
+          <t>MUSAB EDER ÇİFTLİĞİ KANATLI (ETLİK PİLİÇ) KÜMESİ — Kocaeli İli Karamürsel İlçesi İnebeyli Mahallesi 138 ada 17 parsel (7.966,67 m²)</t>
         </is>
       </c>
     </row>

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:F170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3714,14 +3714,14 @@
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
+          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
         </is>
       </c>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
+          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
         </is>
       </c>
       <c r="B138" s="6" t="n"/>
@@ -3773,12 +3773,12 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.120.1101</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
@@ -3787,382 +3787,354 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>260.942</v>
+        <v>88.75</v>
       </c>
     </row>
     <row r="141" ht="31.5" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="n">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="142" ht="31.5" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
+      <c r="B142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D141" s="11" t="inlineStr">
+      <c r="D142" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E141" s="12" t="inlineStr">
+      <c r="E142" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F141" s="13" t="n">
+      <c r="F142" s="13" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="144" ht="21" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F144" s="13" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="145"/>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="24" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="n"/>
+      <c r="C147" s="6" t="n"/>
+      <c r="D147" s="6" t="n"/>
+      <c r="E147" s="6" t="n"/>
+      <c r="F147" s="6" t="n"/>
+    </row>
+    <row r="148" ht="28" customHeight="1">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F149" s="13" t="n">
+        <v>260.942</v>
+      </c>
+    </row>
+    <row r="150" ht="31.5" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F150" s="13" t="n">
         <v>1.566</v>
       </c>
     </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B142" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" s="10" t="inlineStr">
+      <c r="B151" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D142" s="11" t="inlineStr">
+      <c r="D151" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E142" s="12" t="inlineStr">
+      <c r="E151" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F142" s="13" t="n">
+      <c r="F151" s="13" t="n">
         <v>14.4</v>
       </c>
     </row>
-    <row r="143" ht="21" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="152" ht="21" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
+      <c r="B152" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr">
+      <c r="D152" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E143" s="12" t="inlineStr">
+      <c r="E152" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F143" s="13" t="n">
+      <c r="F152" s="13" t="n">
         <v>0.141</v>
       </c>
     </row>
-    <row r="144" ht="14" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>Çevre düzenlemesi ve çit işleri</t>
         </is>
       </c>
-      <c r="B144" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" s="10" t="inlineStr">
+      <c r="B153" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
         <is>
           <t>TKDK-0091</t>
         </is>
       </c>
-      <c r="D144" s="11" t="inlineStr">
+      <c r="D153" s="11" t="inlineStr">
         <is>
           <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
         </is>
       </c>
-      <c r="E144" s="12" t="inlineStr">
+      <c r="E153" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F144" s="13" t="n">
+      <c r="F153" s="13" t="n">
         <v>361.04</v>
       </c>
     </row>
-    <row r="145" ht="21" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="154" ht="21" customHeight="1">
+      <c r="A154" s="8" t="inlineStr">
         <is>
           <t>Kanalizasyon işleri</t>
         </is>
       </c>
-      <c r="B145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
+      <c r="B154" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
         <is>
           <t>43.527.1001</t>
         </is>
       </c>
-      <c r="D145" s="11" t="inlineStr">
+      <c r="D154" s="11" t="inlineStr">
         <is>
           <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
-      <c r="E145" s="12" t="inlineStr">
+      <c r="E154" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F145" s="13" t="n">
+      <c r="F154" s="13" t="n">
         <v>50</v>
-      </c>
-    </row>
-    <row r="146" ht="14" customHeight="1">
-      <c r="A146" s="15" t="n"/>
-      <c r="B146" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C146" s="10" t="inlineStr">
-        <is>
-          <t>15.560.1003</t>
-        </is>
-      </c>
-      <c r="D146" s="11" t="inlineStr">
-        <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E146" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F146" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="147" ht="21" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
-        <is>
-          <t>30.100.1104</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F147" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" ht="14" customHeight="1">
-      <c r="A148" s="14" t="n"/>
-      <c r="B148" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C148" s="10" t="inlineStr">
-        <is>
-          <t>30.100.2106</t>
-        </is>
-      </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
-        </is>
-      </c>
-      <c r="E148" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F148" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" ht="14" customHeight="1">
-      <c r="A149" s="14" t="n"/>
-      <c r="B149" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>30.135.3201</t>
-        </is>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
-        </is>
-      </c>
-      <c r="E149" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F149" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" ht="14" customHeight="1">
-      <c r="A150" s="14" t="n"/>
-      <c r="B150" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
-        <is>
-          <t>30.110.1104</t>
-        </is>
-      </c>
-      <c r="D150" s="11" t="inlineStr">
-        <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
-        </is>
-      </c>
-      <c r="E150" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" ht="14" customHeight="1">
-      <c r="A151" s="14" t="n"/>
-      <c r="B151" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C151" s="10" t="inlineStr">
-        <is>
-          <t>30.115.1003</t>
-        </is>
-      </c>
-      <c r="D151" s="11" t="inlineStr">
-        <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
-        </is>
-      </c>
-      <c r="E151" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F151" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="14" t="n"/>
-      <c r="B152" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C152" s="10" t="inlineStr">
-        <is>
-          <t>30.140.3105</t>
-        </is>
-      </c>
-      <c r="D152" s="11" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
-        </is>
-      </c>
-      <c r="E152" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F152" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="153" ht="14" customHeight="1">
-      <c r="A153" s="14" t="n"/>
-      <c r="B153" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="C153" s="10" t="inlineStr">
-        <is>
-          <t>30.140.3101</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F153" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="154" ht="14" customHeight="1">
-      <c r="A154" s="14" t="n"/>
-      <c r="B154" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C154" s="10" t="inlineStr">
-        <is>
-          <t>30.172.1706</t>
-        </is>
-      </c>
-      <c r="D154" s="11" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
-        </is>
-      </c>
-      <c r="E154" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F154" s="13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="155" ht="14" customHeight="1">
       <c r="A155" s="15" t="n"/>
       <c r="B155" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>30.170.4002</t>
+          <t>15.560.1003</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>LED projektör, ışık akısı en az 5100 lm</t>
+          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
@@ -4174,63 +4146,280 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156"/>
-    <row r="157">
-      <c r="A157" s="16" t="inlineStr">
+    <row r="156" ht="21" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>30.100.1104</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F156" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="14" t="n"/>
+      <c r="B157" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>30.100.2106</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F157" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="14" t="n"/>
+      <c r="B158" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>30.135.3201</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F158" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" ht="14" customHeight="1">
+      <c r="A159" s="14" t="n"/>
+      <c r="B159" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>30.110.1104</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F159" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="14" t="n"/>
+      <c r="B160" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>30.115.1003</t>
+        </is>
+      </c>
+      <c r="D160" s="11" t="inlineStr">
+        <is>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F160" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="14" t="n"/>
+      <c r="B161" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>30.140.3105</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F161" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="14" t="n"/>
+      <c r="B162" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>30.140.3101</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F162" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="14" t="n"/>
+      <c r="B163" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>30.172.1706</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F163" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="15" t="n"/>
+      <c r="B164" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>30.170.4002</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>LED projektör, ışık akısı en az 5100 lm</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F164" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165"/>
+    <row r="166">
+      <c r="A166" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B157" s="6" t="n"/>
-      <c r="C157" s="6" t="n"/>
-      <c r="D157" s="6" t="n"/>
-      <c r="E157" s="6" t="n"/>
-      <c r="F157" s="6" t="n"/>
-    </row>
-    <row r="158" ht="13" customHeight="1">
-      <c r="A158" s="17" t="inlineStr">
+      <c r="B166" s="6" t="n"/>
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="6" t="n"/>
+      <c r="E166" s="6" t="n"/>
+      <c r="F166" s="6" t="n"/>
+    </row>
+    <row r="167" ht="13" customHeight="1">
+      <c r="A167" s="17" t="inlineStr">
         <is>
           <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="22" customHeight="1">
-      <c r="A159" s="17" t="inlineStr">
+    <row r="168" ht="22" customHeight="1">
+      <c r="A168" s="17" t="inlineStr">
         <is>
           <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="13" customHeight="1">
-      <c r="A160" s="17" t="inlineStr">
+    <row r="169" ht="13" customHeight="1">
+      <c r="A169" s="17" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="13" customHeight="1">
-      <c r="A161" s="17" t="inlineStr">
+    <row r="170" ht="13" customHeight="1">
+      <c r="A170" s="17" t="inlineStr">
         <is>
           <t>•  Elektrik tesisatı bölümü, kuvvetli akım birim fiyat listesi temin edildikten sonra tamamlanacaktır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="84">
-    <mergeCell ref="A158:F158"/>
+  <mergeCells count="91">
     <mergeCell ref="A52"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A160:F160"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A159:F159"/>
     <mergeCell ref="A123"/>
     <mergeCell ref="A132"/>
-    <mergeCell ref="A161:F161"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A133"/>
     <mergeCell ref="A95"/>
     <mergeCell ref="A104"/>
+    <mergeCell ref="A150"/>
     <mergeCell ref="A144"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A97"/>
@@ -4239,19 +4428,24 @@
     <mergeCell ref="A29"/>
     <mergeCell ref="A134"/>
     <mergeCell ref="A96"/>
+    <mergeCell ref="A152"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A154:A155"/>
     <mergeCell ref="A73"/>
     <mergeCell ref="A51"/>
     <mergeCell ref="A107"/>
     <mergeCell ref="A124"/>
     <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A167:F167"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A108"/>
     <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A149"/>
+    <mergeCell ref="A169:F169"/>
     <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A151"/>
     <mergeCell ref="A126"/>
     <mergeCell ref="A141"/>
     <mergeCell ref="A135"/>
@@ -4265,15 +4459,18 @@
     <mergeCell ref="A30"/>
     <mergeCell ref="A114"/>
     <mergeCell ref="A31:A46"/>
+    <mergeCell ref="A156:A164"/>
+    <mergeCell ref="A153"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="A111:F111"/>
     <mergeCell ref="A54"/>
     <mergeCell ref="A65:A67"/>
     <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A157:F157"/>
+    <mergeCell ref="A166:F166"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A74:A89"/>
+    <mergeCell ref="A168:F168"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="A98:A99"/>
     <mergeCell ref="A116"/>
@@ -4289,14 +4486,16 @@
     <mergeCell ref="A9"/>
     <mergeCell ref="A143"/>
     <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A147:A155"/>
     <mergeCell ref="A142"/>
     <mergeCell ref="A11"/>
     <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A147:F147"/>
     <mergeCell ref="A94"/>
+    <mergeCell ref="A170:F170"/>
     <mergeCell ref="A138:F138"/>
     <mergeCell ref="A105"/>
     <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A146:F146"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A113"/>
     <mergeCell ref="A6:F6"/>
@@ -4313,7 +4512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J503"/>
+  <dimension ref="A1:J527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15134,7 +15333,7 @@
     <row r="444" ht="20" customHeight="1">
       <c r="A444" s="18" t="inlineStr">
         <is>
-          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
+          <t>Yapı/Bina Adı: YAĞMUR SUYU DEPOSU</t>
         </is>
       </c>
     </row>
@@ -15190,18 +15389,18 @@
         </is>
       </c>
     </row>
-    <row r="446" ht="15" customHeight="1">
+    <row r="446" ht="22" customHeight="1">
       <c r="A446" s="19" t="n">
         <v>1</v>
       </c>
       <c r="B446" s="20" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.120.1101</t>
         </is>
       </c>
       <c r="C446" s="8" t="inlineStr">
         <is>
-          <t>[M02]  Makine ile kaba tesviye kazısı — tesis içi yol güzergâhı</t>
+          <t>[M05]  Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
         </is>
       </c>
       <c r="D446" s="21" t="inlineStr">
@@ -15221,7 +15420,7 @@
       <c r="B447" s="6" t="n"/>
       <c r="C447" s="23" t="inlineStr">
         <is>
-          <t>Tesis içi yol güzergâhı: 745,57 m² alan, ortalama 5,00 m genişlik -&gt; 149,11 m uzunluk</t>
+          <t>Yağmur suyu deposu: dış 3.00x3.00; 1,00 m çalışma payı -&gt; 5.00x5.00; derinlik 3.55 m</t>
         </is>
       </c>
       <c r="D447" s="6" t="n"/>
@@ -15232,10 +15431,10 @@
         <v>5</v>
       </c>
       <c r="G447" s="29" t="n">
-        <v>149.11</v>
+        <v>5</v>
       </c>
       <c r="H447" s="29" t="n">
-        <v>0.35</v>
+        <v>3.55</v>
       </c>
       <c r="I447" s="24">
         <f>E447*F447*G447*H447</f>
@@ -15248,7 +15447,7 @@
       <c r="B448" s="22" t="n"/>
       <c r="C448" s="25" t="inlineStr">
         <is>
-          <t>M02 TOPLAMI</t>
+          <t>M05 TOPLAMI</t>
         </is>
       </c>
       <c r="D448" s="26" t="inlineStr">
@@ -15272,17 +15471,17 @@
       </c>
       <c r="B449" s="20" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="C449" s="8" t="inlineStr">
         <is>
-          <t>[M46]  1,50 m yükseklikte sıcak daldırma galvanizli tel örgü ile çit yapılması</t>
+          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
         </is>
       </c>
       <c r="D449" s="21" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E449" s="22" t="n"/>
@@ -15292,63 +15491,73 @@
       <c r="I449" s="22" t="n"/>
       <c r="J449" s="22" t="n"/>
     </row>
-    <row r="450" ht="30" customHeight="1">
+    <row r="450" ht="12" customHeight="1">
       <c r="A450" s="6" t="n"/>
       <c r="B450" s="6" t="n"/>
       <c r="C450" s="23" t="inlineStr">
         <is>
-          <t>Parsel 7.966,67 m²; yerleşim planındaki cephe 113,04 m, buna karşılık gelen derinlik 7.966,67/113,04 = 70,48 m; çevre 2x(113,04+70,48)</t>
+          <t>Yağmur suyu deposu (3.00x3.00 + 0,10 taşma)</t>
         </is>
       </c>
       <c r="D450" s="6" t="n"/>
       <c r="E450" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F450" s="6" t="n"/>
+      <c r="F450" s="29" t="n">
+        <v>3.2</v>
+      </c>
       <c r="G450" s="29" t="n">
-        <v>367.04</v>
-      </c>
-      <c r="H450" s="6" t="n"/>
+        <v>3.2</v>
+      </c>
+      <c r="H450" s="29" t="n">
+        <v>0.1</v>
+      </c>
       <c r="I450" s="24">
-        <f>E450*G450</f>
+        <f>E450*F450*G450*H450</f>
         <v/>
       </c>
       <c r="J450" s="6" t="n"/>
     </row>
-    <row r="451" ht="12" customHeight="1">
-      <c r="A451" s="6" t="n"/>
-      <c r="B451" s="6" t="n"/>
-      <c r="C451" s="23" t="inlineStr">
-        <is>
-          <t>Giriş kapısı açıklığı düşülür</t>
-        </is>
-      </c>
-      <c r="D451" s="6" t="n"/>
-      <c r="E451" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F451" s="6" t="n"/>
-      <c r="G451" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H451" s="6" t="n"/>
-      <c r="I451" s="24">
-        <f>-E451*G451</f>
-        <v/>
-      </c>
-      <c r="J451" s="6" t="n"/>
-    </row>
-    <row r="452">
-      <c r="A452" s="22" t="n"/>
-      <c r="B452" s="22" t="n"/>
-      <c r="C452" s="25" t="inlineStr">
-        <is>
-          <t>M46 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D452" s="26" t="inlineStr">
-        <is>
-          <t>m</t>
+    <row r="451">
+      <c r="A451" s="22" t="n"/>
+      <c r="B451" s="22" t="n"/>
+      <c r="C451" s="25" t="inlineStr">
+        <is>
+          <t>M11 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D451" s="26" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E451" s="22" t="n"/>
+      <c r="F451" s="22" t="n"/>
+      <c r="G451" s="22" t="n"/>
+      <c r="H451" s="22" t="n"/>
+      <c r="I451" s="22" t="n"/>
+      <c r="J451" s="27">
+        <f>SUM(I450:I450)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="452" ht="22" customHeight="1">
+      <c r="A452" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B452" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="C452" s="8" t="inlineStr">
+        <is>
+          <t>[M16]  C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
+        </is>
+      </c>
+      <c r="D452" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
         </is>
       </c>
       <c r="E452" s="22" t="n"/>
@@ -15356,56 +15565,58 @@
       <c r="G452" s="22" t="n"/>
       <c r="H452" s="22" t="n"/>
       <c r="I452" s="22" t="n"/>
-      <c r="J452" s="27">
-        <f>SUM(I450:I451)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="453" ht="22" customHeight="1">
-      <c r="A453" s="19" t="n">
+      <c r="J452" s="22" t="n"/>
+    </row>
+    <row r="453" ht="12" customHeight="1">
+      <c r="A453" s="6" t="n"/>
+      <c r="B453" s="6" t="n"/>
+      <c r="C453" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu radye 30 cm (dış 3.00x3.00)</t>
+        </is>
+      </c>
+      <c r="D453" s="6" t="n"/>
+      <c r="E453" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F453" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B453" s="20" t="inlineStr">
-        <is>
-          <t>43.527.1001</t>
-        </is>
-      </c>
-      <c r="C453" s="8" t="inlineStr">
-        <is>
-          <t>[M59]  ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
-        </is>
-      </c>
-      <c r="D453" s="21" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E453" s="22" t="n"/>
-      <c r="F453" s="22" t="n"/>
-      <c r="G453" s="22" t="n"/>
-      <c r="H453" s="22" t="n"/>
-      <c r="I453" s="22" t="n"/>
-      <c r="J453" s="22" t="n"/>
-    </row>
-    <row r="454" ht="12" customHeight="1">
+      <c r="G453" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H453" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I453" s="24">
+        <f>E453*F453*G453*H453</f>
+        <v/>
+      </c>
+      <c r="J453" s="6" t="n"/>
+    </row>
+    <row r="454" ht="20" customHeight="1">
       <c r="A454" s="6" t="n"/>
       <c r="B454" s="6" t="n"/>
       <c r="C454" s="23" t="inlineStr">
         <is>
-          <t>Kümes A blok servis bölümü - foseptik</t>
+          <t>Yağmur suyu deposu perdeleri: orta çevre 2x(2.75+2.75) = 11.00 m</t>
         </is>
       </c>
       <c r="D454" s="6" t="n"/>
       <c r="E454" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F454" s="6" t="n"/>
+      <c r="F454" s="29" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G454" s="29" t="n">
-        <v>25</v>
-      </c>
-      <c r="H454" s="6" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="H454" s="29" t="n">
+        <v>3</v>
+      </c>
       <c r="I454" s="24">
-        <f>E454*G454</f>
+        <f>E454*F454*G454*H454</f>
         <v/>
       </c>
       <c r="J454" s="6" t="n"/>
@@ -15415,20 +15626,24 @@
       <c r="B455" s="6" t="n"/>
       <c r="C455" s="23" t="inlineStr">
         <is>
-          <t>Kümes B blok servis bölümü - foseptik</t>
+          <t>Yağmur suyu deposu üst döşemesi 15 cm</t>
         </is>
       </c>
       <c r="D455" s="6" t="n"/>
       <c r="E455" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F455" s="6" t="n"/>
+      <c r="F455" s="29" t="n">
+        <v>3</v>
+      </c>
       <c r="G455" s="29" t="n">
-        <v>25</v>
-      </c>
-      <c r="H455" s="6" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H455" s="29" t="n">
+        <v>0.15</v>
+      </c>
       <c r="I455" s="24">
-        <f>E455*G455</f>
+        <f>E455*F455*G455*H455</f>
         <v/>
       </c>
       <c r="J455" s="6" t="n"/>
@@ -15438,12 +15653,12 @@
       <c r="B456" s="22" t="n"/>
       <c r="C456" s="25" t="inlineStr">
         <is>
-          <t>M59 TOPLAMI</t>
+          <t>M16 TOPLAMI</t>
         </is>
       </c>
       <c r="D456" s="26" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E456" s="22" t="n"/>
@@ -15452,7 +15667,7 @@
       <c r="H456" s="22" t="n"/>
       <c r="I456" s="22" t="n"/>
       <c r="J456" s="27">
-        <f>SUM(I454:I455)</f>
+        <f>SUM(I453:I455)</f>
         <v/>
       </c>
     </row>
@@ -15462,17 +15677,17 @@
       </c>
       <c r="B457" s="20" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="C457" s="8" t="inlineStr">
         <is>
-          <t>[M61A]  C 25/30 hazır beton dökülmesi — betonarme rögarlar</t>
+          <t>[M20]  Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
         </is>
       </c>
       <c r="D457" s="21" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E457" s="22" t="n"/>
@@ -15482,29 +15697,27 @@
       <c r="I457" s="22" t="n"/>
       <c r="J457" s="22" t="n"/>
     </row>
-    <row r="458" ht="12" customHeight="1">
+    <row r="458" ht="20" customHeight="1">
       <c r="A458" s="6" t="n"/>
       <c r="B458" s="6" t="n"/>
       <c r="C458" s="23" t="inlineStr">
         <is>
-          <t>Dış prizma: 0,90 x 0,90 x 0,75; 4 adet</t>
+          <t>Yağmur suyu deposu radye çevresi 2x(3.00+3.00) = 12.00 m x 0,40</t>
         </is>
       </c>
       <c r="D458" s="6" t="n"/>
       <c r="E458" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F458" s="29" t="n">
-        <v>0.9</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F458" s="6" t="n"/>
       <c r="G458" s="29" t="n">
-        <v>0.9</v>
+        <v>12</v>
       </c>
       <c r="H458" s="29" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="I458" s="24">
-        <f>E458*F458*G458*H458</f>
+        <f>E458*G458*H458</f>
         <v/>
       </c>
       <c r="J458" s="6" t="n"/>
@@ -15514,66 +15727,60 @@
       <c r="B459" s="6" t="n"/>
       <c r="C459" s="23" t="inlineStr">
         <is>
-          <t>Net iç hacim düşülür: 0,60 x 0,60 x 0,60; 4 adet</t>
+          <t>Yağmur suyu deposu perde iki yüz (11.00 m x 3.00 m)</t>
         </is>
       </c>
       <c r="D459" s="6" t="n"/>
       <c r="E459" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F459" s="29" t="n">
-        <v>0.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F459" s="6" t="n"/>
       <c r="G459" s="29" t="n">
-        <v>0.6</v>
+        <v>11</v>
       </c>
       <c r="H459" s="29" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="I459" s="24">
-        <f>-E459*F459*G459*H459</f>
+        <f>E459*G459*H459</f>
         <v/>
       </c>
       <c r="J459" s="6" t="n"/>
     </row>
-    <row r="460">
-      <c r="A460" s="22" t="n"/>
-      <c r="B460" s="22" t="n"/>
-      <c r="C460" s="25" t="inlineStr">
-        <is>
-          <t>M61A TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D460" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E460" s="22" t="n"/>
-      <c r="F460" s="22" t="n"/>
-      <c r="G460" s="22" t="n"/>
-      <c r="H460" s="22" t="n"/>
-      <c r="I460" s="22" t="n"/>
-      <c r="J460" s="27">
-        <f>SUM(I458:I459)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="461" ht="22" customHeight="1">
-      <c r="A461" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B461" s="20" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C461" s="8" t="inlineStr">
-        <is>
-          <t>[M61B]  Düz yüzeyli beton ve betonarme kalıbı yapılması — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="D461" s="21" t="inlineStr">
+    <row r="460" ht="12" customHeight="1">
+      <c r="A460" s="6" t="n"/>
+      <c r="B460" s="6" t="n"/>
+      <c r="C460" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu tavan kalıbı</t>
+        </is>
+      </c>
+      <c r="D460" s="6" t="n"/>
+      <c r="E460" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F460" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G460" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H460" s="6" t="n"/>
+      <c r="I460" s="24">
+        <f>E460*F460*G460</f>
+        <v/>
+      </c>
+      <c r="J460" s="6" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="22" t="n"/>
+      <c r="B461" s="22" t="n"/>
+      <c r="C461" s="25" t="inlineStr">
+        <is>
+          <t>M20 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D461" s="26" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -15583,217 +15790,224 @@
       <c r="G461" s="22" t="n"/>
       <c r="H461" s="22" t="n"/>
       <c r="I461" s="22" t="n"/>
-      <c r="J461" s="22" t="n"/>
-    </row>
-    <row r="462" ht="12" customHeight="1">
-      <c r="A462" s="6" t="n"/>
-      <c r="B462" s="6" t="n"/>
-      <c r="C462" s="23" t="inlineStr">
-        <is>
-          <t>İç yüzler: 4 yüz x 0,60 x 0,60; 4 adet</t>
-        </is>
-      </c>
-      <c r="D462" s="6" t="n"/>
-      <c r="E462" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F462" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G462" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H462" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I462" s="24">
-        <f>E462*F462*G462*H462</f>
-        <v/>
-      </c>
-      <c r="J462" s="6" t="n"/>
+      <c r="J461" s="27">
+        <f>SUM(I458:I460)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="462" ht="22" customHeight="1">
+      <c r="A462" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B462" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="C462" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D462" s="21" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E462" s="22" t="n"/>
+      <c r="F462" s="22" t="n"/>
+      <c r="G462" s="22" t="n"/>
+      <c r="H462" s="22" t="n"/>
+      <c r="I462" s="22" t="n"/>
+      <c r="J462" s="22" t="n"/>
     </row>
     <row r="463" ht="12" customHeight="1">
       <c r="A463" s="6" t="n"/>
       <c r="B463" s="6" t="n"/>
       <c r="C463" s="23" t="inlineStr">
         <is>
-          <t>Dış yüzler: 4 yüz x 0,90 x 0,60; 4 adet</t>
+          <t>Yağmur suyu deposu radyesi: 3.00x3.00x0,30 m³, 100 kg/m³</t>
         </is>
       </c>
       <c r="D463" s="6" t="n"/>
       <c r="E463" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F463" s="29" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="G463" s="29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H463" s="29" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I463" s="24">
-        <f>E463*F463*G463*H463</f>
-        <v/>
-      </c>
-      <c r="J463" s="6" t="n"/>
-    </row>
-    <row r="464">
-      <c r="A464" s="22" t="n"/>
-      <c r="B464" s="22" t="n"/>
-      <c r="C464" s="25" t="inlineStr">
-        <is>
-          <t>M61B TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D464" s="26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E464" s="22" t="n"/>
-      <c r="F464" s="22" t="n"/>
-      <c r="G464" s="22" t="n"/>
-      <c r="H464" s="22" t="n"/>
-      <c r="I464" s="22" t="n"/>
-      <c r="J464" s="27">
-        <f>SUM(I462:I463)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="465" ht="15" customHeight="1">
-      <c r="A465" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B465" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C465" s="8" t="inlineStr">
-        <is>
-          <t>[M61C]  Nervürlü betonarme çeliği ø8-ø12 — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="D465" s="21" t="inlineStr">
+        <f>E463*F463*G463*H463*J463</f>
+        <v/>
+      </c>
+      <c r="J463" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="464" ht="20" customHeight="1">
+      <c r="A464" s="6" t="n"/>
+      <c r="B464" s="6" t="n"/>
+      <c r="C464" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu perdeleri: 11.00x0,25x3.00 m³, 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D464" s="6" t="n"/>
+      <c r="E464" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F464" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G464" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="H464" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I464" s="24">
+        <f>E464*F464*G464*H464*J464</f>
+        <v/>
+      </c>
+      <c r="J464" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="465" ht="12" customHeight="1">
+      <c r="A465" s="6" t="n"/>
+      <c r="B465" s="6" t="n"/>
+      <c r="C465" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu döşemesi: 3.00x3.00x0,15 m³, 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D465" s="6" t="n"/>
+      <c r="E465" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F465" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G465" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H465" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I465" s="24">
+        <f>E465*F465*G465*H465*J465</f>
+        <v/>
+      </c>
+      <c r="J465" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="22" t="n"/>
+      <c r="B466" s="22" t="n"/>
+      <c r="C466" s="25" t="inlineStr">
+        <is>
+          <t>M26 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D466" s="26" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="E465" s="22" t="n"/>
-      <c r="F465" s="22" t="n"/>
-      <c r="G465" s="22" t="n"/>
-      <c r="H465" s="22" t="n"/>
-      <c r="I465" s="22" t="n"/>
-      <c r="J465" s="22" t="n"/>
-    </row>
-    <row r="466" ht="20" customHeight="1">
-      <c r="A466" s="6" t="n"/>
-      <c r="B466" s="6" t="n"/>
-      <c r="C466" s="23" t="inlineStr">
-        <is>
-          <t>Beton hacmi 1,566 m³, ortalama donatı oranı 90 kg/m³ -&gt; 140,94 kg = 0,141 ton</t>
-        </is>
-      </c>
-      <c r="D466" s="6" t="n"/>
-      <c r="E466" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F466" s="6" t="n"/>
-      <c r="G466" s="29" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="H466" s="6" t="n"/>
-      <c r="I466" s="24">
-        <f>E466*G466*J466</f>
-        <v/>
-      </c>
-      <c r="J466" s="30" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" s="22" t="n"/>
-      <c r="B467" s="22" t="n"/>
-      <c r="C467" s="25" t="inlineStr">
-        <is>
-          <t>M61C TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D467" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E467" s="22" t="n"/>
-      <c r="F467" s="22" t="n"/>
-      <c r="G467" s="22" t="n"/>
-      <c r="H467" s="22" t="n"/>
-      <c r="I467" s="22" t="n"/>
-      <c r="J467" s="27">
-        <f>SUM(I466:I466)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="468" ht="15" customHeight="1">
-      <c r="A468" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B468" s="20" t="inlineStr">
-        <is>
-          <t>15.560.1003</t>
-        </is>
-      </c>
-      <c r="C468" s="8" t="inlineStr">
-        <is>
-          <t>[M61D]  Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D468" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E468" s="22" t="n"/>
-      <c r="F468" s="22" t="n"/>
-      <c r="G468" s="22" t="n"/>
-      <c r="H468" s="22" t="n"/>
-      <c r="I468" s="22" t="n"/>
-      <c r="J468" s="22" t="n"/>
-    </row>
-    <row r="469" ht="12" customHeight="1">
-      <c r="A469" s="6" t="n"/>
-      <c r="B469" s="6" t="n"/>
-      <c r="C469" s="23" t="inlineStr">
-        <is>
-          <t>Pissu hattında 4 adet</t>
-        </is>
-      </c>
-      <c r="D469" s="6" t="n"/>
-      <c r="E469" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F469" s="6" t="n"/>
-      <c r="G469" s="6" t="n"/>
-      <c r="H469" s="6" t="n"/>
-      <c r="I469" s="24">
-        <f>E469</f>
-        <v/>
-      </c>
-      <c r="J469" s="6" t="n"/>
-    </row>
-    <row r="470">
-      <c r="A470" s="22" t="n"/>
-      <c r="B470" s="22" t="n"/>
-      <c r="C470" s="25" t="inlineStr">
-        <is>
-          <t>M61D TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D470" s="26" t="inlineStr">
-        <is>
-          <t>ad</t>
+      <c r="E466" s="22" t="n"/>
+      <c r="F466" s="22" t="n"/>
+      <c r="G466" s="22" t="n"/>
+      <c r="H466" s="22" t="n"/>
+      <c r="I466" s="22" t="n"/>
+      <c r="J466" s="27">
+        <f>SUM(I463:I465)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="467"/>
+    <row r="468" ht="20" customHeight="1">
+      <c r="A468" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="28" customHeight="1">
+      <c r="A469" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B469" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="C469" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı / Ölçünün Alındığı Yer</t>
+        </is>
+      </c>
+      <c r="D469" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="E469" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F469" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="G469" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="H469" s="7" t="inlineStr">
+        <is>
+          <t>Yükseklik (m)</t>
+        </is>
+      </c>
+      <c r="I469" s="7" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="J469" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Miktar</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="15" customHeight="1">
+      <c r="A470" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B470" s="20" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="C470" s="8" t="inlineStr">
+        <is>
+          <t>[M02]  Makine ile kaba tesviye kazısı — tesis içi yol güzergâhı</t>
+        </is>
+      </c>
+      <c r="D470" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
         </is>
       </c>
       <c r="E470" s="22" t="n"/>
@@ -15801,71 +16015,75 @@
       <c r="G470" s="22" t="n"/>
       <c r="H470" s="22" t="n"/>
       <c r="I470" s="22" t="n"/>
-      <c r="J470" s="27">
-        <f>SUM(I469:I469)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="471" ht="22" customHeight="1">
-      <c r="A471" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B471" s="20" t="inlineStr">
-        <is>
-          <t>30.100.1104</t>
-        </is>
-      </c>
-      <c r="C471" s="8" t="inlineStr">
-        <is>
-          <t>[M63]  Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
-        </is>
-      </c>
-      <c r="D471" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E471" s="22" t="n"/>
-      <c r="F471" s="22" t="n"/>
-      <c r="G471" s="22" t="n"/>
-      <c r="H471" s="22" t="n"/>
-      <c r="I471" s="22" t="n"/>
-      <c r="J471" s="22" t="n"/>
-    </row>
-    <row r="472" ht="12" customHeight="1">
-      <c r="A472" s="6" t="n"/>
-      <c r="B472" s="6" t="n"/>
-      <c r="C472" s="23" t="inlineStr">
-        <is>
-          <t>Tesis girişinde 1 adet</t>
-        </is>
-      </c>
-      <c r="D472" s="6" t="n"/>
-      <c r="E472" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F472" s="6" t="n"/>
-      <c r="G472" s="6" t="n"/>
-      <c r="H472" s="6" t="n"/>
-      <c r="I472" s="24">
-        <f>E472*J472</f>
-        <v/>
-      </c>
-      <c r="J472" s="30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" s="22" t="n"/>
-      <c r="B473" s="22" t="n"/>
-      <c r="C473" s="25" t="inlineStr">
-        <is>
-          <t>M63 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D473" s="26" t="inlineStr">
-        <is>
-          <t>ad</t>
+      <c r="J470" s="22" t="n"/>
+    </row>
+    <row r="471" ht="20" customHeight="1">
+      <c r="A471" s="6" t="n"/>
+      <c r="B471" s="6" t="n"/>
+      <c r="C471" s="23" t="inlineStr">
+        <is>
+          <t>Tesis içi yol güzergâhı: 745,57 m² alan, ortalama 5,00 m genişlik -&gt; 149,11 m uzunluk</t>
+        </is>
+      </c>
+      <c r="D471" s="6" t="n"/>
+      <c r="E471" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F471" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G471" s="29" t="n">
+        <v>149.11</v>
+      </c>
+      <c r="H471" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I471" s="24">
+        <f>E471*F471*G471*H471</f>
+        <v/>
+      </c>
+      <c r="J471" s="6" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="22" t="n"/>
+      <c r="B472" s="22" t="n"/>
+      <c r="C472" s="25" t="inlineStr">
+        <is>
+          <t>M02 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D472" s="26" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E472" s="22" t="n"/>
+      <c r="F472" s="22" t="n"/>
+      <c r="G472" s="22" t="n"/>
+      <c r="H472" s="22" t="n"/>
+      <c r="I472" s="22" t="n"/>
+      <c r="J472" s="27">
+        <f>SUM(I471:I471)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="473" ht="22" customHeight="1">
+      <c r="A473" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B473" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0091</t>
+        </is>
+      </c>
+      <c r="C473" s="8" t="inlineStr">
+        <is>
+          <t>[M46]  1,50 m yükseklikte sıcak daldırma galvanizli tel örgü ile çit yapılması</t>
+        </is>
+      </c>
+      <c r="D473" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
         </is>
       </c>
       <c r="E473" s="22" t="n"/>
@@ -15873,43 +16091,37 @@
       <c r="G473" s="22" t="n"/>
       <c r="H473" s="22" t="n"/>
       <c r="I473" s="22" t="n"/>
-      <c r="J473" s="27">
-        <f>SUM(I472:I472)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="474" ht="15" customHeight="1">
-      <c r="A474" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B474" s="20" t="inlineStr">
-        <is>
-          <t>30.100.2106</t>
-        </is>
-      </c>
-      <c r="C474" s="8" t="inlineStr">
-        <is>
-          <t>[M64]  Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
-        </is>
-      </c>
-      <c r="D474" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E474" s="22" t="n"/>
-      <c r="F474" s="22" t="n"/>
-      <c r="G474" s="22" t="n"/>
-      <c r="H474" s="22" t="n"/>
-      <c r="I474" s="22" t="n"/>
-      <c r="J474" s="22" t="n"/>
+      <c r="J473" s="22" t="n"/>
+    </row>
+    <row r="474" ht="30" customHeight="1">
+      <c r="A474" s="6" t="n"/>
+      <c r="B474" s="6" t="n"/>
+      <c r="C474" s="23" t="inlineStr">
+        <is>
+          <t>Parsel 7.966,67 m²; yerleşim planındaki cephe 113,04 m, buna karşılık gelen derinlik 7.966,67/113,04 = 70,48 m; çevre 2x(113,04+70,48)</t>
+        </is>
+      </c>
+      <c r="D474" s="6" t="n"/>
+      <c r="E474" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F474" s="6" t="n"/>
+      <c r="G474" s="29" t="n">
+        <v>367.04</v>
+      </c>
+      <c r="H474" s="6" t="n"/>
+      <c r="I474" s="24">
+        <f>E474*G474</f>
+        <v/>
+      </c>
+      <c r="J474" s="6" t="n"/>
     </row>
     <row r="475" ht="12" customHeight="1">
       <c r="A475" s="6" t="n"/>
       <c r="B475" s="6" t="n"/>
       <c r="C475" s="23" t="inlineStr">
         <is>
-          <t>Tesis girişinde 1 adet</t>
+          <t>Giriş kapısı açıklığı düşülür</t>
         </is>
       </c>
       <c r="D475" s="6" t="n"/>
@@ -15917,27 +16129,27 @@
         <v>1</v>
       </c>
       <c r="F475" s="6" t="n"/>
-      <c r="G475" s="6" t="n"/>
+      <c r="G475" s="29" t="n">
+        <v>6</v>
+      </c>
       <c r="H475" s="6" t="n"/>
       <c r="I475" s="24">
-        <f>E475*J475</f>
-        <v/>
-      </c>
-      <c r="J475" s="30" t="n">
-        <v>1</v>
-      </c>
+        <f>-E475*G475</f>
+        <v/>
+      </c>
+      <c r="J475" s="6" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="22" t="n"/>
       <c r="B476" s="22" t="n"/>
       <c r="C476" s="25" t="inlineStr">
         <is>
-          <t>M64 TOPLAMI</t>
+          <t>M46 TOPLAMI</t>
         </is>
       </c>
       <c r="D476" s="26" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E476" s="22" t="n"/>
@@ -15946,27 +16158,27 @@
       <c r="H476" s="22" t="n"/>
       <c r="I476" s="22" t="n"/>
       <c r="J476" s="27">
-        <f>SUM(I475:I475)</f>
+        <f>SUM(I474:I475)</f>
         <v/>
       </c>
     </row>
     <row r="477" ht="22" customHeight="1">
       <c r="A477" s="19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B477" s="20" t="inlineStr">
         <is>
-          <t>30.135.3201</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="C477" s="8" t="inlineStr">
         <is>
-          <t>[M65]  Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+          <t>[M59]  ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="D477" s="21" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E477" s="22" t="n"/>
@@ -15981,7 +16193,7 @@
       <c r="B478" s="6" t="n"/>
       <c r="C478" s="23" t="inlineStr">
         <is>
-          <t>Sayaç panosu içinde 1 adet</t>
+          <t>Kümes A blok servis bölümü - foseptik</t>
         </is>
       </c>
       <c r="D478" s="6" t="n"/>
@@ -15989,56 +16201,50 @@
         <v>1</v>
       </c>
       <c r="F478" s="6" t="n"/>
-      <c r="G478" s="6" t="n"/>
+      <c r="G478" s="29" t="n">
+        <v>25</v>
+      </c>
       <c r="H478" s="6" t="n"/>
       <c r="I478" s="24">
-        <f>E478*J478</f>
-        <v/>
-      </c>
-      <c r="J478" s="30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" s="22" t="n"/>
-      <c r="B479" s="22" t="n"/>
-      <c r="C479" s="25" t="inlineStr">
-        <is>
-          <t>M65 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D479" s="26" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E479" s="22" t="n"/>
-      <c r="F479" s="22" t="n"/>
-      <c r="G479" s="22" t="n"/>
-      <c r="H479" s="22" t="n"/>
-      <c r="I479" s="22" t="n"/>
-      <c r="J479" s="27">
-        <f>SUM(I478:I478)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="480" ht="22" customHeight="1">
-      <c r="A480" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="B480" s="20" t="inlineStr">
-        <is>
-          <t>30.110.1104</t>
-        </is>
-      </c>
-      <c r="C480" s="8" t="inlineStr">
-        <is>
-          <t>[M66]  Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
-        </is>
-      </c>
-      <c r="D480" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
+        <f>E478*G478</f>
+        <v/>
+      </c>
+      <c r="J478" s="6" t="n"/>
+    </row>
+    <row r="479" ht="12" customHeight="1">
+      <c r="A479" s="6" t="n"/>
+      <c r="B479" s="6" t="n"/>
+      <c r="C479" s="23" t="inlineStr">
+        <is>
+          <t>Kümes B blok servis bölümü - foseptik</t>
+        </is>
+      </c>
+      <c r="D479" s="6" t="n"/>
+      <c r="E479" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F479" s="6" t="n"/>
+      <c r="G479" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="H479" s="6" t="n"/>
+      <c r="I479" s="24">
+        <f>E479*G479</f>
+        <v/>
+      </c>
+      <c r="J479" s="6" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="22" t="n"/>
+      <c r="B480" s="22" t="n"/>
+      <c r="C480" s="25" t="inlineStr">
+        <is>
+          <t>M59 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D480" s="26" t="inlineStr">
+        <is>
+          <t>m</t>
         </is>
       </c>
       <c r="E480" s="22" t="n"/>
@@ -16046,114 +16252,131 @@
       <c r="G480" s="22" t="n"/>
       <c r="H480" s="22" t="n"/>
       <c r="I480" s="22" t="n"/>
-      <c r="J480" s="22" t="n"/>
-    </row>
-    <row r="481" ht="12" customHeight="1">
-      <c r="A481" s="6" t="n"/>
-      <c r="B481" s="6" t="n"/>
-      <c r="C481" s="23" t="inlineStr">
-        <is>
-          <t>Ana dağıtım panosu girişi</t>
-        </is>
-      </c>
-      <c r="D481" s="6" t="n"/>
-      <c r="E481" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F481" s="6" t="n"/>
-      <c r="G481" s="6" t="n"/>
-      <c r="H481" s="6" t="n"/>
-      <c r="I481" s="24">
-        <f>E481*J481</f>
-        <v/>
-      </c>
-      <c r="J481" s="30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" s="22" t="n"/>
-      <c r="B482" s="22" t="n"/>
-      <c r="C482" s="25" t="inlineStr">
-        <is>
-          <t>M66 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D482" s="26" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E482" s="22" t="n"/>
-      <c r="F482" s="22" t="n"/>
-      <c r="G482" s="22" t="n"/>
-      <c r="H482" s="22" t="n"/>
-      <c r="I482" s="22" t="n"/>
-      <c r="J482" s="27">
-        <f>SUM(I481:I481)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="483" ht="15" customHeight="1">
-      <c r="A483" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B483" s="20" t="inlineStr">
-        <is>
-          <t>30.115.1003</t>
-        </is>
-      </c>
-      <c r="C483" s="8" t="inlineStr">
-        <is>
-          <t>[M69]  Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
-        </is>
-      </c>
-      <c r="D483" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E483" s="22" t="n"/>
-      <c r="F483" s="22" t="n"/>
-      <c r="G483" s="22" t="n"/>
-      <c r="H483" s="22" t="n"/>
-      <c r="I483" s="22" t="n"/>
-      <c r="J483" s="22" t="n"/>
-    </row>
-    <row r="484" ht="12" customHeight="1">
-      <c r="A484" s="6" t="n"/>
-      <c r="B484" s="6" t="n"/>
-      <c r="C484" s="23" t="inlineStr">
-        <is>
-          <t>Ana pano ve sayaç panosunda</t>
-        </is>
-      </c>
-      <c r="D484" s="6" t="n"/>
-      <c r="E484" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F484" s="6" t="n"/>
-      <c r="G484" s="6" t="n"/>
-      <c r="H484" s="6" t="n"/>
-      <c r="I484" s="24">
-        <f>E484*J484</f>
-        <v/>
-      </c>
-      <c r="J484" s="30" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" s="22" t="n"/>
-      <c r="B485" s="22" t="n"/>
-      <c r="C485" s="25" t="inlineStr">
-        <is>
-          <t>M69 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D485" s="26" t="inlineStr">
-        <is>
-          <t>ad</t>
+      <c r="J480" s="27">
+        <f>SUM(I478:I479)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="481" ht="15" customHeight="1">
+      <c r="A481" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B481" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="C481" s="8" t="inlineStr">
+        <is>
+          <t>[M61A]  C 25/30 hazır beton dökülmesi — betonarme rögarlar</t>
+        </is>
+      </c>
+      <c r="D481" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E481" s="22" t="n"/>
+      <c r="F481" s="22" t="n"/>
+      <c r="G481" s="22" t="n"/>
+      <c r="H481" s="22" t="n"/>
+      <c r="I481" s="22" t="n"/>
+      <c r="J481" s="22" t="n"/>
+    </row>
+    <row r="482" ht="12" customHeight="1">
+      <c r="A482" s="6" t="n"/>
+      <c r="B482" s="6" t="n"/>
+      <c r="C482" s="23" t="inlineStr">
+        <is>
+          <t>Dış prizma: 0,90 x 0,90 x 0,75; 4 adet</t>
+        </is>
+      </c>
+      <c r="D482" s="6" t="n"/>
+      <c r="E482" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F482" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G482" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H482" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I482" s="24">
+        <f>E482*F482*G482*H482</f>
+        <v/>
+      </c>
+      <c r="J482" s="6" t="n"/>
+    </row>
+    <row r="483" ht="12" customHeight="1">
+      <c r="A483" s="6" t="n"/>
+      <c r="B483" s="6" t="n"/>
+      <c r="C483" s="23" t="inlineStr">
+        <is>
+          <t>Net iç hacim düşülür: 0,60 x 0,60 x 0,60; 4 adet</t>
+        </is>
+      </c>
+      <c r="D483" s="6" t="n"/>
+      <c r="E483" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F483" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G483" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H483" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I483" s="24">
+        <f>-E483*F483*G483*H483</f>
+        <v/>
+      </c>
+      <c r="J483" s="6" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="22" t="n"/>
+      <c r="B484" s="22" t="n"/>
+      <c r="C484" s="25" t="inlineStr">
+        <is>
+          <t>M61A TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D484" s="26" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E484" s="22" t="n"/>
+      <c r="F484" s="22" t="n"/>
+      <c r="G484" s="22" t="n"/>
+      <c r="H484" s="22" t="n"/>
+      <c r="I484" s="22" t="n"/>
+      <c r="J484" s="27">
+        <f>SUM(I482:I483)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="485" ht="22" customHeight="1">
+      <c r="A485" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B485" s="20" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="C485" s="8" t="inlineStr">
+        <is>
+          <t>[M61B]  Düz yüzeyli beton ve betonarme kalıbı yapılması — betonarme rögarlar</t>
+        </is>
+      </c>
+      <c r="D485" s="21" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="E485" s="22" t="n"/>
@@ -16161,71 +16384,73 @@
       <c r="G485" s="22" t="n"/>
       <c r="H485" s="22" t="n"/>
       <c r="I485" s="22" t="n"/>
-      <c r="J485" s="27">
-        <f>SUM(I484:I484)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="486" ht="22" customHeight="1">
-      <c r="A486" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="B486" s="20" t="inlineStr">
-        <is>
-          <t>30.140.3105</t>
-        </is>
-      </c>
-      <c r="C486" s="8" t="inlineStr">
-        <is>
-          <t>[M70]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
-        </is>
-      </c>
-      <c r="D486" s="21" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E486" s="22" t="n"/>
-      <c r="F486" s="22" t="n"/>
-      <c r="G486" s="22" t="n"/>
-      <c r="H486" s="22" t="n"/>
-      <c r="I486" s="22" t="n"/>
-      <c r="J486" s="22" t="n"/>
+      <c r="J485" s="22" t="n"/>
+    </row>
+    <row r="486" ht="12" customHeight="1">
+      <c r="A486" s="6" t="n"/>
+      <c r="B486" s="6" t="n"/>
+      <c r="C486" s="23" t="inlineStr">
+        <is>
+          <t>İç yüzler: 4 yüz x 0,60 x 0,60; 4 adet</t>
+        </is>
+      </c>
+      <c r="D486" s="6" t="n"/>
+      <c r="E486" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F486" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G486" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H486" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I486" s="24">
+        <f>E486*F486*G486*H486</f>
+        <v/>
+      </c>
+      <c r="J486" s="6" t="n"/>
     </row>
     <row r="487" ht="12" customHeight="1">
       <c r="A487" s="6" t="n"/>
       <c r="B487" s="6" t="n"/>
       <c r="C487" s="23" t="inlineStr">
         <is>
-          <t>Şebeke bağlantı noktası - ana dağıtım panosu</t>
+          <t>Dış yüzler: 4 yüz x 0,90 x 0,60; 4 adet</t>
         </is>
       </c>
       <c r="D487" s="6" t="n"/>
       <c r="E487" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F487" s="6" t="n"/>
-      <c r="G487" s="6" t="n"/>
-      <c r="H487" s="6" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F487" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G487" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H487" s="29" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I487" s="24">
-        <f>E487*J487</f>
-        <v/>
-      </c>
-      <c r="J487" s="30" t="n">
-        <v>50</v>
-      </c>
+        <f>E487*F487*G487*H487</f>
+        <v/>
+      </c>
+      <c r="J487" s="6" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="22" t="n"/>
       <c r="B488" s="22" t="n"/>
       <c r="C488" s="25" t="inlineStr">
         <is>
-          <t>M70 TOPLAMI</t>
+          <t>M61B TOPLAMI</t>
         </is>
       </c>
       <c r="D488" s="26" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E488" s="22" t="n"/>
@@ -16234,27 +16459,27 @@
       <c r="H488" s="22" t="n"/>
       <c r="I488" s="22" t="n"/>
       <c r="J488" s="27">
-        <f>SUM(I487:I487)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="489" ht="22" customHeight="1">
+        <f>SUM(I486:I487)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="489" ht="15" customHeight="1">
       <c r="A489" s="19" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B489" s="20" t="inlineStr">
         <is>
-          <t>30.140.3101</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="C489" s="8" t="inlineStr">
         <is>
-          <t>[M72]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+          <t>[M61C]  Nervürlü betonarme çeliği ø8-ø12 — betonarme rögarlar</t>
         </is>
       </c>
       <c r="D489" s="21" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="E489" s="22" t="n"/>
@@ -16264,12 +16489,12 @@
       <c r="I489" s="22" t="n"/>
       <c r="J489" s="22" t="n"/>
     </row>
-    <row r="490" ht="12" customHeight="1">
+    <row r="490" ht="20" customHeight="1">
       <c r="A490" s="6" t="n"/>
       <c r="B490" s="6" t="n"/>
       <c r="C490" s="23" t="inlineStr">
         <is>
-          <t>Saha aydınlatma direkleri besleme hattı</t>
+          <t>Beton hacmi 1,566 m³, ortalama donatı oranı 90 kg/m³ -&gt; 140,94 kg = 0,141 ton</t>
         </is>
       </c>
       <c r="D490" s="6" t="n"/>
@@ -16277,14 +16502,16 @@
         <v>1</v>
       </c>
       <c r="F490" s="6" t="n"/>
-      <c r="G490" s="6" t="n"/>
+      <c r="G490" s="29" t="n">
+        <v>1.566</v>
+      </c>
       <c r="H490" s="6" t="n"/>
       <c r="I490" s="24">
-        <f>E490*J490</f>
+        <f>E490*G490*J490</f>
         <v/>
       </c>
       <c r="J490" s="30" t="n">
-        <v>50</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="491">
@@ -16292,12 +16519,12 @@
       <c r="B491" s="22" t="n"/>
       <c r="C491" s="25" t="inlineStr">
         <is>
-          <t>M72 TOPLAMI</t>
+          <t>M61C TOPLAMI</t>
         </is>
       </c>
       <c r="D491" s="26" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="E491" s="22" t="n"/>
@@ -16310,18 +16537,18 @@
         <v/>
       </c>
     </row>
-    <row r="492" ht="22" customHeight="1">
+    <row r="492" ht="15" customHeight="1">
       <c r="A492" s="19" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B492" s="20" t="inlineStr">
         <is>
-          <t>30.172.1706</t>
+          <t>15.560.1003</t>
         </is>
       </c>
       <c r="C492" s="8" t="inlineStr">
         <is>
-          <t>[M82]  Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
+          <t>[M61D]  Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
       <c r="D492" s="21" t="inlineStr">
@@ -16341,30 +16568,28 @@
       <c r="B493" s="6" t="n"/>
       <c r="C493" s="23" t="inlineStr">
         <is>
-          <t>Tesis içi yol ve saha aydınlatması</t>
+          <t>Pissu hattında 4 adet</t>
         </is>
       </c>
       <c r="D493" s="6" t="n"/>
       <c r="E493" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F493" s="6" t="n"/>
       <c r="G493" s="6" t="n"/>
       <c r="H493" s="6" t="n"/>
       <c r="I493" s="24">
-        <f>E493*J493</f>
-        <v/>
-      </c>
-      <c r="J493" s="30" t="n">
-        <v>4</v>
-      </c>
+        <f>E493</f>
+        <v/>
+      </c>
+      <c r="J493" s="6" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="22" t="n"/>
       <c r="B494" s="22" t="n"/>
       <c r="C494" s="25" t="inlineStr">
         <is>
-          <t>M82 TOPLAMI</t>
+          <t>M61D TOPLAMI</t>
         </is>
       </c>
       <c r="D494" s="26" t="inlineStr">
@@ -16382,18 +16607,18 @@
         <v/>
       </c>
     </row>
-    <row r="495" ht="15" customHeight="1">
+    <row r="495" ht="22" customHeight="1">
       <c r="A495" s="19" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B495" s="20" t="inlineStr">
         <is>
-          <t>30.170.4002</t>
+          <t>30.100.1104</t>
         </is>
       </c>
       <c r="C495" s="8" t="inlineStr">
         <is>
-          <t>[M83]  LED projektör, ışık akısı en az 5100 lm</t>
+          <t>[M63]  Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
         </is>
       </c>
       <c r="D495" s="21" t="inlineStr">
@@ -16413,7 +16638,7 @@
       <c r="B496" s="6" t="n"/>
       <c r="C496" s="23" t="inlineStr">
         <is>
-          <t>Aydınlatma direği başına 1 adet</t>
+          <t>Tesis girişinde 1 adet</t>
         </is>
       </c>
       <c r="D496" s="6" t="n"/>
@@ -16428,7 +16653,7 @@
         <v/>
       </c>
       <c r="J496" s="30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497">
@@ -16436,7 +16661,7 @@
       <c r="B497" s="22" t="n"/>
       <c r="C497" s="25" t="inlineStr">
         <is>
-          <t>M83 TOPLAMI</t>
+          <t>M63 TOPLAMI</t>
         </is>
       </c>
       <c r="D497" s="26" t="inlineStr">
@@ -16454,69 +16679,646 @@
         <v/>
       </c>
     </row>
-    <row r="498"/>
-    <row r="499">
-      <c r="A499" s="16" t="inlineStr">
-        <is>
-          <t>AÇIKLAMALAR</t>
-        </is>
-      </c>
+    <row r="498" ht="15" customHeight="1">
+      <c r="A498" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B498" s="20" t="inlineStr">
+        <is>
+          <t>30.100.2106</t>
+        </is>
+      </c>
+      <c r="C498" s="8" t="inlineStr">
+        <is>
+          <t>[M64]  Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+        </is>
+      </c>
+      <c r="D498" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E498" s="22" t="n"/>
+      <c r="F498" s="22" t="n"/>
+      <c r="G498" s="22" t="n"/>
+      <c r="H498" s="22" t="n"/>
+      <c r="I498" s="22" t="n"/>
+      <c r="J498" s="22" t="n"/>
+    </row>
+    <row r="499" ht="12" customHeight="1">
+      <c r="A499" s="6" t="n"/>
       <c r="B499" s="6" t="n"/>
-      <c r="C499" s="6" t="n"/>
+      <c r="C499" s="23" t="inlineStr">
+        <is>
+          <t>Tesis girişinde 1 adet</t>
+        </is>
+      </c>
       <c r="D499" s="6" t="n"/>
-      <c r="E499" s="6" t="n"/>
+      <c r="E499" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="F499" s="6" t="n"/>
       <c r="G499" s="6" t="n"/>
       <c r="H499" s="6" t="n"/>
-      <c r="I499" s="6" t="n"/>
-      <c r="J499" s="6" t="n"/>
-    </row>
-    <row r="500" ht="13" customHeight="1">
-      <c r="A500" s="17" t="inlineStr">
+      <c r="I499" s="24">
+        <f>E499*J499</f>
+        <v/>
+      </c>
+      <c r="J499" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="22" t="n"/>
+      <c r="B500" s="22" t="n"/>
+      <c r="C500" s="25" t="inlineStr">
+        <is>
+          <t>M64 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D500" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E500" s="22" t="n"/>
+      <c r="F500" s="22" t="n"/>
+      <c r="G500" s="22" t="n"/>
+      <c r="H500" s="22" t="n"/>
+      <c r="I500" s="22" t="n"/>
+      <c r="J500" s="27">
+        <f>SUM(I499:I499)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="501" ht="22" customHeight="1">
+      <c r="A501" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B501" s="20" t="inlineStr">
+        <is>
+          <t>30.135.3201</t>
+        </is>
+      </c>
+      <c r="C501" s="8" t="inlineStr">
+        <is>
+          <t>[M65]  Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+        </is>
+      </c>
+      <c r="D501" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E501" s="22" t="n"/>
+      <c r="F501" s="22" t="n"/>
+      <c r="G501" s="22" t="n"/>
+      <c r="H501" s="22" t="n"/>
+      <c r="I501" s="22" t="n"/>
+      <c r="J501" s="22" t="n"/>
+    </row>
+    <row r="502" ht="12" customHeight="1">
+      <c r="A502" s="6" t="n"/>
+      <c r="B502" s="6" t="n"/>
+      <c r="C502" s="23" t="inlineStr">
+        <is>
+          <t>Sayaç panosu içinde 1 adet</t>
+        </is>
+      </c>
+      <c r="D502" s="6" t="n"/>
+      <c r="E502" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F502" s="6" t="n"/>
+      <c r="G502" s="6" t="n"/>
+      <c r="H502" s="6" t="n"/>
+      <c r="I502" s="24">
+        <f>E502*J502</f>
+        <v/>
+      </c>
+      <c r="J502" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="22" t="n"/>
+      <c r="B503" s="22" t="n"/>
+      <c r="C503" s="25" t="inlineStr">
+        <is>
+          <t>M65 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D503" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E503" s="22" t="n"/>
+      <c r="F503" s="22" t="n"/>
+      <c r="G503" s="22" t="n"/>
+      <c r="H503" s="22" t="n"/>
+      <c r="I503" s="22" t="n"/>
+      <c r="J503" s="27">
+        <f>SUM(I502:I502)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="504" ht="22" customHeight="1">
+      <c r="A504" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B504" s="20" t="inlineStr">
+        <is>
+          <t>30.110.1104</t>
+        </is>
+      </c>
+      <c r="C504" s="8" t="inlineStr">
+        <is>
+          <t>[M66]  Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
+        </is>
+      </c>
+      <c r="D504" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E504" s="22" t="n"/>
+      <c r="F504" s="22" t="n"/>
+      <c r="G504" s="22" t="n"/>
+      <c r="H504" s="22" t="n"/>
+      <c r="I504" s="22" t="n"/>
+      <c r="J504" s="22" t="n"/>
+    </row>
+    <row r="505" ht="12" customHeight="1">
+      <c r="A505" s="6" t="n"/>
+      <c r="B505" s="6" t="n"/>
+      <c r="C505" s="23" t="inlineStr">
+        <is>
+          <t>Ana dağıtım panosu girişi</t>
+        </is>
+      </c>
+      <c r="D505" s="6" t="n"/>
+      <c r="E505" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F505" s="6" t="n"/>
+      <c r="G505" s="6" t="n"/>
+      <c r="H505" s="6" t="n"/>
+      <c r="I505" s="24">
+        <f>E505*J505</f>
+        <v/>
+      </c>
+      <c r="J505" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="22" t="n"/>
+      <c r="B506" s="22" t="n"/>
+      <c r="C506" s="25" t="inlineStr">
+        <is>
+          <t>M66 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D506" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E506" s="22" t="n"/>
+      <c r="F506" s="22" t="n"/>
+      <c r="G506" s="22" t="n"/>
+      <c r="H506" s="22" t="n"/>
+      <c r="I506" s="22" t="n"/>
+      <c r="J506" s="27">
+        <f>SUM(I505:I505)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="507" ht="15" customHeight="1">
+      <c r="A507" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B507" s="20" t="inlineStr">
+        <is>
+          <t>30.115.1003</t>
+        </is>
+      </c>
+      <c r="C507" s="8" t="inlineStr">
+        <is>
+          <t>[M69]  Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+        </is>
+      </c>
+      <c r="D507" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E507" s="22" t="n"/>
+      <c r="F507" s="22" t="n"/>
+      <c r="G507" s="22" t="n"/>
+      <c r="H507" s="22" t="n"/>
+      <c r="I507" s="22" t="n"/>
+      <c r="J507" s="22" t="n"/>
+    </row>
+    <row r="508" ht="12" customHeight="1">
+      <c r="A508" s="6" t="n"/>
+      <c r="B508" s="6" t="n"/>
+      <c r="C508" s="23" t="inlineStr">
+        <is>
+          <t>Ana pano ve sayaç panosunda</t>
+        </is>
+      </c>
+      <c r="D508" s="6" t="n"/>
+      <c r="E508" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F508" s="6" t="n"/>
+      <c r="G508" s="6" t="n"/>
+      <c r="H508" s="6" t="n"/>
+      <c r="I508" s="24">
+        <f>E508*J508</f>
+        <v/>
+      </c>
+      <c r="J508" s="30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="22" t="n"/>
+      <c r="B509" s="22" t="n"/>
+      <c r="C509" s="25" t="inlineStr">
+        <is>
+          <t>M69 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D509" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E509" s="22" t="n"/>
+      <c r="F509" s="22" t="n"/>
+      <c r="G509" s="22" t="n"/>
+      <c r="H509" s="22" t="n"/>
+      <c r="I509" s="22" t="n"/>
+      <c r="J509" s="27">
+        <f>SUM(I508:I508)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="510" ht="22" customHeight="1">
+      <c r="A510" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B510" s="20" t="inlineStr">
+        <is>
+          <t>30.140.3105</t>
+        </is>
+      </c>
+      <c r="C510" s="8" t="inlineStr">
+        <is>
+          <t>[M70]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
+        </is>
+      </c>
+      <c r="D510" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E510" s="22" t="n"/>
+      <c r="F510" s="22" t="n"/>
+      <c r="G510" s="22" t="n"/>
+      <c r="H510" s="22" t="n"/>
+      <c r="I510" s="22" t="n"/>
+      <c r="J510" s="22" t="n"/>
+    </row>
+    <row r="511" ht="12" customHeight="1">
+      <c r="A511" s="6" t="n"/>
+      <c r="B511" s="6" t="n"/>
+      <c r="C511" s="23" t="inlineStr">
+        <is>
+          <t>Şebeke bağlantı noktası - ana dağıtım panosu</t>
+        </is>
+      </c>
+      <c r="D511" s="6" t="n"/>
+      <c r="E511" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F511" s="6" t="n"/>
+      <c r="G511" s="6" t="n"/>
+      <c r="H511" s="6" t="n"/>
+      <c r="I511" s="24">
+        <f>E511*J511</f>
+        <v/>
+      </c>
+      <c r="J511" s="30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="22" t="n"/>
+      <c r="B512" s="22" t="n"/>
+      <c r="C512" s="25" t="inlineStr">
+        <is>
+          <t>M70 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D512" s="26" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E512" s="22" t="n"/>
+      <c r="F512" s="22" t="n"/>
+      <c r="G512" s="22" t="n"/>
+      <c r="H512" s="22" t="n"/>
+      <c r="I512" s="22" t="n"/>
+      <c r="J512" s="27">
+        <f>SUM(I511:I511)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="513" ht="22" customHeight="1">
+      <c r="A513" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B513" s="20" t="inlineStr">
+        <is>
+          <t>30.140.3101</t>
+        </is>
+      </c>
+      <c r="C513" s="8" t="inlineStr">
+        <is>
+          <t>[M72]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+        </is>
+      </c>
+      <c r="D513" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E513" s="22" t="n"/>
+      <c r="F513" s="22" t="n"/>
+      <c r="G513" s="22" t="n"/>
+      <c r="H513" s="22" t="n"/>
+      <c r="I513" s="22" t="n"/>
+      <c r="J513" s="22" t="n"/>
+    </row>
+    <row r="514" ht="12" customHeight="1">
+      <c r="A514" s="6" t="n"/>
+      <c r="B514" s="6" t="n"/>
+      <c r="C514" s="23" t="inlineStr">
+        <is>
+          <t>Saha aydınlatma direkleri besleme hattı</t>
+        </is>
+      </c>
+      <c r="D514" s="6" t="n"/>
+      <c r="E514" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F514" s="6" t="n"/>
+      <c r="G514" s="6" t="n"/>
+      <c r="H514" s="6" t="n"/>
+      <c r="I514" s="24">
+        <f>E514*J514</f>
+        <v/>
+      </c>
+      <c r="J514" s="30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="22" t="n"/>
+      <c r="B515" s="22" t="n"/>
+      <c r="C515" s="25" t="inlineStr">
+        <is>
+          <t>M72 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D515" s="26" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E515" s="22" t="n"/>
+      <c r="F515" s="22" t="n"/>
+      <c r="G515" s="22" t="n"/>
+      <c r="H515" s="22" t="n"/>
+      <c r="I515" s="22" t="n"/>
+      <c r="J515" s="27">
+        <f>SUM(I514:I514)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="516" ht="22" customHeight="1">
+      <c r="A516" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B516" s="20" t="inlineStr">
+        <is>
+          <t>30.172.1706</t>
+        </is>
+      </c>
+      <c r="C516" s="8" t="inlineStr">
+        <is>
+          <t>[M82]  Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
+        </is>
+      </c>
+      <c r="D516" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E516" s="22" t="n"/>
+      <c r="F516" s="22" t="n"/>
+      <c r="G516" s="22" t="n"/>
+      <c r="H516" s="22" t="n"/>
+      <c r="I516" s="22" t="n"/>
+      <c r="J516" s="22" t="n"/>
+    </row>
+    <row r="517" ht="12" customHeight="1">
+      <c r="A517" s="6" t="n"/>
+      <c r="B517" s="6" t="n"/>
+      <c r="C517" s="23" t="inlineStr">
+        <is>
+          <t>Tesis içi yol ve saha aydınlatması</t>
+        </is>
+      </c>
+      <c r="D517" s="6" t="n"/>
+      <c r="E517" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F517" s="6" t="n"/>
+      <c r="G517" s="6" t="n"/>
+      <c r="H517" s="6" t="n"/>
+      <c r="I517" s="24">
+        <f>E517*J517</f>
+        <v/>
+      </c>
+      <c r="J517" s="30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="22" t="n"/>
+      <c r="B518" s="22" t="n"/>
+      <c r="C518" s="25" t="inlineStr">
+        <is>
+          <t>M82 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D518" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E518" s="22" t="n"/>
+      <c r="F518" s="22" t="n"/>
+      <c r="G518" s="22" t="n"/>
+      <c r="H518" s="22" t="n"/>
+      <c r="I518" s="22" t="n"/>
+      <c r="J518" s="27">
+        <f>SUM(I517:I517)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="519" ht="15" customHeight="1">
+      <c r="A519" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B519" s="20" t="inlineStr">
+        <is>
+          <t>30.170.4002</t>
+        </is>
+      </c>
+      <c r="C519" s="8" t="inlineStr">
+        <is>
+          <t>[M83]  LED projektör, ışık akısı en az 5100 lm</t>
+        </is>
+      </c>
+      <c r="D519" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E519" s="22" t="n"/>
+      <c r="F519" s="22" t="n"/>
+      <c r="G519" s="22" t="n"/>
+      <c r="H519" s="22" t="n"/>
+      <c r="I519" s="22" t="n"/>
+      <c r="J519" s="22" t="n"/>
+    </row>
+    <row r="520" ht="12" customHeight="1">
+      <c r="A520" s="6" t="n"/>
+      <c r="B520" s="6" t="n"/>
+      <c r="C520" s="23" t="inlineStr">
+        <is>
+          <t>Aydınlatma direği başına 1 adet</t>
+        </is>
+      </c>
+      <c r="D520" s="6" t="n"/>
+      <c r="E520" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F520" s="6" t="n"/>
+      <c r="G520" s="6" t="n"/>
+      <c r="H520" s="6" t="n"/>
+      <c r="I520" s="24">
+        <f>E520*J520</f>
+        <v/>
+      </c>
+      <c r="J520" s="30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="22" t="n"/>
+      <c r="B521" s="22" t="n"/>
+      <c r="C521" s="25" t="inlineStr">
+        <is>
+          <t>M83 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D521" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E521" s="22" t="n"/>
+      <c r="F521" s="22" t="n"/>
+      <c r="G521" s="22" t="n"/>
+      <c r="H521" s="22" t="n"/>
+      <c r="I521" s="22" t="n"/>
+      <c r="J521" s="27">
+        <f>SUM(I520:I520)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="522"/>
+    <row r="523">
+      <c r="A523" s="16" t="inlineStr">
+        <is>
+          <t>AÇIKLAMALAR</t>
+        </is>
+      </c>
+      <c r="B523" s="6" t="n"/>
+      <c r="C523" s="6" t="n"/>
+      <c r="D523" s="6" t="n"/>
+      <c r="E523" s="6" t="n"/>
+      <c r="F523" s="6" t="n"/>
+      <c r="G523" s="6" t="n"/>
+      <c r="H523" s="6" t="n"/>
+      <c r="I523" s="6" t="n"/>
+      <c r="J523" s="6" t="n"/>
+    </row>
+    <row r="524" ht="13" customHeight="1">
+      <c r="A524" s="17" t="inlineStr">
         <is>
           <t>•  Miktar sütunundaki her formül yalnızca o satırdaki ölçü hücrelerini çarpar; hiçbir sayı formülün içine gömülmemiştir.</t>
         </is>
       </c>
     </row>
-    <row r="501" ht="13" customHeight="1">
-      <c r="A501" s="17" t="inlineStr">
+    <row r="525" ht="13" customHeight="1">
+      <c r="A525" s="17" t="inlineStr">
         <is>
           <t>•  Son sütundaki katsayı, birim ağırlık (kg/m², kg/m³, ton/m²), bindirme payı, üçgen alan çarpanı (0,50) veya adet çarpanıdır.</t>
         </is>
       </c>
     </row>
-    <row r="502" ht="22" customHeight="1">
-      <c r="A502" s="17" t="inlineStr">
+    <row r="526" ht="22" customHeight="1">
+      <c r="A526" s="17" t="inlineStr">
         <is>
           <t>•  Ölçüler mimari ve betonarme paftalardan alınmıştır; kümes temellerinin beton, kalıp ve donatı miktarları doğrudan betonarme paftasındaki METRAJ tablosundandır.</t>
         </is>
       </c>
     </row>
-    <row r="503" ht="13" customHeight="1">
-      <c r="A503" s="17" t="inlineStr">
+    <row r="527" ht="13" customHeight="1">
+      <c r="A527" s="17" t="inlineStr">
         <is>
           <t>•  (-) işaretli satırlar minha edilen (düşülen) miktarlardır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="A524:J524"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A325:J325"/>
     <mergeCell ref="A444:J444"/>
-    <mergeCell ref="A501:J501"/>
-    <mergeCell ref="A500:J500"/>
+    <mergeCell ref="A527:J527"/>
+    <mergeCell ref="A523:J523"/>
+    <mergeCell ref="A526:J526"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A356:J356"/>
     <mergeCell ref="A403:J403"/>
     <mergeCell ref="A421:J421"/>
-    <mergeCell ref="A503:J503"/>
-    <mergeCell ref="A499:J499"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A468:J468"/>
     <mergeCell ref="A165:J165"/>
+    <mergeCell ref="A525:J525"/>
     <mergeCell ref="A379:J379"/>
-    <mergeCell ref="A502:J502"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -1294,7 +1294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" ht="14" customHeight="1">
+    <row r="31" ht="21" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -1322,7 +1322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" ht="14" customHeight="1">
+    <row r="32" ht="21" customHeight="1">
       <c r="A32" s="14" t="n"/>
       <c r="B32" s="9" t="n">
         <v>2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -1370,7 +1370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" ht="14" customHeight="1">
+    <row r="34" ht="21" customHeight="1">
       <c r="A34" s="14" t="n"/>
       <c r="B34" s="9" t="n">
         <v>4</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -1490,7 +1490,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="39" ht="14" customHeight="1">
+    <row r="39" ht="21" customHeight="1">
       <c r="A39" s="14" t="n"/>
       <c r="B39" s="9" t="n">
         <v>9</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
@@ -1514,7 +1514,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
+    <row r="40" ht="21" customHeight="1">
       <c r="A40" s="14" t="n"/>
       <c r="B40" s="9" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -1562,7 +1562,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
+    <row r="42" ht="21" customHeight="1">
       <c r="A42" s="14" t="n"/>
       <c r="B42" s="9" t="n">
         <v>12</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
@@ -1586,7 +1586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
+    <row r="43" ht="21" customHeight="1">
       <c r="A43" s="14" t="n"/>
       <c r="B43" s="9" t="n">
         <v>13</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
@@ -2338,7 +2338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" ht="14" customHeight="1">
+    <row r="74" ht="21" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
@@ -2366,7 +2366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" ht="14" customHeight="1">
+    <row r="75" ht="21" customHeight="1">
       <c r="A75" s="14" t="n"/>
       <c r="B75" s="9" t="n">
         <v>2</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
@@ -2414,7 +2414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" ht="14" customHeight="1">
+    <row r="77" ht="21" customHeight="1">
       <c r="A77" s="14" t="n"/>
       <c r="B77" s="9" t="n">
         <v>4</v>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
@@ -2534,7 +2534,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="82" ht="14" customHeight="1">
+    <row r="82" ht="21" customHeight="1">
       <c r="A82" s="14" t="n"/>
       <c r="B82" s="9" t="n">
         <v>9</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
@@ -2558,7 +2558,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="83" ht="14" customHeight="1">
+    <row r="83" ht="21" customHeight="1">
       <c r="A83" s="14" t="n"/>
       <c r="B83" s="9" t="n">
         <v>10</v>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
@@ -2606,7 +2606,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="85" ht="14" customHeight="1">
+    <row r="85" ht="21" customHeight="1">
       <c r="A85" s="14" t="n"/>
       <c r="B85" s="9" t="n">
         <v>12</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
@@ -2630,7 +2630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" ht="14" customHeight="1">
+    <row r="86" ht="21" customHeight="1">
       <c r="A86" s="14" t="n"/>
       <c r="B86" s="9" t="n">
         <v>13</v>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" ht="14" customHeight="1">
+    <row r="157" ht="21" customHeight="1">
       <c r="A157" s="14" t="n"/>
       <c r="B157" s="9" t="n">
         <v>2</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
@@ -4198,7 +4198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" ht="14" customHeight="1">
+    <row r="158" ht="21" customHeight="1">
       <c r="A158" s="14" t="n"/>
       <c r="B158" s="9" t="n">
         <v>3</v>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
@@ -4222,7 +4222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" ht="14" customHeight="1">
+    <row r="159" ht="21" customHeight="1">
       <c r="A159" s="14" t="n"/>
       <c r="B159" s="9" t="n">
         <v>4</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
@@ -4270,7 +4270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" ht="14" customHeight="1">
+    <row r="161" ht="21" customHeight="1">
       <c r="A161" s="14" t="n"/>
       <c r="B161" s="9" t="n">
         <v>6</v>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
@@ -4294,7 +4294,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="162" ht="14" customHeight="1">
+    <row r="162" ht="21" customHeight="1">
       <c r="A162" s="14" t="n"/>
       <c r="B162" s="9" t="n">
         <v>7</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
@@ -4318,7 +4318,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="163" ht="14" customHeight="1">
+    <row r="163" ht="21" customHeight="1">
       <c r="A163" s="14" t="n"/>
       <c r="B163" s="9" t="n">
         <v>8</v>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>LED projektör, ışık akısı en az 5100 lm</t>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F170"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1035,7 +1035,7 @@
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="15" t="n"/>
+      <c r="A21" s="14" t="n"/>
       <c r="B21" s="9" t="n">
         <v>2</v>
       </c>
@@ -1055,310 +1055,310 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>360.16</v>
-      </c>
-    </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+        <v>319.2</v>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>15.315.1001</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="B23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>TKDK-0151</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F23" s="13" t="n">
         <v>13.4</v>
       </c>
     </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="14" t="n"/>
-      <c r="B23" s="9" t="n">
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>TKDK-0175</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F24" s="13" t="n">
         <v>5.67</v>
       </c>
     </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="15" t="n"/>
-      <c r="B24" s="9" t="n">
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>15.550.1002</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F25" s="13" t="n">
         <v>54.315</v>
       </c>
     </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="B26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>15.275.1116</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F26" s="13" t="n">
         <v>557.76</v>
       </c>
     </row>
-    <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="9" t="n">
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>15.275.1117</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F27" s="13" t="n">
         <v>647.76</v>
       </c>
     </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="B28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>15.540.1606</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F28" s="13" t="n">
         <v>557.76</v>
       </c>
     </row>
-    <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="15" t="n"/>
-      <c r="B28" s="9" t="n">
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>15.540.1537</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F29" s="13" t="n">
         <v>612.76</v>
       </c>
     </row>
-    <row r="29" ht="31.5" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="30" ht="31.5" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>TKDK-0177</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F30" s="13" t="n">
         <v>60</v>
-      </c>
-    </row>
-    <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Kanalizasyon işleri</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>43.527.1001</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>Kanalizasyon işleri</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="B32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>30.100.2105</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F31" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="14" t="n"/>
-      <c r="B32" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>30.110.1102</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
       <c r="F32" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="14" customHeight="1">
+    <row r="33" ht="21" customHeight="1">
       <c r="A33" s="14" t="n"/>
       <c r="B33" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -1367,70 +1367,70 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
       <c r="A34" s="14" t="n"/>
       <c r="B34" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="14" t="n"/>
       <c r="B35" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="14" t="n"/>
       <c r="B36" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -1439,46 +1439,46 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" ht="14" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
       <c r="A37" s="14" t="n"/>
       <c r="B37" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="14" t="n"/>
       <c r="B38" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -1487,22 +1487,22 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="39" ht="21" customHeight="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1">
       <c r="A39" s="14" t="n"/>
       <c r="B39" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
@@ -1511,22 +1511,22 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="14" t="n"/>
       <c r="B40" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
@@ -1535,22 +1535,22 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="14" t="n"/>
       <c r="B41" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -1559,681 +1559,677 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>186</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="14" t="n"/>
       <c r="B42" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="14" t="n"/>
       <c r="B43" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="14" t="n"/>
       <c r="B44" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" ht="14" customHeight="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>30.740.1106</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="14" t="n"/>
+      <c r="B46" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>30.740.5406</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F45" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="15" t="n"/>
-      <c r="B46" s="9" t="n">
+      <c r="F46" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="15" t="n"/>
+      <c r="B47" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>30.120.2016</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F46" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="F47" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>&lt; Kümes B Blok &gt;   —   inşaat alanı 1.106.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>A blok ile geometrik olarak birebir aynıdır.</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="B52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>15.120.1001</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="F52" s="13" t="n">
         <v>1684.38</v>
-      </c>
-    </row>
-    <row r="52" ht="31.5" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F52" s="13" t="n">
-        <v>31.428</v>
       </c>
     </row>
     <row r="53" ht="31.5" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>31.428</v>
+      </c>
+    </row>
+    <row r="54" ht="31.5" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B53" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="B54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="F54" s="13" t="n">
         <v>278.34</v>
       </c>
     </row>
-    <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B54" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="B55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="F55" s="13" t="n">
         <v>551.26</v>
       </c>
     </row>
-    <row r="55" ht="21" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B55" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="B56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F55" s="13" t="n">
+      <c r="F56" s="13" t="n">
         <v>4.16</v>
       </c>
     </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="A56" s="14" t="n"/>
-      <c r="B56" s="9" t="n">
+    <row r="57" ht="21" customHeight="1">
+      <c r="A57" s="14" t="n"/>
+      <c r="B57" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>15.160.1004</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F56" s="13" t="n">
+      <c r="F57" s="13" t="n">
         <v>7.287</v>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="15" t="n"/>
-      <c r="B57" s="9" t="n">
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="15" t="n"/>
+      <c r="B58" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>15.160.1002</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>Nervürlü çelik hasırın yerine konulması</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F57" s="13" t="n">
+      <c r="F58" s="13" t="n">
         <v>3.637</v>
       </c>
     </row>
-    <row r="58" ht="21" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="59" ht="21" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="B59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>15.165.1003</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F58" s="13" t="n">
+      <c r="F59" s="13" t="n">
         <v>44.048</v>
       </c>
     </row>
-    <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="15" t="n"/>
-      <c r="B59" s="9" t="n">
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="15" t="n"/>
+      <c r="B60" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>15.550.1202</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D60" s="11" t="inlineStr">
         <is>
           <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F59" s="13" t="n">
+      <c r="F60" s="13" t="n">
         <v>674</v>
       </c>
     </row>
-    <row r="60" ht="21" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="B61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>15.225.1010</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F60" s="13" t="n">
+      <c r="F61" s="13" t="n">
         <v>507.91</v>
       </c>
     </row>
-    <row r="61" ht="14" customHeight="1">
-      <c r="A61" s="14" t="n"/>
-      <c r="B61" s="9" t="n">
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="14" t="n"/>
+      <c r="B62" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>15.225.1410</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D62" s="11" t="inlineStr">
         <is>
           <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F61" s="13" t="n">
+      <c r="F62" s="13" t="n">
         <v>49.85</v>
       </c>
     </row>
-    <row r="62" ht="21" customHeight="1">
-      <c r="A62" s="15" t="n"/>
-      <c r="B62" s="9" t="n">
+    <row r="63" ht="21" customHeight="1">
+      <c r="A63" s="15" t="n"/>
+      <c r="B63" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>15.225.1004</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F62" s="13" t="n">
+      <c r="F63" s="13" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="63" ht="21" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
-      <c r="B63" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="B64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>TKDK-0042</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D64" s="11" t="inlineStr">
         <is>
           <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F63" s="13" t="n">
+      <c r="F64" s="13" t="n">
         <v>1204.98</v>
       </c>
     </row>
-    <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="15" t="n"/>
-      <c r="B64" s="9" t="n">
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="14" t="n"/>
+      <c r="B65" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>TKDK-0115</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
-      <c r="E64" s="12" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F64" s="13" t="n">
-        <v>360.16</v>
-      </c>
-    </row>
-    <row r="65" ht="21" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+      <c r="F65" s="13" t="n">
+        <v>319.2</v>
+      </c>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="15" t="n"/>
+      <c r="B66" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>15.315.1001</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
-      <c r="B65" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="B67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>TKDK-0151</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F65" s="13" t="n">
+      <c r="F67" s="13" t="n">
         <v>13.4</v>
       </c>
     </row>
-    <row r="66" ht="21" customHeight="1">
-      <c r="A66" s="14" t="n"/>
-      <c r="B66" s="9" t="n">
+    <row r="68" ht="21" customHeight="1">
+      <c r="A68" s="14" t="n"/>
+      <c r="B68" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>TKDK-0175</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D68" s="11" t="inlineStr">
         <is>
           <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F66" s="13" t="n">
+      <c r="F68" s="13" t="n">
         <v>5.67</v>
       </c>
     </row>
-    <row r="67" ht="21" customHeight="1">
-      <c r="A67" s="15" t="n"/>
-      <c r="B67" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>15.550.1002</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>54.315</v>
-      </c>
-    </row>
-    <row r="68" ht="14" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>15.275.1116</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F68" s="13" t="n">
-        <v>557.76</v>
-      </c>
-    </row>
-    <row r="69" ht="14" customHeight="1">
+    <row r="69" ht="21" customHeight="1">
       <c r="A69" s="15" t="n"/>
       <c r="B69" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>647.76</v>
-      </c>
-    </row>
-    <row r="70" ht="21" customHeight="1">
+        <v>54.315</v>
+      </c>
+    </row>
+    <row r="70" ht="14" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B70" s="9" t="n">
@@ -2241,12 +2237,12 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -2258,199 +2254,203 @@
         <v>557.76</v>
       </c>
     </row>
-    <row r="71" ht="21" customHeight="1">
+    <row r="71" ht="14" customHeight="1">
       <c r="A71" s="15" t="n"/>
       <c r="B71" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
+          <t>15.275.1117</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>647.76</v>
+      </c>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>Boya, badana ve cila işleri</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>15.540.1606</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>557.76</v>
+      </c>
+    </row>
+    <row r="73" ht="21" customHeight="1">
+      <c r="A73" s="15" t="n"/>
+      <c r="B73" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
           <t>15.540.1537</t>
         </is>
       </c>
-      <c r="D71" s="11" t="inlineStr">
+      <c r="D73" s="11" t="inlineStr">
         <is>
           <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F71" s="13" t="n">
+      <c r="F73" s="13" t="n">
         <v>612.76</v>
       </c>
     </row>
-    <row r="72" ht="31.5" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
+    <row r="74" ht="31.5" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
-      <c r="B72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="B74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>TKDK-0177</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D74" s="11" t="inlineStr">
         <is>
           <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
-      <c r="E72" s="12" t="inlineStr">
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F72" s="13" t="n">
+      <c r="F74" s="13" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="73" ht="21" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
+    <row r="75" ht="21" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>Kanalizasyon işleri</t>
         </is>
       </c>
-      <c r="B73" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="B75" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>43.527.1001</t>
         </is>
       </c>
-      <c r="D73" s="11" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
         <is>
           <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F73" s="13" t="n">
+      <c r="F75" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="74" ht="21" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="76" ht="21" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
+      <c r="B76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>30.100.2105</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="D76" s="11" t="inlineStr">
         <is>
           <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F74" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" ht="21" customHeight="1">
-      <c r="A75" s="14" t="n"/>
-      <c r="B75" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>30.110.1102</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E75" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F75" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="14" t="n"/>
-      <c r="B76" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>30.115.1003</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
       <c r="F76" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="14" t="n"/>
       <c r="B77" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="78" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" ht="14" customHeight="1">
       <c r="A78" s="14" t="n"/>
       <c r="B78" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -2459,94 +2459,94 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
       <c r="A79" s="14" t="n"/>
       <c r="B79" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" ht="14" customHeight="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="80" ht="21" customHeight="1">
       <c r="A80" s="14" t="n"/>
       <c r="B80" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="81" ht="14" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" ht="21" customHeight="1">
       <c r="A81" s="14" t="n"/>
       <c r="B81" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="82" ht="21" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" ht="14" customHeight="1">
       <c r="A82" s="14" t="n"/>
       <c r="B82" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
@@ -2555,22 +2555,22 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="83" ht="21" customHeight="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="83" ht="14" customHeight="1">
       <c r="A83" s="14" t="n"/>
       <c r="B83" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -2579,22 +2579,22 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
       <c r="A84" s="14" t="n"/>
       <c r="B84" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
@@ -2603,46 +2603,46 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>186</v>
+        <v>600</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
       <c r="A85" s="14" t="n"/>
       <c r="B85" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
       <c r="A86" s="14" t="n"/>
       <c r="B86" s="9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
@@ -2651,22 +2651,22 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>16</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
       <c r="A87" s="14" t="n"/>
       <c r="B87" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
@@ -2678,1342 +2678,1334 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" ht="14" customHeight="1">
+    <row r="88" ht="21" customHeight="1">
       <c r="A88" s="14" t="n"/>
       <c r="B88" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>30.750.2001</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" ht="21" customHeight="1">
+      <c r="A89" s="14" t="n"/>
+      <c r="B89" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>30.740.1106</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="14" t="n"/>
+      <c r="B90" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C90" s="10" t="inlineStr">
         <is>
           <t>30.740.5406</t>
         </is>
       </c>
-      <c r="D88" s="11" t="inlineStr">
+      <c r="D90" s="11" t="inlineStr">
         <is>
           <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E88" s="12" t="inlineStr">
+      <c r="E90" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F88" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="15" t="n"/>
-      <c r="B89" s="9" t="n">
+      <c r="F90" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="15" t="n"/>
+      <c r="B91" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>30.120.2016</t>
         </is>
       </c>
-      <c r="D89" s="11" t="inlineStr">
+      <c r="D91" s="11" t="inlineStr">
         <is>
           <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E89" s="12" t="inlineStr">
+      <c r="E91" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F89" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90"/>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="F91" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>&lt; Gübre Çukuru &gt;   —   inşaat alanı 115.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="24" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 11,50 x 10,00 m; betonarme radye, perde ve üst döşeme.</t>
         </is>
       </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
-    </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="6" t="n"/>
+    </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="14" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B94" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="B96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D94" s="11" t="inlineStr">
+      <c r="D96" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E94" s="12" t="inlineStr">
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F94" s="13" t="n">
+      <c r="F96" s="13" t="n">
         <v>542.7</v>
       </c>
     </row>
-    <row r="95" ht="31.5" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+    <row r="97" ht="31.5" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B95" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="B97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D95" s="11" t="inlineStr">
+      <c r="D97" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E95" s="12" t="inlineStr">
+      <c r="E97" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F95" s="13" t="n">
+      <c r="F97" s="13" t="n">
         <v>11.934</v>
       </c>
     </row>
-    <row r="96" ht="31.5" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
+    <row r="98" ht="31.5" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B96" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="B98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D96" s="11" t="inlineStr">
+      <c r="D98" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E96" s="12" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F96" s="13" t="n">
+      <c r="F98" s="13" t="n">
         <v>93.19</v>
       </c>
     </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B97" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="B99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D97" s="11" t="inlineStr">
+      <c r="D99" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E97" s="12" t="inlineStr">
+      <c r="E99" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F97" s="13" t="n">
+      <c r="F99" s="13" t="n">
         <v>363.26</v>
       </c>
     </row>
-    <row r="98" ht="21" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
+    <row r="100" ht="21" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B98" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" s="10" t="inlineStr">
+      <c r="B100" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D98" s="11" t="inlineStr">
+      <c r="D100" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E98" s="12" t="inlineStr">
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F98" s="13" t="n">
+      <c r="F100" s="13" t="n">
         <v>7.599</v>
       </c>
     </row>
-    <row r="99" ht="21" customHeight="1">
-      <c r="A99" s="15" t="n"/>
-      <c r="B99" s="9" t="n">
+    <row r="101" ht="21" customHeight="1">
+      <c r="A101" s="15" t="n"/>
+      <c r="B101" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>15.160.1004</t>
         </is>
       </c>
-      <c r="D99" s="11" t="inlineStr">
+      <c r="D101" s="11" t="inlineStr">
         <is>
           <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E99" s="12" t="inlineStr">
+      <c r="E101" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F99" s="13" t="n">
+      <c r="F101" s="13" t="n">
         <v>0.5639999999999999</v>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="102"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>&lt; Ölü Atma Çukuru &gt;   —   inşaat alanı 18.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 6,00 x 3,00 m, betonarme sızdırmaz çukur.</t>
         </is>
       </c>
-      <c r="B102" s="6" t="n"/>
-      <c r="C102" s="6" t="n"/>
-      <c r="D102" s="6" t="n"/>
-      <c r="E102" s="6" t="n"/>
-      <c r="F102" s="6" t="n"/>
-    </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="A103" s="7" t="inlineStr">
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="6" t="n"/>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F103" s="7" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="14" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B104" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="B106" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D104" s="11" t="inlineStr">
+      <c r="D106" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E104" s="12" t="inlineStr">
+      <c r="E106" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F104" s="13" t="n">
+      <c r="F106" s="13" t="n">
         <v>142</v>
       </c>
     </row>
-    <row r="105" ht="31.5" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
+    <row r="107" ht="31.5" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="B107" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D105" s="11" t="inlineStr">
+      <c r="D107" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E105" s="12" t="inlineStr">
+      <c r="E107" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F105" s="13" t="n">
+      <c r="F107" s="13" t="n">
         <v>1.984</v>
       </c>
     </row>
-    <row r="106" ht="31.5" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+    <row r="108" ht="31.5" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="B108" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D106" s="11" t="inlineStr">
+      <c r="D108" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E106" s="12" t="inlineStr">
+      <c r="E108" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F106" s="13" t="n">
+      <c r="F108" s="13" t="n">
         <v>20.85</v>
       </c>
     </row>
-    <row r="107" ht="14" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B107" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="B109" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D107" s="11" t="inlineStr">
+      <c r="D109" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E107" s="12" t="inlineStr">
+      <c r="E109" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F107" s="13" t="n">
+      <c r="F109" s="13" t="n">
         <v>127.2</v>
       </c>
     </row>
-    <row r="108" ht="21" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+    <row r="110" ht="21" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="B110" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D108" s="11" t="inlineStr">
+      <c r="D110" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E108" s="12" t="inlineStr">
+      <c r="E110" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F108" s="13" t="n">
+      <c r="F110" s="13" t="n">
         <v>1.657</v>
       </c>
     </row>
-    <row r="109"/>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="4" t="inlineStr">
+    <row r="111"/>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>&lt; Foseptik &gt;   —   inşaat alanı 4.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="24" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
+    <row r="113" ht="24" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
         </is>
       </c>
-      <c r="B111" s="6" t="n"/>
-      <c r="C111" s="6" t="n"/>
-      <c r="D111" s="6" t="n"/>
-      <c r="E111" s="6" t="n"/>
-      <c r="F111" s="6" t="n"/>
-    </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="F113" s="6" t="n"/>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C112" s="7" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D112" s="7" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E112" s="7" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F112" s="7" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="14" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B113" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C113" s="10" t="inlineStr">
+      <c r="B115" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D113" s="11" t="inlineStr">
+      <c r="D115" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E113" s="12" t="inlineStr">
+      <c r="E115" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F113" s="13" t="n">
+      <c r="F115" s="13" t="n">
         <v>48.8</v>
       </c>
     </row>
-    <row r="114" ht="31.5" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
+    <row r="116" ht="31.5" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B114" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="B116" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr">
+      <c r="D116" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E114" s="12" t="inlineStr">
+      <c r="E116" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F114" s="13" t="n">
+      <c r="F116" s="13" t="n">
         <v>0.484</v>
       </c>
     </row>
-    <row r="115" ht="31.5" customHeight="1">
-      <c r="A115" s="8" t="inlineStr">
+    <row r="117" ht="31.5" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B115" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C115" s="10" t="inlineStr">
+      <c r="B117" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D115" s="11" t="inlineStr">
+      <c r="D117" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E115" s="12" t="inlineStr">
+      <c r="E117" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F115" s="13" t="n">
+      <c r="F117" s="13" t="n">
         <v>6.175</v>
       </c>
     </row>
-    <row r="116" ht="14" customHeight="1">
-      <c r="A116" s="8" t="inlineStr">
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="B118" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="D118" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E116" s="12" t="inlineStr">
+      <c r="E118" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F116" s="13" t="n">
+      <c r="F118" s="13" t="n">
         <v>41.4</v>
       </c>
     </row>
-    <row r="117" ht="21" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
+    <row r="119" ht="21" customHeight="1">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B117" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="B119" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D117" s="11" t="inlineStr">
+      <c r="D119" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E117" s="12" t="inlineStr">
+      <c r="E119" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F117" s="13" t="n">
+      <c r="F119" s="13" t="n">
         <v>0.587</v>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
+    <row r="120"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>2 adet, her biri 2,90 x 2,90 m.</t>
         </is>
       </c>
-      <c r="B120" s="6" t="n"/>
-      <c r="C120" s="6" t="n"/>
-      <c r="D120" s="6" t="n"/>
-      <c r="E120" s="6" t="n"/>
-      <c r="F120" s="6" t="n"/>
-    </row>
-    <row r="121" ht="28" customHeight="1">
-      <c r="A121" s="7" t="inlineStr">
+      <c r="B122" s="6" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="6" t="n"/>
+      <c r="E122" s="6" t="n"/>
+      <c r="F122" s="6" t="n"/>
+    </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D121" s="7" t="inlineStr">
+      <c r="D123" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F121" s="7" t="inlineStr">
+      <c r="F123" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="14" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B122" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C122" s="10" t="inlineStr">
+      <c r="B124" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D122" s="11" t="inlineStr">
+      <c r="D124" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E122" s="12" t="inlineStr">
+      <c r="E124" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F122" s="13" t="n">
+      <c r="F124" s="13" t="n">
         <v>48.02</v>
       </c>
     </row>
-    <row r="123" ht="31.5" customHeight="1">
-      <c r="A123" s="8" t="inlineStr">
+    <row r="125" ht="31.5" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="B125" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr">
+      <c r="D125" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E123" s="12" t="inlineStr">
+      <c r="E125" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F123" s="13" t="n">
+      <c r="F125" s="13" t="n">
         <v>1.922</v>
       </c>
     </row>
-    <row r="124" ht="31.5" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+    <row r="126" ht="31.5" customHeight="1">
+      <c r="A126" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B124" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="B126" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
+      <c r="D126" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E124" s="12" t="inlineStr">
+      <c r="E126" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F124" s="13" t="n">
+      <c r="F126" s="13" t="n">
         <v>8.41</v>
       </c>
     </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="B127" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D127" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E125" s="12" t="inlineStr">
+      <c r="E127" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F125" s="13" t="n">
+      <c r="F127" s="13" t="n">
         <v>11.6</v>
       </c>
     </row>
-    <row r="126" ht="21" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
+    <row r="128" ht="21" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="B128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
+      <c r="D128" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E126" s="12" t="inlineStr">
+      <c r="E128" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F126" s="13" t="n">
+      <c r="F128" s="13" t="n">
         <v>0.757</v>
       </c>
     </row>
-    <row r="127"/>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="4" t="inlineStr">
+    <row r="129"/>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="24" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
+    <row r="131" ht="24" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
         </is>
       </c>
-      <c r="B129" s="6" t="n"/>
-      <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6" t="n"/>
-      <c r="E129" s="6" t="n"/>
-      <c r="F129" s="6" t="n"/>
-    </row>
-    <row r="130" ht="28" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
+      <c r="B131" s="6" t="n"/>
+      <c r="C131" s="6" t="n"/>
+      <c r="D131" s="6" t="n"/>
+      <c r="E131" s="6" t="n"/>
+      <c r="F131" s="6" t="n"/>
+    </row>
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C130" s="7" t="inlineStr">
+      <c r="C132" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D130" s="7" t="inlineStr">
+      <c r="D132" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E130" s="7" t="inlineStr">
+      <c r="E132" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F130" s="7" t="inlineStr">
+      <c r="F132" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="14" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="B133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
+      <c r="D133" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E131" s="12" t="inlineStr">
+      <c r="E133" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F131" s="13" t="n">
+      <c r="F133" s="13" t="n">
         <v>106.5</v>
       </c>
     </row>
-    <row r="132" ht="31.5" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
+    <row r="134" ht="31.5" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="B134" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D132" s="11" t="inlineStr">
+      <c r="D134" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E132" s="12" t="inlineStr">
+      <c r="E134" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F132" s="13" t="n">
+      <c r="F134" s="13" t="n">
         <v>1.344</v>
       </c>
     </row>
-    <row r="133" ht="31.5" customHeight="1">
-      <c r="A133" s="8" t="inlineStr">
+    <row r="135" ht="31.5" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
+      <c r="B135" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D133" s="11" t="inlineStr">
+      <c r="D135" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E133" s="12" t="inlineStr">
+      <c r="E135" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F133" s="13" t="n">
+      <c r="F135" s="13" t="n">
         <v>15.15</v>
       </c>
     </row>
-    <row r="134" ht="14" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="B136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D134" s="11" t="inlineStr">
+      <c r="D136" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E134" s="12" t="inlineStr">
+      <c r="E136" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F134" s="13" t="n">
+      <c r="F136" s="13" t="n">
         <v>95.59999999999999</v>
       </c>
     </row>
-    <row r="135" ht="21" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="137" ht="21" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="B137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D135" s="11" t="inlineStr">
+      <c r="D137" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E135" s="12" t="inlineStr">
+      <c r="E137" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F135" s="13" t="n">
+      <c r="F137" s="13" t="n">
         <v>1.232</v>
       </c>
     </row>
-    <row r="136"/>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="4" t="inlineStr">
+    <row r="138"/>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="24" customHeight="1">
-      <c r="A138" s="5" t="inlineStr">
+    <row r="140" ht="24" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
         </is>
       </c>
-      <c r="B138" s="6" t="n"/>
-      <c r="C138" s="6" t="n"/>
-      <c r="D138" s="6" t="n"/>
-      <c r="E138" s="6" t="n"/>
-      <c r="F138" s="6" t="n"/>
-    </row>
-    <row r="139" ht="28" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
+      <c r="B140" s="6" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="6" t="n"/>
+      <c r="E140" s="6" t="n"/>
+      <c r="F140" s="6" t="n"/>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B139" s="7" t="inlineStr">
+      <c r="B141" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C139" s="7" t="inlineStr">
+      <c r="C141" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D139" s="7" t="inlineStr">
+      <c r="D141" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E139" s="7" t="inlineStr">
+      <c r="E141" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F139" s="7" t="inlineStr">
+      <c r="F141" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B140" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="B142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D142" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E140" s="12" t="inlineStr">
+      <c r="E142" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F140" s="13" t="n">
+      <c r="F142" s="13" t="n">
         <v>88.75</v>
       </c>
     </row>
-    <row r="141" ht="31.5" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+    <row r="143" ht="31.5" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
+      <c r="B143" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D141" s="11" t="inlineStr">
+      <c r="D143" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E141" s="12" t="inlineStr">
+      <c r="E143" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F141" s="13" t="n">
+      <c r="F143" s="13" t="n">
         <v>1.024</v>
       </c>
     </row>
-    <row r="142" ht="31.5" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+    <row r="144" ht="31.5" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B142" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" s="10" t="inlineStr">
+      <c r="B144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D142" s="11" t="inlineStr">
+      <c r="D144" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E142" s="12" t="inlineStr">
+      <c r="E144" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F142" s="13" t="n">
+      <c r="F144" s="13" t="n">
         <v>12.3</v>
       </c>
     </row>
-    <row r="143" ht="14" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
+      <c r="B145" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr">
+      <c r="D145" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E143" s="12" t="inlineStr">
+      <c r="E145" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F143" s="13" t="n">
+      <c r="F145" s="13" t="n">
         <v>79.8</v>
       </c>
     </row>
-    <row r="144" ht="21" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+    <row r="146" ht="21" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B144" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" s="10" t="inlineStr">
+      <c r="B146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D144" s="11" t="inlineStr">
+      <c r="D146" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E144" s="12" t="inlineStr">
+      <c r="E146" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F144" s="13" t="n">
+      <c r="F146" s="13" t="n">
         <v>1.23</v>
       </c>
     </row>
-    <row r="145"/>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="4" t="inlineStr">
+    <row r="147"/>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="24" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
+    <row r="149" ht="24" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
         </is>
       </c>
-      <c r="B147" s="6" t="n"/>
-      <c r="C147" s="6" t="n"/>
-      <c r="D147" s="6" t="n"/>
-      <c r="E147" s="6" t="n"/>
-      <c r="F147" s="6" t="n"/>
-    </row>
-    <row r="148" ht="28" customHeight="1">
-      <c r="A148" s="7" t="inlineStr">
+      <c r="B149" s="6" t="n"/>
+      <c r="C149" s="6" t="n"/>
+      <c r="D149" s="6" t="n"/>
+      <c r="E149" s="6" t="n"/>
+      <c r="F149" s="6" t="n"/>
+    </row>
+    <row r="150" ht="28" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B148" s="7" t="inlineStr">
+      <c r="B150" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C148" s="7" t="inlineStr">
+      <c r="C150" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D148" s="7" t="inlineStr">
+      <c r="D150" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E148" s="7" t="inlineStr">
+      <c r="E150" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F148" s="7" t="inlineStr">
+      <c r="F150" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
-      </c>
-    </row>
-    <row r="149" ht="14" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1001</t>
-        </is>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E149" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F149" s="13" t="n">
-        <v>260.942</v>
-      </c>
-    </row>
-    <row r="150" ht="31.5" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D150" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E150" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="n">
-        <v>1.566</v>
       </c>
     </row>
     <row r="151" ht="14" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B151" s="9" t="n">
@@ -4021,27 +4013,27 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F151" s="13" t="n">
-        <v>14.4</v>
-      </c>
-    </row>
-    <row r="152" ht="21" customHeight="1">
+        <v>260.942</v>
+      </c>
+    </row>
+    <row r="152" ht="31.5" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B152" s="9" t="n">
@@ -4049,27 +4041,27 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F152" s="13" t="n">
-        <v>0.141</v>
+        <v>1.566</v>
       </c>
     </row>
     <row r="153" ht="14" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
         <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B153" s="9" t="n">
@@ -4077,27 +4069,27 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F153" s="13" t="n">
-        <v>361.04</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="154" ht="21" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B154" s="9" t="n">
@@ -4105,51 +4097,55 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
         <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F154" s="13" t="n">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>Çevre düzenlemesi ve çit işleri</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0091</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F154" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="155" ht="14" customHeight="1">
-      <c r="A155" s="15" t="n"/>
-      <c r="B155" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C155" s="10" t="inlineStr">
-        <is>
-          <t>15.560.1003</t>
-        </is>
-      </c>
-      <c r="D155" s="11" t="inlineStr">
-        <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
       <c r="F155" s="13" t="n">
-        <v>4</v>
+        <v>361.04</v>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B156" s="9" t="n">
@@ -4157,36 +4153,36 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>30.100.1104</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F156" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" ht="21" customHeight="1">
-      <c r="A157" s="14" t="n"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="15" t="n"/>
       <c r="B157" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>30.100.2106</t>
+          <t>15.560.1003</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
@@ -4195,22 +4191,26 @@
         </is>
       </c>
       <c r="F157" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" ht="21" customHeight="1">
-      <c r="A158" s="14" t="n"/>
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
       <c r="B158" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>30.135.3201</t>
+          <t>30.100.1104</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
@@ -4225,16 +4225,16 @@
     <row r="159" ht="21" customHeight="1">
       <c r="A159" s="14" t="n"/>
       <c r="B159" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>30.110.1104</t>
+          <t>30.100.2106</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
@@ -4246,19 +4246,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" ht="14" customHeight="1">
+    <row r="160" ht="21" customHeight="1">
       <c r="A160" s="14" t="n"/>
       <c r="B160" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.135.3201</t>
         </is>
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
@@ -4267,141 +4267,189 @@
         </is>
       </c>
       <c r="F160" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" ht="21" customHeight="1">
       <c r="A161" s="14" t="n"/>
       <c r="B161" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>30.140.3105</t>
+          <t>30.110.1104</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F161" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="162" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" ht="14" customHeight="1">
       <c r="A162" s="14" t="n"/>
       <c r="B162" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>30.140.3101</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F162" s="13" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" ht="21" customHeight="1">
       <c r="A163" s="14" t="n"/>
       <c r="B163" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>30.140.3105</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F163" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" ht="21" customHeight="1">
+      <c r="A164" s="14" t="n"/>
+      <c r="B164" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>30.140.3101</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F164" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="165" ht="21" customHeight="1">
+      <c r="A165" s="14" t="n"/>
+      <c r="B165" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C163" s="10" t="inlineStr">
+      <c r="C165" s="10" t="inlineStr">
         <is>
           <t>30.172.1706</t>
         </is>
       </c>
-      <c r="D163" s="11" t="inlineStr">
+      <c r="D165" s="11" t="inlineStr">
         <is>
           <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E163" s="12" t="inlineStr">
+      <c r="E165" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F163" s="13" t="n">
+      <c r="F165" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="164" ht="14" customHeight="1">
-      <c r="A164" s="15" t="n"/>
-      <c r="B164" s="9" t="n">
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="15" t="n"/>
+      <c r="B166" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C164" s="10" t="inlineStr">
+      <c r="C166" s="10" t="inlineStr">
         <is>
           <t>30.170.4002</t>
         </is>
       </c>
-      <c r="D164" s="11" t="inlineStr">
+      <c r="D166" s="11" t="inlineStr">
         <is>
           <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E164" s="12" t="inlineStr">
+      <c r="E166" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F164" s="13" t="n">
+      <c r="F166" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="165"/>
-    <row r="166">
-      <c r="A166" s="16" t="inlineStr">
+    <row r="167"/>
+    <row r="168">
+      <c r="A168" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B166" s="6" t="n"/>
-      <c r="C166" s="6" t="n"/>
-      <c r="D166" s="6" t="n"/>
-      <c r="E166" s="6" t="n"/>
-      <c r="F166" s="6" t="n"/>
-    </row>
-    <row r="167" ht="13" customHeight="1">
-      <c r="A167" s="17" t="inlineStr">
-        <is>
-          <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="22" customHeight="1">
-      <c r="A168" s="17" t="inlineStr">
-        <is>
-          <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
-        </is>
-      </c>
+      <c r="B168" s="6" t="n"/>
+      <c r="C168" s="6" t="n"/>
+      <c r="D168" s="6" t="n"/>
+      <c r="E168" s="6" t="n"/>
+      <c r="F168" s="6" t="n"/>
     </row>
     <row r="169" ht="13" customHeight="1">
       <c r="A169" s="17" t="inlineStr">
         <is>
+          <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="22" customHeight="1">
+      <c r="A170" s="17" t="inlineStr">
+        <is>
+          <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="13" customHeight="1">
+      <c r="A171" s="17" t="inlineStr">
+        <is>
           <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="13" customHeight="1">
-      <c r="A170" s="17" t="inlineStr">
+    <row r="172" ht="13" customHeight="1">
+      <c r="A172" s="17" t="inlineStr">
         <is>
           <t>•  Elektrik tesisatı bölümü, kuvvetli akım birim fiyat listesi temin edildikten sonra tamamlanacaktır.</t>
         </is>
@@ -4409,97 +4457,97 @@
     </row>
   </sheetData>
   <mergeCells count="91">
+    <mergeCell ref="A20:A22"/>
     <mergeCell ref="A52"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A155"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A123"/>
-    <mergeCell ref="A132"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A110"/>
+    <mergeCell ref="A119"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A118"/>
+    <mergeCell ref="A75"/>
     <mergeCell ref="A133"/>
-    <mergeCell ref="A95"/>
-    <mergeCell ref="A104"/>
-    <mergeCell ref="A150"/>
+    <mergeCell ref="A55"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A172:F172"/>
     <mergeCell ref="A144"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A97"/>
     <mergeCell ref="A106"/>
     <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A29"/>
     <mergeCell ref="A134"/>
     <mergeCell ref="A96"/>
     <mergeCell ref="A152"/>
-    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A149:F149"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A73"/>
-    <mergeCell ref="A51"/>
+    <mergeCell ref="A31"/>
+    <mergeCell ref="A26:A27"/>
     <mergeCell ref="A107"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A146"/>
     <mergeCell ref="A124"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A167:F167"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A99"/>
     <mergeCell ref="A108"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A149"/>
     <mergeCell ref="A169:F169"/>
-    <mergeCell ref="A55:A57"/>
     <mergeCell ref="A151"/>
     <mergeCell ref="A126"/>
-    <mergeCell ref="A141"/>
     <mergeCell ref="A135"/>
-    <mergeCell ref="A137:F137"/>
     <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A122"/>
     <mergeCell ref="A125"/>
-    <mergeCell ref="A72"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A32:A47"/>
+    <mergeCell ref="A127"/>
     <mergeCell ref="A30"/>
-    <mergeCell ref="A114"/>
-    <mergeCell ref="A31:A46"/>
-    <mergeCell ref="A156:A164"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A98"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A171:F171"/>
+    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A153"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A111:F111"/>
     <mergeCell ref="A54"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A137"/>
+    <mergeCell ref="A61:A63"/>
     <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A74"/>
+    <mergeCell ref="A145"/>
+    <mergeCell ref="A154"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A74:A89"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A103:F103"/>
     <mergeCell ref="A168:F168"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A98:A99"/>
     <mergeCell ref="A116"/>
+    <mergeCell ref="A56:A58"/>
     <mergeCell ref="A8"/>
-    <mergeCell ref="A131"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A140"/>
+    <mergeCell ref="A76:A91"/>
     <mergeCell ref="A53"/>
-    <mergeCell ref="A120:F120"/>
+    <mergeCell ref="A109"/>
     <mergeCell ref="A10"/>
     <mergeCell ref="A115"/>
+    <mergeCell ref="A158:A166"/>
+    <mergeCell ref="A104:F104"/>
     <mergeCell ref="A117"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A67:A69"/>
     <mergeCell ref="A9"/>
     <mergeCell ref="A143"/>
-    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A142"/>
     <mergeCell ref="A11"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A147:F147"/>
-    <mergeCell ref="A94"/>
     <mergeCell ref="A170:F170"/>
-    <mergeCell ref="A138:F138"/>
-    <mergeCell ref="A105"/>
-    <mergeCell ref="A110:F110"/>
-    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A128"/>
+    <mergeCell ref="A130:F130"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A136"/>
+    <mergeCell ref="A28:A29"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A113"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A119:F119"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -6487,23 +6535,23 @@
         <v/>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1">
+    <row r="83" ht="22" customHeight="1">
       <c r="A83" s="19" t="n">
         <v>19</v>
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>[M36]  Galvanizli düz sacdan iniş borusu yapılması — ø100</t>
+          <t>[M36]  Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="D83" s="21" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E83" s="22" t="n"/>
@@ -6513,17 +6561,17 @@
       <c r="I83" s="22" t="n"/>
       <c r="J83" s="22" t="n"/>
     </row>
-    <row r="84" ht="40" customHeight="1">
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="n"/>
       <c r="B84" s="6" t="n"/>
       <c r="C84" s="23" t="inlineStr">
         <is>
-          <t>Blok başına 8 adet (yaklaşık 10 m aralıkla), 2 blok = 16 adet; boy 3,00 saçak kotu + 0,20 zemin altı = 3,20 m; gelişmiş genişlik 0,40 m, 0,50 mm sac -&gt; 0,40 x 0,0005 x 7.850 = 1,57 kg/m, kenet payı ile 1,60 kg/m — bu yapıya düşen pay 0.500000</t>
+          <t>Sıhhi tesisat projesi: blok başına 16 adet Ø70 iniş borusu (Y1-Y16), 2 blok = 32 adet; boy 3.00 m saçak kotu + 0,20 m zemin altı = 3,20 m — bu yapıya düşen pay 0.500000</t>
         </is>
       </c>
       <c r="D84" s="6" t="n"/>
       <c r="E84" s="28" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F84" s="6" t="n"/>
       <c r="G84" s="29" t="n">
@@ -6535,7 +6583,7 @@
         <v/>
       </c>
       <c r="J84" s="30" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
@@ -6548,7 +6596,7 @@
       </c>
       <c r="D85" s="26" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E85" s="22" t="n"/>
@@ -10411,23 +10459,23 @@
         <v/>
       </c>
     </row>
-    <row r="243" ht="15" customHeight="1">
+    <row r="243" ht="22" customHeight="1">
       <c r="A243" s="19" t="n">
         <v>19</v>
       </c>
       <c r="B243" s="20" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="C243" s="8" t="inlineStr">
         <is>
-          <t>[M36]  Galvanizli düz sacdan iniş borusu yapılması — ø100</t>
+          <t>[M36]  Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="D243" s="21" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E243" s="22" t="n"/>
@@ -10437,17 +10485,17 @@
       <c r="I243" s="22" t="n"/>
       <c r="J243" s="22" t="n"/>
     </row>
-    <row r="244" ht="40" customHeight="1">
+    <row r="244" ht="30" customHeight="1">
       <c r="A244" s="6" t="n"/>
       <c r="B244" s="6" t="n"/>
       <c r="C244" s="23" t="inlineStr">
         <is>
-          <t>Blok başına 8 adet (yaklaşık 10 m aralıkla), 2 blok = 16 adet; boy 3,00 saçak kotu + 0,20 zemin altı = 3,20 m; gelişmiş genişlik 0,40 m, 0,50 mm sac -&gt; 0,40 x 0,0005 x 7.850 = 1,57 kg/m, kenet payı ile 1,60 kg/m — bu yapıya düşen pay 0.500000</t>
+          <t>Sıhhi tesisat projesi: blok başına 16 adet Ø70 iniş borusu (Y1-Y16), 2 blok = 32 adet; boy 3.00 m saçak kotu + 0,20 m zemin altı = 3,20 m — bu yapıya düşen pay 0.500000</t>
         </is>
       </c>
       <c r="D244" s="6" t="n"/>
       <c r="E244" s="28" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F244" s="6" t="n"/>
       <c r="G244" s="29" t="n">
@@ -10459,7 +10507,7 @@
         <v/>
       </c>
       <c r="J244" s="30" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="245">
@@ -10472,7 +10520,7 @@
       </c>
       <c r="D245" s="26" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E245" s="22" t="n"/>

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>31.428</v>
+        <v>31.429</v>
       </c>
     </row>
     <row r="10" ht="31.5" customHeight="1">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>7.287</v>
+        <v>7.288</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>31.428</v>
+        <v>31.429</v>
       </c>
     </row>
     <row r="54" ht="31.5" customHeight="1">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>7.287</v>
+        <v>7.288</v>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="F151" s="13" t="n">
-        <v>260.942</v>
+        <v>260.943</v>
       </c>
     </row>
     <row r="152" ht="31.5" customHeight="1">

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>1684.39</v>
+        <v>1684.385</v>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>1684.38</v>
+        <v>1684.385</v>
       </c>
     </row>
     <row r="58" ht="31.5" customHeight="1">
@@ -4936,7 +4936,7 @@
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="25" t="n">
-        <v>1684.39</v>
+        <v>1684.385</v>
       </c>
       <c r="J8" s="6" t="n"/>
     </row>
@@ -9218,7 +9218,7 @@
       <c r="G183" s="6" t="n"/>
       <c r="H183" s="6" t="n"/>
       <c r="I183" s="25" t="n">
-        <v>1684.38</v>
+        <v>1684.385</v>
       </c>
       <c r="J183" s="6" t="n"/>
     </row>

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3337,7 +3337,7 @@
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
+          <t>Prefabrik polietilen sızdırmaz foseptik tankı, 6 m³; kazı ve grobeton oturma yatağı üzerine yerleştirilir (çukur dış ölçüsü 2,00 x 2,00 m).</t>
         </is>
       </c>
       <c r="B119" s="6" t="n"/>
@@ -3434,722 +3434,722 @@
         <v>0.484</v>
       </c>
     </row>
-    <row r="123" ht="31.5" customHeight="1">
+    <row r="123" ht="21" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
+          <t>Kanalizasyon işleri</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>ÖP-15</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>Prefabrik polietilen sızdırmaz foseptik tankı — 6 m³, rotasyon kalıplı, temini, yerine konulması ve giriş-çıkış bağlantılarının yapılması</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124"/>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="24" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2 adet, her biri 2,90 x 2,90 m.</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="n"/>
+      <c r="C126" s="6" t="n"/>
+      <c r="D126" s="6" t="n"/>
+      <c r="E126" s="6" t="n"/>
+      <c r="F126" s="6" t="n"/>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>48.02</v>
+      </c>
+    </row>
+    <row r="129" ht="31.5" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>1.922</v>
+      </c>
+    </row>
+    <row r="130" ht="31.5" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="B130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E123" s="12" t="inlineStr">
+      <c r="E130" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F123" s="13" t="n">
-        <v>6.175</v>
-      </c>
-    </row>
-    <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+      <c r="F130" s="13" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B124" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="B131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
+      <c r="D131" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E124" s="12" t="inlineStr">
+      <c r="E131" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F124" s="13" t="n">
-        <v>41.4</v>
-      </c>
-    </row>
-    <row r="125" ht="21" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
+      <c r="F131" s="13" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="132" ht="21" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="B132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D132" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E125" s="12" t="inlineStr">
+      <c r="E132" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F125" s="13" t="n">
-        <v>0.587</v>
-      </c>
-    </row>
-    <row r="126"/>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="24" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>2 adet, her biri 2,90 x 2,90 m.</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="n"/>
-      <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6" t="n"/>
-      <c r="E128" s="6" t="n"/>
-      <c r="F128" s="6" t="n"/>
-    </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="F132" s="13" t="n">
+        <v>0.757</v>
+      </c>
+    </row>
+    <row r="133"/>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="n"/>
+      <c r="C135" s="6" t="n"/>
+      <c r="D135" s="6" t="n"/>
+      <c r="E135" s="6" t="n"/>
+      <c r="F135" s="6" t="n"/>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B136" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C136" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr">
+      <c r="D136" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="E136" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F129" s="7" t="inlineStr">
+      <c r="F136" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="14" customHeight="1">
-      <c r="A130" s="8" t="inlineStr">
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B130" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C130" s="10" t="inlineStr">
+      <c r="B137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D130" s="11" t="inlineStr">
+      <c r="D137" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E130" s="12" t="inlineStr">
+      <c r="E137" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F130" s="13" t="n">
-        <v>48.02</v>
-      </c>
-    </row>
-    <row r="131" ht="31.5" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="F137" s="13" t="n">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="138" ht="31.5" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="B138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
+      <c r="D138" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E131" s="12" t="inlineStr">
+      <c r="E138" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F131" s="13" t="n">
-        <v>1.922</v>
-      </c>
-    </row>
-    <row r="132" ht="31.5" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
+      <c r="F138" s="13" t="n">
+        <v>1.344</v>
+      </c>
+    </row>
+    <row r="139" ht="31.5" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="B139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D132" s="11" t="inlineStr">
+      <c r="D139" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E132" s="12" t="inlineStr">
+      <c r="E139" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F132" s="13" t="n">
-        <v>8.41</v>
-      </c>
-    </row>
-    <row r="133" ht="14" customHeight="1">
-      <c r="A133" s="8" t="inlineStr">
+      <c r="F139" s="13" t="n">
+        <v>15.15</v>
+      </c>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
+      <c r="B140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D133" s="11" t="inlineStr">
+      <c r="D140" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E133" s="12" t="inlineStr">
+      <c r="E140" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F133" s="13" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="134" ht="21" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+      <c r="F140" s="13" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="141" ht="21" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="B141" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D134" s="11" t="inlineStr">
+      <c r="D141" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E134" s="12" t="inlineStr">
+      <c r="E141" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F134" s="13" t="n">
-        <v>0.757</v>
-      </c>
-    </row>
-    <row r="135"/>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="24" customHeight="1">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="n"/>
-      <c r="C137" s="6" t="n"/>
-      <c r="D137" s="6" t="n"/>
-      <c r="E137" s="6" t="n"/>
-      <c r="F137" s="6" t="n"/>
-    </row>
-    <row r="138" ht="28" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
+      <c r="F141" s="13" t="n">
+        <v>1.232</v>
+      </c>
+    </row>
+    <row r="142"/>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="24" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="6" t="n"/>
+      <c r="F144" s="6" t="n"/>
+    </row>
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B138" s="7" t="inlineStr">
+      <c r="B145" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C138" s="7" t="inlineStr">
+      <c r="C145" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr">
+      <c r="D145" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E138" s="7" t="inlineStr">
+      <c r="E145" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F138" s="7" t="inlineStr">
+      <c r="F145" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="14" customHeight="1">
-      <c r="A139" s="8" t="inlineStr">
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B139" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="B146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr">
+      <c r="D146" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E139" s="12" t="inlineStr">
+      <c r="E146" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F139" s="13" t="n">
-        <v>106.5</v>
-      </c>
-    </row>
-    <row r="140" ht="31.5" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+      <c r="F146" s="13" t="n">
+        <v>88.75</v>
+      </c>
+    </row>
+    <row r="147" ht="31.5" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B140" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="B147" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D147" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E140" s="12" t="inlineStr">
+      <c r="E147" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F140" s="13" t="n">
-        <v>1.344</v>
-      </c>
-    </row>
-    <row r="141" ht="31.5" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+      <c r="F147" s="13" t="n">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="148" ht="31.5" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
+      <c r="B148" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D141" s="11" t="inlineStr">
+      <c r="D148" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E141" s="12" t="inlineStr">
+      <c r="E148" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F141" s="13" t="n">
-        <v>15.15</v>
-      </c>
-    </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+      <c r="F148" s="13" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B142" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" s="10" t="inlineStr">
+      <c r="B149" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D142" s="11" t="inlineStr">
+      <c r="D149" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E142" s="12" t="inlineStr">
+      <c r="E149" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F142" s="13" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="143" ht="21" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="F149" s="13" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="150" ht="21" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
+      <c r="B150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr">
+      <c r="D150" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E143" s="12" t="inlineStr">
+      <c r="E150" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F143" s="13" t="n">
-        <v>1.232</v>
-      </c>
-    </row>
-    <row r="144"/>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="24" customHeight="1">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="n"/>
-      <c r="C146" s="6" t="n"/>
-      <c r="D146" s="6" t="n"/>
-      <c r="E146" s="6" t="n"/>
-      <c r="F146" s="6" t="n"/>
-    </row>
-    <row r="147" ht="28" customHeight="1">
-      <c r="A147" s="7" t="inlineStr">
+      <c r="F150" s="13" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="151"/>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="24" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="n"/>
+      <c r="C153" s="6" t="n"/>
+      <c r="D153" s="6" t="n"/>
+      <c r="E153" s="6" t="n"/>
+      <c r="F153" s="6" t="n"/>
+    </row>
+    <row r="154" ht="28" customHeight="1">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B154" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C147" s="7" t="inlineStr">
+      <c r="C154" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D147" s="7" t="inlineStr">
+      <c r="D154" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E147" s="7" t="inlineStr">
+      <c r="E154" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F147" s="7" t="inlineStr">
+      <c r="F154" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="14" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C148" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E148" s="12" t="inlineStr">
+      <c r="B155" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F148" s="13" t="n">
-        <v>88.75</v>
-      </c>
-    </row>
-    <row r="149" ht="31.5" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E149" s="12" t="inlineStr">
+      <c r="F155" s="13" t="n">
+        <v>260.943</v>
+      </c>
+    </row>
+    <row r="156" ht="31.5" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F149" s="13" t="n">
-        <v>1.024</v>
-      </c>
-    </row>
-    <row r="150" ht="31.5" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D150" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E150" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="n">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="151" ht="14" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B151" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C151" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D151" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E151" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F151" s="13" t="n">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="152" ht="21" customHeight="1">
-      <c r="A152" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C152" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D152" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E152" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F152" s="13" t="n">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="153"/>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="24" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="n"/>
-      <c r="C155" s="6" t="n"/>
-      <c r="D155" s="6" t="n"/>
-      <c r="E155" s="6" t="n"/>
-      <c r="F155" s="6" t="n"/>
-    </row>
-    <row r="156" ht="28" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C156" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D156" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F156" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
+      <c r="F156" s="13" t="n">
+        <v>1.566</v>
       </c>
     </row>
     <row r="157" ht="14" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B157" s="9" t="n">
@@ -4157,27 +4157,27 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F157" s="13" t="n">
-        <v>260.943</v>
-      </c>
-    </row>
-    <row r="158" ht="31.5" customHeight="1">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="158" ht="21" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B158" s="9" t="n">
@@ -4185,27 +4185,27 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F158" s="13" t="n">
-        <v>1.566</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="159" ht="14" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Çevre düzenlemesi ve çit işleri</t>
         </is>
       </c>
       <c r="B159" s="9" t="n">
@@ -4213,27 +4213,27 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>TKDK-0091</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F159" s="13" t="n">
-        <v>14.4</v>
+        <v>361.04</v>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B160" s="9" t="n">
@@ -4241,55 +4241,51 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F160" s="13" t="n">
-        <v>0.141</v>
+        <v>50</v>
       </c>
     </row>
     <row r="161" ht="14" customHeight="1">
-      <c r="A161" s="8" t="inlineStr">
-        <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
-        </is>
-      </c>
+      <c r="A161" s="15" t="n"/>
       <c r="B161" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>15.560.1003</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F161" s="13" t="n">
-        <v>361.04</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" ht="21" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B162" s="9" t="n">
@@ -4297,36 +4293,36 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.100.1104</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F162" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="15" t="n"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" ht="21" customHeight="1">
+      <c r="A163" s="14" t="n"/>
       <c r="B163" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>15.560.1003</t>
+          <t>35.100.2106</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -4335,26 +4331,22 @@
         </is>
       </c>
       <c r="F163" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
+      <c r="A164" s="14" t="n"/>
       <c r="B164" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>35.100.1104</t>
+          <t>35.135.3201</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
@@ -4369,16 +4361,16 @@
     <row r="165" ht="21" customHeight="1">
       <c r="A165" s="14" t="n"/>
       <c r="B165" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>35.100.2106</t>
+          <t>35.110.1104</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
@@ -4390,19 +4382,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" ht="21" customHeight="1">
+    <row r="166" ht="14" customHeight="1">
       <c r="A166" s="14" t="n"/>
       <c r="B166" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>35.135.3201</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
@@ -4411,246 +4403,195 @@
         </is>
       </c>
       <c r="F166" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1">
       <c r="A167" s="14" t="n"/>
       <c r="B167" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>35.110.1104</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F167" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" ht="14" customHeight="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="168" ht="21" customHeight="1">
       <c r="A168" s="14" t="n"/>
       <c r="B168" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.140.3101</t>
         </is>
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F168" s="13" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1">
       <c r="A169" s="14" t="n"/>
       <c r="B169" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>35.140.3105</t>
+          <t>35.172.1706</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F169" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="170" ht="21" customHeight="1">
-      <c r="A170" s="14" t="n"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="15" t="n"/>
       <c r="B170" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>35.140.3101</t>
+          <t>35.170.4002</t>
         </is>
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F170" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="171" ht="21" customHeight="1">
-      <c r="A171" s="14" t="n"/>
-      <c r="B171" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C171" s="10" t="inlineStr">
-        <is>
-          <t>35.172.1706</t>
-        </is>
-      </c>
-      <c r="D171" s="11" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E171" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F171" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="15" t="n"/>
-      <c r="B172" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C172" s="10" t="inlineStr">
-        <is>
-          <t>35.170.4002</t>
-        </is>
-      </c>
-      <c r="D172" s="11" t="inlineStr">
-        <is>
-          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E172" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F172" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="173"/>
-    <row r="174">
-      <c r="A174" s="16" t="inlineStr">
+    <row r="171"/>
+    <row r="172">
+      <c r="A172" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B174" s="6" t="n"/>
-      <c r="C174" s="6" t="n"/>
-      <c r="D174" s="6" t="n"/>
-      <c r="E174" s="6" t="n"/>
-      <c r="F174" s="6" t="n"/>
+      <c r="B172" s="6" t="n"/>
+      <c r="C172" s="6" t="n"/>
+      <c r="D172" s="6" t="n"/>
+      <c r="E172" s="6" t="n"/>
+      <c r="F172" s="6" t="n"/>
+    </row>
+    <row r="173" ht="13" customHeight="1">
+      <c r="A173" s="17" t="inlineStr">
+        <is>
+          <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="17" t="inlineStr">
+        <is>
+          <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="13" customHeight="1">
       <c r="A175" s="17" t="inlineStr">
         <is>
-          <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="22" customHeight="1">
+          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="13" customHeight="1">
       <c r="A176" s="17" t="inlineStr">
         <is>
-          <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="13" customHeight="1">
-      <c r="A177" s="17" t="inlineStr">
-        <is>
-          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="13" customHeight="1">
-      <c r="A178" s="17" t="inlineStr">
-        <is>
           <t>•  Elektrik tesisatı bölümü, kuvvetli akım birim fiyat listesi temin edildikten sonra tamamlanacaktır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="89">
     <mergeCell ref="A174:F174"/>
     <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A147"/>
     <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A156"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A155"/>
     <mergeCell ref="A175:F175"/>
     <mergeCell ref="A130"/>
     <mergeCell ref="A77"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A148"/>
+    <mergeCell ref="A144:F144"/>
     <mergeCell ref="A157"/>
     <mergeCell ref="A123"/>
+    <mergeCell ref="A138"/>
     <mergeCell ref="A132"/>
+    <mergeCell ref="A134:F134"/>
+    <mergeCell ref="A152:F152"/>
     <mergeCell ref="A70:A72"/>
-    <mergeCell ref="A133"/>
     <mergeCell ref="A158"/>
     <mergeCell ref="A55"/>
     <mergeCell ref="A104"/>
-    <mergeCell ref="A160"/>
     <mergeCell ref="A150"/>
+    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A162:A170"/>
     <mergeCell ref="A159"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A134"/>
-    <mergeCell ref="A152"/>
     <mergeCell ref="A121"/>
-    <mergeCell ref="A164:A172"/>
-    <mergeCell ref="A161"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A31"/>
     <mergeCell ref="A58"/>
     <mergeCell ref="A79:A97"/>
     <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A124"/>
-    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A146"/>
     <mergeCell ref="A176:F176"/>
     <mergeCell ref="A149"/>
-    <mergeCell ref="A178:F178"/>
-    <mergeCell ref="A151"/>
+    <mergeCell ref="A153:F153"/>
     <mergeCell ref="A141"/>
-    <mergeCell ref="A137:F137"/>
-    <mergeCell ref="A177:F177"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A122"/>
-    <mergeCell ref="A125"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A112"/>
-    <mergeCell ref="A154:F154"/>
     <mergeCell ref="A59:A61"/>
     <mergeCell ref="A30"/>
     <mergeCell ref="A114"/>
@@ -4658,14 +4599,17 @@
     <mergeCell ref="A100:F100"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A137"/>
+    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A106:A107"/>
     <mergeCell ref="A56"/>
     <mergeCell ref="A139"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A129"/>
     <mergeCell ref="A116"/>
     <mergeCell ref="A8"/>
     <mergeCell ref="A131"/>
-    <mergeCell ref="A128:F128"/>
     <mergeCell ref="A140"/>
     <mergeCell ref="A10"/>
     <mergeCell ref="A115"/>
@@ -4673,19 +4617,17 @@
     <mergeCell ref="A75:A76"/>
     <mergeCell ref="A67:A69"/>
     <mergeCell ref="A9"/>
-    <mergeCell ref="A143"/>
-    <mergeCell ref="A142"/>
     <mergeCell ref="A11"/>
     <mergeCell ref="A103"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A78"/>
-    <mergeCell ref="A155:F155"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A128"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A32:A50"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A105"/>
     <mergeCell ref="A110:F110"/>
-    <mergeCell ref="A146:F146"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A57"/>
     <mergeCell ref="A6:F6"/>
@@ -4704,7 +4646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J545"/>
+  <dimension ref="A1:J533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14266,7 +14208,7 @@
       </c>
       <c r="C392" s="8" t="inlineStr">
         <is>
-          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
+          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo ve silo kaideleri</t>
         </is>
       </c>
       <c r="D392" s="21" t="inlineStr">
@@ -14568,23 +14510,23 @@
         <v/>
       </c>
     </row>
-    <row r="405" ht="15" customHeight="1">
+    <row r="405" ht="22" customHeight="1">
       <c r="A405" s="19" t="n">
         <v>3</v>
       </c>
       <c r="B405" s="20" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>ÖP-15</t>
         </is>
       </c>
       <c r="C405" s="8" t="inlineStr">
         <is>
-          <t>[M17]  C 25/30 hazır beton dökülmesi — foseptik ve silo kaideleri</t>
+          <t>[M62]  Prefabrik polietilen sızdırmaz foseptik tankı — 6 m³, temini, yerine konulması ve bağlantıları</t>
         </is>
       </c>
       <c r="D405" s="21" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E405" s="22" t="n"/>
@@ -14594,222 +14536,203 @@
       <c r="I405" s="22" t="n"/>
       <c r="J405" s="22" t="n"/>
     </row>
-    <row r="406" ht="12" customHeight="1">
+    <row r="406" ht="20" customHeight="1">
       <c r="A406" s="6" t="n"/>
       <c r="B406" s="6" t="n"/>
       <c r="C406" s="23" t="inlineStr">
         <is>
-          <t>Foseptik radye 30 cm (dış 2.00x2.00)</t>
+          <t>Foseptik — betonarme gövdenin iç hacmi 1.50x1.50x2.50 = 5.62 m³; en yakın standart tank 6 m³</t>
         </is>
       </c>
       <c r="D406" s="6" t="n"/>
       <c r="E406" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F406" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G406" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H406" s="29" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="F406" s="6" t="n"/>
+      <c r="G406" s="6" t="n"/>
+      <c r="H406" s="6" t="n"/>
       <c r="I406" s="24">
-        <f>E406*F406*G406*H406</f>
+        <f>E406</f>
         <v/>
       </c>
       <c r="J406" s="6" t="n"/>
     </row>
-    <row r="407" ht="20" customHeight="1">
-      <c r="A407" s="6" t="n"/>
-      <c r="B407" s="6" t="n"/>
-      <c r="C407" s="23" t="inlineStr">
-        <is>
-          <t>Foseptik perdeleri: orta çevre 2x(1.75+1.75) = 7.00 m, kalınlık 0,25, yükseklik 2.50</t>
-        </is>
-      </c>
-      <c r="D407" s="6" t="n"/>
-      <c r="E407" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F407" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G407" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="H407" s="29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I407" s="24">
-        <f>E407*F407*G407*H407</f>
-        <v/>
-      </c>
-      <c r="J407" s="6" t="n"/>
-    </row>
-    <row r="408" ht="12" customHeight="1">
-      <c r="A408" s="6" t="n"/>
-      <c r="B408" s="6" t="n"/>
-      <c r="C408" s="23" t="inlineStr">
-        <is>
-          <t>Foseptik üst döşemesi 15 cm</t>
-        </is>
-      </c>
-      <c r="D408" s="6" t="n"/>
-      <c r="E408" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F408" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G408" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H408" s="29" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I408" s="24">
-        <f>E408*F408*G408*H408</f>
-        <v/>
-      </c>
-      <c r="J408" s="6" t="n"/>
-    </row>
-    <row r="409">
-      <c r="A409" s="22" t="n"/>
-      <c r="B409" s="22" t="n"/>
-      <c r="C409" s="25" t="inlineStr">
-        <is>
-          <t>M17 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D409" s="26" t="inlineStr">
+    <row r="407">
+      <c r="A407" s="22" t="n"/>
+      <c r="B407" s="22" t="n"/>
+      <c r="C407" s="25" t="inlineStr">
+        <is>
+          <t>M62 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D407" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E407" s="22" t="n"/>
+      <c r="F407" s="22" t="n"/>
+      <c r="G407" s="22" t="n"/>
+      <c r="H407" s="22" t="n"/>
+      <c r="I407" s="22" t="n"/>
+      <c r="J407" s="27">
+        <f>SUM(I406:I406)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="408"/>
+    <row r="409" ht="20" customHeight="1">
+      <c r="A409" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: YEM SILOSU BETONARME KAIDELERI</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="28" customHeight="1">
+      <c r="A410" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B410" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="C410" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı / Ölçünün Alındığı Yer</t>
+        </is>
+      </c>
+      <c r="D410" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="E410" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F410" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="G410" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="H410" s="7" t="inlineStr">
+        <is>
+          <t>Yükseklik (m)</t>
+        </is>
+      </c>
+      <c r="I410" s="7" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="J410" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Miktar</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="22" customHeight="1">
+      <c r="A411" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B411" s="20" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="C411" s="8" t="inlineStr">
+        <is>
+          <t>[M05]  Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D411" s="21" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E409" s="22" t="n"/>
-      <c r="F409" s="22" t="n"/>
-      <c r="G409" s="22" t="n"/>
-      <c r="H409" s="22" t="n"/>
-      <c r="I409" s="22" t="n"/>
-      <c r="J409" s="27">
-        <f>SUM(I406:I408)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="410" ht="22" customHeight="1">
-      <c r="A410" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B410" s="20" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C410" s="8" t="inlineStr">
-        <is>
-          <t>[M21]  Plywood ile düz yüzeyli betonarme kalıbı — foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="D410" s="21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E410" s="22" t="n"/>
-      <c r="F410" s="22" t="n"/>
-      <c r="G410" s="22" t="n"/>
-      <c r="H410" s="22" t="n"/>
-      <c r="I410" s="22" t="n"/>
-      <c r="J410" s="22" t="n"/>
-    </row>
-    <row r="411" ht="12" customHeight="1">
-      <c r="A411" s="6" t="n"/>
-      <c r="B411" s="6" t="n"/>
-      <c r="C411" s="23" t="inlineStr">
-        <is>
-          <t>Foseptik radye çevresi 2x(2.00+2.00) = 8.00 m x 0,30</t>
-        </is>
-      </c>
-      <c r="D411" s="6" t="n"/>
-      <c r="E411" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F411" s="6" t="n"/>
-      <c r="G411" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="H411" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I411" s="24">
-        <f>E411*G411*H411</f>
-        <v/>
-      </c>
-      <c r="J411" s="6" t="n"/>
-    </row>
-    <row r="412" ht="12" customHeight="1">
+      <c r="E411" s="22" t="n"/>
+      <c r="F411" s="22" t="n"/>
+      <c r="G411" s="22" t="n"/>
+      <c r="H411" s="22" t="n"/>
+      <c r="I411" s="22" t="n"/>
+      <c r="J411" s="22" t="n"/>
+    </row>
+    <row r="412" ht="20" customHeight="1">
       <c r="A412" s="6" t="n"/>
       <c r="B412" s="6" t="n"/>
       <c r="C412" s="23" t="inlineStr">
         <is>
-          <t>Foseptik perde iki yüz (7.00 m x 2.50 m)</t>
+          <t>Silo kaideleri: 2.90x2.90 kaide; 1,00 m çalışma payı -&gt; 4.90x4.90; derinlik 1,00 m</t>
         </is>
       </c>
       <c r="D412" s="6" t="n"/>
       <c r="E412" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="F412" s="6" t="n"/>
+      <c r="F412" s="29" t="n">
+        <v>4.9</v>
+      </c>
       <c r="G412" s="29" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="H412" s="29" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I412" s="24">
-        <f>E412*G412*H412</f>
+        <f>E412*F412*G412*H412</f>
         <v/>
       </c>
       <c r="J412" s="6" t="n"/>
     </row>
-    <row r="413" ht="12" customHeight="1">
-      <c r="A413" s="6" t="n"/>
-      <c r="B413" s="6" t="n"/>
-      <c r="C413" s="23" t="inlineStr">
-        <is>
-          <t>Foseptik tavan kalıbı</t>
-        </is>
-      </c>
-      <c r="D413" s="6" t="n"/>
-      <c r="E413" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F413" s="29" t="n">
+    <row r="413">
+      <c r="A413" s="22" t="n"/>
+      <c r="B413" s="22" t="n"/>
+      <c r="C413" s="25" t="inlineStr">
+        <is>
+          <t>M05 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D413" s="26" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E413" s="22" t="n"/>
+      <c r="F413" s="22" t="n"/>
+      <c r="G413" s="22" t="n"/>
+      <c r="H413" s="22" t="n"/>
+      <c r="I413" s="22" t="n"/>
+      <c r="J413" s="27">
+        <f>SUM(I412:I412)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="414" ht="22" customHeight="1">
+      <c r="A414" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="G413" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H413" s="6" t="n"/>
-      <c r="I413" s="24">
-        <f>E413*F413*G413</f>
-        <v/>
-      </c>
-      <c r="J413" s="6" t="n"/>
-    </row>
-    <row r="414">
-      <c r="A414" s="22" t="n"/>
-      <c r="B414" s="22" t="n"/>
-      <c r="C414" s="25" t="inlineStr">
-        <is>
-          <t>M21 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D414" s="26" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="B414" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="C414" s="8" t="inlineStr">
+        <is>
+          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
+        </is>
+      </c>
+      <c r="D414" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
         </is>
       </c>
       <c r="E414" s="22" t="n"/>
@@ -14817,135 +14740,122 @@
       <c r="G414" s="22" t="n"/>
       <c r="H414" s="22" t="n"/>
       <c r="I414" s="22" t="n"/>
-      <c r="J414" s="27">
-        <f>SUM(I411:I413)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="415" ht="22" customHeight="1">
-      <c r="A415" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B415" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C415" s="8" t="inlineStr">
-        <is>
-          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="D415" s="21" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E415" s="22" t="n"/>
-      <c r="F415" s="22" t="n"/>
-      <c r="G415" s="22" t="n"/>
-      <c r="H415" s="22" t="n"/>
-      <c r="I415" s="22" t="n"/>
-      <c r="J415" s="22" t="n"/>
-    </row>
-    <row r="416" ht="12" customHeight="1">
-      <c r="A416" s="6" t="n"/>
-      <c r="B416" s="6" t="n"/>
-      <c r="C416" s="23" t="inlineStr">
-        <is>
-          <t>Foseptik radyesi: 2.00x2.00x0,30 m³, 95 kg/m³</t>
-        </is>
-      </c>
-      <c r="D416" s="6" t="n"/>
-      <c r="E416" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F416" s="29" t="n">
+      <c r="J414" s="22" t="n"/>
+    </row>
+    <row r="415" ht="12" customHeight="1">
+      <c r="A415" s="6" t="n"/>
+      <c r="B415" s="6" t="n"/>
+      <c r="C415" s="23" t="inlineStr">
+        <is>
+          <t>Silo kaideleri (2.90x2.90 + 0,10 taşma), 2 adet</t>
+        </is>
+      </c>
+      <c r="D415" s="6" t="n"/>
+      <c r="E415" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G416" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H416" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I416" s="24">
-        <f>E416*F416*G416*H416*J416</f>
-        <v/>
-      </c>
-      <c r="J416" s="30" t="n">
-        <v>0.095</v>
-      </c>
-    </row>
-    <row r="417" ht="12" customHeight="1">
-      <c r="A417" s="6" t="n"/>
-      <c r="B417" s="6" t="n"/>
-      <c r="C417" s="23" t="inlineStr">
-        <is>
-          <t>Foseptik perdeleri: 7.00x0,25x2.50 m³, 95 kg/m³</t>
-        </is>
-      </c>
-      <c r="D417" s="6" t="n"/>
-      <c r="E417" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F417" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G417" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="H417" s="29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I417" s="24">
-        <f>E417*F417*G417*H417*J417</f>
-        <v/>
-      </c>
-      <c r="J417" s="30" t="n">
-        <v>0.095</v>
-      </c>
+      <c r="F415" s="29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G415" s="29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H415" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I415" s="24">
+        <f>E415*F415*G415*H415</f>
+        <v/>
+      </c>
+      <c r="J415" s="6" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="22" t="n"/>
+      <c r="B416" s="22" t="n"/>
+      <c r="C416" s="25" t="inlineStr">
+        <is>
+          <t>M11 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D416" s="26" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E416" s="22" t="n"/>
+      <c r="F416" s="22" t="n"/>
+      <c r="G416" s="22" t="n"/>
+      <c r="H416" s="22" t="n"/>
+      <c r="I416" s="22" t="n"/>
+      <c r="J416" s="27">
+        <f>SUM(I415:I415)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="417" ht="15" customHeight="1">
+      <c r="A417" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B417" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="C417" s="8" t="inlineStr">
+        <is>
+          <t>[M17]  C 25/30 hazır beton dökülmesi — silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D417" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E417" s="22" t="n"/>
+      <c r="F417" s="22" t="n"/>
+      <c r="G417" s="22" t="n"/>
+      <c r="H417" s="22" t="n"/>
+      <c r="I417" s="22" t="n"/>
+      <c r="J417" s="22" t="n"/>
     </row>
     <row r="418" ht="12" customHeight="1">
       <c r="A418" s="6" t="n"/>
       <c r="B418" s="6" t="n"/>
       <c r="C418" s="23" t="inlineStr">
         <is>
-          <t>Foseptik döşemesi: 2.00x2.00x0,15 m³, 95 kg/m³</t>
+          <t>Silo betonarme kaidesi (2 adet)</t>
         </is>
       </c>
       <c r="D418" s="6" t="n"/>
       <c r="E418" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F418" s="29" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="G418" s="29" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="H418" s="29" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="I418" s="24">
-        <f>E418*F418*G418*H418*J418</f>
-        <v/>
-      </c>
-      <c r="J418" s="30" t="n">
-        <v>0.095</v>
-      </c>
+        <f>E418*F418*G418*H418</f>
+        <v/>
+      </c>
+      <c r="J418" s="6" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="22" t="n"/>
       <c r="B419" s="22" t="n"/>
       <c r="C419" s="25" t="inlineStr">
         <is>
-          <t>M26 TOPLAMI</t>
+          <t>M17 TOPLAMI</t>
         </is>
       </c>
       <c r="D419" s="26" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E419" s="22" t="n"/>
@@ -14954,87 +14864,101 @@
       <c r="H419" s="22" t="n"/>
       <c r="I419" s="22" t="n"/>
       <c r="J419" s="27">
-        <f>SUM(I416:I418)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="420"/>
+        <f>SUM(I418:I418)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="420" ht="15" customHeight="1">
+      <c r="A420" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B420" s="20" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="C420" s="8" t="inlineStr">
+        <is>
+          <t>[M21]  Plywood ile düz yüzeyli betonarme kalıbı — silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D420" s="21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E420" s="22" t="n"/>
+      <c r="F420" s="22" t="n"/>
+      <c r="G420" s="22" t="n"/>
+      <c r="H420" s="22" t="n"/>
+      <c r="I420" s="22" t="n"/>
+      <c r="J420" s="22" t="n"/>
+    </row>
     <row r="421" ht="20" customHeight="1">
-      <c r="A421" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: YEM SILOSU BETONARME KAIDELERI</t>
-        </is>
-      </c>
-    </row>
-    <row r="422" ht="28" customHeight="1">
-      <c r="A422" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B422" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C422" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı / Ölçünün Alındığı Yer</t>
-        </is>
-      </c>
-      <c r="D422" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="E422" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F422" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="G422" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="H422" s="7" t="inlineStr">
-        <is>
-          <t>Yükseklik (m)</t>
-        </is>
-      </c>
-      <c r="I422" s="7" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="J422" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Miktar</t>
-        </is>
+      <c r="A421" s="6" t="n"/>
+      <c r="B421" s="6" t="n"/>
+      <c r="C421" s="23" t="inlineStr">
+        <is>
+          <t>Silo kaidesi yan yüzleri: 4 yüz x 2 adet, boy 2.90, yükseklik 0.50</t>
+        </is>
+      </c>
+      <c r="D421" s="6" t="n"/>
+      <c r="E421" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F421" s="6" t="n"/>
+      <c r="G421" s="29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H421" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I421" s="24">
+        <f>E421*G421*H421</f>
+        <v/>
+      </c>
+      <c r="J421" s="6" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="22" t="n"/>
+      <c r="B422" s="22" t="n"/>
+      <c r="C422" s="25" t="inlineStr">
+        <is>
+          <t>M21 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D422" s="26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E422" s="22" t="n"/>
+      <c r="F422" s="22" t="n"/>
+      <c r="G422" s="22" t="n"/>
+      <c r="H422" s="22" t="n"/>
+      <c r="I422" s="22" t="n"/>
+      <c r="J422" s="27">
+        <f>SUM(I421:I421)</f>
+        <v/>
       </c>
     </row>
     <row r="423" ht="22" customHeight="1">
       <c r="A423" s="19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B423" s="20" t="inlineStr">
         <is>
-          <t>15.120.1101</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="C423" s="8" t="inlineStr">
         <is>
-          <t>[M05]  Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
+          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo ve silo kaideleri</t>
         </is>
       </c>
       <c r="D423" s="21" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="E423" s="22" t="n"/>
@@ -15044,12 +14968,12 @@
       <c r="I423" s="22" t="n"/>
       <c r="J423" s="22" t="n"/>
     </row>
-    <row r="424" ht="20" customHeight="1">
+    <row r="424" ht="12" customHeight="1">
       <c r="A424" s="6" t="n"/>
       <c r="B424" s="6" t="n"/>
       <c r="C424" s="23" t="inlineStr">
         <is>
-          <t>Silo kaideleri: 2.90x2.90 kaide; 1,00 m çalışma payı -&gt; 4.90x4.90; derinlik 1,00 m</t>
+          <t>Silo kaideleri: 2.90x2.90x0.50 m³ x 2, 90 kg/m³</t>
         </is>
       </c>
       <c r="D424" s="6" t="n"/>
@@ -15057,31 +14981,33 @@
         <v>2</v>
       </c>
       <c r="F424" s="29" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="G424" s="29" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="H424" s="29" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I424" s="24">
-        <f>E424*F424*G424*H424</f>
-        <v/>
-      </c>
-      <c r="J424" s="6" t="n"/>
+        <f>E424*F424*G424*H424*J424</f>
+        <v/>
+      </c>
+      <c r="J424" s="30" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="22" t="n"/>
       <c r="B425" s="22" t="n"/>
       <c r="C425" s="25" t="inlineStr">
         <is>
-          <t>M05 TOPLAMI</t>
+          <t>M26 TOPLAMI</t>
         </is>
       </c>
       <c r="D425" s="26" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="E425" s="22" t="n"/>
@@ -15094,94 +15020,78 @@
         <v/>
       </c>
     </row>
-    <row r="426" ht="22" customHeight="1">
-      <c r="A426" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B426" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C426" s="8" t="inlineStr">
-        <is>
-          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
-        </is>
-      </c>
-      <c r="D426" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E426" s="22" t="n"/>
-      <c r="F426" s="22" t="n"/>
-      <c r="G426" s="22" t="n"/>
-      <c r="H426" s="22" t="n"/>
-      <c r="I426" s="22" t="n"/>
-      <c r="J426" s="22" t="n"/>
-    </row>
-    <row r="427" ht="12" customHeight="1">
-      <c r="A427" s="6" t="n"/>
-      <c r="B427" s="6" t="n"/>
-      <c r="C427" s="23" t="inlineStr">
-        <is>
-          <t>Silo kaideleri (2.90x2.90 + 0,10 taşma), 2 adet</t>
-        </is>
-      </c>
-      <c r="D427" s="6" t="n"/>
-      <c r="E427" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F427" s="29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G427" s="29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H427" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I427" s="24">
-        <f>E427*F427*G427*H427</f>
-        <v/>
-      </c>
-      <c r="J427" s="6" t="n"/>
-    </row>
-    <row r="428">
-      <c r="A428" s="22" t="n"/>
-      <c r="B428" s="22" t="n"/>
-      <c r="C428" s="25" t="inlineStr">
-        <is>
-          <t>M11 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D428" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E428" s="22" t="n"/>
-      <c r="F428" s="22" t="n"/>
-      <c r="G428" s="22" t="n"/>
-      <c r="H428" s="22" t="n"/>
-      <c r="I428" s="22" t="n"/>
-      <c r="J428" s="27">
-        <f>SUM(I427:I427)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="429" ht="15" customHeight="1">
+    <row r="426"/>
+    <row r="427" ht="20" customHeight="1">
+      <c r="A427" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: SU DEPOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="28" customHeight="1">
+      <c r="A428" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B428" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="C428" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı / Ölçünün Alındığı Yer</t>
+        </is>
+      </c>
+      <c r="D428" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="E428" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F428" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="G428" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="H428" s="7" t="inlineStr">
+        <is>
+          <t>Yükseklik (m)</t>
+        </is>
+      </c>
+      <c r="I428" s="7" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="J428" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Miktar</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="22" customHeight="1">
       <c r="A429" s="19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B429" s="20" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.120.1101</t>
         </is>
       </c>
       <c r="C429" s="8" t="inlineStr">
         <is>
-          <t>[M17]  C 25/30 hazır beton dökülmesi — foseptik ve silo kaideleri</t>
+          <t>[M05]  Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
         </is>
       </c>
       <c r="D429" s="21" t="inlineStr">
@@ -15196,26 +15106,26 @@
       <c r="I429" s="22" t="n"/>
       <c r="J429" s="22" t="n"/>
     </row>
-    <row r="430" ht="12" customHeight="1">
+    <row r="430" ht="20" customHeight="1">
       <c r="A430" s="6" t="n"/>
       <c r="B430" s="6" t="n"/>
       <c r="C430" s="23" t="inlineStr">
         <is>
-          <t>Silo betonarme kaidesi (2 adet)</t>
+          <t>Su deposu: dış 4.00x3.00; 1,00 m çalışma payı -&gt; 6.00x5.00; derinlik 3.55 m</t>
         </is>
       </c>
       <c r="D430" s="6" t="n"/>
       <c r="E430" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F430" s="29" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="G430" s="29" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="H430" s="29" t="n">
-        <v>0.5</v>
+        <v>3.55</v>
       </c>
       <c r="I430" s="24">
         <f>E430*F430*G430*H430</f>
@@ -15228,7 +15138,7 @@
       <c r="B431" s="22" t="n"/>
       <c r="C431" s="25" t="inlineStr">
         <is>
-          <t>M17 TOPLAMI</t>
+          <t>M05 TOPLAMI</t>
         </is>
       </c>
       <c r="D431" s="26" t="inlineStr">
@@ -15248,21 +15158,21 @@
     </row>
     <row r="432" ht="22" customHeight="1">
       <c r="A432" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B432" s="20" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="C432" s="8" t="inlineStr">
         <is>
-          <t>[M21]  Plywood ile düz yüzeyli betonarme kalıbı — foseptik ve silo kaideleri</t>
+          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
         </is>
       </c>
       <c r="D432" s="21" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E432" s="22" t="n"/>
@@ -15272,27 +15182,29 @@
       <c r="I432" s="22" t="n"/>
       <c r="J432" s="22" t="n"/>
     </row>
-    <row r="433" ht="20" customHeight="1">
+    <row r="433" ht="12" customHeight="1">
       <c r="A433" s="6" t="n"/>
       <c r="B433" s="6" t="n"/>
       <c r="C433" s="23" t="inlineStr">
         <is>
-          <t>Silo kaidesi yan yüzleri: 4 yüz x 2 adet, boy 2.90, yükseklik 0.50</t>
+          <t>Su deposu (4.00x3.00 + 0,10 taşma)</t>
         </is>
       </c>
       <c r="D433" s="6" t="n"/>
       <c r="E433" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="F433" s="6" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F433" s="29" t="n">
+        <v>3.2</v>
+      </c>
       <c r="G433" s="29" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="H433" s="29" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="I433" s="24">
-        <f>E433*G433*H433</f>
+        <f>E433*F433*G433*H433</f>
         <v/>
       </c>
       <c r="J433" s="6" t="n"/>
@@ -15302,12 +15214,12 @@
       <c r="B434" s="22" t="n"/>
       <c r="C434" s="25" t="inlineStr">
         <is>
-          <t>M21 TOPLAMI</t>
+          <t>M11 TOPLAMI</t>
         </is>
       </c>
       <c r="D434" s="26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E434" s="22" t="n"/>
@@ -15322,21 +15234,21 @@
     </row>
     <row r="435" ht="22" customHeight="1">
       <c r="A435" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B435" s="20" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="C435" s="8" t="inlineStr">
         <is>
-          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
+          <t>[M16]  C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
         </is>
       </c>
       <c r="D435" s="21" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E435" s="22" t="n"/>
@@ -15351,206 +15263,217 @@
       <c r="B436" s="6" t="n"/>
       <c r="C436" s="23" t="inlineStr">
         <is>
-          <t>Silo kaideleri: 2.90x2.90x0.50 m³ x 2, 90 kg/m³</t>
+          <t>Su deposu radye 30 cm (dış 4.00x3.00)</t>
         </is>
       </c>
       <c r="D436" s="6" t="n"/>
       <c r="E436" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F436" s="29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G436" s="29" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="H436" s="29" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I436" s="24">
-        <f>E436*F436*G436*H436*J436</f>
-        <v/>
-      </c>
-      <c r="J436" s="30" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" s="22" t="n"/>
-      <c r="B437" s="22" t="n"/>
-      <c r="C437" s="25" t="inlineStr">
-        <is>
-          <t>M26 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D437" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E437" s="22" t="n"/>
-      <c r="F437" s="22" t="n"/>
-      <c r="G437" s="22" t="n"/>
-      <c r="H437" s="22" t="n"/>
-      <c r="I437" s="22" t="n"/>
-      <c r="J437" s="27">
-        <f>SUM(I436:I436)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="438"/>
-    <row r="439" ht="20" customHeight="1">
-      <c r="A439" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: SU DEPOSU</t>
-        </is>
-      </c>
-    </row>
-    <row r="440" ht="28" customHeight="1">
-      <c r="A440" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B440" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C440" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı / Ölçünün Alındığı Yer</t>
-        </is>
-      </c>
-      <c r="D440" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="E440" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F440" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="G440" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="H440" s="7" t="inlineStr">
-        <is>
-          <t>Yükseklik (m)</t>
-        </is>
-      </c>
-      <c r="I440" s="7" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="J440" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Miktar</t>
-        </is>
-      </c>
-    </row>
-    <row r="441" ht="22" customHeight="1">
-      <c r="A441" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B441" s="20" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="C441" s="8" t="inlineStr">
-        <is>
-          <t>[M05]  Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="D441" s="21" t="inlineStr">
+        <f>E436*F436*G436*H436</f>
+        <v/>
+      </c>
+      <c r="J436" s="6" t="n"/>
+    </row>
+    <row r="437" ht="12" customHeight="1">
+      <c r="A437" s="6" t="n"/>
+      <c r="B437" s="6" t="n"/>
+      <c r="C437" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu perdeleri: orta çevre 2x(3.75+2.75) = 13.00 m</t>
+        </is>
+      </c>
+      <c r="D437" s="6" t="n"/>
+      <c r="E437" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F437" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G437" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="H437" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I437" s="24">
+        <f>E437*F437*G437*H437</f>
+        <v/>
+      </c>
+      <c r="J437" s="6" t="n"/>
+    </row>
+    <row r="438" ht="12" customHeight="1">
+      <c r="A438" s="6" t="n"/>
+      <c r="B438" s="6" t="n"/>
+      <c r="C438" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu üst döşemesi 15 cm</t>
+        </is>
+      </c>
+      <c r="D438" s="6" t="n"/>
+      <c r="E438" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F438" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G438" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H438" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I438" s="24">
+        <f>E438*F438*G438*H438</f>
+        <v/>
+      </c>
+      <c r="J438" s="6" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="22" t="n"/>
+      <c r="B439" s="22" t="n"/>
+      <c r="C439" s="25" t="inlineStr">
+        <is>
+          <t>M16 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D439" s="26" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E441" s="22" t="n"/>
-      <c r="F441" s="22" t="n"/>
-      <c r="G441" s="22" t="n"/>
-      <c r="H441" s="22" t="n"/>
-      <c r="I441" s="22" t="n"/>
-      <c r="J441" s="22" t="n"/>
-    </row>
-    <row r="442" ht="20" customHeight="1">
+      <c r="E439" s="22" t="n"/>
+      <c r="F439" s="22" t="n"/>
+      <c r="G439" s="22" t="n"/>
+      <c r="H439" s="22" t="n"/>
+      <c r="I439" s="22" t="n"/>
+      <c r="J439" s="27">
+        <f>SUM(I436:I438)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="440" ht="15" customHeight="1">
+      <c r="A440" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B440" s="20" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="C440" s="8" t="inlineStr">
+        <is>
+          <t>[M20]  Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
+        </is>
+      </c>
+      <c r="D440" s="21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E440" s="22" t="n"/>
+      <c r="F440" s="22" t="n"/>
+      <c r="G440" s="22" t="n"/>
+      <c r="H440" s="22" t="n"/>
+      <c r="I440" s="22" t="n"/>
+      <c r="J440" s="22" t="n"/>
+    </row>
+    <row r="441" ht="12" customHeight="1">
+      <c r="A441" s="6" t="n"/>
+      <c r="B441" s="6" t="n"/>
+      <c r="C441" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu radye çevresi 2x(4.00+3.00) = 14.00 m x 0,40</t>
+        </is>
+      </c>
+      <c r="D441" s="6" t="n"/>
+      <c r="E441" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F441" s="6" t="n"/>
+      <c r="G441" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H441" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I441" s="24">
+        <f>E441*G441*H441</f>
+        <v/>
+      </c>
+      <c r="J441" s="6" t="n"/>
+    </row>
+    <row r="442" ht="12" customHeight="1">
       <c r="A442" s="6" t="n"/>
       <c r="B442" s="6" t="n"/>
       <c r="C442" s="23" t="inlineStr">
         <is>
-          <t>Su deposu: dış 4.00x3.00; 1,00 m çalışma payı -&gt; 6.00x5.00; derinlik 3.55 m</t>
+          <t>Su deposu perde iki yüz (13.00 m x 3.00 m)</t>
         </is>
       </c>
       <c r="D442" s="6" t="n"/>
       <c r="E442" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F442" s="29" t="n">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F442" s="6" t="n"/>
       <c r="G442" s="29" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H442" s="29" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="I442" s="24">
-        <f>E442*F442*G442*H442</f>
+        <f>E442*G442*H442</f>
         <v/>
       </c>
       <c r="J442" s="6" t="n"/>
     </row>
-    <row r="443">
-      <c r="A443" s="22" t="n"/>
-      <c r="B443" s="22" t="n"/>
-      <c r="C443" s="25" t="inlineStr">
-        <is>
-          <t>M05 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D443" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E443" s="22" t="n"/>
-      <c r="F443" s="22" t="n"/>
-      <c r="G443" s="22" t="n"/>
-      <c r="H443" s="22" t="n"/>
-      <c r="I443" s="22" t="n"/>
-      <c r="J443" s="27">
-        <f>SUM(I442:I442)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="444" ht="22" customHeight="1">
-      <c r="A444" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B444" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C444" s="8" t="inlineStr">
-        <is>
-          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
-        </is>
-      </c>
-      <c r="D444" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
+    <row r="443" ht="12" customHeight="1">
+      <c r="A443" s="6" t="n"/>
+      <c r="B443" s="6" t="n"/>
+      <c r="C443" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu tavan kalıbı</t>
+        </is>
+      </c>
+      <c r="D443" s="6" t="n"/>
+      <c r="E443" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F443" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G443" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H443" s="6" t="n"/>
+      <c r="I443" s="24">
+        <f>E443*F443*G443</f>
+        <v/>
+      </c>
+      <c r="J443" s="6" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="22" t="n"/>
+      <c r="B444" s="22" t="n"/>
+      <c r="C444" s="25" t="inlineStr">
+        <is>
+          <t>M20 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D444" s="26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="E444" s="22" t="n"/>
@@ -15558,205 +15481,189 @@
       <c r="G444" s="22" t="n"/>
       <c r="H444" s="22" t="n"/>
       <c r="I444" s="22" t="n"/>
-      <c r="J444" s="22" t="n"/>
-    </row>
-    <row r="445" ht="12" customHeight="1">
-      <c r="A445" s="6" t="n"/>
-      <c r="B445" s="6" t="n"/>
-      <c r="C445" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu (4.00x3.00 + 0,10 taşma)</t>
-        </is>
-      </c>
-      <c r="D445" s="6" t="n"/>
-      <c r="E445" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F445" s="29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G445" s="29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H445" s="29" t="n">
+      <c r="J444" s="27">
+        <f>SUM(I441:I443)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445" ht="22" customHeight="1">
+      <c r="A445" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B445" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="C445" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo ve silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D445" s="21" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E445" s="22" t="n"/>
+      <c r="F445" s="22" t="n"/>
+      <c r="G445" s="22" t="n"/>
+      <c r="H445" s="22" t="n"/>
+      <c r="I445" s="22" t="n"/>
+      <c r="J445" s="22" t="n"/>
+    </row>
+    <row r="446" ht="20" customHeight="1">
+      <c r="A446" s="6" t="n"/>
+      <c r="B446" s="6" t="n"/>
+      <c r="C446" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu radye ve döşeme — proje metrajı 223,70+32,90 = 256,60 kg</t>
+        </is>
+      </c>
+      <c r="D446" s="6" t="n"/>
+      <c r="E446" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F446" s="6" t="n"/>
+      <c r="G446" s="6" t="n"/>
+      <c r="H446" s="6" t="n"/>
+      <c r="I446" s="24">
+        <f>E446*J446</f>
+        <v/>
+      </c>
+      <c r="J446" s="30" t="n">
+        <v>0.2566</v>
+      </c>
+    </row>
+    <row r="447" ht="12" customHeight="1">
+      <c r="A447" s="6" t="n"/>
+      <c r="B447" s="6" t="n"/>
+      <c r="C447" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu perdeleri: 13.00x0,25x3.00 m³, 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D447" s="6" t="n"/>
+      <c r="E447" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F447" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G447" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="H447" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I447" s="24">
+        <f>E447*F447*G447*H447*J447</f>
+        <v/>
+      </c>
+      <c r="J447" s="30" t="n">
         <v>0.1</v>
       </c>
-      <c r="I445" s="24">
-        <f>E445*F445*G445*H445</f>
-        <v/>
-      </c>
-      <c r="J445" s="6" t="n"/>
-    </row>
-    <row r="446">
-      <c r="A446" s="22" t="n"/>
-      <c r="B446" s="22" t="n"/>
-      <c r="C446" s="25" t="inlineStr">
-        <is>
-          <t>M11 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D446" s="26" t="inlineStr">
+    </row>
+    <row r="448">
+      <c r="A448" s="22" t="n"/>
+      <c r="B448" s="22" t="n"/>
+      <c r="C448" s="25" t="inlineStr">
+        <is>
+          <t>M26 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D448" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E448" s="22" t="n"/>
+      <c r="F448" s="22" t="n"/>
+      <c r="G448" s="22" t="n"/>
+      <c r="H448" s="22" t="n"/>
+      <c r="I448" s="22" t="n"/>
+      <c r="J448" s="27">
+        <f>SUM(I446:I447)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="449"/>
+    <row r="450" ht="20" customHeight="1">
+      <c r="A450" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: YAĞMUR SUYU DEPOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="28" customHeight="1">
+      <c r="A451" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B451" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="C451" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı / Ölçünün Alındığı Yer</t>
+        </is>
+      </c>
+      <c r="D451" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="E451" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F451" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="G451" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="H451" s="7" t="inlineStr">
+        <is>
+          <t>Yükseklik (m)</t>
+        </is>
+      </c>
+      <c r="I451" s="7" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="J451" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Miktar</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="22" customHeight="1">
+      <c r="A452" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B452" s="20" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="C452" s="8" t="inlineStr">
+        <is>
+          <t>[M05]  Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D452" s="21" t="inlineStr">
         <is>
           <t>m³</t>
-        </is>
-      </c>
-      <c r="E446" s="22" t="n"/>
-      <c r="F446" s="22" t="n"/>
-      <c r="G446" s="22" t="n"/>
-      <c r="H446" s="22" t="n"/>
-      <c r="I446" s="22" t="n"/>
-      <c r="J446" s="27">
-        <f>SUM(I445:I445)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="447" ht="22" customHeight="1">
-      <c r="A447" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B447" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C447" s="8" t="inlineStr">
-        <is>
-          <t>[M16]  C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
-        </is>
-      </c>
-      <c r="D447" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E447" s="22" t="n"/>
-      <c r="F447" s="22" t="n"/>
-      <c r="G447" s="22" t="n"/>
-      <c r="H447" s="22" t="n"/>
-      <c r="I447" s="22" t="n"/>
-      <c r="J447" s="22" t="n"/>
-    </row>
-    <row r="448" ht="12" customHeight="1">
-      <c r="A448" s="6" t="n"/>
-      <c r="B448" s="6" t="n"/>
-      <c r="C448" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu radye 30 cm (dış 4.00x3.00)</t>
-        </is>
-      </c>
-      <c r="D448" s="6" t="n"/>
-      <c r="E448" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F448" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G448" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H448" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I448" s="24">
-        <f>E448*F448*G448*H448</f>
-        <v/>
-      </c>
-      <c r="J448" s="6" t="n"/>
-    </row>
-    <row r="449" ht="12" customHeight="1">
-      <c r="A449" s="6" t="n"/>
-      <c r="B449" s="6" t="n"/>
-      <c r="C449" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu perdeleri: orta çevre 2x(3.75+2.75) = 13.00 m</t>
-        </is>
-      </c>
-      <c r="D449" s="6" t="n"/>
-      <c r="E449" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F449" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G449" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="H449" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I449" s="24">
-        <f>E449*F449*G449*H449</f>
-        <v/>
-      </c>
-      <c r="J449" s="6" t="n"/>
-    </row>
-    <row r="450" ht="12" customHeight="1">
-      <c r="A450" s="6" t="n"/>
-      <c r="B450" s="6" t="n"/>
-      <c r="C450" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu üst döşemesi 15 cm</t>
-        </is>
-      </c>
-      <c r="D450" s="6" t="n"/>
-      <c r="E450" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F450" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G450" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H450" s="29" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I450" s="24">
-        <f>E450*F450*G450*H450</f>
-        <v/>
-      </c>
-      <c r="J450" s="6" t="n"/>
-    </row>
-    <row r="451">
-      <c r="A451" s="22" t="n"/>
-      <c r="B451" s="22" t="n"/>
-      <c r="C451" s="25" t="inlineStr">
-        <is>
-          <t>M16 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D451" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E451" s="22" t="n"/>
-      <c r="F451" s="22" t="n"/>
-      <c r="G451" s="22" t="n"/>
-      <c r="H451" s="22" t="n"/>
-      <c r="I451" s="22" t="n"/>
-      <c r="J451" s="27">
-        <f>SUM(I448:I450)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="452" ht="15" customHeight="1">
-      <c r="A452" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B452" s="20" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C452" s="8" t="inlineStr">
-        <is>
-          <t>[M20]  Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
-        </is>
-      </c>
-      <c r="D452" s="21" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="E452" s="22" t="n"/>
@@ -15766,121 +15673,120 @@
       <c r="I452" s="22" t="n"/>
       <c r="J452" s="22" t="n"/>
     </row>
-    <row r="453" ht="12" customHeight="1">
+    <row r="453" ht="20" customHeight="1">
       <c r="A453" s="6" t="n"/>
       <c r="B453" s="6" t="n"/>
       <c r="C453" s="23" t="inlineStr">
         <is>
-          <t>Su deposu radye çevresi 2x(4.00+3.00) = 14.00 m x 0,40</t>
+          <t>Yağmur suyu deposu: dış 3.00x3.00; 1,00 m çalışma payı -&gt; 5.00x5.00; derinlik 3.55 m</t>
         </is>
       </c>
       <c r="D453" s="6" t="n"/>
       <c r="E453" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F453" s="6" t="n"/>
+      <c r="F453" s="29" t="n">
+        <v>5</v>
+      </c>
       <c r="G453" s="29" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H453" s="29" t="n">
-        <v>0.4</v>
+        <v>3.55</v>
       </c>
       <c r="I453" s="24">
-        <f>E453*G453*H453</f>
+        <f>E453*F453*G453*H453</f>
         <v/>
       </c>
       <c r="J453" s="6" t="n"/>
     </row>
-    <row r="454" ht="12" customHeight="1">
-      <c r="A454" s="6" t="n"/>
-      <c r="B454" s="6" t="n"/>
-      <c r="C454" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu perde iki yüz (13.00 m x 3.00 m)</t>
-        </is>
-      </c>
-      <c r="D454" s="6" t="n"/>
-      <c r="E454" s="28" t="n">
+    <row r="454">
+      <c r="A454" s="22" t="n"/>
+      <c r="B454" s="22" t="n"/>
+      <c r="C454" s="25" t="inlineStr">
+        <is>
+          <t>M05 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D454" s="26" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E454" s="22" t="n"/>
+      <c r="F454" s="22" t="n"/>
+      <c r="G454" s="22" t="n"/>
+      <c r="H454" s="22" t="n"/>
+      <c r="I454" s="22" t="n"/>
+      <c r="J454" s="27">
+        <f>SUM(I453:I453)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="1">
+      <c r="A455" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F454" s="6" t="n"/>
-      <c r="G454" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="H454" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I454" s="24">
-        <f>E454*G454*H454</f>
-        <v/>
-      </c>
-      <c r="J454" s="6" t="n"/>
-    </row>
-    <row r="455" ht="12" customHeight="1">
-      <c r="A455" s="6" t="n"/>
-      <c r="B455" s="6" t="n"/>
-      <c r="C455" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu tavan kalıbı</t>
-        </is>
-      </c>
-      <c r="D455" s="6" t="n"/>
-      <c r="E455" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F455" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G455" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H455" s="6" t="n"/>
-      <c r="I455" s="24">
-        <f>E455*F455*G455</f>
-        <v/>
-      </c>
-      <c r="J455" s="6" t="n"/>
-    </row>
-    <row r="456">
-      <c r="A456" s="22" t="n"/>
-      <c r="B456" s="22" t="n"/>
-      <c r="C456" s="25" t="inlineStr">
-        <is>
-          <t>M20 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D456" s="26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E456" s="22" t="n"/>
-      <c r="F456" s="22" t="n"/>
-      <c r="G456" s="22" t="n"/>
-      <c r="H456" s="22" t="n"/>
-      <c r="I456" s="22" t="n"/>
-      <c r="J456" s="27">
-        <f>SUM(I453:I455)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="457" ht="22" customHeight="1">
-      <c r="A457" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B457" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C457" s="8" t="inlineStr">
-        <is>
-          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="D457" s="21" t="inlineStr">
-        <is>
-          <t>ton</t>
+      <c r="B455" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="C455" s="8" t="inlineStr">
+        <is>
+          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
+        </is>
+      </c>
+      <c r="D455" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E455" s="22" t="n"/>
+      <c r="F455" s="22" t="n"/>
+      <c r="G455" s="22" t="n"/>
+      <c r="H455" s="22" t="n"/>
+      <c r="I455" s="22" t="n"/>
+      <c r="J455" s="22" t="n"/>
+    </row>
+    <row r="456" ht="12" customHeight="1">
+      <c r="A456" s="6" t="n"/>
+      <c r="B456" s="6" t="n"/>
+      <c r="C456" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu (3.00x3.00 + 0,10 taşma)</t>
+        </is>
+      </c>
+      <c r="D456" s="6" t="n"/>
+      <c r="E456" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F456" s="29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G456" s="29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H456" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I456" s="24">
+        <f>E456*F456*G456*H456</f>
+        <v/>
+      </c>
+      <c r="J456" s="6" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="22" t="n"/>
+      <c r="B457" s="22" t="n"/>
+      <c r="C457" s="25" t="inlineStr">
+        <is>
+          <t>M11 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D457" s="26" t="inlineStr">
+        <is>
+          <t>m³</t>
         </is>
       </c>
       <c r="E457" s="22" t="n"/>
@@ -15888,37 +15794,43 @@
       <c r="G457" s="22" t="n"/>
       <c r="H457" s="22" t="n"/>
       <c r="I457" s="22" t="n"/>
-      <c r="J457" s="22" t="n"/>
-    </row>
-    <row r="458" ht="20" customHeight="1">
-      <c r="A458" s="6" t="n"/>
-      <c r="B458" s="6" t="n"/>
-      <c r="C458" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu radye ve döşeme — proje metrajı 223,70+32,90 = 256,60 kg</t>
-        </is>
-      </c>
-      <c r="D458" s="6" t="n"/>
-      <c r="E458" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F458" s="6" t="n"/>
-      <c r="G458" s="6" t="n"/>
-      <c r="H458" s="6" t="n"/>
-      <c r="I458" s="24">
-        <f>E458*J458</f>
-        <v/>
-      </c>
-      <c r="J458" s="30" t="n">
-        <v>0.2566</v>
-      </c>
+      <c r="J457" s="27">
+        <f>SUM(I456:I456)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458" ht="22" customHeight="1">
+      <c r="A458" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B458" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="C458" s="8" t="inlineStr">
+        <is>
+          <t>[M16]  C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
+        </is>
+      </c>
+      <c r="D458" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E458" s="22" t="n"/>
+      <c r="F458" s="22" t="n"/>
+      <c r="G458" s="22" t="n"/>
+      <c r="H458" s="22" t="n"/>
+      <c r="I458" s="22" t="n"/>
+      <c r="J458" s="22" t="n"/>
     </row>
     <row r="459" ht="12" customHeight="1">
       <c r="A459" s="6" t="n"/>
       <c r="B459" s="6" t="n"/>
       <c r="C459" s="23" t="inlineStr">
         <is>
-          <t>Su deposu perdeleri: 13.00x0,25x3.00 m³, 100 kg/m³</t>
+          <t>Yağmur suyu deposu radye 30 cm (dış 3.00x3.00)</t>
         </is>
       </c>
       <c r="D459" s="6" t="n"/>
@@ -15926,198 +15838,209 @@
         <v>1</v>
       </c>
       <c r="F459" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G459" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H459" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I459" s="24">
+        <f>E459*F459*G459*H459</f>
+        <v/>
+      </c>
+      <c r="J459" s="6" t="n"/>
+    </row>
+    <row r="460" ht="20" customHeight="1">
+      <c r="A460" s="6" t="n"/>
+      <c r="B460" s="6" t="n"/>
+      <c r="C460" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu perdeleri: orta çevre 2x(2.75+2.75) = 11.00 m</t>
+        </is>
+      </c>
+      <c r="D460" s="6" t="n"/>
+      <c r="E460" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F460" s="29" t="n">
         <v>0.25</v>
       </c>
-      <c r="G459" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="H459" s="29" t="n">
+      <c r="G460" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="H460" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="I459" s="24">
-        <f>E459*F459*G459*H459*J459</f>
-        <v/>
-      </c>
-      <c r="J459" s="30" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" s="22" t="n"/>
-      <c r="B460" s="22" t="n"/>
-      <c r="C460" s="25" t="inlineStr">
-        <is>
-          <t>M26 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D460" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E460" s="22" t="n"/>
-      <c r="F460" s="22" t="n"/>
-      <c r="G460" s="22" t="n"/>
-      <c r="H460" s="22" t="n"/>
-      <c r="I460" s="22" t="n"/>
-      <c r="J460" s="27">
-        <f>SUM(I458:I459)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="461"/>
-    <row r="462" ht="20" customHeight="1">
-      <c r="A462" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: YAĞMUR SUYU DEPOSU</t>
-        </is>
-      </c>
-    </row>
-    <row r="463" ht="28" customHeight="1">
-      <c r="A463" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B463" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C463" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı / Ölçünün Alındığı Yer</t>
-        </is>
-      </c>
-      <c r="D463" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="E463" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F463" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="G463" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="H463" s="7" t="inlineStr">
-        <is>
-          <t>Yükseklik (m)</t>
-        </is>
-      </c>
-      <c r="I463" s="7" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="J463" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Miktar</t>
-        </is>
-      </c>
-    </row>
-    <row r="464" ht="22" customHeight="1">
-      <c r="A464" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B464" s="20" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="C464" s="8" t="inlineStr">
-        <is>
-          <t>[M05]  Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="D464" s="21" t="inlineStr">
+      <c r="I460" s="24">
+        <f>E460*F460*G460*H460</f>
+        <v/>
+      </c>
+      <c r="J460" s="6" t="n"/>
+    </row>
+    <row r="461" ht="12" customHeight="1">
+      <c r="A461" s="6" t="n"/>
+      <c r="B461" s="6" t="n"/>
+      <c r="C461" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu üst döşemesi 15 cm</t>
+        </is>
+      </c>
+      <c r="D461" s="6" t="n"/>
+      <c r="E461" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F461" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G461" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H461" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I461" s="24">
+        <f>E461*F461*G461*H461</f>
+        <v/>
+      </c>
+      <c r="J461" s="6" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="22" t="n"/>
+      <c r="B462" s="22" t="n"/>
+      <c r="C462" s="25" t="inlineStr">
+        <is>
+          <t>M16 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D462" s="26" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E464" s="22" t="n"/>
-      <c r="F464" s="22" t="n"/>
-      <c r="G464" s="22" t="n"/>
-      <c r="H464" s="22" t="n"/>
-      <c r="I464" s="22" t="n"/>
-      <c r="J464" s="22" t="n"/>
-    </row>
-    <row r="465" ht="20" customHeight="1">
+      <c r="E462" s="22" t="n"/>
+      <c r="F462" s="22" t="n"/>
+      <c r="G462" s="22" t="n"/>
+      <c r="H462" s="22" t="n"/>
+      <c r="I462" s="22" t="n"/>
+      <c r="J462" s="27">
+        <f>SUM(I459:I461)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="463" ht="15" customHeight="1">
+      <c r="A463" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B463" s="20" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="C463" s="8" t="inlineStr">
+        <is>
+          <t>[M20]  Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
+        </is>
+      </c>
+      <c r="D463" s="21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E463" s="22" t="n"/>
+      <c r="F463" s="22" t="n"/>
+      <c r="G463" s="22" t="n"/>
+      <c r="H463" s="22" t="n"/>
+      <c r="I463" s="22" t="n"/>
+      <c r="J463" s="22" t="n"/>
+    </row>
+    <row r="464" ht="20" customHeight="1">
+      <c r="A464" s="6" t="n"/>
+      <c r="B464" s="6" t="n"/>
+      <c r="C464" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu radye çevresi 2x(3.00+3.00) = 12.00 m x 0,40</t>
+        </is>
+      </c>
+      <c r="D464" s="6" t="n"/>
+      <c r="E464" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F464" s="6" t="n"/>
+      <c r="G464" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="H464" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I464" s="24">
+        <f>E464*G464*H464</f>
+        <v/>
+      </c>
+      <c r="J464" s="6" t="n"/>
+    </row>
+    <row r="465" ht="12" customHeight="1">
       <c r="A465" s="6" t="n"/>
       <c r="B465" s="6" t="n"/>
       <c r="C465" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu: dış 3.00x3.00; 1,00 m çalışma payı -&gt; 5.00x5.00; derinlik 3.55 m</t>
+          <t>Yağmur suyu deposu perde iki yüz (11.00 m x 3.00 m)</t>
         </is>
       </c>
       <c r="D465" s="6" t="n"/>
       <c r="E465" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F465" s="29" t="n">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F465" s="6" t="n"/>
       <c r="G465" s="29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H465" s="29" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="I465" s="24">
-        <f>E465*F465*G465*H465</f>
+        <f>E465*G465*H465</f>
         <v/>
       </c>
       <c r="J465" s="6" t="n"/>
     </row>
-    <row r="466">
-      <c r="A466" s="22" t="n"/>
-      <c r="B466" s="22" t="n"/>
-      <c r="C466" s="25" t="inlineStr">
-        <is>
-          <t>M05 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D466" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E466" s="22" t="n"/>
-      <c r="F466" s="22" t="n"/>
-      <c r="G466" s="22" t="n"/>
-      <c r="H466" s="22" t="n"/>
-      <c r="I466" s="22" t="n"/>
-      <c r="J466" s="27">
-        <f>SUM(I465:I465)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="467" ht="22" customHeight="1">
-      <c r="A467" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B467" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C467" s="8" t="inlineStr">
-        <is>
-          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
-        </is>
-      </c>
-      <c r="D467" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
+    <row r="466" ht="12" customHeight="1">
+      <c r="A466" s="6" t="n"/>
+      <c r="B466" s="6" t="n"/>
+      <c r="C466" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu tavan kalıbı</t>
+        </is>
+      </c>
+      <c r="D466" s="6" t="n"/>
+      <c r="E466" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F466" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G466" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H466" s="6" t="n"/>
+      <c r="I466" s="24">
+        <f>E466*F466*G466</f>
+        <v/>
+      </c>
+      <c r="J466" s="6" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="22" t="n"/>
+      <c r="B467" s="22" t="n"/>
+      <c r="C467" s="25" t="inlineStr">
+        <is>
+          <t>M20 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D467" s="26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="E467" s="22" t="n"/>
@@ -16125,90 +16048,101 @@
       <c r="G467" s="22" t="n"/>
       <c r="H467" s="22" t="n"/>
       <c r="I467" s="22" t="n"/>
-      <c r="J467" s="22" t="n"/>
-    </row>
-    <row r="468" ht="12" customHeight="1">
-      <c r="A468" s="6" t="n"/>
-      <c r="B468" s="6" t="n"/>
-      <c r="C468" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu (3.00x3.00 + 0,10 taşma)</t>
-        </is>
-      </c>
-      <c r="D468" s="6" t="n"/>
-      <c r="E468" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F468" s="29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G468" s="29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H468" s="29" t="n">
+      <c r="J467" s="27">
+        <f>SUM(I464:I466)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="468" ht="22" customHeight="1">
+      <c r="A468" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B468" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="C468" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo ve silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D468" s="21" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E468" s="22" t="n"/>
+      <c r="F468" s="22" t="n"/>
+      <c r="G468" s="22" t="n"/>
+      <c r="H468" s="22" t="n"/>
+      <c r="I468" s="22" t="n"/>
+      <c r="J468" s="22" t="n"/>
+    </row>
+    <row r="469" ht="12" customHeight="1">
+      <c r="A469" s="6" t="n"/>
+      <c r="B469" s="6" t="n"/>
+      <c r="C469" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu radyesi: 3.00x3.00x0,30 m³, 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D469" s="6" t="n"/>
+      <c r="E469" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F469" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G469" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H469" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I469" s="24">
+        <f>E469*F469*G469*H469*J469</f>
+        <v/>
+      </c>
+      <c r="J469" s="30" t="n">
         <v>0.1</v>
       </c>
-      <c r="I468" s="24">
-        <f>E468*F468*G468*H468</f>
-        <v/>
-      </c>
-      <c r="J468" s="6" t="n"/>
-    </row>
-    <row r="469">
-      <c r="A469" s="22" t="n"/>
-      <c r="B469" s="22" t="n"/>
-      <c r="C469" s="25" t="inlineStr">
-        <is>
-          <t>M11 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D469" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E469" s="22" t="n"/>
-      <c r="F469" s="22" t="n"/>
-      <c r="G469" s="22" t="n"/>
-      <c r="H469" s="22" t="n"/>
-      <c r="I469" s="22" t="n"/>
-      <c r="J469" s="27">
-        <f>SUM(I468:I468)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="470" ht="22" customHeight="1">
-      <c r="A470" s="19" t="n">
+    </row>
+    <row r="470" ht="20" customHeight="1">
+      <c r="A470" s="6" t="n"/>
+      <c r="B470" s="6" t="n"/>
+      <c r="C470" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu perdeleri: 11.00x0,25x3.00 m³, 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D470" s="6" t="n"/>
+      <c r="E470" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F470" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G470" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="H470" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B470" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C470" s="8" t="inlineStr">
-        <is>
-          <t>[M16]  C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
-        </is>
-      </c>
-      <c r="D470" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E470" s="22" t="n"/>
-      <c r="F470" s="22" t="n"/>
-      <c r="G470" s="22" t="n"/>
-      <c r="H470" s="22" t="n"/>
-      <c r="I470" s="22" t="n"/>
-      <c r="J470" s="22" t="n"/>
+      <c r="I470" s="24">
+        <f>E470*F470*G470*H470*J470</f>
+        <v/>
+      </c>
+      <c r="J470" s="30" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="471" ht="12" customHeight="1">
       <c r="A471" s="6" t="n"/>
       <c r="B471" s="6" t="n"/>
       <c r="C471" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu radye 30 cm (dış 3.00x3.00)</t>
+          <t>Yağmur suyu deposu döşemesi: 3.00x3.00x0,15 m³, 100 kg/m³</t>
         </is>
       </c>
       <c r="D471" s="6" t="n"/>
@@ -16222,203 +16156,192 @@
         <v>3</v>
       </c>
       <c r="H471" s="29" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="I471" s="24">
-        <f>E471*F471*G471*H471</f>
-        <v/>
-      </c>
-      <c r="J471" s="6" t="n"/>
-    </row>
-    <row r="472" ht="20" customHeight="1">
-      <c r="A472" s="6" t="n"/>
-      <c r="B472" s="6" t="n"/>
-      <c r="C472" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu perdeleri: orta çevre 2x(2.75+2.75) = 11.00 m</t>
-        </is>
-      </c>
-      <c r="D472" s="6" t="n"/>
-      <c r="E472" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F472" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G472" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="H472" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I472" s="24">
-        <f>E472*F472*G472*H472</f>
-        <v/>
-      </c>
-      <c r="J472" s="6" t="n"/>
-    </row>
-    <row r="473" ht="12" customHeight="1">
-      <c r="A473" s="6" t="n"/>
-      <c r="B473" s="6" t="n"/>
-      <c r="C473" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu üst döşemesi 15 cm</t>
-        </is>
-      </c>
-      <c r="D473" s="6" t="n"/>
-      <c r="E473" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F473" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G473" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H473" s="29" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I473" s="24">
-        <f>E473*F473*G473*H473</f>
-        <v/>
-      </c>
-      <c r="J473" s="6" t="n"/>
-    </row>
-    <row r="474">
-      <c r="A474" s="22" t="n"/>
-      <c r="B474" s="22" t="n"/>
-      <c r="C474" s="25" t="inlineStr">
-        <is>
-          <t>M16 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D474" s="26" t="inlineStr">
+        <f>E471*F471*G471*H471*J471</f>
+        <v/>
+      </c>
+      <c r="J471" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="22" t="n"/>
+      <c r="B472" s="22" t="n"/>
+      <c r="C472" s="25" t="inlineStr">
+        <is>
+          <t>M26 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D472" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E472" s="22" t="n"/>
+      <c r="F472" s="22" t="n"/>
+      <c r="G472" s="22" t="n"/>
+      <c r="H472" s="22" t="n"/>
+      <c r="I472" s="22" t="n"/>
+      <c r="J472" s="27">
+        <f>SUM(I469:I471)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="473"/>
+    <row r="474" ht="20" customHeight="1">
+      <c r="A474" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="28" customHeight="1">
+      <c r="A475" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B475" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="C475" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı / Ölçünün Alındığı Yer</t>
+        </is>
+      </c>
+      <c r="D475" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="E475" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F475" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="G475" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="H475" s="7" t="inlineStr">
+        <is>
+          <t>Yükseklik (m)</t>
+        </is>
+      </c>
+      <c r="I475" s="7" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="J475" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Miktar</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="15" customHeight="1">
+      <c r="A476" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B476" s="20" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="C476" s="8" t="inlineStr">
+        <is>
+          <t>[M02]  Makine ile kaba tesviye kazısı — tesis içi yol güzergâhı</t>
+        </is>
+      </c>
+      <c r="D476" s="21" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E474" s="22" t="n"/>
-      <c r="F474" s="22" t="n"/>
-      <c r="G474" s="22" t="n"/>
-      <c r="H474" s="22" t="n"/>
-      <c r="I474" s="22" t="n"/>
-      <c r="J474" s="27">
-        <f>SUM(I471:I473)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="475" ht="15" customHeight="1">
-      <c r="A475" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B475" s="20" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C475" s="8" t="inlineStr">
-        <is>
-          <t>[M20]  Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
-        </is>
-      </c>
-      <c r="D475" s="21" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E475" s="22" t="n"/>
-      <c r="F475" s="22" t="n"/>
-      <c r="G475" s="22" t="n"/>
-      <c r="H475" s="22" t="n"/>
-      <c r="I475" s="22" t="n"/>
-      <c r="J475" s="22" t="n"/>
-    </row>
-    <row r="476" ht="20" customHeight="1">
-      <c r="A476" s="6" t="n"/>
-      <c r="B476" s="6" t="n"/>
-      <c r="C476" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu radye çevresi 2x(3.00+3.00) = 12.00 m x 0,40</t>
-        </is>
-      </c>
-      <c r="D476" s="6" t="n"/>
-      <c r="E476" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F476" s="6" t="n"/>
-      <c r="G476" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="H476" s="29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I476" s="24">
-        <f>E476*G476*H476</f>
-        <v/>
-      </c>
-      <c r="J476" s="6" t="n"/>
-    </row>
-    <row r="477" ht="12" customHeight="1">
+      <c r="E476" s="22" t="n"/>
+      <c r="F476" s="22" t="n"/>
+      <c r="G476" s="22" t="n"/>
+      <c r="H476" s="22" t="n"/>
+      <c r="I476" s="22" t="n"/>
+      <c r="J476" s="22" t="n"/>
+    </row>
+    <row r="477" ht="20" customHeight="1">
       <c r="A477" s="6" t="n"/>
       <c r="B477" s="6" t="n"/>
       <c r="C477" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu perde iki yüz (11.00 m x 3.00 m)</t>
+          <t>Tesis içi yol güzergâhı: 745,57 m² alan, ortalama 5,00 m genişlik -&gt; 149,11 m uzunluk</t>
         </is>
       </c>
       <c r="D477" s="6" t="n"/>
       <c r="E477" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F477" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G477" s="29" t="n">
+        <v>149.11</v>
+      </c>
+      <c r="H477" s="29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I477" s="24">
+        <f>E477*F477*G477*H477</f>
+        <v/>
+      </c>
+      <c r="J477" s="6" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="22" t="n"/>
+      <c r="B478" s="22" t="n"/>
+      <c r="C478" s="25" t="inlineStr">
+        <is>
+          <t>M02 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D478" s="26" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E478" s="22" t="n"/>
+      <c r="F478" s="22" t="n"/>
+      <c r="G478" s="22" t="n"/>
+      <c r="H478" s="22" t="n"/>
+      <c r="I478" s="22" t="n"/>
+      <c r="J478" s="27">
+        <f>SUM(I477:I477)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="479" ht="22" customHeight="1">
+      <c r="A479" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F477" s="6" t="n"/>
-      <c r="G477" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="H477" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I477" s="24">
-        <f>E477*G477*H477</f>
-        <v/>
-      </c>
-      <c r="J477" s="6" t="n"/>
-    </row>
-    <row r="478" ht="12" customHeight="1">
-      <c r="A478" s="6" t="n"/>
-      <c r="B478" s="6" t="n"/>
-      <c r="C478" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu tavan kalıbı</t>
-        </is>
-      </c>
-      <c r="D478" s="6" t="n"/>
-      <c r="E478" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F478" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G478" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H478" s="6" t="n"/>
-      <c r="I478" s="24">
-        <f>E478*F478*G478</f>
-        <v/>
-      </c>
-      <c r="J478" s="6" t="n"/>
-    </row>
-    <row r="479">
-      <c r="A479" s="22" t="n"/>
-      <c r="B479" s="22" t="n"/>
-      <c r="C479" s="25" t="inlineStr">
-        <is>
-          <t>M20 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D479" s="26" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="B479" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0091</t>
+        </is>
+      </c>
+      <c r="C479" s="8" t="inlineStr">
+        <is>
+          <t>[M46]  1,50 m yükseklikte sıcak daldırma galvanizli tel örgü ile çit yapılması</t>
+        </is>
+      </c>
+      <c r="D479" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
         </is>
       </c>
       <c r="E479" s="22" t="n"/>
@@ -16426,256 +16349,248 @@
       <c r="G479" s="22" t="n"/>
       <c r="H479" s="22" t="n"/>
       <c r="I479" s="22" t="n"/>
-      <c r="J479" s="27">
-        <f>SUM(I476:I478)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="480" ht="22" customHeight="1">
-      <c r="A480" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B480" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C480" s="8" t="inlineStr">
-        <is>
-          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="D480" s="21" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E480" s="22" t="n"/>
-      <c r="F480" s="22" t="n"/>
-      <c r="G480" s="22" t="n"/>
-      <c r="H480" s="22" t="n"/>
-      <c r="I480" s="22" t="n"/>
-      <c r="J480" s="22" t="n"/>
+      <c r="J479" s="22" t="n"/>
+    </row>
+    <row r="480" ht="30" customHeight="1">
+      <c r="A480" s="6" t="n"/>
+      <c r="B480" s="6" t="n"/>
+      <c r="C480" s="23" t="inlineStr">
+        <is>
+          <t>Parsel 7.966,67 m²; yerleşim planındaki cephe 113,04 m, buna karşılık gelen derinlik 7.966,67/113,04 = 70,48 m; çevre 2x(113,04+70,48)</t>
+        </is>
+      </c>
+      <c r="D480" s="6" t="n"/>
+      <c r="E480" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F480" s="6" t="n"/>
+      <c r="G480" s="29" t="n">
+        <v>367.04</v>
+      </c>
+      <c r="H480" s="6" t="n"/>
+      <c r="I480" s="24">
+        <f>E480*G480</f>
+        <v/>
+      </c>
+      <c r="J480" s="6" t="n"/>
     </row>
     <row r="481" ht="12" customHeight="1">
       <c r="A481" s="6" t="n"/>
       <c r="B481" s="6" t="n"/>
       <c r="C481" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu radyesi: 3.00x3.00x0,30 m³, 100 kg/m³</t>
+          <t>Giriş kapısı açıklığı düşülür</t>
         </is>
       </c>
       <c r="D481" s="6" t="n"/>
       <c r="E481" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F481" s="29" t="n">
+      <c r="F481" s="6" t="n"/>
+      <c r="G481" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H481" s="6" t="n"/>
+      <c r="I481" s="24">
+        <f>-E481*G481</f>
+        <v/>
+      </c>
+      <c r="J481" s="6" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="22" t="n"/>
+      <c r="B482" s="22" t="n"/>
+      <c r="C482" s="25" t="inlineStr">
+        <is>
+          <t>M46 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D482" s="26" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E482" s="22" t="n"/>
+      <c r="F482" s="22" t="n"/>
+      <c r="G482" s="22" t="n"/>
+      <c r="H482" s="22" t="n"/>
+      <c r="I482" s="22" t="n"/>
+      <c r="J482" s="27">
+        <f>SUM(I480:I481)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="483" ht="22" customHeight="1">
+      <c r="A483" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="G481" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H481" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I481" s="24">
-        <f>E481*F481*G481*H481*J481</f>
-        <v/>
-      </c>
-      <c r="J481" s="30" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="482" ht="20" customHeight="1">
-      <c r="A482" s="6" t="n"/>
-      <c r="B482" s="6" t="n"/>
-      <c r="C482" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu perdeleri: 11.00x0,25x3.00 m³, 100 kg/m³</t>
-        </is>
-      </c>
-      <c r="D482" s="6" t="n"/>
-      <c r="E482" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F482" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G482" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="H482" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I482" s="24">
-        <f>E482*F482*G482*H482*J482</f>
-        <v/>
-      </c>
-      <c r="J482" s="30" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="483" ht="12" customHeight="1">
-      <c r="A483" s="6" t="n"/>
-      <c r="B483" s="6" t="n"/>
-      <c r="C483" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu döşemesi: 3.00x3.00x0,15 m³, 100 kg/m³</t>
-        </is>
-      </c>
-      <c r="D483" s="6" t="n"/>
-      <c r="E483" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F483" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G483" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H483" s="29" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I483" s="24">
-        <f>E483*F483*G483*H483*J483</f>
-        <v/>
-      </c>
-      <c r="J483" s="30" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" s="22" t="n"/>
-      <c r="B484" s="22" t="n"/>
-      <c r="C484" s="25" t="inlineStr">
-        <is>
-          <t>M26 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D484" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E484" s="22" t="n"/>
-      <c r="F484" s="22" t="n"/>
-      <c r="G484" s="22" t="n"/>
-      <c r="H484" s="22" t="n"/>
-      <c r="I484" s="22" t="n"/>
-      <c r="J484" s="27">
-        <f>SUM(I481:I483)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="485"/>
-    <row r="486" ht="20" customHeight="1">
-      <c r="A486" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
-        </is>
-      </c>
-    </row>
-    <row r="487" ht="28" customHeight="1">
-      <c r="A487" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B487" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="C487" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı / Ölçünün Alındığı Yer</t>
-        </is>
-      </c>
-      <c r="D487" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="E487" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F487" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="G487" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="H487" s="7" t="inlineStr">
-        <is>
-          <t>Yükseklik (m)</t>
-        </is>
-      </c>
-      <c r="I487" s="7" t="inlineStr">
-        <is>
-          <t>Miktar</t>
-        </is>
-      </c>
-      <c r="J487" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Miktar</t>
-        </is>
-      </c>
-    </row>
-    <row r="488" ht="15" customHeight="1">
-      <c r="A488" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B488" s="20" t="inlineStr">
-        <is>
-          <t>15.120.1001</t>
-        </is>
-      </c>
-      <c r="C488" s="8" t="inlineStr">
-        <is>
-          <t>[M02]  Makine ile kaba tesviye kazısı — tesis içi yol güzergâhı</t>
-        </is>
-      </c>
-      <c r="D488" s="21" t="inlineStr">
+      <c r="B483" s="20" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="C483" s="8" t="inlineStr">
+        <is>
+          <t>[M59]  ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+        </is>
+      </c>
+      <c r="D483" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E483" s="22" t="n"/>
+      <c r="F483" s="22" t="n"/>
+      <c r="G483" s="22" t="n"/>
+      <c r="H483" s="22" t="n"/>
+      <c r="I483" s="22" t="n"/>
+      <c r="J483" s="22" t="n"/>
+    </row>
+    <row r="484" ht="12" customHeight="1">
+      <c r="A484" s="6" t="n"/>
+      <c r="B484" s="6" t="n"/>
+      <c r="C484" s="23" t="inlineStr">
+        <is>
+          <t>Kümes A blok servis bölümü - foseptik</t>
+        </is>
+      </c>
+      <c r="D484" s="6" t="n"/>
+      <c r="E484" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F484" s="6" t="n"/>
+      <c r="G484" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="H484" s="6" t="n"/>
+      <c r="I484" s="24">
+        <f>E484*G484</f>
+        <v/>
+      </c>
+      <c r="J484" s="6" t="n"/>
+    </row>
+    <row r="485" ht="12" customHeight="1">
+      <c r="A485" s="6" t="n"/>
+      <c r="B485" s="6" t="n"/>
+      <c r="C485" s="23" t="inlineStr">
+        <is>
+          <t>Kümes B blok servis bölümü - foseptik</t>
+        </is>
+      </c>
+      <c r="D485" s="6" t="n"/>
+      <c r="E485" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F485" s="6" t="n"/>
+      <c r="G485" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="H485" s="6" t="n"/>
+      <c r="I485" s="24">
+        <f>E485*G485</f>
+        <v/>
+      </c>
+      <c r="J485" s="6" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="22" t="n"/>
+      <c r="B486" s="22" t="n"/>
+      <c r="C486" s="25" t="inlineStr">
+        <is>
+          <t>M59 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D486" s="26" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E486" s="22" t="n"/>
+      <c r="F486" s="22" t="n"/>
+      <c r="G486" s="22" t="n"/>
+      <c r="H486" s="22" t="n"/>
+      <c r="I486" s="22" t="n"/>
+      <c r="J486" s="27">
+        <f>SUM(I484:I485)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="487" ht="15" customHeight="1">
+      <c r="A487" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B487" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="C487" s="8" t="inlineStr">
+        <is>
+          <t>[M61A]  C 25/30 hazır beton dökülmesi — betonarme rögarlar</t>
+        </is>
+      </c>
+      <c r="D487" s="21" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E488" s="22" t="n"/>
-      <c r="F488" s="22" t="n"/>
-      <c r="G488" s="22" t="n"/>
-      <c r="H488" s="22" t="n"/>
-      <c r="I488" s="22" t="n"/>
-      <c r="J488" s="22" t="n"/>
-    </row>
-    <row r="489" ht="20" customHeight="1">
+      <c r="E487" s="22" t="n"/>
+      <c r="F487" s="22" t="n"/>
+      <c r="G487" s="22" t="n"/>
+      <c r="H487" s="22" t="n"/>
+      <c r="I487" s="22" t="n"/>
+      <c r="J487" s="22" t="n"/>
+    </row>
+    <row r="488" ht="12" customHeight="1">
+      <c r="A488" s="6" t="n"/>
+      <c r="B488" s="6" t="n"/>
+      <c r="C488" s="23" t="inlineStr">
+        <is>
+          <t>Dış prizma: 0,90 x 0,90 x 0,75; 4 adet</t>
+        </is>
+      </c>
+      <c r="D488" s="6" t="n"/>
+      <c r="E488" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F488" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G488" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H488" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I488" s="24">
+        <f>E488*F488*G488*H488</f>
+        <v/>
+      </c>
+      <c r="J488" s="6" t="n"/>
+    </row>
+    <row r="489" ht="12" customHeight="1">
       <c r="A489" s="6" t="n"/>
       <c r="B489" s="6" t="n"/>
       <c r="C489" s="23" t="inlineStr">
         <is>
-          <t>Tesis içi yol güzergâhı: 745,57 m² alan, ortalama 5,00 m genişlik -&gt; 149,11 m uzunluk</t>
+          <t>Net iç hacim düşülür: 0,60 x 0,60 x 0,60; 4 adet</t>
         </is>
       </c>
       <c r="D489" s="6" t="n"/>
       <c r="E489" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F489" s="29" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="G489" s="29" t="n">
-        <v>149.11</v>
+        <v>0.6</v>
       </c>
       <c r="H489" s="29" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="I489" s="24">
-        <f>E489*F489*G489*H489</f>
+        <f>-E489*F489*G489*H489</f>
         <v/>
       </c>
       <c r="J489" s="6" t="n"/>
@@ -16685,7 +16600,7 @@
       <c r="B490" s="22" t="n"/>
       <c r="C490" s="25" t="inlineStr">
         <is>
-          <t>M02 TOPLAMI</t>
+          <t>M61A TOPLAMI</t>
         </is>
       </c>
       <c r="D490" s="26" t="inlineStr">
@@ -16699,27 +16614,27 @@
       <c r="H490" s="22" t="n"/>
       <c r="I490" s="22" t="n"/>
       <c r="J490" s="27">
-        <f>SUM(I489:I489)</f>
+        <f>SUM(I488:I489)</f>
         <v/>
       </c>
     </row>
     <row r="491" ht="22" customHeight="1">
       <c r="A491" s="19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B491" s="20" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="C491" s="8" t="inlineStr">
         <is>
-          <t>[M46]  1,50 m yükseklikte sıcak daldırma galvanizli tel örgü ile çit yapılması</t>
+          <t>[M61B]  Düz yüzeyli beton ve betonarme kalıbı yapılması — betonarme rögarlar</t>
         </is>
       </c>
       <c r="D491" s="21" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E491" s="22" t="n"/>
@@ -16729,25 +16644,29 @@
       <c r="I491" s="22" t="n"/>
       <c r="J491" s="22" t="n"/>
     </row>
-    <row r="492" ht="30" customHeight="1">
+    <row r="492" ht="12" customHeight="1">
       <c r="A492" s="6" t="n"/>
       <c r="B492" s="6" t="n"/>
       <c r="C492" s="23" t="inlineStr">
         <is>
-          <t>Parsel 7.966,67 m²; yerleşim planındaki cephe 113,04 m, buna karşılık gelen derinlik 7.966,67/113,04 = 70,48 m; çevre 2x(113,04+70,48)</t>
+          <t>İç yüzler: 4 yüz x 0,60 x 0,60; 4 adet</t>
         </is>
       </c>
       <c r="D492" s="6" t="n"/>
       <c r="E492" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F492" s="6" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F492" s="29" t="n">
+        <v>0.6</v>
+      </c>
       <c r="G492" s="29" t="n">
-        <v>367.04</v>
-      </c>
-      <c r="H492" s="6" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H492" s="29" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I492" s="24">
-        <f>E492*G492</f>
+        <f>E492*F492*G492*H492</f>
         <v/>
       </c>
       <c r="J492" s="6" t="n"/>
@@ -16757,20 +16676,24 @@
       <c r="B493" s="6" t="n"/>
       <c r="C493" s="23" t="inlineStr">
         <is>
-          <t>Giriş kapısı açıklığı düşülür</t>
+          <t>Dış yüzler: 4 yüz x 0,90 x 0,60; 4 adet</t>
         </is>
       </c>
       <c r="D493" s="6" t="n"/>
       <c r="E493" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F493" s="6" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F493" s="29" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G493" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H493" s="6" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H493" s="29" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I493" s="24">
-        <f>-E493*G493</f>
+        <f>E493*F493*G493*H493</f>
         <v/>
       </c>
       <c r="J493" s="6" t="n"/>
@@ -16780,12 +16703,12 @@
       <c r="B494" s="22" t="n"/>
       <c r="C494" s="25" t="inlineStr">
         <is>
-          <t>M46 TOPLAMI</t>
+          <t>M61B TOPLAMI</t>
         </is>
       </c>
       <c r="D494" s="26" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E494" s="22" t="n"/>
@@ -16798,23 +16721,23 @@
         <v/>
       </c>
     </row>
-    <row r="495" ht="22" customHeight="1">
+    <row r="495" ht="15" customHeight="1">
       <c r="A495" s="19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B495" s="20" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="C495" s="8" t="inlineStr">
         <is>
-          <t>[M59]  ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>[M61C]  Nervürlü betonarme çeliği ø8-ø12 — betonarme rögarlar</t>
         </is>
       </c>
       <c r="D495" s="21" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="E495" s="22" t="n"/>
@@ -16824,12 +16747,12 @@
       <c r="I495" s="22" t="n"/>
       <c r="J495" s="22" t="n"/>
     </row>
-    <row r="496" ht="12" customHeight="1">
+    <row r="496" ht="20" customHeight="1">
       <c r="A496" s="6" t="n"/>
       <c r="B496" s="6" t="n"/>
       <c r="C496" s="23" t="inlineStr">
         <is>
-          <t>Kümes A blok servis bölümü - foseptik</t>
+          <t>Beton hacmi 1,566 m³, ortalama donatı oranı 90 kg/m³ -&gt; 140,94 kg = 0,141 ton</t>
         </is>
       </c>
       <c r="D496" s="6" t="n"/>
@@ -16838,49 +16761,57 @@
       </c>
       <c r="F496" s="6" t="n"/>
       <c r="G496" s="29" t="n">
-        <v>25</v>
+        <v>1.566</v>
       </c>
       <c r="H496" s="6" t="n"/>
       <c r="I496" s="24">
-        <f>E496*G496</f>
-        <v/>
-      </c>
-      <c r="J496" s="6" t="n"/>
-    </row>
-    <row r="497" ht="12" customHeight="1">
-      <c r="A497" s="6" t="n"/>
-      <c r="B497" s="6" t="n"/>
-      <c r="C497" s="23" t="inlineStr">
-        <is>
-          <t>Kümes B blok servis bölümü - foseptik</t>
-        </is>
-      </c>
-      <c r="D497" s="6" t="n"/>
-      <c r="E497" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F497" s="6" t="n"/>
-      <c r="G497" s="29" t="n">
-        <v>25</v>
-      </c>
-      <c r="H497" s="6" t="n"/>
-      <c r="I497" s="24">
-        <f>E497*G497</f>
-        <v/>
-      </c>
-      <c r="J497" s="6" t="n"/>
-    </row>
-    <row r="498">
-      <c r="A498" s="22" t="n"/>
-      <c r="B498" s="22" t="n"/>
-      <c r="C498" s="25" t="inlineStr">
-        <is>
-          <t>M59 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D498" s="26" t="inlineStr">
-        <is>
-          <t>m</t>
+        <f>E496*G496*J496</f>
+        <v/>
+      </c>
+      <c r="J496" s="30" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="22" t="n"/>
+      <c r="B497" s="22" t="n"/>
+      <c r="C497" s="25" t="inlineStr">
+        <is>
+          <t>M61C TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D497" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E497" s="22" t="n"/>
+      <c r="F497" s="22" t="n"/>
+      <c r="G497" s="22" t="n"/>
+      <c r="H497" s="22" t="n"/>
+      <c r="I497" s="22" t="n"/>
+      <c r="J497" s="27">
+        <f>SUM(I496:I496)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="498" ht="15" customHeight="1">
+      <c r="A498" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B498" s="20" t="inlineStr">
+        <is>
+          <t>15.560.1003</t>
+        </is>
+      </c>
+      <c r="C498" s="8" t="inlineStr">
+        <is>
+          <t>[M61D]  Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="D498" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
         </is>
       </c>
       <c r="E498" s="22" t="n"/>
@@ -16888,131 +16819,112 @@
       <c r="G498" s="22" t="n"/>
       <c r="H498" s="22" t="n"/>
       <c r="I498" s="22" t="n"/>
-      <c r="J498" s="27">
-        <f>SUM(I496:I497)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="499" ht="15" customHeight="1">
-      <c r="A499" s="19" t="n">
+      <c r="J498" s="22" t="n"/>
+    </row>
+    <row r="499" ht="12" customHeight="1">
+      <c r="A499" s="6" t="n"/>
+      <c r="B499" s="6" t="n"/>
+      <c r="C499" s="23" t="inlineStr">
+        <is>
+          <t>Pissu hattında 4 adet</t>
+        </is>
+      </c>
+      <c r="D499" s="6" t="n"/>
+      <c r="E499" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B499" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C499" s="8" t="inlineStr">
-        <is>
-          <t>[M61A]  C 25/30 hazır beton dökülmesi — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="D499" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E499" s="22" t="n"/>
-      <c r="F499" s="22" t="n"/>
-      <c r="G499" s="22" t="n"/>
-      <c r="H499" s="22" t="n"/>
-      <c r="I499" s="22" t="n"/>
-      <c r="J499" s="22" t="n"/>
-    </row>
-    <row r="500" ht="12" customHeight="1">
-      <c r="A500" s="6" t="n"/>
-      <c r="B500" s="6" t="n"/>
-      <c r="C500" s="23" t="inlineStr">
-        <is>
-          <t>Dış prizma: 0,90 x 0,90 x 0,75; 4 adet</t>
-        </is>
-      </c>
-      <c r="D500" s="6" t="n"/>
-      <c r="E500" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F500" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G500" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H500" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I500" s="24">
-        <f>E500*F500*G500*H500</f>
-        <v/>
-      </c>
-      <c r="J500" s="6" t="n"/>
-    </row>
-    <row r="501" ht="12" customHeight="1">
-      <c r="A501" s="6" t="n"/>
-      <c r="B501" s="6" t="n"/>
-      <c r="C501" s="23" t="inlineStr">
-        <is>
-          <t>Net iç hacim düşülür: 0,60 x 0,60 x 0,60; 4 adet</t>
-        </is>
-      </c>
-      <c r="D501" s="6" t="n"/>
-      <c r="E501" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F501" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G501" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H501" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I501" s="24">
-        <f>-E501*F501*G501*H501</f>
-        <v/>
-      </c>
-      <c r="J501" s="6" t="n"/>
-    </row>
-    <row r="502">
-      <c r="A502" s="22" t="n"/>
-      <c r="B502" s="22" t="n"/>
-      <c r="C502" s="25" t="inlineStr">
-        <is>
-          <t>M61A TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D502" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E502" s="22" t="n"/>
-      <c r="F502" s="22" t="n"/>
-      <c r="G502" s="22" t="n"/>
-      <c r="H502" s="22" t="n"/>
-      <c r="I502" s="22" t="n"/>
-      <c r="J502" s="27">
-        <f>SUM(I500:I501)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="503" ht="22" customHeight="1">
-      <c r="A503" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B503" s="20" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C503" s="8" t="inlineStr">
-        <is>
-          <t>[M61B]  Düz yüzeyli beton ve betonarme kalıbı yapılması — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="D503" s="21" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="F499" s="6" t="n"/>
+      <c r="G499" s="6" t="n"/>
+      <c r="H499" s="6" t="n"/>
+      <c r="I499" s="24">
+        <f>E499</f>
+        <v/>
+      </c>
+      <c r="J499" s="6" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="22" t="n"/>
+      <c r="B500" s="22" t="n"/>
+      <c r="C500" s="25" t="inlineStr">
+        <is>
+          <t>M61D TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D500" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E500" s="22" t="n"/>
+      <c r="F500" s="22" t="n"/>
+      <c r="G500" s="22" t="n"/>
+      <c r="H500" s="22" t="n"/>
+      <c r="I500" s="22" t="n"/>
+      <c r="J500" s="27">
+        <f>SUM(I499:I499)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="501" ht="22" customHeight="1">
+      <c r="A501" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B501" s="20" t="inlineStr">
+        <is>
+          <t>35.100.1104</t>
+        </is>
+      </c>
+      <c r="C501" s="8" t="inlineStr">
+        <is>
+          <t>[M63]  Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
+        </is>
+      </c>
+      <c r="D501" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E501" s="22" t="n"/>
+      <c r="F501" s="22" t="n"/>
+      <c r="G501" s="22" t="n"/>
+      <c r="H501" s="22" t="n"/>
+      <c r="I501" s="22" t="n"/>
+      <c r="J501" s="22" t="n"/>
+    </row>
+    <row r="502" ht="12" customHeight="1">
+      <c r="A502" s="6" t="n"/>
+      <c r="B502" s="6" t="n"/>
+      <c r="C502" s="23" t="inlineStr">
+        <is>
+          <t>Tesis girişinde 1 adet</t>
+        </is>
+      </c>
+      <c r="D502" s="6" t="n"/>
+      <c r="E502" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F502" s="6" t="n"/>
+      <c r="G502" s="6" t="n"/>
+      <c r="H502" s="6" t="n"/>
+      <c r="I502" s="24">
+        <f>E502*J502</f>
+        <v/>
+      </c>
+      <c r="J502" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="22" t="n"/>
+      <c r="B503" s="22" t="n"/>
+      <c r="C503" s="25" t="inlineStr">
+        <is>
+          <t>M63 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D503" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
         </is>
       </c>
       <c r="E503" s="22" t="n"/>
@@ -17020,73 +16932,71 @@
       <c r="G503" s="22" t="n"/>
       <c r="H503" s="22" t="n"/>
       <c r="I503" s="22" t="n"/>
-      <c r="J503" s="22" t="n"/>
-    </row>
-    <row r="504" ht="12" customHeight="1">
-      <c r="A504" s="6" t="n"/>
-      <c r="B504" s="6" t="n"/>
-      <c r="C504" s="23" t="inlineStr">
-        <is>
-          <t>İç yüzler: 4 yüz x 0,60 x 0,60; 4 adet</t>
-        </is>
-      </c>
-      <c r="D504" s="6" t="n"/>
-      <c r="E504" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F504" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G504" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H504" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I504" s="24">
-        <f>E504*F504*G504*H504</f>
-        <v/>
-      </c>
-      <c r="J504" s="6" t="n"/>
+      <c r="J503" s="27">
+        <f>SUM(I502:I502)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="504" ht="15" customHeight="1">
+      <c r="A504" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B504" s="20" t="inlineStr">
+        <is>
+          <t>35.100.2106</t>
+        </is>
+      </c>
+      <c r="C504" s="8" t="inlineStr">
+        <is>
+          <t>[M64]  Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+        </is>
+      </c>
+      <c r="D504" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E504" s="22" t="n"/>
+      <c r="F504" s="22" t="n"/>
+      <c r="G504" s="22" t="n"/>
+      <c r="H504" s="22" t="n"/>
+      <c r="I504" s="22" t="n"/>
+      <c r="J504" s="22" t="n"/>
     </row>
     <row r="505" ht="12" customHeight="1">
       <c r="A505" s="6" t="n"/>
       <c r="B505" s="6" t="n"/>
       <c r="C505" s="23" t="inlineStr">
         <is>
-          <t>Dış yüzler: 4 yüz x 0,90 x 0,60; 4 adet</t>
+          <t>Tesis girişinde 1 adet</t>
         </is>
       </c>
       <c r="D505" s="6" t="n"/>
       <c r="E505" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F505" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G505" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H505" s="29" t="n">
-        <v>0.6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F505" s="6" t="n"/>
+      <c r="G505" s="6" t="n"/>
+      <c r="H505" s="6" t="n"/>
       <c r="I505" s="24">
-        <f>E505*F505*G505*H505</f>
-        <v/>
-      </c>
-      <c r="J505" s="6" t="n"/>
+        <f>E505*J505</f>
+        <v/>
+      </c>
+      <c r="J505" s="30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="22" t="n"/>
       <c r="B506" s="22" t="n"/>
       <c r="C506" s="25" t="inlineStr">
         <is>
-          <t>M61B TOPLAMI</t>
+          <t>M64 TOPLAMI</t>
         </is>
       </c>
       <c r="D506" s="26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E506" s="22" t="n"/>
@@ -17095,27 +17005,27 @@
       <c r="H506" s="22" t="n"/>
       <c r="I506" s="22" t="n"/>
       <c r="J506" s="27">
-        <f>SUM(I504:I505)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="507" ht="15" customHeight="1">
+        <f>SUM(I505:I505)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="507" ht="22" customHeight="1">
       <c r="A507" s="19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B507" s="20" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>35.135.3201</t>
         </is>
       </c>
       <c r="C507" s="8" t="inlineStr">
         <is>
-          <t>[M61C]  Nervürlü betonarme çeliği ø8-ø12 — betonarme rögarlar</t>
+          <t>[M65]  Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
         </is>
       </c>
       <c r="D507" s="21" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E507" s="22" t="n"/>
@@ -17125,12 +17035,12 @@
       <c r="I507" s="22" t="n"/>
       <c r="J507" s="22" t="n"/>
     </row>
-    <row r="508" ht="20" customHeight="1">
+    <row r="508" ht="12" customHeight="1">
       <c r="A508" s="6" t="n"/>
       <c r="B508" s="6" t="n"/>
       <c r="C508" s="23" t="inlineStr">
         <is>
-          <t>Beton hacmi 1,566 m³, ortalama donatı oranı 90 kg/m³ -&gt; 140,94 kg = 0,141 ton</t>
+          <t>Sayaç panosu içinde 1 adet</t>
         </is>
       </c>
       <c r="D508" s="6" t="n"/>
@@ -17138,16 +17048,14 @@
         <v>1</v>
       </c>
       <c r="F508" s="6" t="n"/>
-      <c r="G508" s="29" t="n">
-        <v>1.566</v>
-      </c>
+      <c r="G508" s="6" t="n"/>
       <c r="H508" s="6" t="n"/>
       <c r="I508" s="24">
-        <f>E508*G508*J508</f>
+        <f>E508*J508</f>
         <v/>
       </c>
       <c r="J508" s="30" t="n">
-        <v>0.09</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -17155,12 +17063,12 @@
       <c r="B509" s="22" t="n"/>
       <c r="C509" s="25" t="inlineStr">
         <is>
-          <t>M61C TOPLAMI</t>
+          <t>M65 TOPLAMI</t>
         </is>
       </c>
       <c r="D509" s="26" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="E509" s="22" t="n"/>
@@ -17173,18 +17081,18 @@
         <v/>
       </c>
     </row>
-    <row r="510" ht="15" customHeight="1">
+    <row r="510" ht="22" customHeight="1">
       <c r="A510" s="19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B510" s="20" t="inlineStr">
         <is>
-          <t>15.560.1003</t>
+          <t>35.110.1104</t>
         </is>
       </c>
       <c r="C510" s="8" t="inlineStr">
         <is>
-          <t>[M61D]  Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+          <t>[M66]  Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
         </is>
       </c>
       <c r="D510" s="21" t="inlineStr">
@@ -17204,28 +17112,30 @@
       <c r="B511" s="6" t="n"/>
       <c r="C511" s="23" t="inlineStr">
         <is>
-          <t>Pissu hattında 4 adet</t>
+          <t>Ana dağıtım panosu girişi</t>
         </is>
       </c>
       <c r="D511" s="6" t="n"/>
       <c r="E511" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F511" s="6" t="n"/>
       <c r="G511" s="6" t="n"/>
       <c r="H511" s="6" t="n"/>
       <c r="I511" s="24">
-        <f>E511</f>
-        <v/>
-      </c>
-      <c r="J511" s="6" t="n"/>
+        <f>E511*J511</f>
+        <v/>
+      </c>
+      <c r="J511" s="30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="22" t="n"/>
       <c r="B512" s="22" t="n"/>
       <c r="C512" s="25" t="inlineStr">
         <is>
-          <t>M61D TOPLAMI</t>
+          <t>M66 TOPLAMI</t>
         </is>
       </c>
       <c r="D512" s="26" t="inlineStr">
@@ -17243,18 +17153,18 @@
         <v/>
       </c>
     </row>
-    <row r="513" ht="22" customHeight="1">
+    <row r="513" ht="15" customHeight="1">
       <c r="A513" s="19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B513" s="20" t="inlineStr">
         <is>
-          <t>35.100.1104</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="C513" s="8" t="inlineStr">
         <is>
-          <t>[M63]  Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
+          <t>[M69]  Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="D513" s="21" t="inlineStr">
@@ -17274,7 +17184,7 @@
       <c r="B514" s="6" t="n"/>
       <c r="C514" s="23" t="inlineStr">
         <is>
-          <t>Tesis girişinde 1 adet</t>
+          <t>Ana pano ve sayaç panosunda</t>
         </is>
       </c>
       <c r="D514" s="6" t="n"/>
@@ -17289,7 +17199,7 @@
         <v/>
       </c>
       <c r="J514" s="30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="515">
@@ -17297,7 +17207,7 @@
       <c r="B515" s="22" t="n"/>
       <c r="C515" s="25" t="inlineStr">
         <is>
-          <t>M63 TOPLAMI</t>
+          <t>M69 TOPLAMI</t>
         </is>
       </c>
       <c r="D515" s="26" t="inlineStr">
@@ -17315,23 +17225,23 @@
         <v/>
       </c>
     </row>
-    <row r="516" ht="15" customHeight="1">
+    <row r="516" ht="22" customHeight="1">
       <c r="A516" s="19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B516" s="20" t="inlineStr">
         <is>
-          <t>35.100.2106</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="C516" s="8" t="inlineStr">
         <is>
-          <t>[M64]  Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+          <t>[M70]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
         </is>
       </c>
       <c r="D516" s="21" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E516" s="22" t="n"/>
@@ -17346,7 +17256,7 @@
       <c r="B517" s="6" t="n"/>
       <c r="C517" s="23" t="inlineStr">
         <is>
-          <t>Tesis girişinde 1 adet</t>
+          <t>Şebeke bağlantı noktası - ana dağıtım panosu</t>
         </is>
       </c>
       <c r="D517" s="6" t="n"/>
@@ -17361,7 +17271,7 @@
         <v/>
       </c>
       <c r="J517" s="30" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="518">
@@ -17369,12 +17279,12 @@
       <c r="B518" s="22" t="n"/>
       <c r="C518" s="25" t="inlineStr">
         <is>
-          <t>M64 TOPLAMI</t>
+          <t>M70 TOPLAMI</t>
         </is>
       </c>
       <c r="D518" s="26" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E518" s="22" t="n"/>
@@ -17389,21 +17299,21 @@
     </row>
     <row r="519" ht="22" customHeight="1">
       <c r="A519" s="19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B519" s="20" t="inlineStr">
         <is>
-          <t>35.135.3201</t>
+          <t>35.140.3101</t>
         </is>
       </c>
       <c r="C519" s="8" t="inlineStr">
         <is>
-          <t>[M65]  Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+          <t>[M72]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
         </is>
       </c>
       <c r="D519" s="21" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E519" s="22" t="n"/>
@@ -17418,7 +17328,7 @@
       <c r="B520" s="6" t="n"/>
       <c r="C520" s="23" t="inlineStr">
         <is>
-          <t>Sayaç panosu içinde 1 adet</t>
+          <t>Saha aydınlatma direkleri besleme hattı</t>
         </is>
       </c>
       <c r="D520" s="6" t="n"/>
@@ -17433,7 +17343,7 @@
         <v/>
       </c>
       <c r="J520" s="30" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="521">
@@ -17441,12 +17351,12 @@
       <c r="B521" s="22" t="n"/>
       <c r="C521" s="25" t="inlineStr">
         <is>
-          <t>M65 TOPLAMI</t>
+          <t>M72 TOPLAMI</t>
         </is>
       </c>
       <c r="D521" s="26" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E521" s="22" t="n"/>
@@ -17461,16 +17371,16 @@
     </row>
     <row r="522" ht="22" customHeight="1">
       <c r="A522" s="19" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B522" s="20" t="inlineStr">
         <is>
-          <t>35.110.1104</t>
+          <t>35.172.1706</t>
         </is>
       </c>
       <c r="C522" s="8" t="inlineStr">
         <is>
-          <t>[M66]  Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
+          <t>[M82]  Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
         </is>
       </c>
       <c r="D522" s="21" t="inlineStr">
@@ -17490,7 +17400,7 @@
       <c r="B523" s="6" t="n"/>
       <c r="C523" s="23" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu girişi</t>
+          <t>Tesis içi yol ve saha aydınlatması</t>
         </is>
       </c>
       <c r="D523" s="6" t="n"/>
@@ -17505,7 +17415,7 @@
         <v/>
       </c>
       <c r="J523" s="30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="524">
@@ -17513,7 +17423,7 @@
       <c r="B524" s="22" t="n"/>
       <c r="C524" s="25" t="inlineStr">
         <is>
-          <t>M66 TOPLAMI</t>
+          <t>M82 TOPLAMI</t>
         </is>
       </c>
       <c r="D524" s="26" t="inlineStr">
@@ -17533,16 +17443,16 @@
     </row>
     <row r="525" ht="15" customHeight="1">
       <c r="A525" s="19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B525" s="20" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.170.4002</t>
         </is>
       </c>
       <c r="C525" s="8" t="inlineStr">
         <is>
-          <t>[M69]  Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>[M83]  LED projektör, ışık akısı en az 5100 lm</t>
         </is>
       </c>
       <c r="D525" s="21" t="inlineStr">
@@ -17562,7 +17472,7 @@
       <c r="B526" s="6" t="n"/>
       <c r="C526" s="23" t="inlineStr">
         <is>
-          <t>Ana pano ve sayaç panosunda</t>
+          <t>Aydınlatma direği başına 1 adet</t>
         </is>
       </c>
       <c r="D526" s="6" t="n"/>
@@ -17577,7 +17487,7 @@
         <v/>
       </c>
       <c r="J526" s="30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="527">
@@ -17585,7 +17495,7 @@
       <c r="B527" s="22" t="n"/>
       <c r="C527" s="25" t="inlineStr">
         <is>
-          <t>M69 TOPLAMI</t>
+          <t>M83 TOPLAMI</t>
         </is>
       </c>
       <c r="D527" s="26" t="inlineStr">
@@ -17603,334 +17513,46 @@
         <v/>
       </c>
     </row>
-    <row r="528" ht="22" customHeight="1">
-      <c r="A528" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="B528" s="20" t="inlineStr">
-        <is>
-          <t>35.140.3105</t>
-        </is>
-      </c>
-      <c r="C528" s="8" t="inlineStr">
-        <is>
-          <t>[M70]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
-        </is>
-      </c>
-      <c r="D528" s="21" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E528" s="22" t="n"/>
-      <c r="F528" s="22" t="n"/>
-      <c r="G528" s="22" t="n"/>
-      <c r="H528" s="22" t="n"/>
-      <c r="I528" s="22" t="n"/>
-      <c r="J528" s="22" t="n"/>
-    </row>
-    <row r="529" ht="12" customHeight="1">
-      <c r="A529" s="6" t="n"/>
+    <row r="528"/>
+    <row r="529">
+      <c r="A529" s="16" t="inlineStr">
+        <is>
+          <t>AÇIKLAMALAR</t>
+        </is>
+      </c>
       <c r="B529" s="6" t="n"/>
-      <c r="C529" s="23" t="inlineStr">
-        <is>
-          <t>Şebeke bağlantı noktası - ana dağıtım panosu</t>
-        </is>
-      </c>
+      <c r="C529" s="6" t="n"/>
       <c r="D529" s="6" t="n"/>
-      <c r="E529" s="28" t="n">
-        <v>1</v>
-      </c>
+      <c r="E529" s="6" t="n"/>
       <c r="F529" s="6" t="n"/>
       <c r="G529" s="6" t="n"/>
       <c r="H529" s="6" t="n"/>
-      <c r="I529" s="24">
-        <f>E529*J529</f>
-        <v/>
-      </c>
-      <c r="J529" s="30" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" s="22" t="n"/>
-      <c r="B530" s="22" t="n"/>
-      <c r="C530" s="25" t="inlineStr">
-        <is>
-          <t>M70 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D530" s="26" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E530" s="22" t="n"/>
-      <c r="F530" s="22" t="n"/>
-      <c r="G530" s="22" t="n"/>
-      <c r="H530" s="22" t="n"/>
-      <c r="I530" s="22" t="n"/>
-      <c r="J530" s="27">
-        <f>SUM(I529:I529)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="531" ht="22" customHeight="1">
-      <c r="A531" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B531" s="20" t="inlineStr">
-        <is>
-          <t>35.140.3101</t>
-        </is>
-      </c>
-      <c r="C531" s="8" t="inlineStr">
-        <is>
-          <t>[M72]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
-        </is>
-      </c>
-      <c r="D531" s="21" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E531" s="22" t="n"/>
-      <c r="F531" s="22" t="n"/>
-      <c r="G531" s="22" t="n"/>
-      <c r="H531" s="22" t="n"/>
-      <c r="I531" s="22" t="n"/>
-      <c r="J531" s="22" t="n"/>
-    </row>
-    <row r="532" ht="12" customHeight="1">
-      <c r="A532" s="6" t="n"/>
-      <c r="B532" s="6" t="n"/>
-      <c r="C532" s="23" t="inlineStr">
-        <is>
-          <t>Saha aydınlatma direkleri besleme hattı</t>
-        </is>
-      </c>
-      <c r="D532" s="6" t="n"/>
-      <c r="E532" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F532" s="6" t="n"/>
-      <c r="G532" s="6" t="n"/>
-      <c r="H532" s="6" t="n"/>
-      <c r="I532" s="24">
-        <f>E532*J532</f>
-        <v/>
-      </c>
-      <c r="J532" s="30" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" s="22" t="n"/>
-      <c r="B533" s="22" t="n"/>
-      <c r="C533" s="25" t="inlineStr">
-        <is>
-          <t>M72 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D533" s="26" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E533" s="22" t="n"/>
-      <c r="F533" s="22" t="n"/>
-      <c r="G533" s="22" t="n"/>
-      <c r="H533" s="22" t="n"/>
-      <c r="I533" s="22" t="n"/>
-      <c r="J533" s="27">
-        <f>SUM(I532:I532)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="534" ht="22" customHeight="1">
-      <c r="A534" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B534" s="20" t="inlineStr">
-        <is>
-          <t>35.172.1706</t>
-        </is>
-      </c>
-      <c r="C534" s="8" t="inlineStr">
-        <is>
-          <t>[M82]  Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
-        </is>
-      </c>
-      <c r="D534" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E534" s="22" t="n"/>
-      <c r="F534" s="22" t="n"/>
-      <c r="G534" s="22" t="n"/>
-      <c r="H534" s="22" t="n"/>
-      <c r="I534" s="22" t="n"/>
-      <c r="J534" s="22" t="n"/>
-    </row>
-    <row r="535" ht="12" customHeight="1">
-      <c r="A535" s="6" t="n"/>
-      <c r="B535" s="6" t="n"/>
-      <c r="C535" s="23" t="inlineStr">
-        <is>
-          <t>Tesis içi yol ve saha aydınlatması</t>
-        </is>
-      </c>
-      <c r="D535" s="6" t="n"/>
-      <c r="E535" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F535" s="6" t="n"/>
-      <c r="G535" s="6" t="n"/>
-      <c r="H535" s="6" t="n"/>
-      <c r="I535" s="24">
-        <f>E535*J535</f>
-        <v/>
-      </c>
-      <c r="J535" s="30" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" s="22" t="n"/>
-      <c r="B536" s="22" t="n"/>
-      <c r="C536" s="25" t="inlineStr">
-        <is>
-          <t>M82 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D536" s="26" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E536" s="22" t="n"/>
-      <c r="F536" s="22" t="n"/>
-      <c r="G536" s="22" t="n"/>
-      <c r="H536" s="22" t="n"/>
-      <c r="I536" s="22" t="n"/>
-      <c r="J536" s="27">
-        <f>SUM(I535:I535)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="537" ht="15" customHeight="1">
-      <c r="A537" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B537" s="20" t="inlineStr">
-        <is>
-          <t>35.170.4002</t>
-        </is>
-      </c>
-      <c r="C537" s="8" t="inlineStr">
-        <is>
-          <t>[M83]  LED projektör, ışık akısı en az 5100 lm</t>
-        </is>
-      </c>
-      <c r="D537" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E537" s="22" t="n"/>
-      <c r="F537" s="22" t="n"/>
-      <c r="G537" s="22" t="n"/>
-      <c r="H537" s="22" t="n"/>
-      <c r="I537" s="22" t="n"/>
-      <c r="J537" s="22" t="n"/>
-    </row>
-    <row r="538" ht="12" customHeight="1">
-      <c r="A538" s="6" t="n"/>
-      <c r="B538" s="6" t="n"/>
-      <c r="C538" s="23" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği başına 1 adet</t>
-        </is>
-      </c>
-      <c r="D538" s="6" t="n"/>
-      <c r="E538" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F538" s="6" t="n"/>
-      <c r="G538" s="6" t="n"/>
-      <c r="H538" s="6" t="n"/>
-      <c r="I538" s="24">
-        <f>E538*J538</f>
-        <v/>
-      </c>
-      <c r="J538" s="30" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" s="22" t="n"/>
-      <c r="B539" s="22" t="n"/>
-      <c r="C539" s="25" t="inlineStr">
-        <is>
-          <t>M83 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D539" s="26" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E539" s="22" t="n"/>
-      <c r="F539" s="22" t="n"/>
-      <c r="G539" s="22" t="n"/>
-      <c r="H539" s="22" t="n"/>
-      <c r="I539" s="22" t="n"/>
-      <c r="J539" s="27">
-        <f>SUM(I538:I538)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="540"/>
-    <row r="541">
-      <c r="A541" s="16" t="inlineStr">
-        <is>
-          <t>AÇIKLAMALAR</t>
-        </is>
-      </c>
-      <c r="B541" s="6" t="n"/>
-      <c r="C541" s="6" t="n"/>
-      <c r="D541" s="6" t="n"/>
-      <c r="E541" s="6" t="n"/>
-      <c r="F541" s="6" t="n"/>
-      <c r="G541" s="6" t="n"/>
-      <c r="H541" s="6" t="n"/>
-      <c r="I541" s="6" t="n"/>
-      <c r="J541" s="6" t="n"/>
-    </row>
-    <row r="542" ht="13" customHeight="1">
-      <c r="A542" s="17" t="inlineStr">
+      <c r="I529" s="6" t="n"/>
+      <c r="J529" s="6" t="n"/>
+    </row>
+    <row r="530" ht="13" customHeight="1">
+      <c r="A530" s="17" t="inlineStr">
         <is>
           <t>•  Miktar sütunundaki her formül yalnızca o satırdaki ölçü hücrelerini çarpar; hiçbir sayı formülün içine gömülmemiştir.</t>
         </is>
       </c>
     </row>
-    <row r="543" ht="13" customHeight="1">
-      <c r="A543" s="17" t="inlineStr">
+    <row r="531" ht="13" customHeight="1">
+      <c r="A531" s="17" t="inlineStr">
         <is>
           <t>•  Son sütundaki katsayı, birim ağırlık (kg/m², kg/m³, ton/m²), bindirme payı, üçgen alan çarpanı (0,50) veya adet çarpanıdır.</t>
         </is>
       </c>
     </row>
-    <row r="544" ht="22" customHeight="1">
-      <c r="A544" s="17" t="inlineStr">
+    <row r="532" ht="22" customHeight="1">
+      <c r="A532" s="17" t="inlineStr">
         <is>
           <t>•  Ölçüler mimari ve betonarme paftalardan alınmıştır; kümes temellerinin beton, kalıp ve donatı miktarları doğrudan betonarme paftasındaki METRAJ tablosundandır.</t>
         </is>
       </c>
     </row>
-    <row r="545" ht="13" customHeight="1">
-      <c r="A545" s="17" t="inlineStr">
+    <row r="533" ht="13" customHeight="1">
+      <c r="A533" s="17" t="inlineStr">
         <is>
           <t>•  (-) işaretli satırlar minha edilen (düşülen) miktarlardır.</t>
         </is>
@@ -17939,22 +17561,22 @@
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A374:J374"/>
+    <mergeCell ref="A450:J450"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A397:J397"/>
     <mergeCell ref="A343:J343"/>
-    <mergeCell ref="A541:J541"/>
-    <mergeCell ref="A544:J544"/>
-    <mergeCell ref="A545:J545"/>
-    <mergeCell ref="A439:J439"/>
-    <mergeCell ref="A486:J486"/>
+    <mergeCell ref="A409:J409"/>
+    <mergeCell ref="A474:J474"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A542:J542"/>
-    <mergeCell ref="A421:J421"/>
-    <mergeCell ref="A543:J543"/>
+    <mergeCell ref="A427:J427"/>
+    <mergeCell ref="A531:J531"/>
+    <mergeCell ref="A532:J532"/>
+    <mergeCell ref="A529:J529"/>
     <mergeCell ref="A174:J174"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A462:J462"/>
+    <mergeCell ref="A530:J530"/>
+    <mergeCell ref="A533:J533"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -17967,7 +17589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20493,7 +20115,7 @@
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>Yapı/Bina Adı: FOSEPTIK</t>
+          <t>Yapı/Bina Adı: YEM SILOSU BETONARME KAIDELERI</t>
         </is>
       </c>
     </row>
@@ -20583,21 +20205,21 @@
       <c r="A96" s="6" t="n"/>
       <c r="B96" s="23" t="inlineStr">
         <is>
-          <t>Radye 2,00 x 2,00 x 0,30 m³; 95 kg/m³</t>
+          <t>Kaideler 2,90 x 2,90 x 0,50 m³, 2 adet; 90 kg/m³</t>
         </is>
       </c>
       <c r="C96" s="6" t="n"/>
       <c r="D96" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="29" t="n">
-        <v>4</v>
+        <v>8.41</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H96" s="36" t="inlineStr">
         <is>
@@ -20605,7 +20227,7 @@
         </is>
       </c>
       <c r="I96" s="33" t="n">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="J96" s="34">
         <f>D96*E96*F96*G96*I96</f>
@@ -20613,495 +20235,278 @@
       </c>
       <c r="K96" s="6" t="n"/>
     </row>
-    <row r="97" ht="12" customHeight="1">
-      <c r="A97" s="6" t="n"/>
-      <c r="B97" s="23" t="inlineStr">
-        <is>
-          <t>Perdeler 7,00 x 0,25 x 2,50 m³; 95 kg/m³</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G97" s="29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H97" s="36" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="22" t="n"/>
+      <c r="B97" s="25" t="inlineStr">
+        <is>
+          <t>SL/M26 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C97" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="n"/>
+      <c r="E97" s="22" t="n"/>
+      <c r="F97" s="22" t="n"/>
+      <c r="G97" s="22" t="n"/>
+      <c r="H97" s="22" t="n"/>
+      <c r="I97" s="22" t="n"/>
+      <c r="J97" s="22" t="n"/>
+      <c r="K97" s="35">
+        <f>SUM(J96:J96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: SU DEPOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I100" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="n"/>
+      <c r="E101" s="22" t="n"/>
+      <c r="F101" s="22" t="n"/>
+      <c r="G101" s="22" t="n"/>
+      <c r="H101" s="22" t="n"/>
+      <c r="I101" s="22" t="n"/>
+      <c r="J101" s="22" t="n"/>
+      <c r="K101" s="22" t="n"/>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="6" t="n"/>
+      <c r="B102" s="23" t="inlineStr">
+        <is>
+          <t>Radye ve üst döşeme — proje metrajı 223,70 + 32,90 = 256,60 kg</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="6" t="n"/>
+      <c r="G102" s="6" t="n"/>
+      <c r="H102" s="36" t="inlineStr">
         <is>
           <t>ø8-12 nervürlü</t>
         </is>
       </c>
-      <c r="I97" s="33" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="J97" s="34">
-        <f>D97*E97*F97*G97*I97</f>
-        <v/>
-      </c>
-      <c r="K97" s="6" t="n"/>
-    </row>
-    <row r="98" ht="12" customHeight="1">
-      <c r="A98" s="6" t="n"/>
-      <c r="B98" s="23" t="inlineStr">
-        <is>
-          <t>Üst döşeme 2,00 x 2,00 x 0,15 m³; 95 kg/m³</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="G98" s="29" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H98" s="36" t="inlineStr">
+      <c r="I102" s="33" t="n">
+        <v>0.2566</v>
+      </c>
+      <c r="J102" s="34">
+        <f>D102*E102*I102</f>
+        <v/>
+      </c>
+      <c r="K102" s="6" t="n"/>
+    </row>
+    <row r="103" ht="12" customHeight="1">
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="23" t="inlineStr">
+        <is>
+          <t>Perdeler 13,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G103" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H103" s="36" t="inlineStr">
         <is>
           <t>ø8-12 nervürlü</t>
         </is>
       </c>
-      <c r="I98" s="33" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="J98" s="34">
-        <f>D98*E98*F98*G98*I98</f>
-        <v/>
-      </c>
-      <c r="K98" s="6" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="22" t="n"/>
-      <c r="B99" s="25" t="inlineStr">
-        <is>
-          <t>FS/M26 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C99" s="26" t="inlineStr">
+      <c r="I103" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J103" s="34">
+        <f>D103*E103*F103*G103*I103</f>
+        <v/>
+      </c>
+      <c r="K103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="22" t="n"/>
+      <c r="B104" s="25" t="inlineStr">
+        <is>
+          <t>SD/M26 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C104" s="26" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="D99" s="22" t="n"/>
-      <c r="E99" s="22" t="n"/>
-      <c r="F99" s="22" t="n"/>
-      <c r="G99" s="22" t="n"/>
-      <c r="H99" s="22" t="n"/>
-      <c r="I99" s="22" t="n"/>
-      <c r="J99" s="22" t="n"/>
-      <c r="K99" s="35">
-        <f>SUM(J96:J98)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100"/>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: YEM SILOSU BETONARME KAIDELERI</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="28" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>Benzer</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="H102" s="7" t="inlineStr">
-        <is>
-          <t>Demir çapı veya profil tipi</t>
-        </is>
-      </c>
-      <c r="I102" s="7" t="inlineStr">
-        <is>
-          <t>Birim Ağırlık</t>
-        </is>
-      </c>
-      <c r="J102" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Ağırlık</t>
-        </is>
-      </c>
-      <c r="K102" s="7" t="inlineStr">
-        <is>
-          <t>Genel Toplam</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="C103" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D103" s="22" t="n"/>
-      <c r="E103" s="22" t="n"/>
-      <c r="F103" s="22" t="n"/>
-      <c r="G103" s="22" t="n"/>
-      <c r="H103" s="22" t="n"/>
-      <c r="I103" s="22" t="n"/>
-      <c r="J103" s="22" t="n"/>
-      <c r="K103" s="22" t="n"/>
-    </row>
-    <row r="104" ht="12" customHeight="1">
-      <c r="A104" s="6" t="n"/>
-      <c r="B104" s="23" t="inlineStr">
-        <is>
-          <t>Kaideler 2,90 x 2,90 x 0,50 m³, 2 adet; 90 kg/m³</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="n"/>
-      <c r="D104" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E104" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="29" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="G104" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H104" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I104" s="33" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J104" s="34">
-        <f>D104*E104*F104*G104*I104</f>
-        <v/>
-      </c>
-      <c r="K104" s="6" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="22" t="n"/>
-      <c r="B105" s="25" t="inlineStr">
-        <is>
-          <t>SL/M26 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C105" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D105" s="22" t="n"/>
-      <c r="E105" s="22" t="n"/>
-      <c r="F105" s="22" t="n"/>
-      <c r="G105" s="22" t="n"/>
-      <c r="H105" s="22" t="n"/>
-      <c r="I105" s="22" t="n"/>
-      <c r="J105" s="22" t="n"/>
-      <c r="K105" s="35">
-        <f>SUM(J104:J104)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106"/>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: SU DEPOSU</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="A108" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>Benzer</t>
-        </is>
-      </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>Demir çapı veya profil tipi</t>
-        </is>
-      </c>
-      <c r="I108" s="7" t="inlineStr">
-        <is>
-          <t>Birim Ağırlık</t>
-        </is>
-      </c>
-      <c r="J108" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Ağırlık</t>
-        </is>
-      </c>
-      <c r="K108" s="7" t="inlineStr">
-        <is>
-          <t>Genel Toplam</t>
+      <c r="D104" s="22" t="n"/>
+      <c r="E104" s="22" t="n"/>
+      <c r="F104" s="22" t="n"/>
+      <c r="G104" s="22" t="n"/>
+      <c r="H104" s="22" t="n"/>
+      <c r="I104" s="22" t="n"/>
+      <c r="J104" s="22" t="n"/>
+      <c r="K104" s="35">
+        <f>SUM(J102:J103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>AÇIKLAMALAR VE VARSAYIMLAR</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="n"/>
+      <c r="E106" s="6" t="n"/>
+      <c r="F106" s="6" t="n"/>
+      <c r="G106" s="6" t="n"/>
+      <c r="H106" s="6" t="n"/>
+      <c r="I106" s="6" t="n"/>
+      <c r="J106" s="6" t="n"/>
+      <c r="K106" s="6" t="n"/>
+    </row>
+    <row r="107" ht="13" customHeight="1">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t>•  SARI zeminli 'demir çapı veya profil tipi' hücreleri, proje toplamını tutturmak üzere yapılan dağıtımı gösterir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="33" customHeight="1">
+      <c r="A108" s="17" t="inlineStr">
+        <is>
+          <t>•  Kümes A ve B blok temellerinin donatı TOPLAMLARI betonarme paftasındaki METRAJ tablosundan aynen alınmıştır (blok başına ø6-12 = 4.159,89 kg, ø14-50 = 7.287,50 kg). Bu toplamlar eleman bazında dağıtılmış, dağıtılamayan kısım açıkça 'proje METRAJ tablosunu tamamlayan pay' satırı olarak gösterilmiştir. Genel toplamlar proje tablosuyla birebir tutmaktadır.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="C109" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D109" s="22" t="n"/>
-      <c r="E109" s="22" t="n"/>
-      <c r="F109" s="22" t="n"/>
-      <c r="G109" s="22" t="n"/>
-      <c r="H109" s="22" t="n"/>
-      <c r="I109" s="22" t="n"/>
-      <c r="J109" s="22" t="n"/>
-      <c r="K109" s="22" t="n"/>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="6" t="n"/>
-      <c r="B110" s="23" t="inlineStr">
-        <is>
-          <t>Radye ve üst döşeme — proje metrajı 223,70 + 32,90 = 256,60 kg</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="n"/>
-      <c r="D110" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="6" t="n"/>
-      <c r="G110" s="6" t="n"/>
-      <c r="H110" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I110" s="33" t="n">
-        <v>0.2566</v>
-      </c>
-      <c r="J110" s="34">
-        <f>D110*E110*I110</f>
-        <v/>
-      </c>
-      <c r="K110" s="6" t="n"/>
-    </row>
-    <row r="111" ht="12" customHeight="1">
-      <c r="A111" s="6" t="n"/>
-      <c r="B111" s="23" t="inlineStr">
-        <is>
-          <t>Perdeler 13,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="n"/>
-      <c r="D111" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="G111" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H111" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I111" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J111" s="34">
-        <f>D111*E111*F111*G111*I111</f>
-        <v/>
-      </c>
-      <c r="K111" s="6" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="22" t="n"/>
-      <c r="B112" s="25" t="inlineStr">
-        <is>
-          <t>SD/M26 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C112" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D112" s="22" t="n"/>
-      <c r="E112" s="22" t="n"/>
-      <c r="F112" s="22" t="n"/>
-      <c r="G112" s="22" t="n"/>
-      <c r="H112" s="22" t="n"/>
-      <c r="I112" s="22" t="n"/>
-      <c r="J112" s="22" t="n"/>
-      <c r="K112" s="35">
-        <f>SUM(J110:J111)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113"/>
-    <row r="114">
-      <c r="A114" s="16" t="inlineStr">
-        <is>
-          <t>AÇIKLAMALAR VE VARSAYIMLAR</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="F114" s="6" t="n"/>
-      <c r="G114" s="6" t="n"/>
-      <c r="H114" s="6" t="n"/>
-      <c r="I114" s="6" t="n"/>
-      <c r="J114" s="6" t="n"/>
-      <c r="K114" s="6" t="n"/>
-    </row>
-    <row r="115" ht="13" customHeight="1">
-      <c r="A115" s="17" t="inlineStr">
-        <is>
-          <t>•  SARI zeminli 'demir çapı veya profil tipi' hücreleri, proje toplamını tutturmak üzere yapılan dağıtımı gösterir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="33" customHeight="1">
-      <c r="A116" s="17" t="inlineStr">
-        <is>
-          <t>•  Kümes A ve B blok temellerinin donatı TOPLAMLARI betonarme paftasındaki METRAJ tablosundan aynen alınmıştır (blok başına ø6-12 = 4.159,89 kg, ø14-50 = 7.287,50 kg). Bu toplamlar eleman bazında dağıtılmış, dağıtılamayan kısım açıkça 'proje METRAJ tablosunu tamamlayan pay' satırı olarak gösterilmiştir. Genel toplamlar proje tablosuyla birebir tutmaktadır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="17" t="inlineStr">
+      <c r="A109" s="17" t="inlineStr">
         <is>
           <t>•  ÇELİK TAŞIYICI SİSTEM STATİK ÇELİK PROJESİNDEN ALINMIŞTIR. Profiller SHS 150x150x6 (kolon, ana kiriş, boyuna kiriş), RHS 100x50x3 (çatı aşığı, yan aşık, kuşak) ve SHS 100x100x4 (çapraz); malzeme S235JR. Çerçeve geometrisi projedeki gibidir: aks açıklıkları 3,75 + 6,00 + 3,80 = 13,55 m, kolon üstü +2,84, mahya +4,34.</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="13" customHeight="1">
-      <c r="A118" s="17" t="inlineStr">
+    <row r="110" ht="13" customHeight="1">
+      <c r="A110" s="17" t="inlineStr">
         <is>
           <t>•  Gübre çukuru ve müştemilat donatısı, projedeki METRAJ tablolarından ve eleman hacmi x birim donatı oranı (kg/m³) esasıyla hesaplanmıştır.</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="17" t="inlineStr">
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="17" t="inlineStr">
         <is>
           <t>•  Birim ağırlıklar (ton/m): ø8 0,000395 · ø10 0,000617 · ø12 0,000888 · ø14 0,001210 · ø16 0,001580 · ø20 0,002470 · HEA 200 0,0423 · HEA 260 0,0541 · IPE 270 0,0361 · Z 200x70x2,5 0,00900 · L 70x70x7 0,00738.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A119:K119"/>
-    <mergeCell ref="A114:K114"/>
-    <mergeCell ref="A118:K118"/>
+  <mergeCells count="15">
+    <mergeCell ref="A108:K108"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A101:K101"/>
     <mergeCell ref="A86:K86"/>
+    <mergeCell ref="A109:K109"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A107:K107"/>
-    <mergeCell ref="A115:K115"/>
-    <mergeCell ref="A117:K117"/>
+    <mergeCell ref="A99:K99"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A93:K93"/>
-    <mergeCell ref="A116:K116"/>
     <mergeCell ref="A75:K75"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A110:K110"/>
+    <mergeCell ref="A111:K111"/>
+    <mergeCell ref="A106:K106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -145,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -239,6 +239,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14541,7 +14544,7 @@
       <c r="B406" s="6" t="n"/>
       <c r="C406" s="23" t="inlineStr">
         <is>
-          <t>Foseptik — betonarme gövdenin iç hacmi 1.50x1.50x2.50 = 5.62 m³; en yakın standart tank 6 m³</t>
+          <t>Foseptik — kazı çukurunun net oturma alanına sığan hazne 1.50x1.50x2.50 = 5.62 m³; en yakın standart tank 6 m³</t>
         </is>
       </c>
       <c r="D406" s="6" t="n"/>
@@ -17589,7 +17592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18636,85 +18639,101 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: KÜMES B BLOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Benzer</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>Demir çapı veya profil tipi</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>Birim Ağırlık</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Ağırlık</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>Genel Toplam</t>
-        </is>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0115</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>[M35]  Galvanizli düz sacdan yağmur oluğu (dere) yapılması ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="22" t="n"/>
+      <c r="K39" s="22" t="n"/>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Uzun cepheler boyunca dere — blok başına 2 kenar, saçaklı boy 79,80 m; gelişmiş genişlik 0,50 m, 0,50 mm galvanizli düz sac (0,50 x 0,0005 x 7.850 = 1,96 kg/m), birleşim ve kenet payı ile 2,00 kg/m</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="36" t="inlineStr">
+        <is>
+          <t>0,50 mm galvanizli düz sac</t>
+        </is>
+      </c>
+      <c r="I40" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="34">
+        <f>D40*E40*F40*I40</f>
+        <v/>
+      </c>
+      <c r="K40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n"/>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>KA/M35 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="22" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="22" t="n"/>
+      <c r="K41" s="35">
+        <f>SUM(J40:J40)</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>[M22]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>[M43F]  1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D42" s="22" t="n"/>
@@ -18728,29 +18747,29 @@
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="n"/>
-      <c r="B43" s="31" t="inlineStr">
-        <is>
-          <t>Şerit temel etriyesi T1…T21 (50/60), ø8/20 — aks başına 13,55/0,20 = 68 adet, 21 aks; etriye açılım boyu 2x(0,44+0,54)+0,20 kanca = 2,16 m (blok başına)</t>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Servis bölümü iç kapıları — blok başına 3 adet; kasa çevresi 2x2,10+0,90 = 5,10 m, 1,50 mm sacdan bükme kasa 3,55 kg/m</t>
         </is>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" s="28" t="n">
-        <v>1428</v>
+        <v>1</v>
       </c>
       <c r="F43" s="29" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="G43" s="6" t="n"/>
-      <c r="H43" s="32" t="inlineStr">
-        <is>
-          <t>ø8 nervürlü</t>
+      <c r="H43" s="36" t="inlineStr">
+        <is>
+          <t>1,50 mm bükme sac kasa</t>
         </is>
       </c>
       <c r="I43" s="33" t="n">
-        <v>0.000395</v>
+        <v>3.55</v>
       </c>
       <c r="J43" s="34">
         <f>D43*E43*F43*I43</f>
@@ -18758,75 +18777,60 @@
       </c>
       <c r="K43" s="6" t="n"/>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="31" t="inlineStr">
-        <is>
-          <t>Şerit temel gövde ve montaj donatısı ø12 — aks başına 4 adet, 21 aks, aks boyu 13,55 m (blok başına)</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="28" t="n">
-        <v>84</v>
-      </c>
-      <c r="F44" s="29" t="n">
-        <v>13.55</v>
-      </c>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="32" t="inlineStr">
-        <is>
-          <t>ø12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I44" s="33" t="n">
-        <v>0.000888</v>
-      </c>
-      <c r="J44" s="34">
-        <f>D44*E44*F44*I44</f>
-        <v/>
-      </c>
-      <c r="K44" s="6" t="n"/>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="31" t="inlineStr">
-        <is>
-          <t>Bağ kirişi etriyesi BK (30/30), ø8/20 — hat başına 78.55/0,20 = 393 adet, 4 hat; etriye açılım boyu 2x(0,24+0,24)+0,20 kanca = 1,16 m (blok başına)</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="28" t="n">
-        <v>1572</v>
-      </c>
-      <c r="F45" s="29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="32" t="inlineStr">
-        <is>
-          <t>ø8 nervürlü</t>
-        </is>
-      </c>
-      <c r="I45" s="33" t="n">
-        <v>0.000395</v>
-      </c>
-      <c r="J45" s="34">
-        <f>D45*E45*F45*I45</f>
-        <v/>
-      </c>
-      <c r="K45" s="6" t="n"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
+    <row r="44">
+      <c r="A44" s="22" t="n"/>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>KA/M43F GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="22" t="n"/>
+      <c r="K44" s="35">
+        <f>SUM(J43:J43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>[M87]  Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="22" t="n"/>
+      <c r="K45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="n"/>
-      <c r="B46" s="31" t="inlineStr">
-        <is>
-          <t>Kolon ankraj ve guse donatısı ø12 — 21 aks x 4 kolon = 84 adet, boy 2,50 m (blok başına)</t>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Kümes içi ana kablo güzergâhı — blok başına 200 m; 200x60x1,0 mm perfore tava açınımı 0,320 m x 7,85 kg/m² = 2,510 kg/m</t>
         </is>
       </c>
       <c r="C46" s="6" t="n"/>
@@ -18834,19 +18838,19 @@
         <v>1</v>
       </c>
       <c r="E46" s="28" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="F46" s="29" t="n">
-        <v>2.5</v>
+        <v>200</v>
       </c>
       <c r="G46" s="6" t="n"/>
-      <c r="H46" s="32" t="inlineStr">
-        <is>
-          <t>ø12 nervürlü</t>
+      <c r="H46" s="36" t="inlineStr">
+        <is>
+          <t>200x60x1,0 galvanizli perfore tava</t>
         </is>
       </c>
       <c r="I46" s="33" t="n">
-        <v>0.000888</v>
+        <v>2.51</v>
       </c>
       <c r="J46" s="34">
         <f>D46*E46*F46*I46</f>
@@ -18854,46 +18858,44 @@
       </c>
       <c r="K46" s="6" t="n"/>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="6" t="n"/>
-      <c r="B47" s="31" t="inlineStr">
-        <is>
-          <t>Montaj donatısı, çiroz, pilye ve bindirme payı — betonarme proje METRAJ tablosundaki blok başına 4.159,89 kg toplamını tamamlayan fark</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="32" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I47" s="33" t="n">
-        <v>1.0240284</v>
-      </c>
-      <c r="J47" s="34">
-        <f>D47*E47*I47</f>
-        <v/>
-      </c>
-      <c r="K47" s="6" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="22" t="n"/>
-      <c r="B48" s="25" t="inlineStr">
-        <is>
-          <t>KB/M22 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
+    <row r="47">
+      <c r="A47" s="22" t="n"/>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>KA/M87 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="22" t="n"/>
+      <c r="G47" s="22" t="n"/>
+      <c r="H47" s="22" t="n"/>
+      <c r="I47" s="22" t="n"/>
+      <c r="J47" s="22" t="n"/>
+      <c r="K47" s="35">
+        <f>SUM(J46:J46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>[M89]  Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun 1,0 mm sıcak daldırma galvanizli sac</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="D48" s="22" t="n"/>
@@ -18903,163 +18905,138 @@
       <c r="H48" s="22" t="n"/>
       <c r="I48" s="22" t="n"/>
       <c r="J48" s="22" t="n"/>
-      <c r="K48" s="35">
-        <f>SUM(J43:J47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1004</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>[M23]  Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D49" s="22" t="n"/>
-      <c r="E49" s="22" t="n"/>
-      <c r="F49" s="22" t="n"/>
-      <c r="G49" s="22" t="n"/>
-      <c r="H49" s="22" t="n"/>
-      <c r="I49" s="22" t="n"/>
-      <c r="J49" s="22" t="n"/>
-      <c r="K49" s="22" t="n"/>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="31" t="inlineStr">
-        <is>
-          <t>Şerit temel boyuna donatısı ø16 — aks başına 6 alt + 4 üst = 10 adet, 21 aks, aks boyu 13,55 m (blok başına)</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="28" t="n">
-        <v>210</v>
-      </c>
-      <c r="F50" s="29" t="n">
-        <v>13.55</v>
-      </c>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="32" t="inlineStr">
-        <is>
-          <t>ø16 nervürlü</t>
-        </is>
-      </c>
-      <c r="I50" s="33" t="n">
-        <v>0.00158</v>
-      </c>
-      <c r="J50" s="34">
-        <f>D50*E50*F50*I50</f>
-        <v/>
-      </c>
-      <c r="K50" s="6" t="n"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>Bağ kirişi boyuna donatısı ø14 — hat başına 3 alt + 3 üst = 6 adet, 4 hat, hat boyu 78.55 m (blok başına)</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="F51" s="29" t="n">
-        <v>78.55</v>
-      </c>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="32" t="inlineStr">
-        <is>
-          <t>ø14 nervürlü</t>
-        </is>
-      </c>
-      <c r="I51" s="33" t="n">
-        <v>0.00121</v>
-      </c>
-      <c r="J51" s="34">
-        <f>D51*E51*F51*I51</f>
-        <v/>
-      </c>
-      <c r="K51" s="6" t="n"/>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>Bindirme, filiz ve gönye payı — betonarme proje METRAJ tablosundaki blok başına 7.287,50 kg toplamını tamamlayan fark</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="32" t="inlineStr">
-        <is>
-          <t>ø14-28 nervürlü</t>
-        </is>
-      </c>
-      <c r="I52" s="33" t="n">
-        <v>0.510518</v>
-      </c>
-      <c r="J52" s="34">
-        <f>D52*E52*I52</f>
-        <v/>
-      </c>
-      <c r="K52" s="6" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="22" t="n"/>
-      <c r="B53" s="25" t="inlineStr">
-        <is>
-          <t>KB/M23 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D53" s="22" t="n"/>
-      <c r="E53" s="22" t="n"/>
-      <c r="F53" s="22" t="n"/>
-      <c r="G53" s="22" t="n"/>
-      <c r="H53" s="22" t="n"/>
-      <c r="I53" s="22" t="n"/>
-      <c r="J53" s="22" t="n"/>
-      <c r="K53" s="35">
-        <f>SUM(J50:J52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
+      <c r="K48" s="22" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Tava güzergâhının tamamı — blok başına 200 m; kapak sacı açınımı 0,230 m x 7,85 kg/m² = 1,806 kg/m</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="36" t="inlineStr">
+        <is>
+          <t>1,0 mm galvanizli kapak sacı</t>
+        </is>
+      </c>
+      <c r="I49" s="33" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="J49" s="34">
+        <f>D49*E49*F49*I49</f>
+        <v/>
+      </c>
+      <c r="K49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="n"/>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>KA/M89 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="22" t="n"/>
+      <c r="F50" s="22" t="n"/>
+      <c r="G50" s="22" t="n"/>
+      <c r="H50" s="22" t="n"/>
+      <c r="I50" s="22" t="n"/>
+      <c r="J50" s="22" t="n"/>
+      <c r="K50" s="35">
+        <f>SUM(J49:J49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: KÜMES B BLOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>[M27]  Nervürlü çelik hasırın yerine konulması</t>
+          <t>[M22]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="C54" s="19" t="inlineStr">
@@ -19078,9 +19055,9 @@
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="6" t="n"/>
-      <c r="B55" s="23" t="inlineStr">
-        <is>
-          <t>Kümes zemin döşemesi 78.00 x 13,90 (servis bölümü hariç); Q188 hasır = 3,05 kg/m², %10 bindirme payı ile 3,355 kg/m² (blok başına)</t>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>Şerit temel etriyesi T1…T21 (50/60), ø8/20 — aks başına 13,55/0,20 = 68 adet, 21 aks; etriye açılım boyu 2x(0,44+0,54)+0,20 kanca = 2,16 m (blok başına)</t>
         </is>
       </c>
       <c r="C55" s="6" t="n"/>
@@ -19088,102 +19065,115 @@
         <v>1</v>
       </c>
       <c r="E55" s="28" t="n">
-        <v>1</v>
+        <v>1428</v>
       </c>
       <c r="F55" s="29" t="n">
-        <v>78</v>
-      </c>
-      <c r="G55" s="29" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H55" s="36" t="inlineStr">
-        <is>
-          <t>Q188 çelik hasır</t>
+        <v>2.16</v>
+      </c>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="32" t="inlineStr">
+        <is>
+          <t>ø8 nervürlü</t>
         </is>
       </c>
       <c r="I55" s="33" t="n">
-        <v>0.003355</v>
+        <v>0.000395</v>
       </c>
       <c r="J55" s="34">
-        <f>D55*E55*F55*G55*I55</f>
+        <f>D55*E55*F55*I55</f>
         <v/>
       </c>
       <c r="K55" s="6" t="n"/>
     </row>
-    <row r="56">
-      <c r="A56" s="22" t="n"/>
-      <c r="B56" s="25" t="inlineStr">
-        <is>
-          <t>KB/M27 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C56" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D56" s="22" t="n"/>
-      <c r="E56" s="22" t="n"/>
-      <c r="F56" s="22" t="n"/>
-      <c r="G56" s="22" t="n"/>
-      <c r="H56" s="22" t="n"/>
-      <c r="I56" s="22" t="n"/>
-      <c r="J56" s="22" t="n"/>
-      <c r="K56" s="35">
-        <f>SUM(J55:J55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
-        <is>
-          <t>15.165.1003</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>[M31]  Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="n"/>
-      <c r="E57" s="22" t="n"/>
-      <c r="F57" s="22" t="n"/>
-      <c r="G57" s="22" t="n"/>
-      <c r="H57" s="22" t="n"/>
-      <c r="I57" s="22" t="n"/>
-      <c r="J57" s="22" t="n"/>
-      <c r="K57" s="22" t="n"/>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="31" t="inlineStr">
+        <is>
+          <t>Şerit temel gövde ve montaj donatısı ø12 — aks başına 4 adet, 21 aks, aks boyu 13,55 m (blok başına)</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="28" t="n">
+        <v>84</v>
+      </c>
+      <c r="F56" s="29" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="32" t="inlineStr">
+        <is>
+          <t>ø12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I56" s="33" t="n">
+        <v>0.000888</v>
+      </c>
+      <c r="J56" s="34">
+        <f>D56*E56*F56*I56</f>
+        <v/>
+      </c>
+      <c r="K56" s="6" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>Bağ kirişi etriyesi BK (30/30), ø8/20 — hat başına 78.55/0,20 = 393 adet, 4 hat; etriye açılım boyu 2x(0,24+0,24)+0,20 kanca = 1,16 m (blok başına)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="28" t="n">
+        <v>1572</v>
+      </c>
+      <c r="F57" s="29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="32" t="inlineStr">
+        <is>
+          <t>ø8 nervürlü</t>
+        </is>
+      </c>
+      <c r="I57" s="33" t="n">
+        <v>0.000395</v>
+      </c>
+      <c r="J57" s="34">
+        <f>D57*E57*F57*I57</f>
+        <v/>
+      </c>
+      <c r="K57" s="6" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="6" t="n"/>
-      <c r="B58" s="23" t="inlineStr">
-        <is>
-          <t>KLN dış kolonlar — 21 çerçeve x 2 adet, boy 2,84 m (kolon üstü kotu +2,84)</t>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>Kolon ankraj ve guse donatısı ø12 — 21 aks x 4 kolon = 84 adet, boy 2,50 m (blok başına)</t>
         </is>
       </c>
       <c r="C58" s="6" t="n"/>
       <c r="D58" s="28" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E58" s="28" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="F58" s="29" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="G58" s="6" t="n"/>
-      <c r="H58" s="36" t="inlineStr">
-        <is>
-          <t>SHS 150x150x6</t>
+      <c r="H58" s="32" t="inlineStr">
+        <is>
+          <t>ø12 nervürlü</t>
         </is>
       </c>
       <c r="I58" s="33" t="n">
-        <v>0.02689</v>
+        <v>0.000888</v>
       </c>
       <c r="J58" s="34">
         <f>D58*E58*F58*I58</f>
@@ -19191,127 +19181,110 @@
       </c>
       <c r="K58" s="6" t="n"/>
     </row>
-    <row r="59" ht="20" customHeight="1">
+    <row r="59" ht="30" customHeight="1">
       <c r="A59" s="6" t="n"/>
-      <c r="B59" s="23" t="inlineStr">
-        <is>
-          <t>KLN iç kolonlar — 21 çerçeve x 2 adet, ortalama boy 3,68 m (eğik kiriş altında)</t>
+      <c r="B59" s="31" t="inlineStr">
+        <is>
+          <t>Montaj donatısı, çiroz, pilye ve bindirme payı — betonarme proje METRAJ tablosundaki blok başına 4.159,89 kg toplamını tamamlayan fark</t>
         </is>
       </c>
       <c r="C59" s="6" t="n"/>
       <c r="D59" s="28" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E59" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F59" s="29" t="n">
-        <v>3.6755</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="n"/>
       <c r="G59" s="6" t="n"/>
-      <c r="H59" s="36" t="inlineStr">
-        <is>
-          <t>SHS 150x150x6</t>
+      <c r="H59" s="32" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
         </is>
       </c>
       <c r="I59" s="33" t="n">
-        <v>0.02689</v>
+        <v>1.0240284</v>
       </c>
       <c r="J59" s="34">
-        <f>D59*E59*F59*I59</f>
+        <f>D59*E59*I59</f>
         <v/>
       </c>
       <c r="K59" s="6" t="n"/>
     </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="23" t="inlineStr">
-        <is>
-          <t>AKR ana kirişler — 21 çerçeve x 2 adet, eğik boy 6,94 m (yarım açıklık 6,775 / kot farkı 1,50)</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="28" t="n">
-        <v>21</v>
-      </c>
-      <c r="E60" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="29" t="n">
-        <v>6.939</v>
-      </c>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="36" t="inlineStr">
-        <is>
-          <t>SHS 150x150x6</t>
-        </is>
-      </c>
-      <c r="I60" s="33" t="n">
-        <v>0.02689</v>
-      </c>
-      <c r="J60" s="34">
-        <f>D60*E60*F60*I60</f>
-        <v/>
-      </c>
-      <c r="K60" s="6" t="n"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="n"/>
-      <c r="B61" s="23" t="inlineStr">
-        <is>
-          <t>SKR boyuna kirişler — 2 saçak + 1 mahya hattı, boy 79,00 m</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E61" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="29" t="n">
-        <v>79</v>
-      </c>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="36" t="inlineStr">
-        <is>
-          <t>SHS 150x150x6</t>
-        </is>
-      </c>
-      <c r="I61" s="33" t="n">
-        <v>0.02689</v>
-      </c>
-      <c r="J61" s="34">
-        <f>D61*E61*F61*I61</f>
-        <v/>
-      </c>
-      <c r="K61" s="6" t="n"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
+    <row r="60">
+      <c r="A60" s="22" t="n"/>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>KB/M22 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="n"/>
+      <c r="E60" s="22" t="n"/>
+      <c r="F60" s="22" t="n"/>
+      <c r="G60" s="22" t="n"/>
+      <c r="H60" s="22" t="n"/>
+      <c r="I60" s="22" t="n"/>
+      <c r="J60" s="22" t="n"/>
+      <c r="K60" s="35">
+        <f>SUM(J55:J59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>[M23]  Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D61" s="22" t="n"/>
+      <c r="E61" s="22" t="n"/>
+      <c r="F61" s="22" t="n"/>
+      <c r="G61" s="22" t="n"/>
+      <c r="H61" s="22" t="n"/>
+      <c r="I61" s="22" t="n"/>
+      <c r="J61" s="22" t="n"/>
+      <c r="K61" s="22" t="n"/>
+    </row>
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="n"/>
-      <c r="B62" s="23" t="inlineStr">
-        <is>
-          <t>CAS çatı aşıkları — kesitte sayılan 16 hat, boy 79,80 m (saçak payı dâhil)</t>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>Şerit temel boyuna donatısı ø16 — aks başına 6 alt + 4 üst = 10 adet, 21 aks, aks boyu 13,55 m (blok başına)</t>
         </is>
       </c>
       <c r="C62" s="6" t="n"/>
       <c r="D62" s="28" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E62" s="28" t="n">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="F62" s="29" t="n">
-        <v>79.8</v>
+        <v>13.55</v>
       </c>
       <c r="G62" s="6" t="n"/>
-      <c r="H62" s="36" t="inlineStr">
-        <is>
-          <t>RHS 100x50x3</t>
+      <c r="H62" s="32" t="inlineStr">
+        <is>
+          <t>ø16 nervürlü</t>
         </is>
       </c>
       <c r="I62" s="33" t="n">
-        <v>0.00672</v>
+        <v>0.00158</v>
       </c>
       <c r="J62" s="34">
         <f>D62*E62*F62*I62</f>
@@ -19321,29 +19294,29 @@
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="6" t="n"/>
-      <c r="B63" s="23" t="inlineStr">
-        <is>
-          <t>YAS uzun cephe kuşakları — 4 seviye x 2 cephe, boy 79,00 m</t>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>Bağ kirişi boyuna donatısı ø14 — hat başına 3 alt + 3 üst = 6 adet, 4 hat, hat boyu 78.55 m (blok başına)</t>
         </is>
       </c>
       <c r="C63" s="6" t="n"/>
       <c r="D63" s="28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E63" s="28" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F63" s="29" t="n">
-        <v>79</v>
+        <v>78.55</v>
       </c>
       <c r="G63" s="6" t="n"/>
-      <c r="H63" s="36" t="inlineStr">
-        <is>
-          <t>RHS 100x50x3</t>
+      <c r="H63" s="32" t="inlineStr">
+        <is>
+          <t>ø14 nervürlü</t>
         </is>
       </c>
       <c r="I63" s="33" t="n">
-        <v>0.00672</v>
+        <v>0.00121</v>
       </c>
       <c r="J63" s="34">
         <f>D63*E63*F63*I63</f>
@@ -19351,107 +19324,90 @@
       </c>
       <c r="K63" s="6" t="n"/>
     </row>
-    <row r="64" ht="20" customHeight="1">
+    <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="n"/>
-      <c r="B64" s="23" t="inlineStr">
-        <is>
-          <t>YAS alınlık kuşakları — 4 seviye x 2 alınlık, boy 13,55 m</t>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>Bindirme, filiz ve gönye payı — betonarme proje METRAJ tablosundaki blok başına 7.287,50 kg toplamını tamamlayan fark</t>
         </is>
       </c>
       <c r="C64" s="6" t="n"/>
       <c r="D64" s="28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E64" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="29" t="n">
-        <v>13.55</v>
-      </c>
+      <c r="F64" s="6" t="n"/>
       <c r="G64" s="6" t="n"/>
-      <c r="H64" s="36" t="inlineStr">
-        <is>
-          <t>RHS 100x50x3</t>
+      <c r="H64" s="32" t="inlineStr">
+        <is>
+          <t>ø14-28 nervürlü</t>
         </is>
       </c>
       <c r="I64" s="33" t="n">
-        <v>0.00672</v>
+        <v>0.510518</v>
       </c>
       <c r="J64" s="34">
-        <f>D64*E64*F64*I64</f>
+        <f>D64*E64*I64</f>
         <v/>
       </c>
       <c r="K64" s="6" t="n"/>
     </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="6" t="n"/>
-      <c r="B65" s="23" t="inlineStr">
-        <is>
-          <t>KS iç kuşaklar — 21 çerçeve x 2 adet, orta açıklık 6,00 m</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="28" t="n">
-        <v>21</v>
-      </c>
-      <c r="E65" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F65" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="36" t="inlineStr">
-        <is>
-          <t>RHS 100x50x3</t>
-        </is>
-      </c>
-      <c r="I65" s="33" t="n">
-        <v>0.00672</v>
-      </c>
-      <c r="J65" s="34">
-        <f>D65*E65*F65*I65</f>
-        <v/>
-      </c>
-      <c r="K65" s="6" t="n"/>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="6" t="n"/>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>CCPR ve YCPR çatı ve cephe çaprazları — toplam 270,00 m</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="29" t="n">
-        <v>270</v>
-      </c>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="36" t="inlineStr">
-        <is>
-          <t>SHS 100x100x4</t>
-        </is>
-      </c>
-      <c r="I66" s="33" t="n">
-        <v>0.01195</v>
-      </c>
-      <c r="J66" s="34">
-        <f>D66*E66*F66*I66</f>
-        <v/>
-      </c>
-      <c r="K66" s="6" t="n"/>
-    </row>
-    <row r="67" ht="20" customHeight="1">
+    <row r="65">
+      <c r="A65" s="22" t="n"/>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>KB/M23 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="F65" s="22" t="n"/>
+      <c r="G65" s="22" t="n"/>
+      <c r="H65" s="22" t="n"/>
+      <c r="I65" s="22" t="n"/>
+      <c r="J65" s="22" t="n"/>
+      <c r="K65" s="35">
+        <f>SUM(J62:J64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1002</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>[M27]  Nervürlü çelik hasırın yerine konulması</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="22" t="n"/>
+      <c r="F66" s="22" t="n"/>
+      <c r="G66" s="22" t="n"/>
+      <c r="H66" s="22" t="n"/>
+      <c r="I66" s="22" t="n"/>
+      <c r="J66" s="22" t="n"/>
+      <c r="K66" s="22" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="n"/>
-      <c r="B67" s="31" t="inlineStr">
-        <is>
-          <t>Gusse, alın levhası, taban plakası ve bulonlar — profil ağırlığının %10'u</t>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>Kümes zemin döşemesi 78.00 x 13,90 (servis bölümü hariç); Q188 hasır = 3,05 kg/m², %10 bindirme payı ile 3,355 kg/m² (blok başına)</t>
         </is>
       </c>
       <c r="C67" s="6" t="n"/>
@@ -19461,18 +19417,22 @@
       <c r="E67" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="6" t="n"/>
-      <c r="H67" s="32" t="inlineStr">
-        <is>
-          <t>Levha ve bulon</t>
+      <c r="F67" s="29" t="n">
+        <v>78</v>
+      </c>
+      <c r="G67" s="29" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H67" s="36" t="inlineStr">
+        <is>
+          <t>Q188 çelik hasır</t>
         </is>
       </c>
       <c r="I67" s="33" t="n">
-        <v>4.00439689</v>
+        <v>0.003355</v>
       </c>
       <c r="J67" s="34">
-        <f>D67*E67*I67</f>
+        <f>D67*E67*F67*G67*I67</f>
         <v/>
       </c>
       <c r="K67" s="6" t="n"/>
@@ -19481,7 +19441,7 @@
       <c r="A68" s="22" t="n"/>
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>KB/M31 GENEL TOPLAM</t>
+          <t>KB/M27 GENEL TOPLAM</t>
         </is>
       </c>
       <c r="C68" s="26" t="inlineStr">
@@ -19497,24 +19457,24 @@
       <c r="I68" s="22" t="n"/>
       <c r="J68" s="22" t="n"/>
       <c r="K68" s="35">
-        <f>SUM(J58:J67)</f>
+        <f>SUM(J67:J67)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="20" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>[M34]  Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>[M31]  Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti</t>
         </is>
       </c>
       <c r="C69" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="D69" s="22" t="n"/>
@@ -19526,31 +19486,31 @@
       <c r="J69" s="22" t="n"/>
       <c r="K69" s="22" t="n"/>
     </row>
-    <row r="70" ht="12" customHeight="1">
+    <row r="70" ht="20" customHeight="1">
       <c r="A70" s="6" t="n"/>
       <c r="B70" s="23" t="inlineStr">
         <is>
-          <t>Mahya kapama profili — blok başına, boy 79,80 m</t>
+          <t>KLN dış kolonlar — 21 çerçeve x 2 adet, boy 2,84 m (kolon üstü kotu +2,84)</t>
         </is>
       </c>
       <c r="C70" s="6" t="n"/>
       <c r="D70" s="28" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E70" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="29" t="n">
-        <v>79.8</v>
+        <v>2.84</v>
       </c>
       <c r="G70" s="6" t="n"/>
       <c r="H70" s="36" t="inlineStr">
         <is>
-          <t>50x5 lama</t>
+          <t>SHS 150x150x6</t>
         </is>
       </c>
       <c r="I70" s="33" t="n">
-        <v>2.5</v>
+        <v>0.02689</v>
       </c>
       <c r="J70" s="34">
         <f>D70*E70*F70*I70</f>
@@ -19562,27 +19522,27 @@
       <c r="A71" s="6" t="n"/>
       <c r="B71" s="23" t="inlineStr">
         <is>
-          <t>Saçak kapama profili — blok başına 2 kenar, 2 kenar; boy 79,80 m</t>
+          <t>KLN iç kolonlar — 21 çerçeve x 2 adet, ortalama boy 3,68 m (eğik kiriş altında)</t>
         </is>
       </c>
       <c r="C71" s="6" t="n"/>
       <c r="D71" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="E71" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="E71" s="28" t="n">
-        <v>1</v>
-      </c>
       <c r="F71" s="29" t="n">
-        <v>79.8</v>
+        <v>3.6755</v>
       </c>
       <c r="G71" s="6" t="n"/>
       <c r="H71" s="36" t="inlineStr">
         <is>
-          <t>50x5 lama</t>
+          <t>SHS 150x150x6</t>
         </is>
       </c>
       <c r="I71" s="33" t="n">
-        <v>2.5</v>
+        <v>0.02689</v>
       </c>
       <c r="J71" s="34">
         <f>D71*E71*F71*I71</f>
@@ -19594,27 +19554,27 @@
       <c r="A72" s="6" t="n"/>
       <c r="B72" s="23" t="inlineStr">
         <is>
-          <t>Alınlık eğim kapamaları — alınlık başına 2 eğim, 2 alınlık, 2 blok = 8; eğik boy 7,55 m</t>
+          <t>AKR ana kirişler — 21 çerçeve x 2 adet, eğik boy 6,94 m (yarım açıklık 6,775 / kot farkı 1,50)</t>
         </is>
       </c>
       <c r="C72" s="6" t="n"/>
       <c r="D72" s="28" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E72" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="29" t="n">
-        <v>7.55</v>
+        <v>6.939</v>
       </c>
       <c r="G72" s="6" t="n"/>
       <c r="H72" s="36" t="inlineStr">
         <is>
-          <t>50x5 lama</t>
+          <t>SHS 150x150x6</t>
         </is>
       </c>
       <c r="I72" s="33" t="n">
-        <v>2.5</v>
+        <v>0.02689</v>
       </c>
       <c r="J72" s="34">
         <f>D72*E72*F72*I72</f>
@@ -19622,125 +19582,171 @@
       </c>
       <c r="K72" s="6" t="n"/>
     </row>
-    <row r="73">
-      <c r="A73" s="22" t="n"/>
-      <c r="B73" s="25" t="inlineStr">
-        <is>
-          <t>KB/M34 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C73" s="26" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D73" s="22" t="n"/>
-      <c r="E73" s="22" t="n"/>
-      <c r="F73" s="22" t="n"/>
-      <c r="G73" s="22" t="n"/>
-      <c r="H73" s="22" t="n"/>
-      <c r="I73" s="22" t="n"/>
-      <c r="J73" s="22" t="n"/>
-      <c r="K73" s="35">
-        <f>SUM(J70:J72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>SKR boyuna kirişler — 2 saçak + 1 mahya hattı, boy 79,00 m</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="29" t="n">
+        <v>79</v>
+      </c>
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>SHS 150x150x6</t>
+        </is>
+      </c>
+      <c r="I73" s="33" t="n">
+        <v>0.02689</v>
+      </c>
+      <c r="J73" s="34">
+        <f>D73*E73*F73*I73</f>
+        <v/>
+      </c>
+      <c r="K73" s="6" t="n"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="23" t="inlineStr">
+        <is>
+          <t>CAS çatı aşıkları — kesitte sayılan 16 hat, boy 79,80 m (saçak payı dâhil)</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="E74" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="29" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>RHS 100x50x3</t>
+        </is>
+      </c>
+      <c r="I74" s="33" t="n">
+        <v>0.00672</v>
+      </c>
+      <c r="J74" s="34">
+        <f>D74*E74*F74*I74</f>
+        <v/>
+      </c>
+      <c r="K74" s="6" t="n"/>
+    </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: GÜBRE ÇUKURU</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Benzer</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>Demir çapı veya profil tipi</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Birim Ağırlık</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Ağırlık</t>
-        </is>
-      </c>
-      <c r="K76" s="7" t="inlineStr">
-        <is>
-          <t>Genel Toplam</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>[M24]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="C77" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D77" s="22" t="n"/>
-      <c r="E77" s="22" t="n"/>
-      <c r="F77" s="22" t="n"/>
-      <c r="G77" s="22" t="n"/>
-      <c r="H77" s="22" t="n"/>
-      <c r="I77" s="22" t="n"/>
-      <c r="J77" s="22" t="n"/>
-      <c r="K77" s="22" t="n"/>
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="23" t="inlineStr">
+        <is>
+          <t>YAS uzun cephe kuşakları — 4 seviye x 2 cephe, boy 79,00 m</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="29" t="n">
+        <v>79</v>
+      </c>
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="36" t="inlineStr">
+        <is>
+          <t>RHS 100x50x3</t>
+        </is>
+      </c>
+      <c r="I75" s="33" t="n">
+        <v>0.00672</v>
+      </c>
+      <c r="J75" s="34">
+        <f>D75*E75*F75*I75</f>
+        <v/>
+      </c>
+      <c r="K75" s="6" t="n"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="23" t="inlineStr">
+        <is>
+          <t>YAS alınlık kuşakları — 4 seviye x 2 alınlık, boy 13,55 m</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E76" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="29" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="36" t="inlineStr">
+        <is>
+          <t>RHS 100x50x3</t>
+        </is>
+      </c>
+      <c r="I76" s="33" t="n">
+        <v>0.00672</v>
+      </c>
+      <c r="J76" s="34">
+        <f>D76*E76*F76*I76</f>
+        <v/>
+      </c>
+      <c r="K76" s="6" t="n"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="n"/>
+      <c r="B77" s="23" t="inlineStr">
+        <is>
+          <t>KS iç kuşaklar — 21 çerçeve x 2 adet, orta açıklık 6,00 m</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="E77" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" s="6" t="n"/>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>RHS 100x50x3</t>
+        </is>
+      </c>
+      <c r="I77" s="33" t="n">
+        <v>0.00672</v>
+      </c>
+      <c r="J77" s="34">
+        <f>D77*E77*F77*I77</f>
+        <v/>
+      </c>
+      <c r="K77" s="6" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="6" t="n"/>
       <c r="B78" s="23" t="inlineStr">
         <is>
-          <t>Radye temel 11.50 x 10.00 x 0,40 m; birim donatı oranı 110 kg/m³</t>
+          <t>CCPR ve YCPR çatı ve cephe çaprazları — toplam 270,00 m</t>
         </is>
       </c>
       <c r="C78" s="6" t="n"/>
@@ -19751,30 +19757,28 @@
         <v>1</v>
       </c>
       <c r="F78" s="29" t="n">
-        <v>115</v>
-      </c>
-      <c r="G78" s="29" t="n">
-        <v>0.4</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="G78" s="6" t="n"/>
       <c r="H78" s="36" t="inlineStr">
         <is>
-          <t>ø8-12 nervürlü</t>
+          <t>SHS 100x100x4</t>
         </is>
       </c>
       <c r="I78" s="33" t="n">
-        <v>0.11</v>
+        <v>0.01195</v>
       </c>
       <c r="J78" s="34">
-        <f>D78*E78*F78*G78*I78</f>
+        <f>D78*E78*F78*I78</f>
         <v/>
       </c>
       <c r="K78" s="6" t="n"/>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="6" t="n"/>
-      <c r="B79" s="23" t="inlineStr">
-        <is>
-          <t>Üst döşeme donatısı — proje METRAJ tablosu 577,60 kg, alan oranı (1.000000) ile ölçeklenmiş</t>
+      <c r="B79" s="31" t="inlineStr">
+        <is>
+          <t>Gusse, alın levhası, taban plakası ve bulonlar — profil ağırlığının %10'u</t>
         </is>
       </c>
       <c r="C79" s="6" t="n"/>
@@ -19786,13 +19790,13 @@
       </c>
       <c r="F79" s="6" t="n"/>
       <c r="G79" s="6" t="n"/>
-      <c r="H79" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
+      <c r="H79" s="32" t="inlineStr">
+        <is>
+          <t>Levha ve bulon</t>
         </is>
       </c>
       <c r="I79" s="33" t="n">
-        <v>0.5776</v>
+        <v>4.00439689</v>
       </c>
       <c r="J79" s="34">
         <f>D79*E79*I79</f>
@@ -19800,46 +19804,44 @@
       </c>
       <c r="K79" s="6" t="n"/>
     </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="6" t="n"/>
-      <c r="B80" s="23" t="inlineStr">
-        <is>
-          <t>Perde ve kolon donatısı — proje METRAJ tablosu 1.961,69 kg, alan oranı ile ölçeklenmiş</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="n"/>
-      <c r="D80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="6" t="n"/>
-      <c r="G80" s="6" t="n"/>
-      <c r="H80" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I80" s="33" t="n">
-        <v>1.96169</v>
-      </c>
-      <c r="J80" s="34">
-        <f>D80*E80*I80</f>
-        <v/>
-      </c>
-      <c r="K80" s="6" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="22" t="n"/>
-      <c r="B81" s="25" t="inlineStr">
-        <is>
-          <t>GC/M24 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C81" s="26" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="22" t="n"/>
+      <c r="B80" s="25" t="inlineStr">
+        <is>
+          <t>KB/M31 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C80" s="26" t="inlineStr">
         <is>
           <t>ton</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="n"/>
+      <c r="E80" s="22" t="n"/>
+      <c r="F80" s="22" t="n"/>
+      <c r="G80" s="22" t="n"/>
+      <c r="H80" s="22" t="n"/>
+      <c r="I80" s="22" t="n"/>
+      <c r="J80" s="22" t="n"/>
+      <c r="K80" s="35">
+        <f>SUM(J70:J79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>15.550.1202</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>[M34]  Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="D81" s="22" t="n"/>
@@ -19849,169 +19851,195 @@
       <c r="H81" s="22" t="n"/>
       <c r="I81" s="22" t="n"/>
       <c r="J81" s="22" t="n"/>
-      <c r="K81" s="35">
-        <f>SUM(J78:J80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1004</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>[M25]  Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="C82" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D82" s="22" t="n"/>
-      <c r="E82" s="22" t="n"/>
-      <c r="F82" s="22" t="n"/>
-      <c r="G82" s="22" t="n"/>
-      <c r="H82" s="22" t="n"/>
-      <c r="I82" s="22" t="n"/>
-      <c r="J82" s="22" t="n"/>
-      <c r="K82" s="22" t="n"/>
+      <c r="K81" s="22" t="n"/>
+    </row>
+    <row r="82" ht="12" customHeight="1">
+      <c r="A82" s="6" t="n"/>
+      <c r="B82" s="23" t="inlineStr">
+        <is>
+          <t>Mahya kapama profili — blok başına, boy 79,80 m</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="29" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="G82" s="6" t="n"/>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>50x5 lama</t>
+        </is>
+      </c>
+      <c r="I82" s="33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J82" s="34">
+        <f>D82*E82*F82*I82</f>
+        <v/>
+      </c>
+      <c r="K82" s="6" t="n"/>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="6" t="n"/>
       <c r="B83" s="23" t="inlineStr">
         <is>
-          <t>Gübre çukuru kalın donatı — proje METRAJ tablosu 564,10 kg, alan oranı (1.000000) ile ölçeklenmiş</t>
+          <t>Saçak kapama profili — blok başına 2 kenar, 2 kenar; boy 79,80 m</t>
         </is>
       </c>
       <c r="C83" s="6" t="n"/>
       <c r="D83" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="6" t="n"/>
+      <c r="F83" s="29" t="n">
+        <v>79.8</v>
+      </c>
       <c r="G83" s="6" t="n"/>
       <c r="H83" s="36" t="inlineStr">
         <is>
-          <t>ø14-28 nervürlü</t>
+          <t>50x5 lama</t>
         </is>
       </c>
       <c r="I83" s="33" t="n">
-        <v>0.5641</v>
+        <v>2.5</v>
       </c>
       <c r="J83" s="34">
-        <f>D83*E83*I83</f>
+        <f>D83*E83*F83*I83</f>
         <v/>
       </c>
       <c r="K83" s="6" t="n"/>
     </row>
-    <row r="84">
-      <c r="A84" s="22" t="n"/>
-      <c r="B84" s="25" t="inlineStr">
-        <is>
-          <t>GC/M25 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C84" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D84" s="22" t="n"/>
-      <c r="E84" s="22" t="n"/>
-      <c r="F84" s="22" t="n"/>
-      <c r="G84" s="22" t="n"/>
-      <c r="H84" s="22" t="n"/>
-      <c r="I84" s="22" t="n"/>
-      <c r="J84" s="22" t="n"/>
-      <c r="K84" s="35">
-        <f>SUM(J83:J83)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85"/>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: ÖLÜ ATMA ÇUKURU</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="28" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Benzer</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>Demir çapı veya profil tipi</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Birim Ağırlık</t>
-        </is>
-      </c>
-      <c r="J87" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Ağırlık</t>
-        </is>
-      </c>
-      <c r="K87" s="7" t="inlineStr">
-        <is>
-          <t>Genel Toplam</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="C88" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="6" t="n"/>
+      <c r="B84" s="23" t="inlineStr">
+        <is>
+          <t>Alınlık eğim kapamaları — alınlık başına 2 eğim, 2 alınlık, 2 blok = 8; eğik boy 7,55 m</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="29" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="36" t="inlineStr">
+        <is>
+          <t>50x5 lama</t>
+        </is>
+      </c>
+      <c r="I84" s="33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J84" s="34">
+        <f>D84*E84*F84*I84</f>
+        <v/>
+      </c>
+      <c r="K84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="n"/>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>KB/M34 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C85" s="26" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="n"/>
+      <c r="E85" s="22" t="n"/>
+      <c r="F85" s="22" t="n"/>
+      <c r="G85" s="22" t="n"/>
+      <c r="H85" s="22" t="n"/>
+      <c r="I85" s="22" t="n"/>
+      <c r="J85" s="22" t="n"/>
+      <c r="K85" s="35">
+        <f>SUM(J82:J84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0115</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>[M35]  Galvanizli düz sacdan yağmur oluğu (dere) yapılması ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C86" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="n"/>
+      <c r="E86" s="22" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="22" t="n"/>
+      <c r="H86" s="22" t="n"/>
+      <c r="I86" s="22" t="n"/>
+      <c r="J86" s="22" t="n"/>
+      <c r="K86" s="22" t="n"/>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" s="6" t="n"/>
+      <c r="B87" s="23" t="inlineStr">
+        <is>
+          <t>Uzun cepheler boyunca dere — blok başına 2 kenar, saçaklı boy 79,80 m; gelişmiş genişlik 0,50 m, 0,50 mm galvanizli düz sac (0,50 x 0,0005 x 7.850 = 1,96 kg/m), birleşim ve kenet payı ile 2,00 kg/m</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="29" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="G87" s="6" t="n"/>
+      <c r="H87" s="36" t="inlineStr">
+        <is>
+          <t>0,50 mm galvanizli düz sac</t>
+        </is>
+      </c>
+      <c r="I87" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" s="34">
+        <f>D87*E87*F87*I87</f>
+        <v/>
+      </c>
+      <c r="K87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="n"/>
+      <c r="B88" s="25" t="inlineStr">
+        <is>
+          <t>KB/M35 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C88" s="26" t="inlineStr">
+        <is>
+          <t>kg</t>
         </is>
       </c>
       <c r="D88" s="22" t="n"/>
@@ -20021,68 +20049,64 @@
       <c r="H88" s="22" t="n"/>
       <c r="I88" s="22" t="n"/>
       <c r="J88" s="22" t="n"/>
-      <c r="K88" s="22" t="n"/>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="6" t="n"/>
-      <c r="B89" s="23" t="inlineStr">
-        <is>
-          <t>Radye ve üst döşeme — proje metrajı 335,40 + 46,70 = 382,10 kg</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I89" s="33" t="n">
-        <v>0.3821</v>
-      </c>
-      <c r="J89" s="34">
-        <f>D89*E89*I89</f>
-        <v/>
-      </c>
-      <c r="K89" s="6" t="n"/>
-    </row>
-    <row r="90" ht="12" customHeight="1">
+      <c r="K88" s="35">
+        <f>SUM(J87:J87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>15.550.1002</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>[M43F]  1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="n"/>
+      <c r="E89" s="22" t="n"/>
+      <c r="F89" s="22" t="n"/>
+      <c r="G89" s="22" t="n"/>
+      <c r="H89" s="22" t="n"/>
+      <c r="I89" s="22" t="n"/>
+      <c r="J89" s="22" t="n"/>
+      <c r="K89" s="22" t="n"/>
+    </row>
+    <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="n"/>
       <c r="B90" s="23" t="inlineStr">
         <is>
-          <t>Perdeler 17,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
+          <t>Servis bölümü iç kapıları — blok başına 3 adet; kasa çevresi 2x2,10+0,90 = 5,10 m, 1,50 mm sacdan bükme kasa 3,55 kg/m</t>
         </is>
       </c>
       <c r="C90" s="6" t="n"/>
       <c r="D90" s="28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F90" s="29" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="G90" s="29" t="n">
-        <v>3</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="G90" s="6" t="n"/>
       <c r="H90" s="36" t="inlineStr">
         <is>
-          <t>ø8-12 nervürlü</t>
+          <t>1,50 mm bükme sac kasa</t>
         </is>
       </c>
       <c r="I90" s="33" t="n">
-        <v>0.1</v>
+        <v>3.55</v>
       </c>
       <c r="J90" s="34">
-        <f>D90*E90*F90*G90*I90</f>
+        <f>D90*E90*F90*I90</f>
         <v/>
       </c>
       <c r="K90" s="6" t="n"/>
@@ -20091,12 +20115,12 @@
       <c r="A91" s="22" t="n"/>
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>OC/M26 GENEL TOPLAM</t>
+          <t>KB/M43F GENEL TOPLAM</t>
         </is>
       </c>
       <c r="C91" s="26" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D91" s="22" t="n"/>
@@ -20107,89 +20131,105 @@
       <c r="I91" s="22" t="n"/>
       <c r="J91" s="22" t="n"/>
       <c r="K91" s="35">
-        <f>SUM(J89:J90)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92"/>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: YEM SILOSU BETONARME KAIDELERI</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="28" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Benzer</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>Demir çapı veya profil tipi</t>
-        </is>
-      </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>Birim Ağırlık</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Ağırlık</t>
-        </is>
-      </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>Genel Toplam</t>
-        </is>
+        <f>SUM(J90:J90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>[M87]  Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="n"/>
+      <c r="E92" s="22" t="n"/>
+      <c r="F92" s="22" t="n"/>
+      <c r="G92" s="22" t="n"/>
+      <c r="H92" s="22" t="n"/>
+      <c r="I92" s="22" t="n"/>
+      <c r="J92" s="22" t="n"/>
+      <c r="K92" s="22" t="n"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="23" t="inlineStr">
+        <is>
+          <t>Kümes içi ana kablo güzergâhı — blok başına 200 m; 200x60x1,0 mm perfore tava açınımı 0,320 m x 7,85 kg/m² = 2,510 kg/m</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="G93" s="6" t="n"/>
+      <c r="H93" s="36" t="inlineStr">
+        <is>
+          <t>200x60x1,0 galvanizli perfore tava</t>
+        </is>
+      </c>
+      <c r="I93" s="33" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="J93" s="34">
+        <f>D93*E93*F93*I93</f>
+        <v/>
+      </c>
+      <c r="K93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="n"/>
+      <c r="B94" s="25" t="inlineStr">
+        <is>
+          <t>KB/M87 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D94" s="22" t="n"/>
+      <c r="E94" s="22" t="n"/>
+      <c r="F94" s="22" t="n"/>
+      <c r="G94" s="22" t="n"/>
+      <c r="H94" s="22" t="n"/>
+      <c r="I94" s="22" t="n"/>
+      <c r="J94" s="22" t="n"/>
+      <c r="K94" s="35">
+        <f>SUM(J93:J93)</f>
+        <v/>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>[M89]  Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun 1,0 mm sıcak daldırma galvanizli sac</t>
         </is>
       </c>
       <c r="C95" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D95" s="22" t="n"/>
@@ -20201,36 +20241,34 @@
       <c r="J95" s="22" t="n"/>
       <c r="K95" s="22" t="n"/>
     </row>
-    <row r="96" ht="12" customHeight="1">
+    <row r="96" ht="20" customHeight="1">
       <c r="A96" s="6" t="n"/>
       <c r="B96" s="23" t="inlineStr">
         <is>
-          <t>Kaideler 2,90 x 2,90 x 0,50 m³, 2 adet; 90 kg/m³</t>
+          <t>Tava güzergâhının tamamı — blok başına 200 m; kapak sacı açınımı 0,230 m x 7,85 kg/m² = 1,806 kg/m</t>
         </is>
       </c>
       <c r="C96" s="6" t="n"/>
       <c r="D96" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F96" s="29" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="G96" s="29" t="n">
-        <v>0.5</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="G96" s="6" t="n"/>
       <c r="H96" s="36" t="inlineStr">
         <is>
-          <t>ø8-12 nervürlü</t>
+          <t>1,0 mm galvanizli kapak sacı</t>
         </is>
       </c>
       <c r="I96" s="33" t="n">
-        <v>0.09</v>
+        <v>1.806</v>
       </c>
       <c r="J96" s="34">
-        <f>D96*E96*F96*G96*I96</f>
+        <f>D96*E96*F96*I96</f>
         <v/>
       </c>
       <c r="K96" s="6" t="n"/>
@@ -20239,12 +20277,12 @@
       <c r="A97" s="22" t="n"/>
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>SL/M26 GENEL TOPLAM</t>
+          <t>KB/M89 GENEL TOPLAM</t>
         </is>
       </c>
       <c r="C97" s="26" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D97" s="22" t="n"/>
@@ -20263,7 +20301,7 @@
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="18" t="inlineStr">
         <is>
-          <t>Yapı/Bina Adı: SU DEPOSU</t>
+          <t>Yapı/Bina Adı: GÜBRE ÇUKURU</t>
         </is>
       </c>
     </row>
@@ -20332,7 +20370,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>[M24]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="C101" s="19" t="inlineStr">
@@ -20353,7 +20391,7 @@
       <c r="A102" s="6" t="n"/>
       <c r="B102" s="23" t="inlineStr">
         <is>
-          <t>Radye ve üst döşeme — proje metrajı 223,70 + 32,90 = 256,60 kg</t>
+          <t>Radye temel 11.50 x 10.00 x 0,40 m; birim donatı oranı 110 kg/m³</t>
         </is>
       </c>
       <c r="C102" s="6" t="n"/>
@@ -20363,27 +20401,31 @@
       <c r="E102" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="6" t="n"/>
-      <c r="G102" s="6" t="n"/>
+      <c r="F102" s="29" t="n">
+        <v>115</v>
+      </c>
+      <c r="G102" s="29" t="n">
+        <v>0.4</v>
+      </c>
       <c r="H102" s="36" t="inlineStr">
         <is>
           <t>ø8-12 nervürlü</t>
         </is>
       </c>
       <c r="I102" s="33" t="n">
-        <v>0.2566</v>
+        <v>0.11</v>
       </c>
       <c r="J102" s="34">
-        <f>D102*E102*I102</f>
+        <f>D102*E102*F102*G102*I102</f>
         <v/>
       </c>
       <c r="K102" s="6" t="n"/>
     </row>
-    <row r="103" ht="12" customHeight="1">
+    <row r="103" ht="20" customHeight="1">
       <c r="A103" s="6" t="n"/>
       <c r="B103" s="23" t="inlineStr">
         <is>
-          <t>Perdeler 13,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
+          <t>Üst döşeme donatısı — proje METRAJ tablosu 577,60 kg, alan oranı (1.000000) ile ölçeklenmiş</t>
         </is>
       </c>
       <c r="C103" s="6" t="n"/>
@@ -20393,120 +20435,1093 @@
       <c r="E103" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F103" s="29" t="n">
+      <c r="F103" s="6" t="n"/>
+      <c r="G103" s="6" t="n"/>
+      <c r="H103" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I103" s="33" t="n">
+        <v>0.5776</v>
+      </c>
+      <c r="J103" s="34">
+        <f>D103*E103*I103</f>
+        <v/>
+      </c>
+      <c r="K103" s="6" t="n"/>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="23" t="inlineStr">
+        <is>
+          <t>Perde ve kolon donatısı — proje METRAJ tablosu 1.961,69 kg, alan oranı ile ölçeklenmiş</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="n"/>
+      <c r="G104" s="6" t="n"/>
+      <c r="H104" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I104" s="33" t="n">
+        <v>1.96169</v>
+      </c>
+      <c r="J104" s="34">
+        <f>D104*E104*I104</f>
+        <v/>
+      </c>
+      <c r="K104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="22" t="n"/>
+      <c r="B105" s="25" t="inlineStr">
+        <is>
+          <t>GC/M24 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C105" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="n"/>
+      <c r="E105" s="22" t="n"/>
+      <c r="F105" s="22" t="n"/>
+      <c r="G105" s="22" t="n"/>
+      <c r="H105" s="22" t="n"/>
+      <c r="I105" s="22" t="n"/>
+      <c r="J105" s="22" t="n"/>
+      <c r="K105" s="35">
+        <f>SUM(J102:J104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>[M25]  Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C106" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="n"/>
+      <c r="E106" s="22" t="n"/>
+      <c r="F106" s="22" t="n"/>
+      <c r="G106" s="22" t="n"/>
+      <c r="H106" s="22" t="n"/>
+      <c r="I106" s="22" t="n"/>
+      <c r="J106" s="22" t="n"/>
+      <c r="K106" s="22" t="n"/>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="n"/>
+      <c r="B107" s="23" t="inlineStr">
+        <is>
+          <t>Gübre çukuru kalın donatı — proje METRAJ tablosu 564,10 kg, alan oranı (1.000000) ile ölçeklenmiş</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="6" t="n"/>
+      <c r="G107" s="6" t="n"/>
+      <c r="H107" s="36" t="inlineStr">
+        <is>
+          <t>ø14-28 nervürlü</t>
+        </is>
+      </c>
+      <c r="I107" s="33" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="J107" s="34">
+        <f>D107*E107*I107</f>
+        <v/>
+      </c>
+      <c r="K107" s="6" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="22" t="n"/>
+      <c r="B108" s="25" t="inlineStr">
+        <is>
+          <t>GC/M25 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C108" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="n"/>
+      <c r="E108" s="22" t="n"/>
+      <c r="F108" s="22" t="n"/>
+      <c r="G108" s="22" t="n"/>
+      <c r="H108" s="22" t="n"/>
+      <c r="I108" s="22" t="n"/>
+      <c r="J108" s="22" t="n"/>
+      <c r="K108" s="35">
+        <f>SUM(J107:J107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: ÖLÜ ATMA ÇUKURU</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I111" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="n"/>
+      <c r="E112" s="22" t="n"/>
+      <c r="F112" s="22" t="n"/>
+      <c r="G112" s="22" t="n"/>
+      <c r="H112" s="22" t="n"/>
+      <c r="I112" s="22" t="n"/>
+      <c r="J112" s="22" t="n"/>
+      <c r="K112" s="22" t="n"/>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="n"/>
+      <c r="B113" s="23" t="inlineStr">
+        <is>
+          <t>Radye ve üst döşeme — proje metrajı 335,40 + 46,70 = 382,10 kg</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="6" t="n"/>
+      <c r="G113" s="6" t="n"/>
+      <c r="H113" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I113" s="33" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="J113" s="34">
+        <f>D113*E113*I113</f>
+        <v/>
+      </c>
+      <c r="K113" s="6" t="n"/>
+    </row>
+    <row r="114" ht="12" customHeight="1">
+      <c r="A114" s="6" t="n"/>
+      <c r="B114" s="23" t="inlineStr">
+        <is>
+          <t>Perdeler 17,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="29" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G114" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I114" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J114" s="34">
+        <f>D114*E114*F114*G114*I114</f>
+        <v/>
+      </c>
+      <c r="K114" s="6" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="22" t="n"/>
+      <c r="B115" s="25" t="inlineStr">
+        <is>
+          <t>OC/M26 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C115" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D115" s="22" t="n"/>
+      <c r="E115" s="22" t="n"/>
+      <c r="F115" s="22" t="n"/>
+      <c r="G115" s="22" t="n"/>
+      <c r="H115" s="22" t="n"/>
+      <c r="I115" s="22" t="n"/>
+      <c r="J115" s="22" t="n"/>
+      <c r="K115" s="35">
+        <f>SUM(J113:J114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116"/>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: YEM SILOSU BETONARME KAIDELERI</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I118" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J118" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="n"/>
+      <c r="E119" s="22" t="n"/>
+      <c r="F119" s="22" t="n"/>
+      <c r="G119" s="22" t="n"/>
+      <c r="H119" s="22" t="n"/>
+      <c r="I119" s="22" t="n"/>
+      <c r="J119" s="22" t="n"/>
+      <c r="K119" s="22" t="n"/>
+    </row>
+    <row r="120" ht="12" customHeight="1">
+      <c r="A120" s="6" t="n"/>
+      <c r="B120" s="23" t="inlineStr">
+        <is>
+          <t>Kaideler 2,90 x 2,90 x 0,50 m³, 2 adet; 90 kg/m³</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="29" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="G120" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H120" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I120" s="33" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J120" s="34">
+        <f>D120*E120*F120*G120*I120</f>
+        <v/>
+      </c>
+      <c r="K120" s="6" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="22" t="n"/>
+      <c r="B121" s="25" t="inlineStr">
+        <is>
+          <t>SL/M26 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C121" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="n"/>
+      <c r="E121" s="22" t="n"/>
+      <c r="F121" s="22" t="n"/>
+      <c r="G121" s="22" t="n"/>
+      <c r="H121" s="22" t="n"/>
+      <c r="I121" s="22" t="n"/>
+      <c r="J121" s="22" t="n"/>
+      <c r="K121" s="35">
+        <f>SUM(J120:J120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: SU DEPOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I124" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="n"/>
+      <c r="E125" s="22" t="n"/>
+      <c r="F125" s="22" t="n"/>
+      <c r="G125" s="22" t="n"/>
+      <c r="H125" s="22" t="n"/>
+      <c r="I125" s="22" t="n"/>
+      <c r="J125" s="22" t="n"/>
+      <c r="K125" s="22" t="n"/>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="6" t="n"/>
+      <c r="B126" s="23" t="inlineStr">
+        <is>
+          <t>Radye ve üst döşeme — proje metrajı 223,70 + 32,90 = 256,60 kg</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="n"/>
+      <c r="D126" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="n"/>
+      <c r="G126" s="6" t="n"/>
+      <c r="H126" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I126" s="33" t="n">
+        <v>0.2566</v>
+      </c>
+      <c r="J126" s="34">
+        <f>D126*E126*I126</f>
+        <v/>
+      </c>
+      <c r="K126" s="6" t="n"/>
+    </row>
+    <row r="127" ht="12" customHeight="1">
+      <c r="A127" s="6" t="n"/>
+      <c r="B127" s="23" t="inlineStr">
+        <is>
+          <t>Perdeler 13,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="29" t="n">
         <v>3.25</v>
       </c>
-      <c r="G103" s="29" t="n">
+      <c r="G127" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="H103" s="36" t="inlineStr">
+      <c r="H127" s="36" t="inlineStr">
         <is>
           <t>ø8-12 nervürlü</t>
         </is>
       </c>
-      <c r="I103" s="33" t="n">
+      <c r="I127" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="J103" s="34">
-        <f>D103*E103*F103*G103*I103</f>
-        <v/>
-      </c>
-      <c r="K103" s="6" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="22" t="n"/>
-      <c r="B104" s="25" t="inlineStr">
+      <c r="J127" s="34">
+        <f>D127*E127*F127*G127*I127</f>
+        <v/>
+      </c>
+      <c r="K127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="22" t="n"/>
+      <c r="B128" s="25" t="inlineStr">
         <is>
           <t>SD/M26 GENEL TOPLAM</t>
         </is>
       </c>
-      <c r="C104" s="26" t="inlineStr">
+      <c r="C128" s="26" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="D104" s="22" t="n"/>
-      <c r="E104" s="22" t="n"/>
-      <c r="F104" s="22" t="n"/>
-      <c r="G104" s="22" t="n"/>
-      <c r="H104" s="22" t="n"/>
-      <c r="I104" s="22" t="n"/>
-      <c r="J104" s="22" t="n"/>
-      <c r="K104" s="35">
-        <f>SUM(J102:J103)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105"/>
-    <row r="106">
-      <c r="A106" s="16" t="inlineStr">
+      <c r="D128" s="22" t="n"/>
+      <c r="E128" s="22" t="n"/>
+      <c r="F128" s="22" t="n"/>
+      <c r="G128" s="22" t="n"/>
+      <c r="H128" s="22" t="n"/>
+      <c r="I128" s="22" t="n"/>
+      <c r="J128" s="22" t="n"/>
+      <c r="K128" s="35">
+        <f>SUM(J126:J127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129"/>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: YAĞMUR SUYU DEPOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C132" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="n"/>
+      <c r="E132" s="22" t="n"/>
+      <c r="F132" s="22" t="n"/>
+      <c r="G132" s="22" t="n"/>
+      <c r="H132" s="22" t="n"/>
+      <c r="I132" s="22" t="n"/>
+      <c r="J132" s="22" t="n"/>
+      <c r="K132" s="22" t="n"/>
+    </row>
+    <row r="133" ht="12" customHeight="1">
+      <c r="A133" s="6" t="n"/>
+      <c r="B133" s="23" t="inlineStr">
+        <is>
+          <t>Radye 3,00 x 3,00 x 0,30 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G133" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H133" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I133" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J133" s="34">
+        <f>D133*E133*F133*G133*I133</f>
+        <v/>
+      </c>
+      <c r="K133" s="6" t="n"/>
+    </row>
+    <row r="134" ht="12" customHeight="1">
+      <c r="A134" s="6" t="n"/>
+      <c r="B134" s="23" t="inlineStr">
+        <is>
+          <t>Perdeler 11,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="n"/>
+      <c r="D134" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G134" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H134" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I134" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J134" s="34">
+        <f>D134*E134*F134*G134*I134</f>
+        <v/>
+      </c>
+      <c r="K134" s="6" t="n"/>
+    </row>
+    <row r="135" ht="12" customHeight="1">
+      <c r="A135" s="6" t="n"/>
+      <c r="B135" s="23" t="inlineStr">
+        <is>
+          <t>Üst döşeme 3,00 x 3,00 x 0,15 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="n"/>
+      <c r="D135" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G135" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H135" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I135" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J135" s="34">
+        <f>D135*E135*F135*G135*I135</f>
+        <v/>
+      </c>
+      <c r="K135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="22" t="n"/>
+      <c r="B136" s="25" t="inlineStr">
+        <is>
+          <t>YD/M26 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C136" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="n"/>
+      <c r="E136" s="22" t="n"/>
+      <c r="F136" s="22" t="n"/>
+      <c r="G136" s="22" t="n"/>
+      <c r="H136" s="22" t="n"/>
+      <c r="I136" s="22" t="n"/>
+      <c r="J136" s="22" t="n"/>
+      <c r="K136" s="35">
+        <f>SUM(J133:J135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137"/>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="28" customHeight="1">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I139" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>[M61C]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D140" s="22" t="n"/>
+      <c r="E140" s="22" t="n"/>
+      <c r="F140" s="22" t="n"/>
+      <c r="G140" s="22" t="n"/>
+      <c r="H140" s="22" t="n"/>
+      <c r="I140" s="22" t="n"/>
+      <c r="J140" s="22" t="n"/>
+      <c r="K140" s="22" t="n"/>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="6" t="n"/>
+      <c r="B141" s="23" t="inlineStr">
+        <is>
+          <t>Betonarme rögarlar — beton hacmi 1,566 m³, ortalama donatı oranı 90 kg/m³</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="29" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="G141" s="6" t="n"/>
+      <c r="H141" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I141" s="33" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J141" s="34">
+        <f>D141*E141*F141*I141</f>
+        <v/>
+      </c>
+      <c r="K141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="22" t="n"/>
+      <c r="B142" s="25" t="inlineStr">
+        <is>
+          <t>SA/M61C GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C142" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D142" s="22" t="n"/>
+      <c r="E142" s="22" t="n"/>
+      <c r="F142" s="22" t="n"/>
+      <c r="G142" s="22" t="n"/>
+      <c r="H142" s="22" t="n"/>
+      <c r="I142" s="22" t="n"/>
+      <c r="J142" s="22" t="n"/>
+      <c r="K142" s="35">
+        <f>SUM(J141:J141)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143"/>
+    <row r="144">
+      <c r="A144" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR VE VARSAYIMLAR</t>
         </is>
       </c>
-      <c r="B106" s="6" t="n"/>
-      <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6" t="n"/>
-      <c r="E106" s="6" t="n"/>
-      <c r="F106" s="6" t="n"/>
-      <c r="G106" s="6" t="n"/>
-      <c r="H106" s="6" t="n"/>
-      <c r="I106" s="6" t="n"/>
-      <c r="J106" s="6" t="n"/>
-      <c r="K106" s="6" t="n"/>
-    </row>
-    <row r="107" ht="13" customHeight="1">
-      <c r="A107" s="17" t="inlineStr">
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="6" t="n"/>
+      <c r="F144" s="6" t="n"/>
+      <c r="G144" s="6" t="n"/>
+      <c r="H144" s="6" t="n"/>
+      <c r="I144" s="6" t="n"/>
+      <c r="J144" s="6" t="n"/>
+      <c r="K144" s="6" t="n"/>
+    </row>
+    <row r="145" ht="13" customHeight="1">
+      <c r="A145" s="17" t="inlineStr">
         <is>
           <t>•  SARI zeminli 'demir çapı veya profil tipi' hücreleri, proje toplamını tutturmak üzere yapılan dağıtımı gösterir.</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="33" customHeight="1">
-      <c r="A108" s="17" t="inlineStr">
+    <row r="146" ht="33" customHeight="1">
+      <c r="A146" s="17" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok temellerinin donatı TOPLAMLARI betonarme paftasındaki METRAJ tablosundan aynen alınmıştır (blok başına ø6-12 = 4.159,89 kg, ø14-50 = 7.287,50 kg). Bu toplamlar eleman bazında dağıtılmış, dağıtılamayan kısım açıkça 'proje METRAJ tablosunu tamamlayan pay' satırı olarak gösterilmiştir. Genel toplamlar proje tablosuyla birebir tutmaktadır.</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="17" t="inlineStr">
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="17" t="inlineStr">
         <is>
           <t>•  ÇELİK TAŞIYICI SİSTEM STATİK ÇELİK PROJESİNDEN ALINMIŞTIR. Profiller SHS 150x150x6 (kolon, ana kiriş, boyuna kiriş), RHS 100x50x3 (çatı aşığı, yan aşık, kuşak) ve SHS 100x100x4 (çapraz); malzeme S235JR. Çerçeve geometrisi projedeki gibidir: aks açıklıkları 3,75 + 6,00 + 3,80 = 13,55 m, kolon üstü +2,84, mahya +4,34.</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="13" customHeight="1">
-      <c r="A110" s="17" t="inlineStr">
+    <row r="148" ht="13" customHeight="1">
+      <c r="A148" s="17" t="inlineStr">
         <is>
           <t>•  Gübre çukuru ve müştemilat donatısı, projedeki METRAJ tablolarından ve eleman hacmi x birim donatı oranı (kg/m³) esasıyla hesaplanmıştır.</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="17" t="inlineStr">
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="17" t="inlineStr">
         <is>
           <t>•  Birim ağırlıklar (ton/m): ø8 0,000395 · ø10 0,000617 · ø12 0,000888 · ø14 0,001210 · ø16 0,001580 · ø20 0,002470 · HEA 200 0,0423 · HEA 260 0,0541 · IPE 270 0,0361 · Z 200x70x2,5 0,00900 · L 70x70x7 0,00738.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A108:K108"/>
+  <mergeCells count="17">
+    <mergeCell ref="A149:K149"/>
+    <mergeCell ref="A145:K145"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A86:K86"/>
-    <mergeCell ref="A109:K109"/>
+    <mergeCell ref="A130:K130"/>
+    <mergeCell ref="A147:K147"/>
+    <mergeCell ref="A148:K148"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A107:K107"/>
+    <mergeCell ref="A52:K52"/>
     <mergeCell ref="A99:K99"/>
+    <mergeCell ref="A117:K117"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A93:K93"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A123:K123"/>
+    <mergeCell ref="A138:K138"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A110:K110"/>
-    <mergeCell ref="A111:K111"/>
-    <mergeCell ref="A106:K106"/>
+    <mergeCell ref="A146:K146"/>
+    <mergeCell ref="A144:K144"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -20519,7 +21534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -20669,17 +21684,17 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J6" s="38" t="inlineStr"/>
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L6" s="38" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="14" t="n"/>
@@ -20803,17 +21818,17 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="38" t="inlineStr"/>
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L9" s="38" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="15" t="n"/>
@@ -20895,11 +21910,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J11" s="38" t="inlineStr"/>
       <c r="K11" s="38" t="inlineStr"/>
       <c r="L11" s="38" t="inlineStr"/>
     </row>
@@ -21023,23 +22034,19 @@
       <c r="K15" s="38" t="inlineStr"/>
       <c r="L15" s="38" t="inlineStr"/>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu kaba sıva — dış yüz</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>10 cm teçhizatsız gazbeton blok bölme duvarı (servis bölümü)</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="inlineStr"/>
       <c r="E16" s="21" t="inlineStr">
         <is>
           <t>X</t>
@@ -21057,12 +22064,12 @@
       <c r="A17" s="14" t="n"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="C17" s="37" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı kaba sıva — iç yüz</t>
+          <t>250 kg çimento dozlu kaba sıva — dış yüz</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -21087,12 +22094,12 @@
       <c r="A18" s="14" t="n"/>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>Silikon esaslı su bazlı dış cephe boyası</t>
+          <t>200 kg çimento ve kireç karışımı kaba sıva — iç yüz</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -21117,12 +22124,12 @@
       <c r="A19" s="14" t="n"/>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="C19" s="37" t="inlineStr">
         <is>
-          <t>Su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>Silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -21144,155 +22151,151 @@
       <c r="L19" s="38" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="15" t="n"/>
+      <c r="A20" s="14" t="n"/>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>Brüt betonarme perde (kaplamasız)</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="inlineStr"/>
-      <c r="E20" s="38" t="inlineStr"/>
+          <t>Su bazlı plastik antibakteriyel iç cephe boyası</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F20" s="38" t="inlineStr"/>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="G20" s="38" t="inlineStr"/>
+      <c r="H20" s="38" t="inlineStr"/>
+      <c r="I20" s="38" t="inlineStr"/>
+      <c r="J20" s="38" t="inlineStr"/>
       <c r="K20" s="38" t="inlineStr"/>
       <c r="L20" s="38" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Tavan Kaplaması</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>TKDK-0042</t>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="C21" s="37" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu sandviç panel (alttan görünür yüz)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
+          <t>Brüt betonarme perde (kaplamasız)</t>
+        </is>
+      </c>
+      <c r="D21" s="38" t="inlineStr"/>
+      <c r="E21" s="38" t="inlineStr"/>
+      <c r="F21" s="38" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F21" s="38" t="inlineStr"/>
-      <c r="G21" s="38" t="inlineStr"/>
-      <c r="H21" s="38" t="inlineStr"/>
-      <c r="I21" s="38" t="inlineStr"/>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J21" s="38" t="inlineStr"/>
       <c r="K21" s="38" t="inlineStr"/>
       <c r="L21" s="38" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Tavan Kaplaması</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0042</t>
         </is>
       </c>
       <c r="C22" s="37" t="inlineStr">
         <is>
-          <t>C 25/30 betonarme üst döşeme</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="inlineStr"/>
-      <c r="E22" s="38" t="inlineStr"/>
+          <t>6 cm poliüretan dolgulu sandviç panel (alttan görünür yüz)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F22" s="38" t="inlineStr"/>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="G22" s="38" t="inlineStr"/>
+      <c r="H22" s="38" t="inlineStr"/>
+      <c r="I22" s="38" t="inlineStr"/>
+      <c r="J22" s="38" t="inlineStr"/>
       <c r="K22" s="38" t="inlineStr"/>
       <c r="L22" s="38" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Çatı İmalatları</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>TKDK-0042</t>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="C23" s="37" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu ısı yalıtımlı sandviç çatı paneli</t>
+          <t>C 25/30 betonarme üst döşeme</t>
         </is>
       </c>
       <c r="D23" s="38" t="inlineStr"/>
       <c r="E23" s="38" t="inlineStr"/>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="38" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="G23" s="38" t="inlineStr"/>
-      <c r="H23" s="38" t="inlineStr"/>
-      <c r="I23" s="38" t="inlineStr"/>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J23" s="38" t="inlineStr"/>
       <c r="K23" s="38" t="inlineStr"/>
       <c r="L23" s="38" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>15.550.1202</t>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Çatı İmalatları</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0042</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr">
         <is>
-          <t>Lama ve profil demirden mahya, saçak ve köşe kapaması</t>
+          <t>6 cm poliüretan dolgulu ısı yalıtımlı sandviç çatı paneli</t>
         </is>
       </c>
       <c r="D24" s="38" t="inlineStr"/>
@@ -21310,15 +22313,15 @@
       <c r="L24" s="38" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="15" t="n"/>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>TKDK-0115</t>
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="C25" s="37" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu ve ø100 iniş borusu</t>
+          <t>Lama ve profil demirden mahya, saçak ve köşe kapaması</t>
         </is>
       </c>
       <c r="D25" s="38" t="inlineStr"/>
@@ -21335,29 +22338,25 @@
       <c r="K25" s="38" t="inlineStr"/>
       <c r="L25" s="38" t="inlineStr"/>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Kapı Doğraması</t>
-        </is>
-      </c>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="14" t="n"/>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu ısı yalıtımlı kapı — servis kapısı 100/220 ve yükleme kapısı 300/300</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
+          <t>Galvanizli düz sacdan yağmur oluğu (dere)</t>
+        </is>
+      </c>
+      <c r="D26" s="38" t="inlineStr"/>
+      <c r="E26" s="38" t="inlineStr"/>
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E26" s="38" t="inlineStr"/>
-      <c r="F26" s="38" t="inlineStr"/>
       <c r="G26" s="38" t="inlineStr"/>
       <c r="H26" s="38" t="inlineStr"/>
       <c r="I26" s="38" t="inlineStr"/>
@@ -21365,25 +22364,25 @@
       <c r="K26" s="38" t="inlineStr"/>
       <c r="L26" s="38" t="inlineStr"/>
     </row>
-    <row r="27" ht="22" customHeight="1">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="15" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>TKDK-0175</t>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı (hijyen bölmesi, ofis ve WC)</t>
+          <t>Ø70 sert PVC yağmur suyu iniş borusu</t>
         </is>
       </c>
       <c r="D27" s="38" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="38" t="inlineStr"/>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F27" s="38" t="inlineStr"/>
       <c r="G27" s="38" t="inlineStr"/>
       <c r="H27" s="38" t="inlineStr"/>
       <c r="I27" s="38" t="inlineStr"/>
@@ -21394,20 +22393,24 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Çit İmalatları</t>
+          <t>Kapı Doğraması</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit (h = 1,50 m, göz 60x60 mm)</t>
-        </is>
-      </c>
-      <c r="D28" s="38" t="inlineStr"/>
+          <t>5 cm poliüretan dolgulu ısı yalıtımlı kapı — servis kapısı 100/220 ve yükleme kapısı 300/300</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="E28" s="38" t="inlineStr"/>
       <c r="F28" s="38" t="inlineStr"/>
       <c r="G28" s="38" t="inlineStr"/>
@@ -21415,82 +22418,247 @@
       <c r="I28" s="38" t="inlineStr"/>
       <c r="J28" s="38" t="inlineStr"/>
       <c r="K28" s="38" t="inlineStr"/>
-      <c r="L28" s="21" t="inlineStr">
+      <c r="L28" s="38" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı (hijyen bölmesi, ofis ve WC)</t>
+        </is>
+      </c>
+      <c r="D29" s="38" t="inlineStr"/>
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="F29" s="38" t="inlineStr"/>
+      <c r="G29" s="38" t="inlineStr"/>
+      <c r="H29" s="38" t="inlineStr"/>
+      <c r="I29" s="38" t="inlineStr"/>
+      <c r="J29" s="38" t="inlineStr"/>
+      <c r="K29" s="38" t="inlineStr"/>
+      <c r="L29" s="38" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>15.550.1002</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>1,50 mm sacdan bükme kapı kasası (hijyen bölmesi, ofis ve WC)</t>
+        </is>
+      </c>
+      <c r="D30" s="38" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F30" s="38" t="inlineStr"/>
+      <c r="G30" s="38" t="inlineStr"/>
+      <c r="H30" s="38" t="inlineStr"/>
+      <c r="I30" s="38" t="inlineStr"/>
+      <c r="J30" s="38" t="inlineStr"/>
+      <c r="K30" s="38" t="inlineStr"/>
+      <c r="L30" s="38" t="inlineStr"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Kanalizasyon İmalatları</t>
+        </is>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>ÖP-15</t>
+        </is>
+      </c>
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>Prefabrik polietilen sızdırmaz foseptik tankı — 6 m³</t>
+        </is>
+      </c>
+      <c r="D31" s="38" t="inlineStr"/>
+      <c r="E31" s="38" t="inlineStr"/>
+      <c r="F31" s="38" t="inlineStr"/>
+      <c r="G31" s="38" t="inlineStr"/>
+      <c r="H31" s="38" t="inlineStr"/>
+      <c r="I31" s="38" t="inlineStr"/>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" s="38" t="inlineStr"/>
+      <c r="L31" s="38" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="C32" s="37" t="inlineStr">
+        <is>
+          <t>Ø150 HDPE koruge pissu borusu (SN 8)</t>
+        </is>
+      </c>
+      <c r="D32" s="38" t="inlineStr"/>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F32" s="38" t="inlineStr"/>
+      <c r="G32" s="38" t="inlineStr"/>
+      <c r="H32" s="38" t="inlineStr"/>
+      <c r="I32" s="38" t="inlineStr"/>
+      <c r="J32" s="38" t="inlineStr"/>
+      <c r="K32" s="38" t="inlineStr"/>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>15.560.1003</t>
+        </is>
+      </c>
+      <c r="C33" s="37" t="inlineStr">
+        <is>
+          <t>Betonarme kompozit rögar kapağı</t>
+        </is>
+      </c>
+      <c r="D33" s="38" t="inlineStr"/>
+      <c r="E33" s="38" t="inlineStr"/>
+      <c r="F33" s="38" t="inlineStr"/>
+      <c r="G33" s="38" t="inlineStr"/>
+      <c r="H33" s="38" t="inlineStr"/>
+      <c r="I33" s="38" t="inlineStr"/>
+      <c r="J33" s="38" t="inlineStr"/>
+      <c r="K33" s="38" t="inlineStr"/>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Çit İmalatları</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0091</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="inlineStr">
+        <is>
+          <t>Betonarme direkli galvanizli tel örgü çit (h = 1,50 m, göz 60x60 mm)</t>
+        </is>
+      </c>
+      <c r="D34" s="38" t="inlineStr"/>
+      <c r="E34" s="38" t="inlineStr"/>
+      <c r="F34" s="38" t="inlineStr"/>
+      <c r="G34" s="38" t="inlineStr"/>
+      <c r="H34" s="38" t="inlineStr"/>
+      <c r="I34" s="38" t="inlineStr"/>
+      <c r="J34" s="38" t="inlineStr"/>
+      <c r="K34" s="38" t="inlineStr"/>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="6" t="n"/>
+      <c r="J36" s="6" t="n"/>
+      <c r="K36" s="6" t="n"/>
+      <c r="L36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>•  Mahal listesi, mimari projenin ekinde sunulmak üzere hazırlanmıştır; mahal kodları mimari plandaki blok ve hacim adlarıyla eşleşir.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>•  Listede kullanılan poz numaraları metraj cetveli ve keşif özetiyle birebir aynıdır.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok birebir özdeş olduğundan tek mahal sütununda gösterilmiştir.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>•  Listedeki pozların tamamı birim fiyat kitaplarındandır: 15.xxx ÇŞB 2026 birim fiyat kitabı, TKDK-xxxx ise TKDK 17.02.2026 Özel Poz Tablosu pozudur.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>•  Gübre çukuru, ölü atma çukuru, foseptik ve depoların iç yüzeyleri kaplamasız brüt betonarmedir; su yalıtımı bu hesabın kapsamı dışında bırakılmıştır.</t>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>•  Gübre çukuru, ölü atma çukuru ve depoların iç yüzeyleri kaplamasız brüt betonarmedir; su yalıtımı bu hesabın kapsamı dışında bırakılmıştır. Foseptik betonarme değildir: kazı ve grobeton oturma yatağı üzerine yerleştirilen prefabrik polietilen sızdırmaz tanktır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A30:L30"/>
+  <mergeCells count="16">
+    <mergeCell ref="A38:L38"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A24:A27"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A36:L36"/>
     <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="A31:A33"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A39:L39"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -21534,7 +21534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -22588,77 +22588,250 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Sıhhi Tesisat</t>
+        </is>
+      </c>
+      <c r="B35" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="37" t="inlineStr">
+        <is>
+          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, küresel vanalar, askı ve kılıflar</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F35" s="38" t="inlineStr"/>
+      <c r="G35" s="38" t="inlineStr"/>
+      <c r="H35" s="38" t="inlineStr"/>
+      <c r="I35" s="38" t="inlineStr"/>
+      <c r="J35" s="38" t="inlineStr"/>
+      <c r="K35" s="38" t="inlineStr"/>
+      <c r="L35" s="38" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
+        <is>
+          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, temizleme kapağı, yer süzgeci</t>
+        </is>
+      </c>
+      <c r="D36" s="38" t="inlineStr"/>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F36" s="38" t="inlineStr"/>
+      <c r="G36" s="38" t="inlineStr"/>
+      <c r="H36" s="38" t="inlineStr"/>
+      <c r="I36" s="38" t="inlineStr"/>
+      <c r="J36" s="38" t="inlineStr"/>
+      <c r="K36" s="38" t="inlineStr"/>
+      <c r="L36" s="38" t="inlineStr"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C37" s="37" t="inlineStr">
+        <is>
+          <t>Termosifon — sıcak su üretimi</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="inlineStr"/>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F37" s="38" t="inlineStr"/>
+      <c r="G37" s="38" t="inlineStr"/>
+      <c r="H37" s="38" t="inlineStr"/>
+      <c r="I37" s="38" t="inlineStr"/>
+      <c r="J37" s="38" t="inlineStr"/>
+      <c r="K37" s="38" t="inlineStr"/>
+      <c r="L37" s="38" t="inlineStr"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>Şebeke su bağlantısı ve 2" su sayacı</t>
+        </is>
+      </c>
+      <c r="D38" s="38" t="inlineStr"/>
+      <c r="E38" s="38" t="inlineStr"/>
+      <c r="F38" s="38" t="inlineStr"/>
+      <c r="G38" s="38" t="inlineStr"/>
+      <c r="H38" s="38" t="inlineStr"/>
+      <c r="I38" s="38" t="inlineStr"/>
+      <c r="J38" s="38" t="inlineStr"/>
+      <c r="K38" s="38" t="inlineStr"/>
+      <c r="L38" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C39" s="37" t="inlineStr">
+        <is>
+          <t>Hidrofor — Q = 2 m³/h, P = 33-38 mSS</t>
+        </is>
+      </c>
+      <c r="D39" s="38" t="inlineStr"/>
+      <c r="E39" s="38" t="inlineStr"/>
+      <c r="F39" s="38" t="inlineStr"/>
+      <c r="G39" s="38" t="inlineStr"/>
+      <c r="H39" s="38" t="inlineStr"/>
+      <c r="I39" s="38" t="inlineStr"/>
+      <c r="J39" s="38" t="inlineStr"/>
+      <c r="K39" s="38" t="inlineStr"/>
+      <c r="L39" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>Tesisat hidroforu — 0,3 m³/h, 30 mSS</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="inlineStr"/>
+      <c r="E40" s="38" t="inlineStr"/>
+      <c r="F40" s="38" t="inlineStr"/>
+      <c r="G40" s="38" t="inlineStr"/>
+      <c r="H40" s="38" t="inlineStr"/>
+      <c r="I40" s="38" t="inlineStr"/>
+      <c r="J40" s="38" t="inlineStr"/>
+      <c r="K40" s="38" t="inlineStr"/>
+      <c r="L40" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="6" t="n"/>
-      <c r="I36" s="6" t="n"/>
-      <c r="J36" s="6" t="n"/>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="6" t="n"/>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="6" t="n"/>
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="n"/>
+      <c r="L42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>•  Mahal listesi, mimari projenin ekinde sunulmak üzere hazırlanmıştır; mahal kodları mimari plandaki blok ve hacim adlarıyla eşleşir.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>•  Listede kullanılan poz numaraları metraj cetveli ve keşif özetiyle birebir aynıdır.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok birebir özdeş olduğundan tek mahal sütununda gösterilmiştir.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>•  Listedeki pozların tamamı birim fiyat kitaplarındandır: 15.xxx ÇŞB 2026 birim fiyat kitabı, TKDK-xxxx ise TKDK 17.02.2026 Özel Poz Tablosu pozudur.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>•  Sıhhi tesisat kalemlerinin kitap pozu yoktur ve keşif özetinde yer almazlar: miktarları onaylı sıhhi tesisat projesinden, bedelleri piyasa araştırmasından gelir ve 36 numaralı proforma ile beyan edilir. Poz sütununda “—” işareti bunu gösterir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>•  Gübre çukuru, ölü atma çukuru ve depoların iç yüzeyleri kaplamasız brüt betonarmedir; su yalıtımı bu hesabın kapsamı dışında bırakılmıştır. Foseptik betonarme değildir: kazı ve grobeton oturma yatağı üzerine yerleştirilen prefabrik polietilen sızdırmaz tanktır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A38:L38"/>
+  <mergeCells count="18">
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A42:L42"/>
     <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A43:L43"/>
     <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A47:L47"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A46:L46"/>
     <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A44:L44"/>
     <mergeCell ref="A14:A21"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A48:L48"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -22802,7 +22802,7 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>•  Sıhhi tesisat kalemlerinin kitap pozu yoktur ve keşif özetinde yer almazlar: miktarları onaylı sıhhi tesisat projesinden, bedelleri piyasa araştırmasından gelir ve 36 numaralı proforma ile beyan edilir. Poz sütununda “—” işareti bunu gösterir.</t>
+          <t>•  Sıhhi tesisat kalemlerinin kitap pozu yoktur ve keşif özetinde yer almazlar: miktarları onaylı sıhhi tesisat projesinden (39) gelir. Poz sütununda “—” işareti bunu gösterir.</t>
         </is>
       </c>
     </row>

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -609,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3476,7 +3476,7 @@
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>2 adet, her biri 2,90 x 2,90 m.</t>
+          <t>2 adet; her biri 2,90 x 2,90 m radye temel (H = 0,40 m, kot -0,10 / +0,30) ve üzerinde 4 adet SB01…SB04 kolonu (40/40, kot +0,30 / +1,40).</t>
         </is>
       </c>
       <c r="B126" s="6" t="n"/>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>48.02</v>
+        <v>6.084</v>
       </c>
     </row>
     <row r="129" ht="31.5" customHeight="1">
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>8.41</v>
+        <v>8.135999999999999</v>
       </c>
     </row>
     <row r="131" ht="14" customHeight="1">
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>11.6</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="132" ht="21" customHeight="1">
@@ -3654,678 +3654,678 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.757</v>
-      </c>
-    </row>
-    <row r="133"/>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="133" ht="21" customHeight="1">
+      <c r="A133" s="15" t="n"/>
+      <c r="B133" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="n">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="134"/>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="24" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
+    <row r="136" ht="24" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
         </is>
       </c>
-      <c r="B135" s="6" t="n"/>
-      <c r="C135" s="6" t="n"/>
-      <c r="D135" s="6" t="n"/>
-      <c r="E135" s="6" t="n"/>
-      <c r="F135" s="6" t="n"/>
-    </row>
-    <row r="136" ht="28" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
+      <c r="B136" s="6" t="n"/>
+      <c r="C136" s="6" t="n"/>
+      <c r="D136" s="6" t="n"/>
+      <c r="E136" s="6" t="n"/>
+      <c r="F136" s="6" t="n"/>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="C137" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
+      <c r="D137" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
+      <c r="E137" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr">
+      <c r="F137" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="14" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B137" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
+      <c r="B138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D138" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E137" s="12" t="inlineStr">
+      <c r="E138" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F137" s="13" t="n">
+      <c r="F138" s="13" t="n">
         <v>106.5</v>
-      </c>
-    </row>
-    <row r="138" ht="31.5" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B138" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D138" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F138" s="13" t="n">
-        <v>1.344</v>
       </c>
     </row>
     <row r="139" ht="31.5" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>1.344</v>
+      </c>
+    </row>
+    <row r="140" ht="31.5" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B139" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="B140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr">
+      <c r="D140" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E139" s="12" t="inlineStr">
+      <c r="E140" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F139" s="13" t="n">
+      <c r="F140" s="13" t="n">
         <v>15.15</v>
       </c>
     </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+    <row r="141" ht="14" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B140" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="B141" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D141" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E140" s="12" t="inlineStr">
+      <c r="E141" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F140" s="13" t="n">
+      <c r="F141" s="13" t="n">
         <v>95.59999999999999</v>
       </c>
     </row>
-    <row r="141" ht="21" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+    <row r="142" ht="21" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
+      <c r="B142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D141" s="11" t="inlineStr">
+      <c r="D142" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E141" s="12" t="inlineStr">
+      <c r="E142" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F141" s="13" t="n">
+      <c r="F142" s="13" t="n">
         <v>1.232</v>
       </c>
     </row>
-    <row r="142"/>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
+    <row r="143"/>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="24" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
+    <row r="145" ht="24" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
         </is>
       </c>
-      <c r="B144" s="6" t="n"/>
-      <c r="C144" s="6" t="n"/>
-      <c r="D144" s="6" t="n"/>
-      <c r="E144" s="6" t="n"/>
-      <c r="F144" s="6" t="n"/>
-    </row>
-    <row r="145" ht="28" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
+      <c r="B145" s="6" t="n"/>
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="n"/>
+      <c r="E145" s="6" t="n"/>
+      <c r="F145" s="6" t="n"/>
+    </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B145" s="7" t="inlineStr">
+      <c r="B146" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C146" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
+      <c r="D146" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E145" s="7" t="inlineStr">
+      <c r="E146" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F145" s="7" t="inlineStr">
+      <c r="F146" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="14" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="B147" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D146" s="11" t="inlineStr">
+      <c r="D147" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E146" s="12" t="inlineStr">
+      <c r="E147" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F146" s="13" t="n">
+      <c r="F147" s="13" t="n">
         <v>88.75</v>
-      </c>
-    </row>
-    <row r="147" ht="31.5" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F147" s="13" t="n">
-        <v>1.024</v>
       </c>
     </row>
     <row r="148" ht="31.5" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F148" s="13" t="n">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="149" ht="31.5" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C148" s="10" t="inlineStr">
+      <c r="B149" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D148" s="11" t="inlineStr">
+      <c r="D149" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E148" s="12" t="inlineStr">
+      <c r="E149" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F148" s="13" t="n">
+      <c r="F149" s="13" t="n">
         <v>12.3</v>
       </c>
     </row>
-    <row r="149" ht="14" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
+      <c r="B150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D149" s="11" t="inlineStr">
+      <c r="D150" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E149" s="12" t="inlineStr">
+      <c r="E150" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F149" s="13" t="n">
+      <c r="F150" s="13" t="n">
         <v>79.8</v>
       </c>
     </row>
-    <row r="150" ht="21" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
+    <row r="151" ht="21" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
+      <c r="B151" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D150" s="11" t="inlineStr">
+      <c r="D151" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E150" s="12" t="inlineStr">
+      <c r="E151" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F150" s="13" t="n">
+      <c r="F151" s="13" t="n">
         <v>1.23</v>
       </c>
     </row>
-    <row r="151"/>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="4" t="inlineStr">
+    <row r="152"/>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="24" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
+    <row r="154" ht="24" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
         </is>
       </c>
-      <c r="B153" s="6" t="n"/>
-      <c r="C153" s="6" t="n"/>
-      <c r="D153" s="6" t="n"/>
-      <c r="E153" s="6" t="n"/>
-      <c r="F153" s="6" t="n"/>
-    </row>
-    <row r="154" ht="28" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
+      <c r="B154" s="6" t="n"/>
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="n"/>
+      <c r="E154" s="6" t="n"/>
+      <c r="F154" s="6" t="n"/>
+    </row>
+    <row r="155" ht="28" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C154" s="7" t="inlineStr">
+      <c r="C155" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D154" s="7" t="inlineStr">
+      <c r="D155" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E154" s="7" t="inlineStr">
+      <c r="E155" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F154" s="7" t="inlineStr">
+      <c r="F155" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="14" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B155" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C155" s="10" t="inlineStr">
+      <c r="B156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
         <is>
           <t>15.120.1001</t>
         </is>
       </c>
-      <c r="D155" s="11" t="inlineStr">
+      <c r="D156" s="11" t="inlineStr">
         <is>
           <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E155" s="12" t="inlineStr">
+      <c r="E156" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F155" s="13" t="n">
+      <c r="F156" s="13" t="n">
         <v>260.943</v>
       </c>
     </row>
-    <row r="156" ht="31.5" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+    <row r="157" ht="31.5" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B156" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" s="10" t="inlineStr">
+      <c r="B157" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D156" s="11" t="inlineStr">
+      <c r="D157" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E156" s="12" t="inlineStr">
+      <c r="E157" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F156" s="13" t="n">
+      <c r="F157" s="13" t="n">
         <v>1.566</v>
       </c>
     </row>
-    <row r="157" ht="14" customHeight="1">
-      <c r="A157" s="8" t="inlineStr">
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B157" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C157" s="10" t="inlineStr">
+      <c r="B158" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D157" s="11" t="inlineStr">
+      <c r="D158" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E157" s="12" t="inlineStr">
+      <c r="E158" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F157" s="13" t="n">
+      <c r="F158" s="13" t="n">
         <v>14.4</v>
       </c>
     </row>
-    <row r="158" ht="21" customHeight="1">
-      <c r="A158" s="8" t="inlineStr">
+    <row r="159" ht="21" customHeight="1">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B158" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C158" s="10" t="inlineStr">
+      <c r="B159" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D158" s="11" t="inlineStr">
+      <c r="D159" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E158" s="12" t="inlineStr">
+      <c r="E159" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F158" s="13" t="n">
+      <c r="F159" s="13" t="n">
         <v>0.141</v>
       </c>
     </row>
-    <row r="159" ht="14" customHeight="1">
-      <c r="A159" s="8" t="inlineStr">
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="8" t="inlineStr">
         <is>
           <t>Çevre düzenlemesi ve çit işleri</t>
         </is>
       </c>
-      <c r="B159" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C159" s="10" t="inlineStr">
+      <c r="B160" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
         <is>
           <t>TKDK-0091</t>
         </is>
       </c>
-      <c r="D159" s="11" t="inlineStr">
+      <c r="D160" s="11" t="inlineStr">
         <is>
           <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
         </is>
       </c>
-      <c r="E159" s="12" t="inlineStr">
+      <c r="E160" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F159" s="13" t="n">
+      <c r="F160" s="13" t="n">
         <v>361.04</v>
       </c>
     </row>
-    <row r="160" ht="21" customHeight="1">
-      <c r="A160" s="8" t="inlineStr">
+    <row r="161" ht="21" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
         <is>
           <t>Kanalizasyon işleri</t>
         </is>
       </c>
-      <c r="B160" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C160" s="10" t="inlineStr">
+      <c r="B161" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
         <is>
           <t>43.527.1001</t>
         </is>
       </c>
-      <c r="D160" s="11" t="inlineStr">
+      <c r="D161" s="11" t="inlineStr">
         <is>
           <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
-      <c r="E160" s="12" t="inlineStr">
+      <c r="E161" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F160" s="13" t="n">
+      <c r="F161" s="13" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="161" ht="14" customHeight="1">
-      <c r="A161" s="15" t="n"/>
-      <c r="B161" s="9" t="n">
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="15" t="n"/>
+      <c r="B162" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C161" s="10" t="inlineStr">
+      <c r="C162" s="10" t="inlineStr">
         <is>
           <t>15.560.1003</t>
         </is>
       </c>
-      <c r="D161" s="11" t="inlineStr">
+      <c r="D162" s="11" t="inlineStr">
         <is>
           <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
-      <c r="E161" s="12" t="inlineStr">
+      <c r="E162" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F161" s="13" t="n">
+      <c r="F162" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="162" ht="21" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
+    <row r="163" ht="21" customHeight="1">
+      <c r="A163" s="8" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
-      <c r="B162" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C162" s="10" t="inlineStr">
+      <c r="B163" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
         <is>
           <t>35.100.1104</t>
         </is>
       </c>
-      <c r="D162" s="11" t="inlineStr">
+      <c r="D163" s="11" t="inlineStr">
         <is>
           <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E162" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F162" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" ht="21" customHeight="1">
-      <c r="A163" s="14" t="n"/>
-      <c r="B163" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C163" s="10" t="inlineStr">
-        <is>
-          <t>35.100.2106</t>
-        </is>
-      </c>
-      <c r="D163" s="11" t="inlineStr">
-        <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -4340,16 +4340,16 @@
     <row r="164" ht="21" customHeight="1">
       <c r="A164" s="14" t="n"/>
       <c r="B164" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>35.135.3201</t>
+          <t>35.100.2106</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
@@ -4364,16 +4364,16 @@
     <row r="165" ht="21" customHeight="1">
       <c r="A165" s="14" t="n"/>
       <c r="B165" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>35.110.1104</t>
+          <t>35.135.3201</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
@@ -4385,19 +4385,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" ht="14" customHeight="1">
+    <row r="166" ht="21" customHeight="1">
       <c r="A166" s="14" t="n"/>
       <c r="B166" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.110.1104</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
@@ -4406,46 +4406,46 @@
         </is>
       </c>
       <c r="F166" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="167" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" ht="14" customHeight="1">
       <c r="A167" s="14" t="n"/>
       <c r="B167" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>35.140.3105</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F167" s="13" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1">
       <c r="A168" s="14" t="n"/>
       <c r="B168" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>35.140.3101</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
@@ -4460,40 +4460,40 @@
     <row r="169" ht="21" customHeight="1">
       <c r="A169" s="14" t="n"/>
       <c r="B169" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>35.140.3101</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F169" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="170" ht="21" customHeight="1">
+      <c r="A170" s="14" t="n"/>
+      <c r="B170" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C169" s="10" t="inlineStr">
+      <c r="C170" s="10" t="inlineStr">
         <is>
           <t>35.172.1706</t>
         </is>
       </c>
-      <c r="D169" s="11" t="inlineStr">
+      <c r="D170" s="11" t="inlineStr">
         <is>
           <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E169" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F169" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="170" ht="14" customHeight="1">
-      <c r="A170" s="15" t="n"/>
-      <c r="B170" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C170" s="10" t="inlineStr">
-        <is>
-          <t>35.170.4002</t>
-        </is>
-      </c>
-      <c r="D170" s="11" t="inlineStr">
-        <is>
-          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
@@ -4505,42 +4505,66 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171"/>
-    <row r="172">
-      <c r="A172" s="16" t="inlineStr">
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="15" t="n"/>
+      <c r="B171" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>35.170.4002</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F171" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172"/>
+    <row r="173">
+      <c r="A173" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B172" s="6" t="n"/>
-      <c r="C172" s="6" t="n"/>
-      <c r="D172" s="6" t="n"/>
-      <c r="E172" s="6" t="n"/>
-      <c r="F172" s="6" t="n"/>
-    </row>
-    <row r="173" ht="13" customHeight="1">
-      <c r="A173" s="17" t="inlineStr">
+      <c r="B173" s="6" t="n"/>
+      <c r="C173" s="6" t="n"/>
+      <c r="D173" s="6" t="n"/>
+      <c r="E173" s="6" t="n"/>
+      <c r="F173" s="6" t="n"/>
+    </row>
+    <row r="174" ht="13" customHeight="1">
+      <c r="A174" s="17" t="inlineStr">
         <is>
           <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="22" customHeight="1">
-      <c r="A174" s="17" t="inlineStr">
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="17" t="inlineStr">
         <is>
           <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="13" customHeight="1">
-      <c r="A175" s="17" t="inlineStr">
-        <is>
-          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
         </is>
       </c>
     </row>
     <row r="176" ht="13" customHeight="1">
       <c r="A176" s="17" t="inlineStr">
+        <is>
+          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="13" customHeight="1">
+      <c r="A177" s="17" t="inlineStr">
         <is>
           <t>•  Elektrik tesisatı bölümü, kuvvetli akım birim fiyat listesi temin edildikten sonra tamamlanacaktır.</t>
         </is>
@@ -4555,7 +4579,7 @@
     <mergeCell ref="A156"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A155"/>
+    <mergeCell ref="A163:A171"/>
     <mergeCell ref="A175:F175"/>
     <mergeCell ref="A130"/>
     <mergeCell ref="A77"/>
@@ -4565,16 +4589,12 @@
     <mergeCell ref="A157"/>
     <mergeCell ref="A123"/>
     <mergeCell ref="A138"/>
-    <mergeCell ref="A132"/>
-    <mergeCell ref="A134:F134"/>
-    <mergeCell ref="A152:F152"/>
     <mergeCell ref="A70:A72"/>
     <mergeCell ref="A158"/>
     <mergeCell ref="A55"/>
     <mergeCell ref="A104"/>
+    <mergeCell ref="A160"/>
     <mergeCell ref="A150"/>
-    <mergeCell ref="A172:F172"/>
-    <mergeCell ref="A162:A170"/>
     <mergeCell ref="A159"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A99:F99"/>
@@ -4587,14 +4607,18 @@
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A135:F135"/>
     <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A146"/>
     <mergeCell ref="A176:F176"/>
     <mergeCell ref="A149"/>
     <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A151"/>
     <mergeCell ref="A141"/>
+    <mergeCell ref="A177:F177"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A122"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A112"/>
+    <mergeCell ref="A154:F154"/>
     <mergeCell ref="A59:A61"/>
     <mergeCell ref="A30"/>
     <mergeCell ref="A114"/>
@@ -4603,14 +4627,14 @@
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A109:F109"/>
     <mergeCell ref="A173:F173"/>
-    <mergeCell ref="A137"/>
-    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A106:A107"/>
     <mergeCell ref="A56"/>
     <mergeCell ref="A139"/>
+    <mergeCell ref="A161:A162"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A129"/>
     <mergeCell ref="A116"/>
+    <mergeCell ref="A132:A133"/>
     <mergeCell ref="A8"/>
     <mergeCell ref="A131"/>
     <mergeCell ref="A140"/>
@@ -4620,11 +4644,11 @@
     <mergeCell ref="A75:A76"/>
     <mergeCell ref="A67:A69"/>
     <mergeCell ref="A9"/>
+    <mergeCell ref="A142"/>
     <mergeCell ref="A11"/>
     <mergeCell ref="A103"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A78"/>
-    <mergeCell ref="A160:A161"/>
     <mergeCell ref="A128"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A32:A50"/>
@@ -4649,7 +4673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J551"/>
+  <dimension ref="A1:J556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15171,12 +15195,12 @@
       <c r="I429" s="22" t="n"/>
       <c r="J429" s="22" t="n"/>
     </row>
-    <row r="430" ht="20" customHeight="1">
+    <row r="430" ht="30" customHeight="1">
       <c r="A430" s="6" t="n"/>
       <c r="B430" s="6" t="n"/>
       <c r="C430" s="23" t="inlineStr">
         <is>
-          <t>Silo kaideleri: 2.90x2.90 kaide; 1,00 m çalışma payı -&gt; 4.90x4.90; derinlik 1,00 m</t>
+          <t>Silo kaideleri: radye 2,90x2,90; 0,50 m çalışma payı -&gt; 3,90x3,90; radye altı -0,10 + 10 cm grobeton = 0,20 m derinlik</t>
         </is>
       </c>
       <c r="D430" s="6" t="n"/>
@@ -15184,13 +15208,13 @@
         <v>2</v>
       </c>
       <c r="F430" s="29" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="G430" s="29" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="H430" s="29" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I430" s="24">
         <f>E430*F430*G430*H430</f>
@@ -15323,12 +15347,12 @@
       <c r="I435" s="22" t="n"/>
       <c r="J435" s="22" t="n"/>
     </row>
-    <row r="436" ht="12" customHeight="1">
+    <row r="436" ht="20" customHeight="1">
       <c r="A436" s="6" t="n"/>
       <c r="B436" s="6" t="n"/>
       <c r="C436" s="23" t="inlineStr">
         <is>
-          <t>Silo betonarme kaidesi (2 adet)</t>
+          <t>Radye temel 2,90x2,90, H = 0,40 m (-0,10 / +0,30); 2 kaide — proje METRAJ tablosu 3,36 m³/kaide</t>
         </is>
       </c>
       <c r="D436" s="6" t="n"/>
@@ -15342,7 +15366,7 @@
         <v>2.9</v>
       </c>
       <c r="H436" s="29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I436" s="24">
         <f>E436*F436*G436*H436</f>
@@ -15350,46 +15374,44 @@
       </c>
       <c r="J436" s="6" t="n"/>
     </row>
-    <row r="437">
-      <c r="A437" s="22" t="n"/>
-      <c r="B437" s="22" t="n"/>
-      <c r="C437" s="25" t="inlineStr">
+    <row r="437" ht="30" customHeight="1">
+      <c r="A437" s="6" t="n"/>
+      <c r="B437" s="6" t="n"/>
+      <c r="C437" s="23" t="inlineStr">
+        <is>
+          <t>SB01…SB04 bodrum kat kolonları 40/40 (+0,30 / +1,40): 4 ad x 2 kaide, yükseklik 1,10 m — proje METRAJ tablosu 0,70 m³/kaide</t>
+        </is>
+      </c>
+      <c r="D437" s="6" t="n"/>
+      <c r="E437" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F437" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G437" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H437" s="29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I437" s="24">
+        <f>E437*F437*G437*H437</f>
+        <v/>
+      </c>
+      <c r="J437" s="6" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="22" t="n"/>
+      <c r="B438" s="22" t="n"/>
+      <c r="C438" s="25" t="inlineStr">
         <is>
           <t>M17 TOPLAMI</t>
         </is>
       </c>
-      <c r="D437" s="26" t="inlineStr">
+      <c r="D438" s="26" t="inlineStr">
         <is>
           <t>m³</t>
-        </is>
-      </c>
-      <c r="E437" s="22" t="n"/>
-      <c r="F437" s="22" t="n"/>
-      <c r="G437" s="22" t="n"/>
-      <c r="H437" s="22" t="n"/>
-      <c r="I437" s="22" t="n"/>
-      <c r="J437" s="27">
-        <f>SUM(I436:I436)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="438" ht="15" customHeight="1">
-      <c r="A438" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B438" s="20" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C438" s="8" t="inlineStr">
-        <is>
-          <t>[M21]  Plywood ile düz yüzeyli betonarme kalıbı — silo kaideleri</t>
-        </is>
-      </c>
-      <c r="D438" s="21" t="inlineStr">
-        <is>
-          <t>m²</t>
         </is>
       </c>
       <c r="E438" s="22" t="n"/>
@@ -15397,120 +15419,125 @@
       <c r="G438" s="22" t="n"/>
       <c r="H438" s="22" t="n"/>
       <c r="I438" s="22" t="n"/>
-      <c r="J438" s="22" t="n"/>
-    </row>
-    <row r="439" ht="20" customHeight="1">
-      <c r="A439" s="6" t="n"/>
-      <c r="B439" s="6" t="n"/>
-      <c r="C439" s="23" t="inlineStr">
-        <is>
-          <t>Silo kaidesi yan yüzleri: 4 yüz x 2 adet, boy 2.90, yükseklik 0.50</t>
-        </is>
-      </c>
-      <c r="D439" s="6" t="n"/>
-      <c r="E439" s="28" t="n">
+      <c r="J438" s="27">
+        <f>SUM(I436:I437)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="439" ht="15" customHeight="1">
+      <c r="A439" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B439" s="20" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="C439" s="8" t="inlineStr">
+        <is>
+          <t>[M21]  Plywood ile düz yüzeyli betonarme kalıbı — silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D439" s="21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E439" s="22" t="n"/>
+      <c r="F439" s="22" t="n"/>
+      <c r="G439" s="22" t="n"/>
+      <c r="H439" s="22" t="n"/>
+      <c r="I439" s="22" t="n"/>
+      <c r="J439" s="22" t="n"/>
+    </row>
+    <row r="440" ht="20" customHeight="1">
+      <c r="A440" s="6" t="n"/>
+      <c r="B440" s="6" t="n"/>
+      <c r="C440" s="23" t="inlineStr">
+        <is>
+          <t>Radye temel yan yüzleri: 4 yüz x 2 kaide, boy 2,90 m, yükseklik 0,40 m — proje METRAJ tablosu 4,64 m²/kaide</t>
+        </is>
+      </c>
+      <c r="D440" s="6" t="n"/>
+      <c r="E440" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="F439" s="6" t="n"/>
-      <c r="G439" s="29" t="n">
+      <c r="F440" s="6" t="n"/>
+      <c r="G440" s="29" t="n">
         <v>2.9</v>
       </c>
-      <c r="H439" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I439" s="24">
-        <f>E439*G439*H439</f>
-        <v/>
-      </c>
-      <c r="J439" s="6" t="n"/>
-    </row>
-    <row r="440">
-      <c r="A440" s="22" t="n"/>
-      <c r="B440" s="22" t="n"/>
-      <c r="C440" s="25" t="inlineStr">
+      <c r="H440" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I440" s="24">
+        <f>E440*G440*H440</f>
+        <v/>
+      </c>
+      <c r="J440" s="6" t="n"/>
+    </row>
+    <row r="441" ht="30" customHeight="1">
+      <c r="A441" s="6" t="n"/>
+      <c r="B441" s="6" t="n"/>
+      <c r="C441" s="23" t="inlineStr">
+        <is>
+          <t>SB01…SB04 kolon yüzleri: 4 kolon x 4 yüz x 2 kaide = 32; genişlik 0,40 m, yükseklik 1,10 m — proje METRAJ tablosu 7,04 m²/kaide</t>
+        </is>
+      </c>
+      <c r="D441" s="6" t="n"/>
+      <c r="E441" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="F441" s="6" t="n"/>
+      <c r="G441" s="29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H441" s="29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I441" s="24">
+        <f>E441*G441*H441</f>
+        <v/>
+      </c>
+      <c r="J441" s="6" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="22" t="n"/>
+      <c r="B442" s="22" t="n"/>
+      <c r="C442" s="25" t="inlineStr">
         <is>
           <t>M21 TOPLAMI</t>
         </is>
       </c>
-      <c r="D440" s="26" t="inlineStr">
+      <c r="D442" s="26" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E440" s="22" t="n"/>
-      <c r="F440" s="22" t="n"/>
-      <c r="G440" s="22" t="n"/>
-      <c r="H440" s="22" t="n"/>
-      <c r="I440" s="22" t="n"/>
-      <c r="J440" s="27">
-        <f>SUM(I439:I439)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="441" ht="22" customHeight="1">
-      <c r="A441" s="19" t="n">
+      <c r="E442" s="22" t="n"/>
+      <c r="F442" s="22" t="n"/>
+      <c r="G442" s="22" t="n"/>
+      <c r="H442" s="22" t="n"/>
+      <c r="I442" s="22" t="n"/>
+      <c r="J442" s="27">
+        <f>SUM(I440:I441)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="443" ht="22" customHeight="1">
+      <c r="A443" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B441" s="20" t="inlineStr">
+      <c r="B443" s="20" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="C441" s="8" t="inlineStr">
+      <c r="C443" s="8" t="inlineStr">
         <is>
           <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo ve silo kaideleri</t>
         </is>
       </c>
-      <c r="D441" s="21" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="E441" s="22" t="n"/>
-      <c r="F441" s="22" t="n"/>
-      <c r="G441" s="22" t="n"/>
-      <c r="H441" s="22" t="n"/>
-      <c r="I441" s="22" t="n"/>
-      <c r="J441" s="22" t="n"/>
-    </row>
-    <row r="442" ht="12" customHeight="1">
-      <c r="A442" s="6" t="n"/>
-      <c r="B442" s="6" t="n"/>
-      <c r="C442" s="23" t="inlineStr">
-        <is>
-          <t>Silo kaideleri: 2.90x2.90x0.50 m³ x 2, 90 kg/m³</t>
-        </is>
-      </c>
-      <c r="D442" s="6" t="n"/>
-      <c r="E442" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F442" s="29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G442" s="29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H442" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I442" s="24">
-        <f>E442*F442*G442*H442*J442</f>
-        <v/>
-      </c>
-      <c r="J442" s="30" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" s="22" t="n"/>
-      <c r="B443" s="22" t="n"/>
-      <c r="C443" s="25" t="inlineStr">
-        <is>
-          <t>M26 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D443" s="26" t="inlineStr">
+      <c r="D443" s="21" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
@@ -15520,209 +15547,201 @@
       <c r="G443" s="22" t="n"/>
       <c r="H443" s="22" t="n"/>
       <c r="I443" s="22" t="n"/>
-      <c r="J443" s="27">
-        <f>SUM(I442:I442)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="444"/>
-    <row r="445" ht="20" customHeight="1">
-      <c r="A445" s="18" t="inlineStr">
+      <c r="J443" s="22" t="n"/>
+    </row>
+    <row r="444" ht="20" customHeight="1">
+      <c r="A444" s="6" t="n"/>
+      <c r="B444" s="6" t="n"/>
+      <c r="C444" s="23" t="inlineStr">
+        <is>
+          <t>Silo kaideleri — proje METRAJ tabloları: radye 198,80 + kolonlar 72,59 = 271,39 kg/kaide; 2 kaide</t>
+        </is>
+      </c>
+      <c r="D444" s="6" t="n"/>
+      <c r="E444" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F444" s="6" t="n"/>
+      <c r="G444" s="6" t="n"/>
+      <c r="H444" s="6" t="n"/>
+      <c r="I444" s="24">
+        <f>E444*J444</f>
+        <v/>
+      </c>
+      <c r="J444" s="30" t="n">
+        <v>0.27139</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="22" t="n"/>
+      <c r="B445" s="22" t="n"/>
+      <c r="C445" s="25" t="inlineStr">
+        <is>
+          <t>M26 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D445" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E445" s="22" t="n"/>
+      <c r="F445" s="22" t="n"/>
+      <c r="G445" s="22" t="n"/>
+      <c r="H445" s="22" t="n"/>
+      <c r="I445" s="22" t="n"/>
+      <c r="J445" s="27">
+        <f>SUM(I444:I444)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="446" ht="15" customHeight="1">
+      <c r="A446" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B446" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="C446" s="8" t="inlineStr">
+        <is>
+          <t>[M28]  Ø14-Ø28 nervürlü beton çelik çubuğu — silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D446" s="21" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E446" s="22" t="n"/>
+      <c r="F446" s="22" t="n"/>
+      <c r="G446" s="22" t="n"/>
+      <c r="H446" s="22" t="n"/>
+      <c r="I446" s="22" t="n"/>
+      <c r="J446" s="22" t="n"/>
+    </row>
+    <row r="447" ht="20" customHeight="1">
+      <c r="A447" s="6" t="n"/>
+      <c r="B447" s="6" t="n"/>
+      <c r="C447" s="23" t="inlineStr">
+        <is>
+          <t>Proje METRAJ tabloları: radye kolon filizleri 92,70 + bodrum kat kolonları 85,70 = 178,40 kg/kaide; 2 kaide</t>
+        </is>
+      </c>
+      <c r="D447" s="6" t="n"/>
+      <c r="E447" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F447" s="6" t="n"/>
+      <c r="G447" s="6" t="n"/>
+      <c r="H447" s="6" t="n"/>
+      <c r="I447" s="24">
+        <f>E447*J447</f>
+        <v/>
+      </c>
+      <c r="J447" s="30" t="n">
+        <v>0.1784</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="22" t="n"/>
+      <c r="B448" s="22" t="n"/>
+      <c r="C448" s="25" t="inlineStr">
+        <is>
+          <t>M28 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D448" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E448" s="22" t="n"/>
+      <c r="F448" s="22" t="n"/>
+      <c r="G448" s="22" t="n"/>
+      <c r="H448" s="22" t="n"/>
+      <c r="I448" s="22" t="n"/>
+      <c r="J448" s="27">
+        <f>SUM(I447:I447)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="449"/>
+    <row r="450" ht="20" customHeight="1">
+      <c r="A450" s="18" t="inlineStr">
         <is>
           <t>Yapı/Bina Adı: SU DEPOSU</t>
         </is>
       </c>
     </row>
-    <row r="446" ht="28" customHeight="1">
-      <c r="A446" s="7" t="inlineStr">
+    <row r="451" ht="28" customHeight="1">
+      <c r="A451" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B446" s="7" t="inlineStr">
+      <c r="B451" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="C446" s="7" t="inlineStr">
+      <c r="C451" s="7" t="inlineStr">
         <is>
           <t>Tanımı / Ölçünün Alındığı Yer</t>
         </is>
       </c>
-      <c r="D446" s="7" t="inlineStr">
+      <c r="D451" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="E446" s="7" t="inlineStr">
+      <c r="E451" s="7" t="inlineStr">
         <is>
           <t>Adet</t>
         </is>
       </c>
-      <c r="F446" s="7" t="inlineStr">
+      <c r="F451" s="7" t="inlineStr">
         <is>
           <t>En (m)</t>
         </is>
       </c>
-      <c r="G446" s="7" t="inlineStr">
+      <c r="G451" s="7" t="inlineStr">
         <is>
           <t>Boy (m)</t>
         </is>
       </c>
-      <c r="H446" s="7" t="inlineStr">
+      <c r="H451" s="7" t="inlineStr">
         <is>
           <t>Yükseklik (m)</t>
         </is>
       </c>
-      <c r="I446" s="7" t="inlineStr">
+      <c r="I451" s="7" t="inlineStr">
         <is>
           <t>Miktar</t>
         </is>
       </c>
-      <c r="J446" s="7" t="inlineStr">
+      <c r="J451" s="7" t="inlineStr">
         <is>
           <t>Toplam Miktar</t>
         </is>
       </c>
     </row>
-    <row r="447" ht="22" customHeight="1">
-      <c r="A447" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B447" s="20" t="inlineStr">
+    <row r="452" ht="22" customHeight="1">
+      <c r="A452" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B452" s="20" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="C447" s="8" t="inlineStr">
+      <c r="C452" s="8" t="inlineStr">
         <is>
           <t>[M05]  Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
         </is>
       </c>
-      <c r="D447" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E447" s="22" t="n"/>
-      <c r="F447" s="22" t="n"/>
-      <c r="G447" s="22" t="n"/>
-      <c r="H447" s="22" t="n"/>
-      <c r="I447" s="22" t="n"/>
-      <c r="J447" s="22" t="n"/>
-    </row>
-    <row r="448" ht="20" customHeight="1">
-      <c r="A448" s="6" t="n"/>
-      <c r="B448" s="6" t="n"/>
-      <c r="C448" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu: dış 4.00x3.00; 1,00 m çalışma payı -&gt; 6.00x5.00; derinlik 3.55 m</t>
-        </is>
-      </c>
-      <c r="D448" s="6" t="n"/>
-      <c r="E448" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F448" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G448" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H448" s="29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="I448" s="24">
-        <f>E448*F448*G448*H448</f>
-        <v/>
-      </c>
-      <c r="J448" s="6" t="n"/>
-    </row>
-    <row r="449">
-      <c r="A449" s="22" t="n"/>
-      <c r="B449" s="22" t="n"/>
-      <c r="C449" s="25" t="inlineStr">
-        <is>
-          <t>M05 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D449" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E449" s="22" t="n"/>
-      <c r="F449" s="22" t="n"/>
-      <c r="G449" s="22" t="n"/>
-      <c r="H449" s="22" t="n"/>
-      <c r="I449" s="22" t="n"/>
-      <c r="J449" s="27">
-        <f>SUM(I448:I448)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="450" ht="22" customHeight="1">
-      <c r="A450" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B450" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C450" s="8" t="inlineStr">
-        <is>
-          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
-        </is>
-      </c>
-      <c r="D450" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E450" s="22" t="n"/>
-      <c r="F450" s="22" t="n"/>
-      <c r="G450" s="22" t="n"/>
-      <c r="H450" s="22" t="n"/>
-      <c r="I450" s="22" t="n"/>
-      <c r="J450" s="22" t="n"/>
-    </row>
-    <row r="451" ht="12" customHeight="1">
-      <c r="A451" s="6" t="n"/>
-      <c r="B451" s="6" t="n"/>
-      <c r="C451" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu (4.00x3.00 + 0,10 taşma)</t>
-        </is>
-      </c>
-      <c r="D451" s="6" t="n"/>
-      <c r="E451" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F451" s="29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G451" s="29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H451" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I451" s="24">
-        <f>E451*F451*G451*H451</f>
-        <v/>
-      </c>
-      <c r="J451" s="6" t="n"/>
-    </row>
-    <row r="452">
-      <c r="A452" s="22" t="n"/>
-      <c r="B452" s="22" t="n"/>
-      <c r="C452" s="25" t="inlineStr">
-        <is>
-          <t>M11 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D452" s="26" t="inlineStr">
+      <c r="D452" s="21" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
@@ -15732,97 +15751,90 @@
       <c r="G452" s="22" t="n"/>
       <c r="H452" s="22" t="n"/>
       <c r="I452" s="22" t="n"/>
-      <c r="J452" s="27">
-        <f>SUM(I451:I451)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="453" ht="22" customHeight="1">
-      <c r="A453" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B453" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C453" s="8" t="inlineStr">
-        <is>
-          <t>[M16]  C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
-        </is>
-      </c>
-      <c r="D453" s="21" t="inlineStr">
+      <c r="J452" s="22" t="n"/>
+    </row>
+    <row r="453" ht="20" customHeight="1">
+      <c r="A453" s="6" t="n"/>
+      <c r="B453" s="6" t="n"/>
+      <c r="C453" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu: dış 4.00x3.00; 1,00 m çalışma payı -&gt; 6.00x5.00; derinlik 3.55 m</t>
+        </is>
+      </c>
+      <c r="D453" s="6" t="n"/>
+      <c r="E453" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F453" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G453" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H453" s="29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I453" s="24">
+        <f>E453*F453*G453*H453</f>
+        <v/>
+      </c>
+      <c r="J453" s="6" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="22" t="n"/>
+      <c r="B454" s="22" t="n"/>
+      <c r="C454" s="25" t="inlineStr">
+        <is>
+          <t>M05 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D454" s="26" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E453" s="22" t="n"/>
-      <c r="F453" s="22" t="n"/>
-      <c r="G453" s="22" t="n"/>
-      <c r="H453" s="22" t="n"/>
-      <c r="I453" s="22" t="n"/>
-      <c r="J453" s="22" t="n"/>
-    </row>
-    <row r="454" ht="12" customHeight="1">
-      <c r="A454" s="6" t="n"/>
-      <c r="B454" s="6" t="n"/>
-      <c r="C454" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu radye 30 cm (dış 4.00x3.00)</t>
-        </is>
-      </c>
-      <c r="D454" s="6" t="n"/>
-      <c r="E454" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F454" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G454" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H454" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I454" s="24">
-        <f>E454*F454*G454*H454</f>
-        <v/>
-      </c>
-      <c r="J454" s="6" t="n"/>
-    </row>
-    <row r="455" ht="12" customHeight="1">
-      <c r="A455" s="6" t="n"/>
-      <c r="B455" s="6" t="n"/>
-      <c r="C455" s="23" t="inlineStr">
-        <is>
-          <t>Su deposu perdeleri: orta çevre 2x(3.75+2.75) = 13.00 m</t>
-        </is>
-      </c>
-      <c r="D455" s="6" t="n"/>
-      <c r="E455" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F455" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G455" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="H455" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I455" s="24">
-        <f>E455*F455*G455*H455</f>
-        <v/>
-      </c>
-      <c r="J455" s="6" t="n"/>
+      <c r="E454" s="22" t="n"/>
+      <c r="F454" s="22" t="n"/>
+      <c r="G454" s="22" t="n"/>
+      <c r="H454" s="22" t="n"/>
+      <c r="I454" s="22" t="n"/>
+      <c r="J454" s="27">
+        <f>SUM(I453:I453)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="455" ht="22" customHeight="1">
+      <c r="A455" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B455" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="C455" s="8" t="inlineStr">
+        <is>
+          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
+        </is>
+      </c>
+      <c r="D455" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E455" s="22" t="n"/>
+      <c r="F455" s="22" t="n"/>
+      <c r="G455" s="22" t="n"/>
+      <c r="H455" s="22" t="n"/>
+      <c r="I455" s="22" t="n"/>
+      <c r="J455" s="22" t="n"/>
     </row>
     <row r="456" ht="12" customHeight="1">
       <c r="A456" s="6" t="n"/>
       <c r="B456" s="6" t="n"/>
       <c r="C456" s="23" t="inlineStr">
         <is>
-          <t>Su deposu üst döşemesi 15 cm</t>
+          <t>Su deposu (4.00x3.00 + 0,10 taşma)</t>
         </is>
       </c>
       <c r="D456" s="6" t="n"/>
@@ -15830,13 +15842,13 @@
         <v>1</v>
       </c>
       <c r="F456" s="29" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G456" s="29" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H456" s="29" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I456" s="24">
         <f>E456*F456*G456*H456</f>
@@ -15849,7 +15861,7 @@
       <c r="B457" s="22" t="n"/>
       <c r="C457" s="25" t="inlineStr">
         <is>
-          <t>M16 TOPLAMI</t>
+          <t>M11 TOPLAMI</t>
         </is>
       </c>
       <c r="D457" s="26" t="inlineStr">
@@ -15863,27 +15875,27 @@
       <c r="H457" s="22" t="n"/>
       <c r="I457" s="22" t="n"/>
       <c r="J457" s="27">
-        <f>SUM(I454:I456)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="458" ht="15" customHeight="1">
+        <f>SUM(I456:I456)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458" ht="22" customHeight="1">
       <c r="A458" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B458" s="20" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="C458" s="8" t="inlineStr">
         <is>
-          <t>[M20]  Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
+          <t>[M16]  C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
         </is>
       </c>
       <c r="D458" s="21" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E458" s="22" t="n"/>
@@ -15898,22 +15910,24 @@
       <c r="B459" s="6" t="n"/>
       <c r="C459" s="23" t="inlineStr">
         <is>
-          <t>Su deposu radye çevresi 2x(4.00+3.00) = 14.00 m x 0,40</t>
+          <t>Su deposu radye 30 cm (dış 4.00x3.00)</t>
         </is>
       </c>
       <c r="D459" s="6" t="n"/>
       <c r="E459" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F459" s="6" t="n"/>
+      <c r="F459" s="29" t="n">
+        <v>3</v>
+      </c>
       <c r="G459" s="29" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H459" s="29" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I459" s="24">
-        <f>E459*G459*H459</f>
+        <f>E459*F459*G459*H459</f>
         <v/>
       </c>
       <c r="J459" s="6" t="n"/>
@@ -15923,14 +15937,16 @@
       <c r="B460" s="6" t="n"/>
       <c r="C460" s="23" t="inlineStr">
         <is>
-          <t>Su deposu perde iki yüz (13.00 m x 3.00 m)</t>
+          <t>Su deposu perdeleri: orta çevre 2x(3.75+2.75) = 13.00 m</t>
         </is>
       </c>
       <c r="D460" s="6" t="n"/>
       <c r="E460" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F460" s="6" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F460" s="29" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G460" s="29" t="n">
         <v>13</v>
       </c>
@@ -15938,7 +15954,7 @@
         <v>3</v>
       </c>
       <c r="I460" s="24">
-        <f>E460*G460*H460</f>
+        <f>E460*F460*G460*H460</f>
         <v/>
       </c>
       <c r="J460" s="6" t="n"/>
@@ -15948,7 +15964,7 @@
       <c r="B461" s="6" t="n"/>
       <c r="C461" s="23" t="inlineStr">
         <is>
-          <t>Su deposu tavan kalıbı</t>
+          <t>Su deposu üst döşemesi 15 cm</t>
         </is>
       </c>
       <c r="D461" s="6" t="n"/>
@@ -15961,9 +15977,11 @@
       <c r="G461" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="H461" s="6" t="n"/>
+      <c r="H461" s="29" t="n">
+        <v>0.15</v>
+      </c>
       <c r="I461" s="24">
-        <f>E461*F461*G461</f>
+        <f>E461*F461*G461*H461</f>
         <v/>
       </c>
       <c r="J461" s="6" t="n"/>
@@ -15973,12 +15991,12 @@
       <c r="B462" s="22" t="n"/>
       <c r="C462" s="25" t="inlineStr">
         <is>
-          <t>M20 TOPLAMI</t>
+          <t>M16 TOPLAMI</t>
         </is>
       </c>
       <c r="D462" s="26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E462" s="22" t="n"/>
@@ -15991,23 +16009,23 @@
         <v/>
       </c>
     </row>
-    <row r="463" ht="22" customHeight="1">
+    <row r="463" ht="15" customHeight="1">
       <c r="A463" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B463" s="20" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="C463" s="8" t="inlineStr">
         <is>
-          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo ve silo kaideleri</t>
+          <t>[M20]  Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
         </is>
       </c>
       <c r="D463" s="21" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E463" s="22" t="n"/>
@@ -16017,12 +16035,12 @@
       <c r="I463" s="22" t="n"/>
       <c r="J463" s="22" t="n"/>
     </row>
-    <row r="464" ht="20" customHeight="1">
+    <row r="464" ht="12" customHeight="1">
       <c r="A464" s="6" t="n"/>
       <c r="B464" s="6" t="n"/>
       <c r="C464" s="23" t="inlineStr">
         <is>
-          <t>Su deposu radye ve döşeme — proje metrajı 223,70+32,90 = 256,60 kg</t>
+          <t>Su deposu radye çevresi 2x(4.00+3.00) = 14.00 m x 0,40</t>
         </is>
       </c>
       <c r="D464" s="6" t="n"/>
@@ -16030,31 +16048,31 @@
         <v>1</v>
       </c>
       <c r="F464" s="6" t="n"/>
-      <c r="G464" s="6" t="n"/>
-      <c r="H464" s="6" t="n"/>
+      <c r="G464" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H464" s="29" t="n">
+        <v>0.4</v>
+      </c>
       <c r="I464" s="24">
-        <f>E464*J464</f>
-        <v/>
-      </c>
-      <c r="J464" s="30" t="n">
-        <v>0.2566</v>
-      </c>
+        <f>E464*G464*H464</f>
+        <v/>
+      </c>
+      <c r="J464" s="6" t="n"/>
     </row>
     <row r="465" ht="12" customHeight="1">
       <c r="A465" s="6" t="n"/>
       <c r="B465" s="6" t="n"/>
       <c r="C465" s="23" t="inlineStr">
         <is>
-          <t>Su deposu perdeleri: 13.00x0,25x3.00 m³, 100 kg/m³</t>
+          <t>Su deposu perde iki yüz (13.00 m x 3.00 m)</t>
         </is>
       </c>
       <c r="D465" s="6" t="n"/>
       <c r="E465" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F465" s="29" t="n">
-        <v>0.25</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F465" s="6" t="n"/>
       <c r="G465" s="29" t="n">
         <v>13</v>
       </c>
@@ -16062,234 +16080,235 @@
         <v>3</v>
       </c>
       <c r="I465" s="24">
-        <f>E465*F465*G465*H465*J465</f>
-        <v/>
-      </c>
-      <c r="J465" s="30" t="n">
+        <f>E465*G465*H465</f>
+        <v/>
+      </c>
+      <c r="J465" s="6" t="n"/>
+    </row>
+    <row r="466" ht="12" customHeight="1">
+      <c r="A466" s="6" t="n"/>
+      <c r="B466" s="6" t="n"/>
+      <c r="C466" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu tavan kalıbı</t>
+        </is>
+      </c>
+      <c r="D466" s="6" t="n"/>
+      <c r="E466" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F466" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G466" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H466" s="6" t="n"/>
+      <c r="I466" s="24">
+        <f>E466*F466*G466</f>
+        <v/>
+      </c>
+      <c r="J466" s="6" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="22" t="n"/>
+      <c r="B467" s="22" t="n"/>
+      <c r="C467" s="25" t="inlineStr">
+        <is>
+          <t>M20 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D467" s="26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E467" s="22" t="n"/>
+      <c r="F467" s="22" t="n"/>
+      <c r="G467" s="22" t="n"/>
+      <c r="H467" s="22" t="n"/>
+      <c r="I467" s="22" t="n"/>
+      <c r="J467" s="27">
+        <f>SUM(I464:I466)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="468" ht="22" customHeight="1">
+      <c r="A468" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B468" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="C468" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo ve silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D468" s="21" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E468" s="22" t="n"/>
+      <c r="F468" s="22" t="n"/>
+      <c r="G468" s="22" t="n"/>
+      <c r="H468" s="22" t="n"/>
+      <c r="I468" s="22" t="n"/>
+      <c r="J468" s="22" t="n"/>
+    </row>
+    <row r="469" ht="20" customHeight="1">
+      <c r="A469" s="6" t="n"/>
+      <c r="B469" s="6" t="n"/>
+      <c r="C469" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu radye ve döşeme — proje metrajı 223,70+32,90 = 256,60 kg</t>
+        </is>
+      </c>
+      <c r="D469" s="6" t="n"/>
+      <c r="E469" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F469" s="6" t="n"/>
+      <c r="G469" s="6" t="n"/>
+      <c r="H469" s="6" t="n"/>
+      <c r="I469" s="24">
+        <f>E469*J469</f>
+        <v/>
+      </c>
+      <c r="J469" s="30" t="n">
+        <v>0.2566</v>
+      </c>
+    </row>
+    <row r="470" ht="12" customHeight="1">
+      <c r="A470" s="6" t="n"/>
+      <c r="B470" s="6" t="n"/>
+      <c r="C470" s="23" t="inlineStr">
+        <is>
+          <t>Su deposu perdeleri: 13.00x0,25x3.00 m³, 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D470" s="6" t="n"/>
+      <c r="E470" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F470" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G470" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="H470" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I470" s="24">
+        <f>E470*F470*G470*H470*J470</f>
+        <v/>
+      </c>
+      <c r="J470" s="30" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="466">
-      <c r="A466" s="22" t="n"/>
-      <c r="B466" s="22" t="n"/>
-      <c r="C466" s="25" t="inlineStr">
+    <row r="471">
+      <c r="A471" s="22" t="n"/>
+      <c r="B471" s="22" t="n"/>
+      <c r="C471" s="25" t="inlineStr">
         <is>
           <t>M26 TOPLAMI</t>
         </is>
       </c>
-      <c r="D466" s="26" t="inlineStr">
+      <c r="D471" s="26" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="E466" s="22" t="n"/>
-      <c r="F466" s="22" t="n"/>
-      <c r="G466" s="22" t="n"/>
-      <c r="H466" s="22" t="n"/>
-      <c r="I466" s="22" t="n"/>
-      <c r="J466" s="27">
-        <f>SUM(I464:I465)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="467"/>
-    <row r="468" ht="20" customHeight="1">
-      <c r="A468" s="18" t="inlineStr">
+      <c r="E471" s="22" t="n"/>
+      <c r="F471" s="22" t="n"/>
+      <c r="G471" s="22" t="n"/>
+      <c r="H471" s="22" t="n"/>
+      <c r="I471" s="22" t="n"/>
+      <c r="J471" s="27">
+        <f>SUM(I469:I470)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="472"/>
+    <row r="473" ht="20" customHeight="1">
+      <c r="A473" s="18" t="inlineStr">
         <is>
           <t>Yapı/Bina Adı: YAĞMUR SUYU DEPOSU</t>
         </is>
       </c>
     </row>
-    <row r="469" ht="28" customHeight="1">
-      <c r="A469" s="7" t="inlineStr">
+    <row r="474" ht="28" customHeight="1">
+      <c r="A474" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B469" s="7" t="inlineStr">
+      <c r="B474" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="C469" s="7" t="inlineStr">
+      <c r="C474" s="7" t="inlineStr">
         <is>
           <t>Tanımı / Ölçünün Alındığı Yer</t>
         </is>
       </c>
-      <c r="D469" s="7" t="inlineStr">
+      <c r="D474" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="E469" s="7" t="inlineStr">
+      <c r="E474" s="7" t="inlineStr">
         <is>
           <t>Adet</t>
         </is>
       </c>
-      <c r="F469" s="7" t="inlineStr">
+      <c r="F474" s="7" t="inlineStr">
         <is>
           <t>En (m)</t>
         </is>
       </c>
-      <c r="G469" s="7" t="inlineStr">
+      <c r="G474" s="7" t="inlineStr">
         <is>
           <t>Boy (m)</t>
         </is>
       </c>
-      <c r="H469" s="7" t="inlineStr">
+      <c r="H474" s="7" t="inlineStr">
         <is>
           <t>Yükseklik (m)</t>
         </is>
       </c>
-      <c r="I469" s="7" t="inlineStr">
+      <c r="I474" s="7" t="inlineStr">
         <is>
           <t>Miktar</t>
         </is>
       </c>
-      <c r="J469" s="7" t="inlineStr">
+      <c r="J474" s="7" t="inlineStr">
         <is>
           <t>Toplam Miktar</t>
         </is>
       </c>
     </row>
-    <row r="470" ht="22" customHeight="1">
-      <c r="A470" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B470" s="20" t="inlineStr">
+    <row r="475" ht="22" customHeight="1">
+      <c r="A475" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B475" s="20" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="C470" s="8" t="inlineStr">
+      <c r="C475" s="8" t="inlineStr">
         <is>
           <t>[M05]  Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
         </is>
       </c>
-      <c r="D470" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E470" s="22" t="n"/>
-      <c r="F470" s="22" t="n"/>
-      <c r="G470" s="22" t="n"/>
-      <c r="H470" s="22" t="n"/>
-      <c r="I470" s="22" t="n"/>
-      <c r="J470" s="22" t="n"/>
-    </row>
-    <row r="471" ht="20" customHeight="1">
-      <c r="A471" s="6" t="n"/>
-      <c r="B471" s="6" t="n"/>
-      <c r="C471" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu: dış 3.00x3.00; 1,00 m çalışma payı -&gt; 5.00x5.00; derinlik 3.55 m</t>
-        </is>
-      </c>
-      <c r="D471" s="6" t="n"/>
-      <c r="E471" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F471" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G471" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="H471" s="29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="I471" s="24">
-        <f>E471*F471*G471*H471</f>
-        <v/>
-      </c>
-      <c r="J471" s="6" t="n"/>
-    </row>
-    <row r="472">
-      <c r="A472" s="22" t="n"/>
-      <c r="B472" s="22" t="n"/>
-      <c r="C472" s="25" t="inlineStr">
-        <is>
-          <t>M05 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D472" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E472" s="22" t="n"/>
-      <c r="F472" s="22" t="n"/>
-      <c r="G472" s="22" t="n"/>
-      <c r="H472" s="22" t="n"/>
-      <c r="I472" s="22" t="n"/>
-      <c r="J472" s="27">
-        <f>SUM(I471:I471)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="473" ht="22" customHeight="1">
-      <c r="A473" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B473" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="C473" s="8" t="inlineStr">
-        <is>
-          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
-        </is>
-      </c>
-      <c r="D473" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E473" s="22" t="n"/>
-      <c r="F473" s="22" t="n"/>
-      <c r="G473" s="22" t="n"/>
-      <c r="H473" s="22" t="n"/>
-      <c r="I473" s="22" t="n"/>
-      <c r="J473" s="22" t="n"/>
-    </row>
-    <row r="474" ht="12" customHeight="1">
-      <c r="A474" s="6" t="n"/>
-      <c r="B474" s="6" t="n"/>
-      <c r="C474" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu (3.00x3.00 + 0,10 taşma)</t>
-        </is>
-      </c>
-      <c r="D474" s="6" t="n"/>
-      <c r="E474" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F474" s="29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G474" s="29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H474" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I474" s="24">
-        <f>E474*F474*G474*H474</f>
-        <v/>
-      </c>
-      <c r="J474" s="6" t="n"/>
-    </row>
-    <row r="475">
-      <c r="A475" s="22" t="n"/>
-      <c r="B475" s="22" t="n"/>
-      <c r="C475" s="25" t="inlineStr">
-        <is>
-          <t>M11 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D475" s="26" t="inlineStr">
+      <c r="D475" s="21" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
@@ -16299,97 +16318,90 @@
       <c r="G475" s="22" t="n"/>
       <c r="H475" s="22" t="n"/>
       <c r="I475" s="22" t="n"/>
-      <c r="J475" s="27">
-        <f>SUM(I474:I474)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="476" ht="22" customHeight="1">
-      <c r="A476" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B476" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C476" s="8" t="inlineStr">
-        <is>
-          <t>[M16]  C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
-        </is>
-      </c>
-      <c r="D476" s="21" t="inlineStr">
+      <c r="J475" s="22" t="n"/>
+    </row>
+    <row r="476" ht="20" customHeight="1">
+      <c r="A476" s="6" t="n"/>
+      <c r="B476" s="6" t="n"/>
+      <c r="C476" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu: dış 3.00x3.00; 1,00 m çalışma payı -&gt; 5.00x5.00; derinlik 3.55 m</t>
+        </is>
+      </c>
+      <c r="D476" s="6" t="n"/>
+      <c r="E476" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F476" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G476" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H476" s="29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I476" s="24">
+        <f>E476*F476*G476*H476</f>
+        <v/>
+      </c>
+      <c r="J476" s="6" t="n"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="22" t="n"/>
+      <c r="B477" s="22" t="n"/>
+      <c r="C477" s="25" t="inlineStr">
+        <is>
+          <t>M05 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D477" s="26" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E476" s="22" t="n"/>
-      <c r="F476" s="22" t="n"/>
-      <c r="G476" s="22" t="n"/>
-      <c r="H476" s="22" t="n"/>
-      <c r="I476" s="22" t="n"/>
-      <c r="J476" s="22" t="n"/>
-    </row>
-    <row r="477" ht="12" customHeight="1">
-      <c r="A477" s="6" t="n"/>
-      <c r="B477" s="6" t="n"/>
-      <c r="C477" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu radye 30 cm (dış 3.00x3.00)</t>
-        </is>
-      </c>
-      <c r="D477" s="6" t="n"/>
-      <c r="E477" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F477" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G477" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H477" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I477" s="24">
-        <f>E477*F477*G477*H477</f>
-        <v/>
-      </c>
-      <c r="J477" s="6" t="n"/>
-    </row>
-    <row r="478" ht="20" customHeight="1">
-      <c r="A478" s="6" t="n"/>
-      <c r="B478" s="6" t="n"/>
-      <c r="C478" s="23" t="inlineStr">
-        <is>
-          <t>Yağmur suyu deposu perdeleri: orta çevre 2x(2.75+2.75) = 11.00 m</t>
-        </is>
-      </c>
-      <c r="D478" s="6" t="n"/>
-      <c r="E478" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F478" s="29" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G478" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="H478" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="I478" s="24">
-        <f>E478*F478*G478*H478</f>
-        <v/>
-      </c>
-      <c r="J478" s="6" t="n"/>
+      <c r="E477" s="22" t="n"/>
+      <c r="F477" s="22" t="n"/>
+      <c r="G477" s="22" t="n"/>
+      <c r="H477" s="22" t="n"/>
+      <c r="I477" s="22" t="n"/>
+      <c r="J477" s="27">
+        <f>SUM(I476:I476)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="478" ht="22" customHeight="1">
+      <c r="A478" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B478" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="C478" s="8" t="inlineStr">
+        <is>
+          <t>[M11]  C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
+        </is>
+      </c>
+      <c r="D478" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E478" s="22" t="n"/>
+      <c r="F478" s="22" t="n"/>
+      <c r="G478" s="22" t="n"/>
+      <c r="H478" s="22" t="n"/>
+      <c r="I478" s="22" t="n"/>
+      <c r="J478" s="22" t="n"/>
     </row>
     <row r="479" ht="12" customHeight="1">
       <c r="A479" s="6" t="n"/>
       <c r="B479" s="6" t="n"/>
       <c r="C479" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu üst döşemesi 15 cm</t>
+          <t>Yağmur suyu deposu (3.00x3.00 + 0,10 taşma)</t>
         </is>
       </c>
       <c r="D479" s="6" t="n"/>
@@ -16397,13 +16409,13 @@
         <v>1</v>
       </c>
       <c r="F479" s="29" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G479" s="29" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H479" s="29" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I479" s="24">
         <f>E479*F479*G479*H479</f>
@@ -16416,7 +16428,7 @@
       <c r="B480" s="22" t="n"/>
       <c r="C480" s="25" t="inlineStr">
         <is>
-          <t>M16 TOPLAMI</t>
+          <t>M11 TOPLAMI</t>
         </is>
       </c>
       <c r="D480" s="26" t="inlineStr">
@@ -16430,27 +16442,27 @@
       <c r="H480" s="22" t="n"/>
       <c r="I480" s="22" t="n"/>
       <c r="J480" s="27">
-        <f>SUM(I477:I479)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="481" ht="15" customHeight="1">
+        <f>SUM(I479:I479)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="481" ht="22" customHeight="1">
       <c r="A481" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B481" s="20" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="C481" s="8" t="inlineStr">
         <is>
-          <t>[M20]  Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
+          <t>[M16]  C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
         </is>
       </c>
       <c r="D481" s="21" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E481" s="22" t="n"/>
@@ -16460,44 +16472,48 @@
       <c r="I481" s="22" t="n"/>
       <c r="J481" s="22" t="n"/>
     </row>
-    <row r="482" ht="20" customHeight="1">
+    <row r="482" ht="12" customHeight="1">
       <c r="A482" s="6" t="n"/>
       <c r="B482" s="6" t="n"/>
       <c r="C482" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu radye çevresi 2x(3.00+3.00) = 12.00 m x 0,40</t>
+          <t>Yağmur suyu deposu radye 30 cm (dış 3.00x3.00)</t>
         </is>
       </c>
       <c r="D482" s="6" t="n"/>
       <c r="E482" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F482" s="6" t="n"/>
+      <c r="F482" s="29" t="n">
+        <v>3</v>
+      </c>
       <c r="G482" s="29" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H482" s="29" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I482" s="24">
-        <f>E482*G482*H482</f>
+        <f>E482*F482*G482*H482</f>
         <v/>
       </c>
       <c r="J482" s="6" t="n"/>
     </row>
-    <row r="483" ht="12" customHeight="1">
+    <row r="483" ht="20" customHeight="1">
       <c r="A483" s="6" t="n"/>
       <c r="B483" s="6" t="n"/>
       <c r="C483" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu perde iki yüz (11.00 m x 3.00 m)</t>
+          <t>Yağmur suyu deposu perdeleri: orta çevre 2x(2.75+2.75) = 11.00 m</t>
         </is>
       </c>
       <c r="D483" s="6" t="n"/>
       <c r="E483" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F483" s="6" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F483" s="29" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G483" s="29" t="n">
         <v>11</v>
       </c>
@@ -16505,7 +16521,7 @@
         <v>3</v>
       </c>
       <c r="I483" s="24">
-        <f>E483*G483*H483</f>
+        <f>E483*F483*G483*H483</f>
         <v/>
       </c>
       <c r="J483" s="6" t="n"/>
@@ -16515,7 +16531,7 @@
       <c r="B484" s="6" t="n"/>
       <c r="C484" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu tavan kalıbı</t>
+          <t>Yağmur suyu deposu üst döşemesi 15 cm</t>
         </is>
       </c>
       <c r="D484" s="6" t="n"/>
@@ -16528,9 +16544,11 @@
       <c r="G484" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="H484" s="6" t="n"/>
+      <c r="H484" s="29" t="n">
+        <v>0.15</v>
+      </c>
       <c r="I484" s="24">
-        <f>E484*F484*G484</f>
+        <f>E484*F484*G484*H484</f>
         <v/>
       </c>
       <c r="J484" s="6" t="n"/>
@@ -16540,12 +16558,12 @@
       <c r="B485" s="22" t="n"/>
       <c r="C485" s="25" t="inlineStr">
         <is>
-          <t>M20 TOPLAMI</t>
+          <t>M16 TOPLAMI</t>
         </is>
       </c>
       <c r="D485" s="26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E485" s="22" t="n"/>
@@ -16558,23 +16576,23 @@
         <v/>
       </c>
     </row>
-    <row r="486" ht="22" customHeight="1">
+    <row r="486" ht="15" customHeight="1">
       <c r="A486" s="19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B486" s="20" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="C486" s="8" t="inlineStr">
         <is>
-          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo ve silo kaideleri</t>
+          <t>[M20]  Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
         </is>
       </c>
       <c r="D486" s="21" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E486" s="22" t="n"/>
@@ -16584,50 +16602,44 @@
       <c r="I486" s="22" t="n"/>
       <c r="J486" s="22" t="n"/>
     </row>
-    <row r="487" ht="12" customHeight="1">
+    <row r="487" ht="20" customHeight="1">
       <c r="A487" s="6" t="n"/>
       <c r="B487" s="6" t="n"/>
       <c r="C487" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu radyesi: 3.00x3.00x0,30 m³, 100 kg/m³</t>
+          <t>Yağmur suyu deposu radye çevresi 2x(3.00+3.00) = 12.00 m x 0,40</t>
         </is>
       </c>
       <c r="D487" s="6" t="n"/>
       <c r="E487" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F487" s="29" t="n">
-        <v>3</v>
-      </c>
+      <c r="F487" s="6" t="n"/>
       <c r="G487" s="29" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H487" s="29" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I487" s="24">
-        <f>E487*F487*G487*H487*J487</f>
-        <v/>
-      </c>
-      <c r="J487" s="30" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="488" ht="20" customHeight="1">
+        <f>E487*G487*H487</f>
+        <v/>
+      </c>
+      <c r="J487" s="6" t="n"/>
+    </row>
+    <row r="488" ht="12" customHeight="1">
       <c r="A488" s="6" t="n"/>
       <c r="B488" s="6" t="n"/>
       <c r="C488" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu perdeleri: 11.00x0,25x3.00 m³, 100 kg/m³</t>
+          <t>Yağmur suyu deposu perde iki yüz (11.00 m x 3.00 m)</t>
         </is>
       </c>
       <c r="D488" s="6" t="n"/>
       <c r="E488" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F488" s="29" t="n">
-        <v>0.25</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F488" s="6" t="n"/>
       <c r="G488" s="29" t="n">
         <v>11</v>
       </c>
@@ -16635,19 +16647,17 @@
         <v>3</v>
       </c>
       <c r="I488" s="24">
-        <f>E488*F488*G488*H488*J488</f>
-        <v/>
-      </c>
-      <c r="J488" s="30" t="n">
-        <v>0.1</v>
-      </c>
+        <f>E488*G488*H488</f>
+        <v/>
+      </c>
+      <c r="J488" s="6" t="n"/>
     </row>
     <row r="489" ht="12" customHeight="1">
       <c r="A489" s="6" t="n"/>
       <c r="B489" s="6" t="n"/>
       <c r="C489" s="23" t="inlineStr">
         <is>
-          <t>Yağmur suyu deposu döşemesi: 3.00x3.00x0,15 m³, 100 kg/m³</t>
+          <t>Yağmur suyu deposu tavan kalıbı</t>
         </is>
       </c>
       <c r="D489" s="6" t="n"/>
@@ -16660,28 +16670,24 @@
       <c r="G489" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="H489" s="29" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="H489" s="6" t="n"/>
       <c r="I489" s="24">
-        <f>E489*F489*G489*H489*J489</f>
-        <v/>
-      </c>
-      <c r="J489" s="30" t="n">
-        <v>0.1</v>
-      </c>
+        <f>E489*F489*G489</f>
+        <v/>
+      </c>
+      <c r="J489" s="6" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="22" t="n"/>
       <c r="B490" s="22" t="n"/>
       <c r="C490" s="25" t="inlineStr">
         <is>
-          <t>M26 TOPLAMI</t>
+          <t>M20 TOPLAMI</t>
         </is>
       </c>
       <c r="D490" s="26" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E490" s="22" t="n"/>
@@ -16694,254 +16700,266 @@
         <v/>
       </c>
     </row>
-    <row r="491"/>
-    <row r="492" ht="20" customHeight="1">
-      <c r="A492" s="18" t="inlineStr">
+    <row r="491" ht="22" customHeight="1">
+      <c r="A491" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B491" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="C491" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo ve silo kaideleri</t>
+        </is>
+      </c>
+      <c r="D491" s="21" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E491" s="22" t="n"/>
+      <c r="F491" s="22" t="n"/>
+      <c r="G491" s="22" t="n"/>
+      <c r="H491" s="22" t="n"/>
+      <c r="I491" s="22" t="n"/>
+      <c r="J491" s="22" t="n"/>
+    </row>
+    <row r="492" ht="12" customHeight="1">
+      <c r="A492" s="6" t="n"/>
+      <c r="B492" s="6" t="n"/>
+      <c r="C492" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu radyesi: 3.00x3.00x0,30 m³, 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D492" s="6" t="n"/>
+      <c r="E492" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F492" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G492" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H492" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I492" s="24">
+        <f>E492*F492*G492*H492*J492</f>
+        <v/>
+      </c>
+      <c r="J492" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="493" ht="20" customHeight="1">
+      <c r="A493" s="6" t="n"/>
+      <c r="B493" s="6" t="n"/>
+      <c r="C493" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu perdeleri: 11.00x0,25x3.00 m³, 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D493" s="6" t="n"/>
+      <c r="E493" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F493" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G493" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="H493" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I493" s="24">
+        <f>E493*F493*G493*H493*J493</f>
+        <v/>
+      </c>
+      <c r="J493" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="494" ht="12" customHeight="1">
+      <c r="A494" s="6" t="n"/>
+      <c r="B494" s="6" t="n"/>
+      <c r="C494" s="23" t="inlineStr">
+        <is>
+          <t>Yağmur suyu deposu döşemesi: 3.00x3.00x0,15 m³, 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="D494" s="6" t="n"/>
+      <c r="E494" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F494" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G494" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H494" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I494" s="24">
+        <f>E494*F494*G494*H494*J494</f>
+        <v/>
+      </c>
+      <c r="J494" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="22" t="n"/>
+      <c r="B495" s="22" t="n"/>
+      <c r="C495" s="25" t="inlineStr">
+        <is>
+          <t>M26 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D495" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E495" s="22" t="n"/>
+      <c r="F495" s="22" t="n"/>
+      <c r="G495" s="22" t="n"/>
+      <c r="H495" s="22" t="n"/>
+      <c r="I495" s="22" t="n"/>
+      <c r="J495" s="27">
+        <f>SUM(I492:I494)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="496"/>
+    <row r="497" ht="20" customHeight="1">
+      <c r="A497" s="18" t="inlineStr">
         <is>
           <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
         </is>
       </c>
     </row>
-    <row r="493" ht="28" customHeight="1">
-      <c r="A493" s="7" t="inlineStr">
+    <row r="498" ht="28" customHeight="1">
+      <c r="A498" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B493" s="7" t="inlineStr">
+      <c r="B498" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="C493" s="7" t="inlineStr">
+      <c r="C498" s="7" t="inlineStr">
         <is>
           <t>Tanımı / Ölçünün Alındığı Yer</t>
         </is>
       </c>
-      <c r="D493" s="7" t="inlineStr">
+      <c r="D498" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="E493" s="7" t="inlineStr">
+      <c r="E498" s="7" t="inlineStr">
         <is>
           <t>Adet</t>
         </is>
       </c>
-      <c r="F493" s="7" t="inlineStr">
+      <c r="F498" s="7" t="inlineStr">
         <is>
           <t>En (m)</t>
         </is>
       </c>
-      <c r="G493" s="7" t="inlineStr">
+      <c r="G498" s="7" t="inlineStr">
         <is>
           <t>Boy (m)</t>
         </is>
       </c>
-      <c r="H493" s="7" t="inlineStr">
+      <c r="H498" s="7" t="inlineStr">
         <is>
           <t>Yükseklik (m)</t>
         </is>
       </c>
-      <c r="I493" s="7" t="inlineStr">
+      <c r="I498" s="7" t="inlineStr">
         <is>
           <t>Miktar</t>
         </is>
       </c>
-      <c r="J493" s="7" t="inlineStr">
+      <c r="J498" s="7" t="inlineStr">
         <is>
           <t>Toplam Miktar</t>
         </is>
       </c>
     </row>
-    <row r="494" ht="15" customHeight="1">
-      <c r="A494" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B494" s="20" t="inlineStr">
+    <row r="499" ht="15" customHeight="1">
+      <c r="A499" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B499" s="20" t="inlineStr">
         <is>
           <t>15.120.1001</t>
         </is>
       </c>
-      <c r="C494" s="8" t="inlineStr">
+      <c r="C499" s="8" t="inlineStr">
         <is>
           <t>[M02]  Makine ile kaba tesviye kazısı — tesis içi yol güzergâhı</t>
         </is>
       </c>
-      <c r="D494" s="21" t="inlineStr">
+      <c r="D499" s="21" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E494" s="22" t="n"/>
-      <c r="F494" s="22" t="n"/>
-      <c r="G494" s="22" t="n"/>
-      <c r="H494" s="22" t="n"/>
-      <c r="I494" s="22" t="n"/>
-      <c r="J494" s="22" t="n"/>
-    </row>
-    <row r="495" ht="20" customHeight="1">
-      <c r="A495" s="6" t="n"/>
-      <c r="B495" s="6" t="n"/>
-      <c r="C495" s="23" t="inlineStr">
+      <c r="E499" s="22" t="n"/>
+      <c r="F499" s="22" t="n"/>
+      <c r="G499" s="22" t="n"/>
+      <c r="H499" s="22" t="n"/>
+      <c r="I499" s="22" t="n"/>
+      <c r="J499" s="22" t="n"/>
+    </row>
+    <row r="500" ht="20" customHeight="1">
+      <c r="A500" s="6" t="n"/>
+      <c r="B500" s="6" t="n"/>
+      <c r="C500" s="23" t="inlineStr">
         <is>
           <t>Tesis içi yol güzergâhı: 745,57 m² alan, ortalama 5,00 m genişlik -&gt; 149,11 m uzunluk</t>
         </is>
       </c>
-      <c r="D495" s="6" t="n"/>
-      <c r="E495" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F495" s="29" t="n">
+      <c r="D500" s="6" t="n"/>
+      <c r="E500" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F500" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="G495" s="29" t="n">
+      <c r="G500" s="29" t="n">
         <v>149.11</v>
       </c>
-      <c r="H495" s="29" t="n">
+      <c r="H500" s="29" t="n">
         <v>0.35</v>
       </c>
-      <c r="I495" s="24">
-        <f>E495*F495*G495*H495</f>
-        <v/>
-      </c>
-      <c r="J495" s="6" t="n"/>
-    </row>
-    <row r="496">
-      <c r="A496" s="22" t="n"/>
-      <c r="B496" s="22" t="n"/>
-      <c r="C496" s="25" t="inlineStr">
+      <c r="I500" s="24">
+        <f>E500*F500*G500*H500</f>
+        <v/>
+      </c>
+      <c r="J500" s="6" t="n"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="22" t="n"/>
+      <c r="B501" s="22" t="n"/>
+      <c r="C501" s="25" t="inlineStr">
         <is>
           <t>M02 TOPLAMI</t>
         </is>
       </c>
-      <c r="D496" s="26" t="inlineStr">
+      <c r="D501" s="26" t="inlineStr">
         <is>
           <t>m³</t>
-        </is>
-      </c>
-      <c r="E496" s="22" t="n"/>
-      <c r="F496" s="22" t="n"/>
-      <c r="G496" s="22" t="n"/>
-      <c r="H496" s="22" t="n"/>
-      <c r="I496" s="22" t="n"/>
-      <c r="J496" s="27">
-        <f>SUM(I495:I495)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="497" ht="22" customHeight="1">
-      <c r="A497" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B497" s="20" t="inlineStr">
-        <is>
-          <t>TKDK-0091</t>
-        </is>
-      </c>
-      <c r="C497" s="8" t="inlineStr">
-        <is>
-          <t>[M46]  1,50 m yükseklikte sıcak daldırma galvanizli tel örgü ile çit yapılması</t>
-        </is>
-      </c>
-      <c r="D497" s="21" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E497" s="22" t="n"/>
-      <c r="F497" s="22" t="n"/>
-      <c r="G497" s="22" t="n"/>
-      <c r="H497" s="22" t="n"/>
-      <c r="I497" s="22" t="n"/>
-      <c r="J497" s="22" t="n"/>
-    </row>
-    <row r="498" ht="30" customHeight="1">
-      <c r="A498" s="6" t="n"/>
-      <c r="B498" s="6" t="n"/>
-      <c r="C498" s="23" t="inlineStr">
-        <is>
-          <t>Parsel 7.966,67 m²; yerleşim planındaki cephe 113,04 m, buna karşılık gelen derinlik 7.966,67/113,04 = 70,48 m; çevre 2x(113,04+70,48)</t>
-        </is>
-      </c>
-      <c r="D498" s="6" t="n"/>
-      <c r="E498" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F498" s="6" t="n"/>
-      <c r="G498" s="29" t="n">
-        <v>367.04</v>
-      </c>
-      <c r="H498" s="6" t="n"/>
-      <c r="I498" s="24">
-        <f>E498*G498</f>
-        <v/>
-      </c>
-      <c r="J498" s="6" t="n"/>
-    </row>
-    <row r="499" ht="12" customHeight="1">
-      <c r="A499" s="6" t="n"/>
-      <c r="B499" s="6" t="n"/>
-      <c r="C499" s="23" t="inlineStr">
-        <is>
-          <t>Giriş kapısı açıklığı düşülür</t>
-        </is>
-      </c>
-      <c r="D499" s="6" t="n"/>
-      <c r="E499" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F499" s="6" t="n"/>
-      <c r="G499" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="H499" s="6" t="n"/>
-      <c r="I499" s="24">
-        <f>-E499*G499</f>
-        <v/>
-      </c>
-      <c r="J499" s="6" t="n"/>
-    </row>
-    <row r="500">
-      <c r="A500" s="22" t="n"/>
-      <c r="B500" s="22" t="n"/>
-      <c r="C500" s="25" t="inlineStr">
-        <is>
-          <t>M46 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D500" s="26" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E500" s="22" t="n"/>
-      <c r="F500" s="22" t="n"/>
-      <c r="G500" s="22" t="n"/>
-      <c r="H500" s="22" t="n"/>
-      <c r="I500" s="22" t="n"/>
-      <c r="J500" s="27">
-        <f>SUM(I498:I499)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="501" ht="22" customHeight="1">
-      <c r="A501" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B501" s="20" t="inlineStr">
-        <is>
-          <t>43.527.1001</t>
-        </is>
-      </c>
-      <c r="C501" s="8" t="inlineStr">
-        <is>
-          <t>[M59]  ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
-        </is>
-      </c>
-      <c r="D501" s="21" t="inlineStr">
-        <is>
-          <t>m</t>
         </is>
       </c>
       <c r="E501" s="22" t="n"/>
@@ -16949,37 +16967,43 @@
       <c r="G501" s="22" t="n"/>
       <c r="H501" s="22" t="n"/>
       <c r="I501" s="22" t="n"/>
-      <c r="J501" s="22" t="n"/>
-    </row>
-    <row r="502" ht="12" customHeight="1">
-      <c r="A502" s="6" t="n"/>
-      <c r="B502" s="6" t="n"/>
-      <c r="C502" s="23" t="inlineStr">
-        <is>
-          <t>Kümes A blok servis bölümü - foseptik</t>
-        </is>
-      </c>
-      <c r="D502" s="6" t="n"/>
-      <c r="E502" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F502" s="6" t="n"/>
-      <c r="G502" s="29" t="n">
-        <v>25</v>
-      </c>
-      <c r="H502" s="6" t="n"/>
-      <c r="I502" s="24">
-        <f>E502*G502</f>
-        <v/>
-      </c>
-      <c r="J502" s="6" t="n"/>
-    </row>
-    <row r="503" ht="12" customHeight="1">
+      <c r="J501" s="27">
+        <f>SUM(I500:I500)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="502" ht="22" customHeight="1">
+      <c r="A502" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B502" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0091</t>
+        </is>
+      </c>
+      <c r="C502" s="8" t="inlineStr">
+        <is>
+          <t>[M46]  1,50 m yükseklikte sıcak daldırma galvanizli tel örgü ile çit yapılması</t>
+        </is>
+      </c>
+      <c r="D502" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E502" s="22" t="n"/>
+      <c r="F502" s="22" t="n"/>
+      <c r="G502" s="22" t="n"/>
+      <c r="H502" s="22" t="n"/>
+      <c r="I502" s="22" t="n"/>
+      <c r="J502" s="22" t="n"/>
+    </row>
+    <row r="503" ht="30" customHeight="1">
       <c r="A503" s="6" t="n"/>
       <c r="B503" s="6" t="n"/>
       <c r="C503" s="23" t="inlineStr">
         <is>
-          <t>Kümes B blok servis bölümü - foseptik</t>
+          <t>Parsel 7.966,67 m²; yerleşim planındaki cephe 113,04 m, buna karşılık gelen derinlik 7.966,67/113,04 = 70,48 m; çevre 2x(113,04+70,48)</t>
         </is>
       </c>
       <c r="D503" s="6" t="n"/>
@@ -16988,7 +17012,7 @@
       </c>
       <c r="F503" s="6" t="n"/>
       <c r="G503" s="29" t="n">
-        <v>25</v>
+        <v>367.04</v>
       </c>
       <c r="H503" s="6" t="n"/>
       <c r="I503" s="24">
@@ -16997,46 +17021,40 @@
       </c>
       <c r="J503" s="6" t="n"/>
     </row>
-    <row r="504">
-      <c r="A504" s="22" t="n"/>
-      <c r="B504" s="22" t="n"/>
-      <c r="C504" s="25" t="inlineStr">
-        <is>
-          <t>M59 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D504" s="26" t="inlineStr">
+    <row r="504" ht="12" customHeight="1">
+      <c r="A504" s="6" t="n"/>
+      <c r="B504" s="6" t="n"/>
+      <c r="C504" s="23" t="inlineStr">
+        <is>
+          <t>Giriş kapısı açıklığı düşülür</t>
+        </is>
+      </c>
+      <c r="D504" s="6" t="n"/>
+      <c r="E504" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F504" s="6" t="n"/>
+      <c r="G504" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H504" s="6" t="n"/>
+      <c r="I504" s="24">
+        <f>-E504*G504</f>
+        <v/>
+      </c>
+      <c r="J504" s="6" t="n"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="22" t="n"/>
+      <c r="B505" s="22" t="n"/>
+      <c r="C505" s="25" t="inlineStr">
+        <is>
+          <t>M46 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D505" s="26" t="inlineStr">
         <is>
           <t>m</t>
-        </is>
-      </c>
-      <c r="E504" s="22" t="n"/>
-      <c r="F504" s="22" t="n"/>
-      <c r="G504" s="22" t="n"/>
-      <c r="H504" s="22" t="n"/>
-      <c r="I504" s="22" t="n"/>
-      <c r="J504" s="27">
-        <f>SUM(I502:I503)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="505" ht="15" customHeight="1">
-      <c r="A505" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B505" s="20" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="C505" s="8" t="inlineStr">
-        <is>
-          <t>[M61A]  C 25/30 hazır beton dökülmesi — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="D505" s="21" t="inlineStr">
-        <is>
-          <t>m³</t>
         </is>
       </c>
       <c r="E505" s="22" t="n"/>
@@ -17044,102 +17062,94 @@
       <c r="G505" s="22" t="n"/>
       <c r="H505" s="22" t="n"/>
       <c r="I505" s="22" t="n"/>
-      <c r="J505" s="22" t="n"/>
-    </row>
-    <row r="506" ht="12" customHeight="1">
-      <c r="A506" s="6" t="n"/>
-      <c r="B506" s="6" t="n"/>
-      <c r="C506" s="23" t="inlineStr">
-        <is>
-          <t>Dış prizma: 0,90 x 0,90 x 0,75; 4 adet</t>
-        </is>
-      </c>
-      <c r="D506" s="6" t="n"/>
-      <c r="E506" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F506" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G506" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H506" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I506" s="24">
-        <f>E506*F506*G506*H506</f>
-        <v/>
-      </c>
-      <c r="J506" s="6" t="n"/>
+      <c r="J505" s="27">
+        <f>SUM(I503:I504)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="506" ht="22" customHeight="1">
+      <c r="A506" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B506" s="20" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="C506" s="8" t="inlineStr">
+        <is>
+          <t>[M59]  ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+        </is>
+      </c>
+      <c r="D506" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E506" s="22" t="n"/>
+      <c r="F506" s="22" t="n"/>
+      <c r="G506" s="22" t="n"/>
+      <c r="H506" s="22" t="n"/>
+      <c r="I506" s="22" t="n"/>
+      <c r="J506" s="22" t="n"/>
     </row>
     <row r="507" ht="12" customHeight="1">
       <c r="A507" s="6" t="n"/>
       <c r="B507" s="6" t="n"/>
       <c r="C507" s="23" t="inlineStr">
         <is>
-          <t>Net iç hacim düşülür: 0,60 x 0,60 x 0,60; 4 adet</t>
+          <t>Kümes A blok servis bölümü - foseptik</t>
         </is>
       </c>
       <c r="D507" s="6" t="n"/>
       <c r="E507" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F507" s="29" t="n">
-        <v>0.6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F507" s="6" t="n"/>
       <c r="G507" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H507" s="29" t="n">
-        <v>0.6</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H507" s="6" t="n"/>
       <c r="I507" s="24">
-        <f>-E507*F507*G507*H507</f>
+        <f>E507*G507</f>
         <v/>
       </c>
       <c r="J507" s="6" t="n"/>
     </row>
-    <row r="508">
-      <c r="A508" s="22" t="n"/>
-      <c r="B508" s="22" t="n"/>
-      <c r="C508" s="25" t="inlineStr">
-        <is>
-          <t>M61A TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D508" s="26" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="E508" s="22" t="n"/>
-      <c r="F508" s="22" t="n"/>
-      <c r="G508" s="22" t="n"/>
-      <c r="H508" s="22" t="n"/>
-      <c r="I508" s="22" t="n"/>
-      <c r="J508" s="27">
-        <f>SUM(I506:I507)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="509" ht="22" customHeight="1">
-      <c r="A509" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B509" s="20" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="C509" s="8" t="inlineStr">
-        <is>
-          <t>[M61B]  Düz yüzeyli beton ve betonarme kalıbı yapılması — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="D509" s="21" t="inlineStr">
-        <is>
-          <t>m²</t>
+    <row r="508" ht="12" customHeight="1">
+      <c r="A508" s="6" t="n"/>
+      <c r="B508" s="6" t="n"/>
+      <c r="C508" s="23" t="inlineStr">
+        <is>
+          <t>Kümes B blok servis bölümü - foseptik</t>
+        </is>
+      </c>
+      <c r="D508" s="6" t="n"/>
+      <c r="E508" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F508" s="6" t="n"/>
+      <c r="G508" s="29" t="n">
+        <v>25</v>
+      </c>
+      <c r="H508" s="6" t="n"/>
+      <c r="I508" s="24">
+        <f>E508*G508</f>
+        <v/>
+      </c>
+      <c r="J508" s="6" t="n"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="22" t="n"/>
+      <c r="B509" s="22" t="n"/>
+      <c r="C509" s="25" t="inlineStr">
+        <is>
+          <t>M59 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D509" s="26" t="inlineStr">
+        <is>
+          <t>m</t>
         </is>
       </c>
       <c r="E509" s="22" t="n"/>
@@ -17147,41 +17157,43 @@
       <c r="G509" s="22" t="n"/>
       <c r="H509" s="22" t="n"/>
       <c r="I509" s="22" t="n"/>
-      <c r="J509" s="22" t="n"/>
-    </row>
-    <row r="510" ht="12" customHeight="1">
-      <c r="A510" s="6" t="n"/>
-      <c r="B510" s="6" t="n"/>
-      <c r="C510" s="23" t="inlineStr">
-        <is>
-          <t>İç yüzler: 4 yüz x 0,60 x 0,60; 4 adet</t>
-        </is>
-      </c>
-      <c r="D510" s="6" t="n"/>
-      <c r="E510" s="28" t="n">
+      <c r="J509" s="27">
+        <f>SUM(I507:I508)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="510" ht="15" customHeight="1">
+      <c r="A510" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F510" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G510" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H510" s="29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I510" s="24">
-        <f>E510*F510*G510*H510</f>
-        <v/>
-      </c>
-      <c r="J510" s="6" t="n"/>
+      <c r="B510" s="20" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="C510" s="8" t="inlineStr">
+        <is>
+          <t>[M61A]  C 25/30 hazır beton dökülmesi — betonarme rögarlar</t>
+        </is>
+      </c>
+      <c r="D510" s="21" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E510" s="22" t="n"/>
+      <c r="F510" s="22" t="n"/>
+      <c r="G510" s="22" t="n"/>
+      <c r="H510" s="22" t="n"/>
+      <c r="I510" s="22" t="n"/>
+      <c r="J510" s="22" t="n"/>
     </row>
     <row r="511" ht="12" customHeight="1">
       <c r="A511" s="6" t="n"/>
       <c r="B511" s="6" t="n"/>
       <c r="C511" s="23" t="inlineStr">
         <is>
-          <t>Dış yüzler: 4 yüz x 0,90 x 0,60; 4 adet</t>
+          <t>Dış prizma: 0,90 x 0,90 x 0,75; 4 adet</t>
         </is>
       </c>
       <c r="D511" s="6" t="n"/>
@@ -17192,10 +17204,10 @@
         <v>0.9</v>
       </c>
       <c r="G511" s="29" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="H511" s="29" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="I511" s="24">
         <f>E511*F511*G511*H511</f>
@@ -17203,46 +17215,44 @@
       </c>
       <c r="J511" s="6" t="n"/>
     </row>
-    <row r="512">
-      <c r="A512" s="22" t="n"/>
-      <c r="B512" s="22" t="n"/>
-      <c r="C512" s="25" t="inlineStr">
-        <is>
-          <t>M61B TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D512" s="26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E512" s="22" t="n"/>
-      <c r="F512" s="22" t="n"/>
-      <c r="G512" s="22" t="n"/>
-      <c r="H512" s="22" t="n"/>
-      <c r="I512" s="22" t="n"/>
-      <c r="J512" s="27">
-        <f>SUM(I510:I511)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="513" ht="15" customHeight="1">
-      <c r="A513" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B513" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="C513" s="8" t="inlineStr">
-        <is>
-          <t>[M61C]  Nervürlü betonarme çeliği ø8-ø12 — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="D513" s="21" t="inlineStr">
-        <is>
-          <t>ton</t>
+    <row r="512" ht="12" customHeight="1">
+      <c r="A512" s="6" t="n"/>
+      <c r="B512" s="6" t="n"/>
+      <c r="C512" s="23" t="inlineStr">
+        <is>
+          <t>Net iç hacim düşülür: 0,60 x 0,60 x 0,60; 4 adet</t>
+        </is>
+      </c>
+      <c r="D512" s="6" t="n"/>
+      <c r="E512" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F512" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G512" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H512" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I512" s="24">
+        <f>-E512*F512*G512*H512</f>
+        <v/>
+      </c>
+      <c r="J512" s="6" t="n"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="22" t="n"/>
+      <c r="B513" s="22" t="n"/>
+      <c r="C513" s="25" t="inlineStr">
+        <is>
+          <t>M61A TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D513" s="26" t="inlineStr">
+        <is>
+          <t>m³</t>
         </is>
       </c>
       <c r="E513" s="22" t="n"/>
@@ -17250,114 +17260,131 @@
       <c r="G513" s="22" t="n"/>
       <c r="H513" s="22" t="n"/>
       <c r="I513" s="22" t="n"/>
-      <c r="J513" s="22" t="n"/>
-    </row>
-    <row r="514" ht="20" customHeight="1">
-      <c r="A514" s="6" t="n"/>
-      <c r="B514" s="6" t="n"/>
-      <c r="C514" s="23" t="inlineStr">
-        <is>
-          <t>Beton hacmi 1,566 m³, ortalama donatı oranı 90 kg/m³ -&gt; 140,94 kg = 0,141 ton</t>
-        </is>
-      </c>
-      <c r="D514" s="6" t="n"/>
-      <c r="E514" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F514" s="6" t="n"/>
-      <c r="G514" s="29" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="H514" s="6" t="n"/>
-      <c r="I514" s="24">
-        <f>E514*G514*J514</f>
-        <v/>
-      </c>
-      <c r="J514" s="30" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" s="22" t="n"/>
-      <c r="B515" s="22" t="n"/>
-      <c r="C515" s="25" t="inlineStr">
-        <is>
-          <t>M61C TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D515" s="26" t="inlineStr">
+      <c r="J513" s="27">
+        <f>SUM(I511:I512)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="514" ht="22" customHeight="1">
+      <c r="A514" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B514" s="20" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="C514" s="8" t="inlineStr">
+        <is>
+          <t>[M61B]  Düz yüzeyli beton ve betonarme kalıbı yapılması — betonarme rögarlar</t>
+        </is>
+      </c>
+      <c r="D514" s="21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E514" s="22" t="n"/>
+      <c r="F514" s="22" t="n"/>
+      <c r="G514" s="22" t="n"/>
+      <c r="H514" s="22" t="n"/>
+      <c r="I514" s="22" t="n"/>
+      <c r="J514" s="22" t="n"/>
+    </row>
+    <row r="515" ht="12" customHeight="1">
+      <c r="A515" s="6" t="n"/>
+      <c r="B515" s="6" t="n"/>
+      <c r="C515" s="23" t="inlineStr">
+        <is>
+          <t>İç yüzler: 4 yüz x 0,60 x 0,60; 4 adet</t>
+        </is>
+      </c>
+      <c r="D515" s="6" t="n"/>
+      <c r="E515" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F515" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G515" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H515" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I515" s="24">
+        <f>E515*F515*G515*H515</f>
+        <v/>
+      </c>
+      <c r="J515" s="6" t="n"/>
+    </row>
+    <row r="516" ht="12" customHeight="1">
+      <c r="A516" s="6" t="n"/>
+      <c r="B516" s="6" t="n"/>
+      <c r="C516" s="23" t="inlineStr">
+        <is>
+          <t>Dış yüzler: 4 yüz x 0,90 x 0,60; 4 adet</t>
+        </is>
+      </c>
+      <c r="D516" s="6" t="n"/>
+      <c r="E516" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F516" s="29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G516" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H516" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I516" s="24">
+        <f>E516*F516*G516*H516</f>
+        <v/>
+      </c>
+      <c r="J516" s="6" t="n"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="22" t="n"/>
+      <c r="B517" s="22" t="n"/>
+      <c r="C517" s="25" t="inlineStr">
+        <is>
+          <t>M61B TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D517" s="26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E517" s="22" t="n"/>
+      <c r="F517" s="22" t="n"/>
+      <c r="G517" s="22" t="n"/>
+      <c r="H517" s="22" t="n"/>
+      <c r="I517" s="22" t="n"/>
+      <c r="J517" s="27">
+        <f>SUM(I515:I516)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="518" ht="15" customHeight="1">
+      <c r="A518" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B518" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="C518" s="8" t="inlineStr">
+        <is>
+          <t>[M61C]  Nervürlü betonarme çeliği ø8-ø12 — betonarme rögarlar</t>
+        </is>
+      </c>
+      <c r="D518" s="21" t="inlineStr">
         <is>
           <t>ton</t>
-        </is>
-      </c>
-      <c r="E515" s="22" t="n"/>
-      <c r="F515" s="22" t="n"/>
-      <c r="G515" s="22" t="n"/>
-      <c r="H515" s="22" t="n"/>
-      <c r="I515" s="22" t="n"/>
-      <c r="J515" s="27">
-        <f>SUM(I514:I514)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="516" ht="15" customHeight="1">
-      <c r="A516" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B516" s="20" t="inlineStr">
-        <is>
-          <t>15.560.1003</t>
-        </is>
-      </c>
-      <c r="C516" s="8" t="inlineStr">
-        <is>
-          <t>[M61D]  Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="D516" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E516" s="22" t="n"/>
-      <c r="F516" s="22" t="n"/>
-      <c r="G516" s="22" t="n"/>
-      <c r="H516" s="22" t="n"/>
-      <c r="I516" s="22" t="n"/>
-      <c r="J516" s="22" t="n"/>
-    </row>
-    <row r="517" ht="12" customHeight="1">
-      <c r="A517" s="6" t="n"/>
-      <c r="B517" s="6" t="n"/>
-      <c r="C517" s="23" t="inlineStr">
-        <is>
-          <t>Pissu hattında 4 adet</t>
-        </is>
-      </c>
-      <c r="D517" s="6" t="n"/>
-      <c r="E517" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="F517" s="6" t="n"/>
-      <c r="G517" s="6" t="n"/>
-      <c r="H517" s="6" t="n"/>
-      <c r="I517" s="24">
-        <f>E517</f>
-        <v/>
-      </c>
-      <c r="J517" s="6" t="n"/>
-    </row>
-    <row r="518">
-      <c r="A518" s="22" t="n"/>
-      <c r="B518" s="22" t="n"/>
-      <c r="C518" s="25" t="inlineStr">
-        <is>
-          <t>M61D TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D518" s="26" t="inlineStr">
-        <is>
-          <t>ad</t>
         </is>
       </c>
       <c r="E518" s="22" t="n"/>
@@ -17365,69 +17392,71 @@
       <c r="G518" s="22" t="n"/>
       <c r="H518" s="22" t="n"/>
       <c r="I518" s="22" t="n"/>
-      <c r="J518" s="27">
-        <f>SUM(I517:I517)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="519" ht="22" customHeight="1">
-      <c r="A519" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B519" s="20" t="inlineStr">
-        <is>
-          <t>35.100.1104</t>
-        </is>
-      </c>
-      <c r="C519" s="8" t="inlineStr">
-        <is>
-          <t>[M63]  Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
-        </is>
-      </c>
-      <c r="D519" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E519" s="22" t="n"/>
-      <c r="F519" s="22" t="n"/>
-      <c r="G519" s="22" t="n"/>
-      <c r="H519" s="22" t="n"/>
-      <c r="I519" s="22" t="n"/>
-      <c r="J519" s="22" t="n"/>
-    </row>
-    <row r="520" ht="12" customHeight="1">
-      <c r="A520" s="6" t="n"/>
-      <c r="B520" s="6" t="n"/>
-      <c r="C520" s="23" t="inlineStr">
-        <is>
-          <t>Tesis girişinde 1 adet</t>
-        </is>
-      </c>
-      <c r="D520" s="6" t="n"/>
-      <c r="E520" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F520" s="6" t="n"/>
-      <c r="G520" s="6" t="n"/>
-      <c r="H520" s="6" t="n"/>
-      <c r="I520" s="24">
-        <f>E520*J520</f>
-        <v/>
-      </c>
-      <c r="J520" s="30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" s="22" t="n"/>
-      <c r="B521" s="22" t="n"/>
-      <c r="C521" s="25" t="inlineStr">
-        <is>
-          <t>M63 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D521" s="26" t="inlineStr">
+      <c r="J518" s="22" t="n"/>
+    </row>
+    <row r="519" ht="20" customHeight="1">
+      <c r="A519" s="6" t="n"/>
+      <c r="B519" s="6" t="n"/>
+      <c r="C519" s="23" t="inlineStr">
+        <is>
+          <t>Beton hacmi 1,566 m³, ortalama donatı oranı 90 kg/m³ -&gt; 140,94 kg = 0,141 ton</t>
+        </is>
+      </c>
+      <c r="D519" s="6" t="n"/>
+      <c r="E519" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F519" s="6" t="n"/>
+      <c r="G519" s="29" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="H519" s="6" t="n"/>
+      <c r="I519" s="24">
+        <f>E519*G519*J519</f>
+        <v/>
+      </c>
+      <c r="J519" s="30" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="22" t="n"/>
+      <c r="B520" s="22" t="n"/>
+      <c r="C520" s="25" t="inlineStr">
+        <is>
+          <t>M61C TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D520" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="E520" s="22" t="n"/>
+      <c r="F520" s="22" t="n"/>
+      <c r="G520" s="22" t="n"/>
+      <c r="H520" s="22" t="n"/>
+      <c r="I520" s="22" t="n"/>
+      <c r="J520" s="27">
+        <f>SUM(I519:I519)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="521" ht="15" customHeight="1">
+      <c r="A521" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B521" s="20" t="inlineStr">
+        <is>
+          <t>15.560.1003</t>
+        </is>
+      </c>
+      <c r="C521" s="8" t="inlineStr">
+        <is>
+          <t>[M61D]  Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="D521" s="21" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
@@ -17437,69 +17466,67 @@
       <c r="G521" s="22" t="n"/>
       <c r="H521" s="22" t="n"/>
       <c r="I521" s="22" t="n"/>
-      <c r="J521" s="27">
-        <f>SUM(I520:I520)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="522" ht="15" customHeight="1">
-      <c r="A522" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B522" s="20" t="inlineStr">
-        <is>
-          <t>35.100.2106</t>
-        </is>
-      </c>
-      <c r="C522" s="8" t="inlineStr">
-        <is>
-          <t>[M64]  Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
-        </is>
-      </c>
-      <c r="D522" s="21" t="inlineStr">
+      <c r="J521" s="22" t="n"/>
+    </row>
+    <row r="522" ht="12" customHeight="1">
+      <c r="A522" s="6" t="n"/>
+      <c r="B522" s="6" t="n"/>
+      <c r="C522" s="23" t="inlineStr">
+        <is>
+          <t>Pissu hattında 4 adet</t>
+        </is>
+      </c>
+      <c r="D522" s="6" t="n"/>
+      <c r="E522" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F522" s="6" t="n"/>
+      <c r="G522" s="6" t="n"/>
+      <c r="H522" s="6" t="n"/>
+      <c r="I522" s="24">
+        <f>E522</f>
+        <v/>
+      </c>
+      <c r="J522" s="6" t="n"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="22" t="n"/>
+      <c r="B523" s="22" t="n"/>
+      <c r="C523" s="25" t="inlineStr">
+        <is>
+          <t>M61D TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D523" s="26" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="E522" s="22" t="n"/>
-      <c r="F522" s="22" t="n"/>
-      <c r="G522" s="22" t="n"/>
-      <c r="H522" s="22" t="n"/>
-      <c r="I522" s="22" t="n"/>
-      <c r="J522" s="22" t="n"/>
-    </row>
-    <row r="523" ht="12" customHeight="1">
-      <c r="A523" s="6" t="n"/>
-      <c r="B523" s="6" t="n"/>
-      <c r="C523" s="23" t="inlineStr">
-        <is>
-          <t>Tesis girişinde 1 adet</t>
-        </is>
-      </c>
-      <c r="D523" s="6" t="n"/>
-      <c r="E523" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F523" s="6" t="n"/>
-      <c r="G523" s="6" t="n"/>
-      <c r="H523" s="6" t="n"/>
-      <c r="I523" s="24">
-        <f>E523*J523</f>
-        <v/>
-      </c>
-      <c r="J523" s="30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" s="22" t="n"/>
-      <c r="B524" s="22" t="n"/>
-      <c r="C524" s="25" t="inlineStr">
-        <is>
-          <t>M64 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D524" s="26" t="inlineStr">
+      <c r="E523" s="22" t="n"/>
+      <c r="F523" s="22" t="n"/>
+      <c r="G523" s="22" t="n"/>
+      <c r="H523" s="22" t="n"/>
+      <c r="I523" s="22" t="n"/>
+      <c r="J523" s="27">
+        <f>SUM(I522:I522)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="524" ht="22" customHeight="1">
+      <c r="A524" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B524" s="20" t="inlineStr">
+        <is>
+          <t>35.100.1104</t>
+        </is>
+      </c>
+      <c r="C524" s="8" t="inlineStr">
+        <is>
+          <t>[M63]  Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
+        </is>
+      </c>
+      <c r="D524" s="21" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
@@ -17509,69 +17536,69 @@
       <c r="G524" s="22" t="n"/>
       <c r="H524" s="22" t="n"/>
       <c r="I524" s="22" t="n"/>
-      <c r="J524" s="27">
-        <f>SUM(I523:I523)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="525" ht="22" customHeight="1">
-      <c r="A525" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B525" s="20" t="inlineStr">
-        <is>
-          <t>35.135.3201</t>
-        </is>
-      </c>
-      <c r="C525" s="8" t="inlineStr">
-        <is>
-          <t>[M65]  Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
-        </is>
-      </c>
-      <c r="D525" s="21" t="inlineStr">
+      <c r="J524" s="22" t="n"/>
+    </row>
+    <row r="525" ht="12" customHeight="1">
+      <c r="A525" s="6" t="n"/>
+      <c r="B525" s="6" t="n"/>
+      <c r="C525" s="23" t="inlineStr">
+        <is>
+          <t>Tesis girişinde 1 adet</t>
+        </is>
+      </c>
+      <c r="D525" s="6" t="n"/>
+      <c r="E525" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F525" s="6" t="n"/>
+      <c r="G525" s="6" t="n"/>
+      <c r="H525" s="6" t="n"/>
+      <c r="I525" s="24">
+        <f>E525*J525</f>
+        <v/>
+      </c>
+      <c r="J525" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="22" t="n"/>
+      <c r="B526" s="22" t="n"/>
+      <c r="C526" s="25" t="inlineStr">
+        <is>
+          <t>M63 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D526" s="26" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="E525" s="22" t="n"/>
-      <c r="F525" s="22" t="n"/>
-      <c r="G525" s="22" t="n"/>
-      <c r="H525" s="22" t="n"/>
-      <c r="I525" s="22" t="n"/>
-      <c r="J525" s="22" t="n"/>
-    </row>
-    <row r="526" ht="12" customHeight="1">
-      <c r="A526" s="6" t="n"/>
-      <c r="B526" s="6" t="n"/>
-      <c r="C526" s="23" t="inlineStr">
-        <is>
-          <t>Sayaç panosu içinde 1 adet</t>
-        </is>
-      </c>
-      <c r="D526" s="6" t="n"/>
-      <c r="E526" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F526" s="6" t="n"/>
-      <c r="G526" s="6" t="n"/>
-      <c r="H526" s="6" t="n"/>
-      <c r="I526" s="24">
-        <f>E526*J526</f>
-        <v/>
-      </c>
-      <c r="J526" s="30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" s="22" t="n"/>
-      <c r="B527" s="22" t="n"/>
-      <c r="C527" s="25" t="inlineStr">
-        <is>
-          <t>M65 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D527" s="26" t="inlineStr">
+      <c r="E526" s="22" t="n"/>
+      <c r="F526" s="22" t="n"/>
+      <c r="G526" s="22" t="n"/>
+      <c r="H526" s="22" t="n"/>
+      <c r="I526" s="22" t="n"/>
+      <c r="J526" s="27">
+        <f>SUM(I525:I525)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="527" ht="15" customHeight="1">
+      <c r="A527" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B527" s="20" t="inlineStr">
+        <is>
+          <t>35.100.2106</t>
+        </is>
+      </c>
+      <c r="C527" s="8" t="inlineStr">
+        <is>
+          <t>[M64]  Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+        </is>
+      </c>
+      <c r="D527" s="21" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
@@ -17581,69 +17608,69 @@
       <c r="G527" s="22" t="n"/>
       <c r="H527" s="22" t="n"/>
       <c r="I527" s="22" t="n"/>
-      <c r="J527" s="27">
-        <f>SUM(I526:I526)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="528" ht="22" customHeight="1">
-      <c r="A528" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="B528" s="20" t="inlineStr">
-        <is>
-          <t>35.110.1104</t>
-        </is>
-      </c>
-      <c r="C528" s="8" t="inlineStr">
-        <is>
-          <t>[M66]  Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
-        </is>
-      </c>
-      <c r="D528" s="21" t="inlineStr">
+      <c r="J527" s="22" t="n"/>
+    </row>
+    <row r="528" ht="12" customHeight="1">
+      <c r="A528" s="6" t="n"/>
+      <c r="B528" s="6" t="n"/>
+      <c r="C528" s="23" t="inlineStr">
+        <is>
+          <t>Tesis girişinde 1 adet</t>
+        </is>
+      </c>
+      <c r="D528" s="6" t="n"/>
+      <c r="E528" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F528" s="6" t="n"/>
+      <c r="G528" s="6" t="n"/>
+      <c r="H528" s="6" t="n"/>
+      <c r="I528" s="24">
+        <f>E528*J528</f>
+        <v/>
+      </c>
+      <c r="J528" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="22" t="n"/>
+      <c r="B529" s="22" t="n"/>
+      <c r="C529" s="25" t="inlineStr">
+        <is>
+          <t>M64 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D529" s="26" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="E528" s="22" t="n"/>
-      <c r="F528" s="22" t="n"/>
-      <c r="G528" s="22" t="n"/>
-      <c r="H528" s="22" t="n"/>
-      <c r="I528" s="22" t="n"/>
-      <c r="J528" s="22" t="n"/>
-    </row>
-    <row r="529" ht="12" customHeight="1">
-      <c r="A529" s="6" t="n"/>
-      <c r="B529" s="6" t="n"/>
-      <c r="C529" s="23" t="inlineStr">
-        <is>
-          <t>Ana dağıtım panosu girişi</t>
-        </is>
-      </c>
-      <c r="D529" s="6" t="n"/>
-      <c r="E529" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F529" s="6" t="n"/>
-      <c r="G529" s="6" t="n"/>
-      <c r="H529" s="6" t="n"/>
-      <c r="I529" s="24">
-        <f>E529*J529</f>
-        <v/>
-      </c>
-      <c r="J529" s="30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" s="22" t="n"/>
-      <c r="B530" s="22" t="n"/>
-      <c r="C530" s="25" t="inlineStr">
-        <is>
-          <t>M66 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D530" s="26" t="inlineStr">
+      <c r="E529" s="22" t="n"/>
+      <c r="F529" s="22" t="n"/>
+      <c r="G529" s="22" t="n"/>
+      <c r="H529" s="22" t="n"/>
+      <c r="I529" s="22" t="n"/>
+      <c r="J529" s="27">
+        <f>SUM(I528:I528)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="530" ht="22" customHeight="1">
+      <c r="A530" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B530" s="20" t="inlineStr">
+        <is>
+          <t>35.135.3201</t>
+        </is>
+      </c>
+      <c r="C530" s="8" t="inlineStr">
+        <is>
+          <t>[M65]  Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+        </is>
+      </c>
+      <c r="D530" s="21" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
@@ -17653,69 +17680,69 @@
       <c r="G530" s="22" t="n"/>
       <c r="H530" s="22" t="n"/>
       <c r="I530" s="22" t="n"/>
-      <c r="J530" s="27">
-        <f>SUM(I529:I529)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="531" ht="15" customHeight="1">
-      <c r="A531" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B531" s="20" t="inlineStr">
-        <is>
-          <t>35.115.1003</t>
-        </is>
-      </c>
-      <c r="C531" s="8" t="inlineStr">
-        <is>
-          <t>[M69]  Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
-        </is>
-      </c>
-      <c r="D531" s="21" t="inlineStr">
+      <c r="J530" s="22" t="n"/>
+    </row>
+    <row r="531" ht="12" customHeight="1">
+      <c r="A531" s="6" t="n"/>
+      <c r="B531" s="6" t="n"/>
+      <c r="C531" s="23" t="inlineStr">
+        <is>
+          <t>Sayaç panosu içinde 1 adet</t>
+        </is>
+      </c>
+      <c r="D531" s="6" t="n"/>
+      <c r="E531" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F531" s="6" t="n"/>
+      <c r="G531" s="6" t="n"/>
+      <c r="H531" s="6" t="n"/>
+      <c r="I531" s="24">
+        <f>E531*J531</f>
+        <v/>
+      </c>
+      <c r="J531" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="22" t="n"/>
+      <c r="B532" s="22" t="n"/>
+      <c r="C532" s="25" t="inlineStr">
+        <is>
+          <t>M65 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D532" s="26" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="E531" s="22" t="n"/>
-      <c r="F531" s="22" t="n"/>
-      <c r="G531" s="22" t="n"/>
-      <c r="H531" s="22" t="n"/>
-      <c r="I531" s="22" t="n"/>
-      <c r="J531" s="22" t="n"/>
-    </row>
-    <row r="532" ht="12" customHeight="1">
-      <c r="A532" s="6" t="n"/>
-      <c r="B532" s="6" t="n"/>
-      <c r="C532" s="23" t="inlineStr">
-        <is>
-          <t>Ana pano ve sayaç panosunda</t>
-        </is>
-      </c>
-      <c r="D532" s="6" t="n"/>
-      <c r="E532" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F532" s="6" t="n"/>
-      <c r="G532" s="6" t="n"/>
-      <c r="H532" s="6" t="n"/>
-      <c r="I532" s="24">
-        <f>E532*J532</f>
-        <v/>
-      </c>
-      <c r="J532" s="30" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" s="22" t="n"/>
-      <c r="B533" s="22" t="n"/>
-      <c r="C533" s="25" t="inlineStr">
-        <is>
-          <t>M69 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D533" s="26" t="inlineStr">
+      <c r="E532" s="22" t="n"/>
+      <c r="F532" s="22" t="n"/>
+      <c r="G532" s="22" t="n"/>
+      <c r="H532" s="22" t="n"/>
+      <c r="I532" s="22" t="n"/>
+      <c r="J532" s="27">
+        <f>SUM(I531:I531)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="533" ht="22" customHeight="1">
+      <c r="A533" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B533" s="20" t="inlineStr">
+        <is>
+          <t>35.110.1104</t>
+        </is>
+      </c>
+      <c r="C533" s="8" t="inlineStr">
+        <is>
+          <t>[M66]  Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
+        </is>
+      </c>
+      <c r="D533" s="21" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
@@ -17725,71 +17752,71 @@
       <c r="G533" s="22" t="n"/>
       <c r="H533" s="22" t="n"/>
       <c r="I533" s="22" t="n"/>
-      <c r="J533" s="27">
-        <f>SUM(I532:I532)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="534" ht="22" customHeight="1">
-      <c r="A534" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="B534" s="20" t="inlineStr">
-        <is>
-          <t>35.140.3105</t>
-        </is>
-      </c>
-      <c r="C534" s="8" t="inlineStr">
-        <is>
-          <t>[M70]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
-        </is>
-      </c>
-      <c r="D534" s="21" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E534" s="22" t="n"/>
-      <c r="F534" s="22" t="n"/>
-      <c r="G534" s="22" t="n"/>
-      <c r="H534" s="22" t="n"/>
-      <c r="I534" s="22" t="n"/>
-      <c r="J534" s="22" t="n"/>
-    </row>
-    <row r="535" ht="12" customHeight="1">
-      <c r="A535" s="6" t="n"/>
-      <c r="B535" s="6" t="n"/>
-      <c r="C535" s="23" t="inlineStr">
-        <is>
-          <t>Şebeke bağlantı noktası - ana dağıtım panosu</t>
-        </is>
-      </c>
-      <c r="D535" s="6" t="n"/>
-      <c r="E535" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F535" s="6" t="n"/>
-      <c r="G535" s="6" t="n"/>
-      <c r="H535" s="6" t="n"/>
-      <c r="I535" s="24">
-        <f>E535*J535</f>
-        <v/>
-      </c>
-      <c r="J535" s="30" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" s="22" t="n"/>
-      <c r="B536" s="22" t="n"/>
-      <c r="C536" s="25" t="inlineStr">
-        <is>
-          <t>M70 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D536" s="26" t="inlineStr">
-        <is>
-          <t>m</t>
+      <c r="J533" s="22" t="n"/>
+    </row>
+    <row r="534" ht="12" customHeight="1">
+      <c r="A534" s="6" t="n"/>
+      <c r="B534" s="6" t="n"/>
+      <c r="C534" s="23" t="inlineStr">
+        <is>
+          <t>Ana dağıtım panosu girişi</t>
+        </is>
+      </c>
+      <c r="D534" s="6" t="n"/>
+      <c r="E534" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F534" s="6" t="n"/>
+      <c r="G534" s="6" t="n"/>
+      <c r="H534" s="6" t="n"/>
+      <c r="I534" s="24">
+        <f>E534*J534</f>
+        <v/>
+      </c>
+      <c r="J534" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="22" t="n"/>
+      <c r="B535" s="22" t="n"/>
+      <c r="C535" s="25" t="inlineStr">
+        <is>
+          <t>M66 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D535" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E535" s="22" t="n"/>
+      <c r="F535" s="22" t="n"/>
+      <c r="G535" s="22" t="n"/>
+      <c r="H535" s="22" t="n"/>
+      <c r="I535" s="22" t="n"/>
+      <c r="J535" s="27">
+        <f>SUM(I534:I534)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="536" ht="15" customHeight="1">
+      <c r="A536" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B536" s="20" t="inlineStr">
+        <is>
+          <t>35.115.1003</t>
+        </is>
+      </c>
+      <c r="C536" s="8" t="inlineStr">
+        <is>
+          <t>[M69]  Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+        </is>
+      </c>
+      <c r="D536" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
         </is>
       </c>
       <c r="E536" s="22" t="n"/>
@@ -17797,69 +17824,69 @@
       <c r="G536" s="22" t="n"/>
       <c r="H536" s="22" t="n"/>
       <c r="I536" s="22" t="n"/>
-      <c r="J536" s="27">
-        <f>SUM(I535:I535)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="537" ht="22" customHeight="1">
-      <c r="A537" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B537" s="20" t="inlineStr">
-        <is>
-          <t>35.140.3101</t>
-        </is>
-      </c>
-      <c r="C537" s="8" t="inlineStr">
-        <is>
-          <t>[M72]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
-        </is>
-      </c>
-      <c r="D537" s="21" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E537" s="22" t="n"/>
-      <c r="F537" s="22" t="n"/>
-      <c r="G537" s="22" t="n"/>
-      <c r="H537" s="22" t="n"/>
-      <c r="I537" s="22" t="n"/>
-      <c r="J537" s="22" t="n"/>
-    </row>
-    <row r="538" ht="12" customHeight="1">
-      <c r="A538" s="6" t="n"/>
-      <c r="B538" s="6" t="n"/>
-      <c r="C538" s="23" t="inlineStr">
-        <is>
-          <t>Saha aydınlatma direkleri besleme hattı</t>
-        </is>
-      </c>
-      <c r="D538" s="6" t="n"/>
-      <c r="E538" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F538" s="6" t="n"/>
-      <c r="G538" s="6" t="n"/>
-      <c r="H538" s="6" t="n"/>
-      <c r="I538" s="24">
-        <f>E538*J538</f>
-        <v/>
-      </c>
-      <c r="J538" s="30" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" s="22" t="n"/>
-      <c r="B539" s="22" t="n"/>
-      <c r="C539" s="25" t="inlineStr">
-        <is>
-          <t>M72 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D539" s="26" t="inlineStr">
+      <c r="J536" s="22" t="n"/>
+    </row>
+    <row r="537" ht="12" customHeight="1">
+      <c r="A537" s="6" t="n"/>
+      <c r="B537" s="6" t="n"/>
+      <c r="C537" s="23" t="inlineStr">
+        <is>
+          <t>Ana pano ve sayaç panosunda</t>
+        </is>
+      </c>
+      <c r="D537" s="6" t="n"/>
+      <c r="E537" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F537" s="6" t="n"/>
+      <c r="G537" s="6" t="n"/>
+      <c r="H537" s="6" t="n"/>
+      <c r="I537" s="24">
+        <f>E537*J537</f>
+        <v/>
+      </c>
+      <c r="J537" s="30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="22" t="n"/>
+      <c r="B538" s="22" t="n"/>
+      <c r="C538" s="25" t="inlineStr">
+        <is>
+          <t>M69 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D538" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E538" s="22" t="n"/>
+      <c r="F538" s="22" t="n"/>
+      <c r="G538" s="22" t="n"/>
+      <c r="H538" s="22" t="n"/>
+      <c r="I538" s="22" t="n"/>
+      <c r="J538" s="27">
+        <f>SUM(I537:I537)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="539" ht="22" customHeight="1">
+      <c r="A539" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B539" s="20" t="inlineStr">
+        <is>
+          <t>35.140.3105</t>
+        </is>
+      </c>
+      <c r="C539" s="8" t="inlineStr">
+        <is>
+          <t>[M70]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
+        </is>
+      </c>
+      <c r="D539" s="21" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -17869,71 +17896,71 @@
       <c r="G539" s="22" t="n"/>
       <c r="H539" s="22" t="n"/>
       <c r="I539" s="22" t="n"/>
-      <c r="J539" s="27">
-        <f>SUM(I538:I538)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="540" ht="22" customHeight="1">
-      <c r="A540" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B540" s="20" t="inlineStr">
-        <is>
-          <t>35.172.1706</t>
-        </is>
-      </c>
-      <c r="C540" s="8" t="inlineStr">
-        <is>
-          <t>[M82]  Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
-        </is>
-      </c>
-      <c r="D540" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E540" s="22" t="n"/>
-      <c r="F540" s="22" t="n"/>
-      <c r="G540" s="22" t="n"/>
-      <c r="H540" s="22" t="n"/>
-      <c r="I540" s="22" t="n"/>
-      <c r="J540" s="22" t="n"/>
-    </row>
-    <row r="541" ht="12" customHeight="1">
-      <c r="A541" s="6" t="n"/>
-      <c r="B541" s="6" t="n"/>
-      <c r="C541" s="23" t="inlineStr">
-        <is>
-          <t>Tesis içi yol ve saha aydınlatması</t>
-        </is>
-      </c>
-      <c r="D541" s="6" t="n"/>
-      <c r="E541" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F541" s="6" t="n"/>
-      <c r="G541" s="6" t="n"/>
-      <c r="H541" s="6" t="n"/>
-      <c r="I541" s="24">
-        <f>E541*J541</f>
-        <v/>
-      </c>
-      <c r="J541" s="30" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" s="22" t="n"/>
-      <c r="B542" s="22" t="n"/>
-      <c r="C542" s="25" t="inlineStr">
-        <is>
-          <t>M82 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D542" s="26" t="inlineStr">
-        <is>
-          <t>ad</t>
+      <c r="J539" s="22" t="n"/>
+    </row>
+    <row r="540" ht="12" customHeight="1">
+      <c r="A540" s="6" t="n"/>
+      <c r="B540" s="6" t="n"/>
+      <c r="C540" s="23" t="inlineStr">
+        <is>
+          <t>Şebeke bağlantı noktası - ana dağıtım panosu</t>
+        </is>
+      </c>
+      <c r="D540" s="6" t="n"/>
+      <c r="E540" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F540" s="6" t="n"/>
+      <c r="G540" s="6" t="n"/>
+      <c r="H540" s="6" t="n"/>
+      <c r="I540" s="24">
+        <f>E540*J540</f>
+        <v/>
+      </c>
+      <c r="J540" s="30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="22" t="n"/>
+      <c r="B541" s="22" t="n"/>
+      <c r="C541" s="25" t="inlineStr">
+        <is>
+          <t>M70 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D541" s="26" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E541" s="22" t="n"/>
+      <c r="F541" s="22" t="n"/>
+      <c r="G541" s="22" t="n"/>
+      <c r="H541" s="22" t="n"/>
+      <c r="I541" s="22" t="n"/>
+      <c r="J541" s="27">
+        <f>SUM(I540:I540)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="542" ht="22" customHeight="1">
+      <c r="A542" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B542" s="20" t="inlineStr">
+        <is>
+          <t>35.140.3101</t>
+        </is>
+      </c>
+      <c r="C542" s="8" t="inlineStr">
+        <is>
+          <t>[M72]  YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+        </is>
+      </c>
+      <c r="D542" s="21" t="inlineStr">
+        <is>
+          <t>m</t>
         </is>
       </c>
       <c r="E542" s="22" t="n"/>
@@ -17941,69 +17968,69 @@
       <c r="G542" s="22" t="n"/>
       <c r="H542" s="22" t="n"/>
       <c r="I542" s="22" t="n"/>
-      <c r="J542" s="27">
-        <f>SUM(I541:I541)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="543" ht="15" customHeight="1">
-      <c r="A543" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B543" s="20" t="inlineStr">
-        <is>
-          <t>35.170.4002</t>
-        </is>
-      </c>
-      <c r="C543" s="8" t="inlineStr">
-        <is>
-          <t>[M83]  LED projektör, ışık akısı en az 5100 lm</t>
-        </is>
-      </c>
-      <c r="D543" s="21" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E543" s="22" t="n"/>
-      <c r="F543" s="22" t="n"/>
-      <c r="G543" s="22" t="n"/>
-      <c r="H543" s="22" t="n"/>
-      <c r="I543" s="22" t="n"/>
-      <c r="J543" s="22" t="n"/>
-    </row>
-    <row r="544" ht="12" customHeight="1">
-      <c r="A544" s="6" t="n"/>
-      <c r="B544" s="6" t="n"/>
-      <c r="C544" s="23" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği başına 1 adet</t>
-        </is>
-      </c>
-      <c r="D544" s="6" t="n"/>
-      <c r="E544" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F544" s="6" t="n"/>
-      <c r="G544" s="6" t="n"/>
-      <c r="H544" s="6" t="n"/>
-      <c r="I544" s="24">
-        <f>E544*J544</f>
-        <v/>
-      </c>
-      <c r="J544" s="30" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" s="22" t="n"/>
-      <c r="B545" s="22" t="n"/>
-      <c r="C545" s="25" t="inlineStr">
-        <is>
-          <t>M83 TOPLAMI</t>
-        </is>
-      </c>
-      <c r="D545" s="26" t="inlineStr">
+      <c r="J542" s="22" t="n"/>
+    </row>
+    <row r="543" ht="12" customHeight="1">
+      <c r="A543" s="6" t="n"/>
+      <c r="B543" s="6" t="n"/>
+      <c r="C543" s="23" t="inlineStr">
+        <is>
+          <t>Saha aydınlatma direkleri besleme hattı</t>
+        </is>
+      </c>
+      <c r="D543" s="6" t="n"/>
+      <c r="E543" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F543" s="6" t="n"/>
+      <c r="G543" s="6" t="n"/>
+      <c r="H543" s="6" t="n"/>
+      <c r="I543" s="24">
+        <f>E543*J543</f>
+        <v/>
+      </c>
+      <c r="J543" s="30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="22" t="n"/>
+      <c r="B544" s="22" t="n"/>
+      <c r="C544" s="25" t="inlineStr">
+        <is>
+          <t>M72 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D544" s="26" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E544" s="22" t="n"/>
+      <c r="F544" s="22" t="n"/>
+      <c r="G544" s="22" t="n"/>
+      <c r="H544" s="22" t="n"/>
+      <c r="I544" s="22" t="n"/>
+      <c r="J544" s="27">
+        <f>SUM(I543:I543)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="545" ht="22" customHeight="1">
+      <c r="A545" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B545" s="20" t="inlineStr">
+        <is>
+          <t>35.172.1706</t>
+        </is>
+      </c>
+      <c r="C545" s="8" t="inlineStr">
+        <is>
+          <t>[M82]  Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
+        </is>
+      </c>
+      <c r="D545" s="21" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
@@ -18013,51 +18040,166 @@
       <c r="G545" s="22" t="n"/>
       <c r="H545" s="22" t="n"/>
       <c r="I545" s="22" t="n"/>
-      <c r="J545" s="27">
-        <f>SUM(I544:I544)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="546"/>
+      <c r="J545" s="22" t="n"/>
+    </row>
+    <row r="546" ht="12" customHeight="1">
+      <c r="A546" s="6" t="n"/>
+      <c r="B546" s="6" t="n"/>
+      <c r="C546" s="23" t="inlineStr">
+        <is>
+          <t>Tesis içi yol ve saha aydınlatması</t>
+        </is>
+      </c>
+      <c r="D546" s="6" t="n"/>
+      <c r="E546" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F546" s="6" t="n"/>
+      <c r="G546" s="6" t="n"/>
+      <c r="H546" s="6" t="n"/>
+      <c r="I546" s="24">
+        <f>E546*J546</f>
+        <v/>
+      </c>
+      <c r="J546" s="30" t="n">
+        <v>4</v>
+      </c>
+    </row>
     <row r="547">
-      <c r="A547" s="16" t="inlineStr">
+      <c r="A547" s="22" t="n"/>
+      <c r="B547" s="22" t="n"/>
+      <c r="C547" s="25" t="inlineStr">
+        <is>
+          <t>M82 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D547" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E547" s="22" t="n"/>
+      <c r="F547" s="22" t="n"/>
+      <c r="G547" s="22" t="n"/>
+      <c r="H547" s="22" t="n"/>
+      <c r="I547" s="22" t="n"/>
+      <c r="J547" s="27">
+        <f>SUM(I546:I546)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="548" ht="15" customHeight="1">
+      <c r="A548" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B548" s="20" t="inlineStr">
+        <is>
+          <t>35.170.4002</t>
+        </is>
+      </c>
+      <c r="C548" s="8" t="inlineStr">
+        <is>
+          <t>[M83]  LED projektör, ışık akısı en az 5100 lm</t>
+        </is>
+      </c>
+      <c r="D548" s="21" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E548" s="22" t="n"/>
+      <c r="F548" s="22" t="n"/>
+      <c r="G548" s="22" t="n"/>
+      <c r="H548" s="22" t="n"/>
+      <c r="I548" s="22" t="n"/>
+      <c r="J548" s="22" t="n"/>
+    </row>
+    <row r="549" ht="12" customHeight="1">
+      <c r="A549" s="6" t="n"/>
+      <c r="B549" s="6" t="n"/>
+      <c r="C549" s="23" t="inlineStr">
+        <is>
+          <t>Aydınlatma direği başına 1 adet</t>
+        </is>
+      </c>
+      <c r="D549" s="6" t="n"/>
+      <c r="E549" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F549" s="6" t="n"/>
+      <c r="G549" s="6" t="n"/>
+      <c r="H549" s="6" t="n"/>
+      <c r="I549" s="24">
+        <f>E549*J549</f>
+        <v/>
+      </c>
+      <c r="J549" s="30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="22" t="n"/>
+      <c r="B550" s="22" t="n"/>
+      <c r="C550" s="25" t="inlineStr">
+        <is>
+          <t>M83 TOPLAMI</t>
+        </is>
+      </c>
+      <c r="D550" s="26" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="E550" s="22" t="n"/>
+      <c r="F550" s="22" t="n"/>
+      <c r="G550" s="22" t="n"/>
+      <c r="H550" s="22" t="n"/>
+      <c r="I550" s="22" t="n"/>
+      <c r="J550" s="27">
+        <f>SUM(I549:I549)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="551"/>
+    <row r="552">
+      <c r="A552" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B547" s="6" t="n"/>
-      <c r="C547" s="6" t="n"/>
-      <c r="D547" s="6" t="n"/>
-      <c r="E547" s="6" t="n"/>
-      <c r="F547" s="6" t="n"/>
-      <c r="G547" s="6" t="n"/>
-      <c r="H547" s="6" t="n"/>
-      <c r="I547" s="6" t="n"/>
-      <c r="J547" s="6" t="n"/>
-    </row>
-    <row r="548" ht="13" customHeight="1">
-      <c r="A548" s="17" t="inlineStr">
+      <c r="B552" s="6" t="n"/>
+      <c r="C552" s="6" t="n"/>
+      <c r="D552" s="6" t="n"/>
+      <c r="E552" s="6" t="n"/>
+      <c r="F552" s="6" t="n"/>
+      <c r="G552" s="6" t="n"/>
+      <c r="H552" s="6" t="n"/>
+      <c r="I552" s="6" t="n"/>
+      <c r="J552" s="6" t="n"/>
+    </row>
+    <row r="553" ht="13" customHeight="1">
+      <c r="A553" s="17" t="inlineStr">
         <is>
           <t>•  Miktar sütunundaki her formül yalnızca o satırdaki ölçü hücrelerini çarpar; hiçbir sayı formülün içine gömülmemiştir.</t>
         </is>
       </c>
     </row>
-    <row r="549" ht="13" customHeight="1">
-      <c r="A549" s="17" t="inlineStr">
+    <row r="554" ht="13" customHeight="1">
+      <c r="A554" s="17" t="inlineStr">
         <is>
           <t>•  Son sütundaki katsayı, birim ağırlık (kg/m², kg/m³, ton/m²), bindirme payı, üçgen alan çarpanı (0,50) veya adet çarpanıdır.</t>
         </is>
       </c>
     </row>
-    <row r="550" ht="22" customHeight="1">
-      <c r="A550" s="17" t="inlineStr">
+    <row r="555" ht="22" customHeight="1">
+      <c r="A555" s="17" t="inlineStr">
         <is>
           <t>•  Ölçüler mimari ve betonarme paftalardan alınmıştır; kümes temellerinin beton, kalıp ve donatı miktarları doğrudan betonarme paftasındaki METRAJ tablosundandır.</t>
         </is>
       </c>
     </row>
-    <row r="551" ht="13" customHeight="1">
-      <c r="A551" s="17" t="inlineStr">
+    <row r="556" ht="13" customHeight="1">
+      <c r="A556" s="17" t="inlineStr">
         <is>
           <t>•  (-) işaretli satırlar minha edilen (düşülen) miktarlardır.</t>
         </is>
@@ -18065,22 +18207,22 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A550:J550"/>
+    <mergeCell ref="A450:J450"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A415:J415"/>
+    <mergeCell ref="A497:J497"/>
     <mergeCell ref="A361:J361"/>
-    <mergeCell ref="A549:J549"/>
-    <mergeCell ref="A492:J492"/>
+    <mergeCell ref="A552:J552"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A427:J427"/>
-    <mergeCell ref="A548:J548"/>
-    <mergeCell ref="A551:J551"/>
+    <mergeCell ref="A556:J556"/>
+    <mergeCell ref="A473:J473"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A468:J468"/>
-    <mergeCell ref="A547:J547"/>
+    <mergeCell ref="A553:J553"/>
+    <mergeCell ref="A555:J555"/>
     <mergeCell ref="A183:J183"/>
-    <mergeCell ref="A445:J445"/>
+    <mergeCell ref="A554:J554"/>
     <mergeCell ref="A392:J392"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18094,7 +18236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K149"/>
+  <dimension ref="A1:K154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21354,11 +21496,11 @@
       <c r="J119" s="22" t="n"/>
       <c r="K119" s="22" t="n"/>
     </row>
-    <row r="120" ht="12" customHeight="1">
+    <row r="120" ht="20" customHeight="1">
       <c r="A120" s="6" t="n"/>
       <c r="B120" s="23" t="inlineStr">
         <is>
-          <t>Kaideler 2,90 x 2,90 x 0,50 m³, 2 adet; 90 kg/m³</t>
+          <t>Radye temel — proje METRAJ tablosu 198,80 kg/kaide; 2 kaide</t>
         </is>
       </c>
       <c r="C120" s="6" t="n"/>
@@ -21368,638 +21510,773 @@
       <c r="E120" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F120" s="29" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="G120" s="29" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="F120" s="6" t="n"/>
+      <c r="G120" s="6" t="n"/>
       <c r="H120" s="36" t="inlineStr">
         <is>
           <t>ø8-12 nervürlü</t>
         </is>
       </c>
       <c r="I120" s="33" t="n">
+        <v>0.1988</v>
+      </c>
+      <c r="J120" s="34">
+        <f>D120*E120*I120</f>
+        <v/>
+      </c>
+      <c r="K120" s="6" t="n"/>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="n"/>
+      <c r="B121" s="23" t="inlineStr">
+        <is>
+          <t>SB01…SB04 kolonları — proje METRAJ tablosu 72,59 kg/kaide; 2 kaide</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="n"/>
+      <c r="G121" s="6" t="n"/>
+      <c r="H121" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I121" s="33" t="n">
+        <v>0.07259</v>
+      </c>
+      <c r="J121" s="34">
+        <f>D121*E121*I121</f>
+        <v/>
+      </c>
+      <c r="K121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="22" t="n"/>
+      <c r="B122" s="25" t="inlineStr">
+        <is>
+          <t>SL/M26 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C122" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="n"/>
+      <c r="E122" s="22" t="n"/>
+      <c r="F122" s="22" t="n"/>
+      <c r="G122" s="22" t="n"/>
+      <c r="H122" s="22" t="n"/>
+      <c r="I122" s="22" t="n"/>
+      <c r="J122" s="22" t="n"/>
+      <c r="K122" s="35">
+        <f>SUM(J120:J121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>[M28]  Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="n"/>
+      <c r="E123" s="22" t="n"/>
+      <c r="F123" s="22" t="n"/>
+      <c r="G123" s="22" t="n"/>
+      <c r="H123" s="22" t="n"/>
+      <c r="I123" s="22" t="n"/>
+      <c r="J123" s="22" t="n"/>
+      <c r="K123" s="22" t="n"/>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="6" t="n"/>
+      <c r="B124" s="23" t="inlineStr">
+        <is>
+          <t>Radye kolon filizleri P07 48ø14 l=160 — proje METRAJ tablosu 92,70 kg/kaide; 2 kaide</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="n"/>
+      <c r="D124" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="n"/>
+      <c r="G124" s="6" t="n"/>
+      <c r="H124" s="36" t="inlineStr">
+        <is>
+          <t>ø14 nervürlü</t>
+        </is>
+      </c>
+      <c r="I124" s="33" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="J124" s="34">
+        <f>D124*E124*I124</f>
+        <v/>
+      </c>
+      <c r="K124" s="6" t="n"/>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="6" t="n"/>
+      <c r="B125" s="23" t="inlineStr">
+        <is>
+          <t>SB01…SB04 kolon boyuna donatısı 12ø14 — proje METRAJ tablosu 85,70 kg/kaide; 2 kaide</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="n"/>
+      <c r="G125" s="6" t="n"/>
+      <c r="H125" s="36" t="inlineStr">
+        <is>
+          <t>ø14 nervürlü</t>
+        </is>
+      </c>
+      <c r="I125" s="33" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="J125" s="34">
+        <f>D125*E125*I125</f>
+        <v/>
+      </c>
+      <c r="K125" s="6" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="22" t="n"/>
+      <c r="B126" s="25" t="inlineStr">
+        <is>
+          <t>SL/M28 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C126" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="n"/>
+      <c r="E126" s="22" t="n"/>
+      <c r="F126" s="22" t="n"/>
+      <c r="G126" s="22" t="n"/>
+      <c r="H126" s="22" t="n"/>
+      <c r="I126" s="22" t="n"/>
+      <c r="J126" s="22" t="n"/>
+      <c r="K126" s="35">
+        <f>SUM(J124:J125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127"/>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: SU DEPOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I129" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="n"/>
+      <c r="E130" s="22" t="n"/>
+      <c r="F130" s="22" t="n"/>
+      <c r="G130" s="22" t="n"/>
+      <c r="H130" s="22" t="n"/>
+      <c r="I130" s="22" t="n"/>
+      <c r="J130" s="22" t="n"/>
+      <c r="K130" s="22" t="n"/>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="6" t="n"/>
+      <c r="B131" s="23" t="inlineStr">
+        <is>
+          <t>Radye ve üst döşeme — proje metrajı 223,70 + 32,90 = 256,60 kg</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="n"/>
+      <c r="D131" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="6" t="n"/>
+      <c r="G131" s="6" t="n"/>
+      <c r="H131" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I131" s="33" t="n">
+        <v>0.2566</v>
+      </c>
+      <c r="J131" s="34">
+        <f>D131*E131*I131</f>
+        <v/>
+      </c>
+      <c r="K131" s="6" t="n"/>
+    </row>
+    <row r="132" ht="12" customHeight="1">
+      <c r="A132" s="6" t="n"/>
+      <c r="B132" s="23" t="inlineStr">
+        <is>
+          <t>Perdeler 13,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="n"/>
+      <c r="D132" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G132" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H132" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I132" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J132" s="34">
+        <f>D132*E132*F132*G132*I132</f>
+        <v/>
+      </c>
+      <c r="K132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="22" t="n"/>
+      <c r="B133" s="25" t="inlineStr">
+        <is>
+          <t>SD/M26 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C133" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="n"/>
+      <c r="E133" s="22" t="n"/>
+      <c r="F133" s="22" t="n"/>
+      <c r="G133" s="22" t="n"/>
+      <c r="H133" s="22" t="n"/>
+      <c r="I133" s="22" t="n"/>
+      <c r="J133" s="22" t="n"/>
+      <c r="K133" s="35">
+        <f>SUM(J131:J132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134"/>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: YAĞMUR SUYU DEPOSU</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K136" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="n"/>
+      <c r="E137" s="22" t="n"/>
+      <c r="F137" s="22" t="n"/>
+      <c r="G137" s="22" t="n"/>
+      <c r="H137" s="22" t="n"/>
+      <c r="I137" s="22" t="n"/>
+      <c r="J137" s="22" t="n"/>
+      <c r="K137" s="22" t="n"/>
+    </row>
+    <row r="138" ht="12" customHeight="1">
+      <c r="A138" s="6" t="n"/>
+      <c r="B138" s="23" t="inlineStr">
+        <is>
+          <t>Radye 3,00 x 3,00 x 0,30 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="n"/>
+      <c r="D138" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G138" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H138" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I138" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J138" s="34">
+        <f>D138*E138*F138*G138*I138</f>
+        <v/>
+      </c>
+      <c r="K138" s="6" t="n"/>
+    </row>
+    <row r="139" ht="12" customHeight="1">
+      <c r="A139" s="6" t="n"/>
+      <c r="B139" s="23" t="inlineStr">
+        <is>
+          <t>Perdeler 11,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G139" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H139" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I139" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J139" s="34">
+        <f>D139*E139*F139*G139*I139</f>
+        <v/>
+      </c>
+      <c r="K139" s="6" t="n"/>
+    </row>
+    <row r="140" ht="12" customHeight="1">
+      <c r="A140" s="6" t="n"/>
+      <c r="B140" s="23" t="inlineStr">
+        <is>
+          <t>Üst döşeme 3,00 x 3,00 x 0,15 m³; 100 kg/m³</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G140" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H140" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I140" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J140" s="34">
+        <f>D140*E140*F140*G140*I140</f>
+        <v/>
+      </c>
+      <c r="K140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="22" t="n"/>
+      <c r="B141" s="25" t="inlineStr">
+        <is>
+          <t>YD/M26 GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C141" s="26" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="n"/>
+      <c r="E141" s="22" t="n"/>
+      <c r="F141" s="22" t="n"/>
+      <c r="G141" s="22" t="n"/>
+      <c r="H141" s="22" t="n"/>
+      <c r="I141" s="22" t="n"/>
+      <c r="J141" s="22" t="n"/>
+      <c r="K141" s="35">
+        <f>SUM(J138:J140)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142"/>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>Tanımı</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>Benzer</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>Adet</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>Boy (m)</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>En (m)</t>
+        </is>
+      </c>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>Demir çapı veya profil tipi</t>
+        </is>
+      </c>
+      <c r="I144" s="7" t="inlineStr">
+        <is>
+          <t>Birim Ağırlık</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>Toplam Ağırlık</t>
+        </is>
+      </c>
+      <c r="K144" s="7" t="inlineStr">
+        <is>
+          <t>Genel Toplam</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="20" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>[M61C]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="D145" s="22" t="n"/>
+      <c r="E145" s="22" t="n"/>
+      <c r="F145" s="22" t="n"/>
+      <c r="G145" s="22" t="n"/>
+      <c r="H145" s="22" t="n"/>
+      <c r="I145" s="22" t="n"/>
+      <c r="J145" s="22" t="n"/>
+      <c r="K145" s="22" t="n"/>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="6" t="n"/>
+      <c r="B146" s="23" t="inlineStr">
+        <is>
+          <t>Betonarme rögarlar — beton hacmi 1,566 m³, ortalama donatı oranı 90 kg/m³</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="n"/>
+      <c r="D146" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="29" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="G146" s="6" t="n"/>
+      <c r="H146" s="36" t="inlineStr">
+        <is>
+          <t>ø8-12 nervürlü</t>
+        </is>
+      </c>
+      <c r="I146" s="33" t="n">
         <v>0.09</v>
       </c>
-      <c r="J120" s="34">
-        <f>D120*E120*F120*G120*I120</f>
-        <v/>
-      </c>
-      <c r="K120" s="6" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="22" t="n"/>
-      <c r="B121" s="25" t="inlineStr">
-        <is>
-          <t>SL/M26 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C121" s="26" t="inlineStr">
+      <c r="J146" s="34">
+        <f>D146*E146*F146*I146</f>
+        <v/>
+      </c>
+      <c r="K146" s="6" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="22" t="n"/>
+      <c r="B147" s="25" t="inlineStr">
+        <is>
+          <t>SA/M61C GENEL TOPLAM</t>
+        </is>
+      </c>
+      <c r="C147" s="26" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="D121" s="22" t="n"/>
-      <c r="E121" s="22" t="n"/>
-      <c r="F121" s="22" t="n"/>
-      <c r="G121" s="22" t="n"/>
-      <c r="H121" s="22" t="n"/>
-      <c r="I121" s="22" t="n"/>
-      <c r="J121" s="22" t="n"/>
-      <c r="K121" s="35">
-        <f>SUM(J120:J120)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122"/>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: SU DEPOSU</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı</t>
-        </is>
-      </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>Benzer</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="H124" s="7" t="inlineStr">
-        <is>
-          <t>Demir çapı veya profil tipi</t>
-        </is>
-      </c>
-      <c r="I124" s="7" t="inlineStr">
-        <is>
-          <t>Birim Ağırlık</t>
-        </is>
-      </c>
-      <c r="J124" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Ağırlık</t>
-        </is>
-      </c>
-      <c r="K124" s="7" t="inlineStr">
-        <is>
-          <t>Genel Toplam</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="B125" s="8" t="inlineStr">
-        <is>
-          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="C125" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D125" s="22" t="n"/>
-      <c r="E125" s="22" t="n"/>
-      <c r="F125" s="22" t="n"/>
-      <c r="G125" s="22" t="n"/>
-      <c r="H125" s="22" t="n"/>
-      <c r="I125" s="22" t="n"/>
-      <c r="J125" s="22" t="n"/>
-      <c r="K125" s="22" t="n"/>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="6" t="n"/>
-      <c r="B126" s="23" t="inlineStr">
-        <is>
-          <t>Radye ve üst döşeme — proje metrajı 223,70 + 32,90 = 256,60 kg</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="n"/>
-      <c r="D126" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="6" t="n"/>
-      <c r="G126" s="6" t="n"/>
-      <c r="H126" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I126" s="33" t="n">
-        <v>0.2566</v>
-      </c>
-      <c r="J126" s="34">
-        <f>D126*E126*I126</f>
-        <v/>
-      </c>
-      <c r="K126" s="6" t="n"/>
-    </row>
-    <row r="127" ht="12" customHeight="1">
-      <c r="A127" s="6" t="n"/>
-      <c r="B127" s="23" t="inlineStr">
-        <is>
-          <t>Perdeler 13,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="n"/>
-      <c r="D127" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" s="29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="G127" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H127" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I127" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J127" s="34">
-        <f>D127*E127*F127*G127*I127</f>
-        <v/>
-      </c>
-      <c r="K127" s="6" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="22" t="n"/>
-      <c r="B128" s="25" t="inlineStr">
-        <is>
-          <t>SD/M26 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C128" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D128" s="22" t="n"/>
-      <c r="E128" s="22" t="n"/>
-      <c r="F128" s="22" t="n"/>
-      <c r="G128" s="22" t="n"/>
-      <c r="H128" s="22" t="n"/>
-      <c r="I128" s="22" t="n"/>
-      <c r="J128" s="22" t="n"/>
-      <c r="K128" s="35">
-        <f>SUM(J126:J127)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129"/>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: YAĞMUR SUYU DEPOSU</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="28" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı</t>
-        </is>
-      </c>
-      <c r="C131" s="7" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Benzer</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F131" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="H131" s="7" t="inlineStr">
-        <is>
-          <t>Demir çapı veya profil tipi</t>
-        </is>
-      </c>
-      <c r="I131" s="7" t="inlineStr">
-        <is>
-          <t>Birim Ağırlık</t>
-        </is>
-      </c>
-      <c r="J131" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Ağırlık</t>
-        </is>
-      </c>
-      <c r="K131" s="7" t="inlineStr">
-        <is>
-          <t>Genel Toplam</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>[M26]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="C132" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D132" s="22" t="n"/>
-      <c r="E132" s="22" t="n"/>
-      <c r="F132" s="22" t="n"/>
-      <c r="G132" s="22" t="n"/>
-      <c r="H132" s="22" t="n"/>
-      <c r="I132" s="22" t="n"/>
-      <c r="J132" s="22" t="n"/>
-      <c r="K132" s="22" t="n"/>
-    </row>
-    <row r="133" ht="12" customHeight="1">
-      <c r="A133" s="6" t="n"/>
-      <c r="B133" s="23" t="inlineStr">
-        <is>
-          <t>Radye 3,00 x 3,00 x 0,30 m³; 100 kg/m³</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="n"/>
-      <c r="D133" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F133" s="29" t="n">
-        <v>9</v>
-      </c>
-      <c r="G133" s="29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H133" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I133" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J133" s="34">
-        <f>D133*E133*F133*G133*I133</f>
-        <v/>
-      </c>
-      <c r="K133" s="6" t="n"/>
-    </row>
-    <row r="134" ht="12" customHeight="1">
-      <c r="A134" s="6" t="n"/>
-      <c r="B134" s="23" t="inlineStr">
-        <is>
-          <t>Perdeler 11,00 x 0,25 x 3,00 m³; 100 kg/m³</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="n"/>
-      <c r="D134" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F134" s="29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="G134" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H134" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I134" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J134" s="34">
-        <f>D134*E134*F134*G134*I134</f>
-        <v/>
-      </c>
-      <c r="K134" s="6" t="n"/>
-    </row>
-    <row r="135" ht="12" customHeight="1">
-      <c r="A135" s="6" t="n"/>
-      <c r="B135" s="23" t="inlineStr">
-        <is>
-          <t>Üst döşeme 3,00 x 3,00 x 0,15 m³; 100 kg/m³</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="n"/>
-      <c r="D135" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F135" s="29" t="n">
-        <v>9</v>
-      </c>
-      <c r="G135" s="29" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H135" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I135" s="33" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J135" s="34">
-        <f>D135*E135*F135*G135*I135</f>
-        <v/>
-      </c>
-      <c r="K135" s="6" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="22" t="n"/>
-      <c r="B136" s="25" t="inlineStr">
-        <is>
-          <t>YD/M26 GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C136" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D136" s="22" t="n"/>
-      <c r="E136" s="22" t="n"/>
-      <c r="F136" s="22" t="n"/>
-      <c r="G136" s="22" t="n"/>
-      <c r="H136" s="22" t="n"/>
-      <c r="I136" s="22" t="n"/>
-      <c r="J136" s="22" t="n"/>
-      <c r="K136" s="35">
-        <f>SUM(J133:J135)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137"/>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="18" t="inlineStr">
-        <is>
-          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="28" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>Tanımı</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>Benzer</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>Adet</t>
-        </is>
-      </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>Boy (m)</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>En (m)</t>
-        </is>
-      </c>
-      <c r="H139" s="7" t="inlineStr">
-        <is>
-          <t>Demir çapı veya profil tipi</t>
-        </is>
-      </c>
-      <c r="I139" s="7" t="inlineStr">
-        <is>
-          <t>Birim Ağırlık</t>
-        </is>
-      </c>
-      <c r="J139" s="7" t="inlineStr">
-        <is>
-          <t>Toplam Ağırlık</t>
-        </is>
-      </c>
-      <c r="K139" s="7" t="inlineStr">
-        <is>
-          <t>Genel Toplam</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="22" customHeight="1">
-      <c r="A140" s="20" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>[M61C]  Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="C140" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D140" s="22" t="n"/>
-      <c r="E140" s="22" t="n"/>
-      <c r="F140" s="22" t="n"/>
-      <c r="G140" s="22" t="n"/>
-      <c r="H140" s="22" t="n"/>
-      <c r="I140" s="22" t="n"/>
-      <c r="J140" s="22" t="n"/>
-      <c r="K140" s="22" t="n"/>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="6" t="n"/>
-      <c r="B141" s="23" t="inlineStr">
-        <is>
-          <t>Betonarme rögarlar — beton hacmi 1,566 m³, ortalama donatı oranı 90 kg/m³</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="n"/>
-      <c r="D141" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F141" s="29" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="G141" s="6" t="n"/>
-      <c r="H141" s="36" t="inlineStr">
-        <is>
-          <t>ø8-12 nervürlü</t>
-        </is>
-      </c>
-      <c r="I141" s="33" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J141" s="34">
-        <f>D141*E141*F141*I141</f>
-        <v/>
-      </c>
-      <c r="K141" s="6" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="22" t="n"/>
-      <c r="B142" s="25" t="inlineStr">
-        <is>
-          <t>SA/M61C GENEL TOPLAM</t>
-        </is>
-      </c>
-      <c r="C142" s="26" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="D142" s="22" t="n"/>
-      <c r="E142" s="22" t="n"/>
-      <c r="F142" s="22" t="n"/>
-      <c r="G142" s="22" t="n"/>
-      <c r="H142" s="22" t="n"/>
-      <c r="I142" s="22" t="n"/>
-      <c r="J142" s="22" t="n"/>
-      <c r="K142" s="35">
-        <f>SUM(J141:J141)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143"/>
-    <row r="144">
-      <c r="A144" s="16" t="inlineStr">
+      <c r="D147" s="22" t="n"/>
+      <c r="E147" s="22" t="n"/>
+      <c r="F147" s="22" t="n"/>
+      <c r="G147" s="22" t="n"/>
+      <c r="H147" s="22" t="n"/>
+      <c r="I147" s="22" t="n"/>
+      <c r="J147" s="22" t="n"/>
+      <c r="K147" s="35">
+        <f>SUM(J146:J146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148"/>
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR VE VARSAYIMLAR</t>
         </is>
       </c>
-      <c r="B144" s="6" t="n"/>
-      <c r="C144" s="6" t="n"/>
-      <c r="D144" s="6" t="n"/>
-      <c r="E144" s="6" t="n"/>
-      <c r="F144" s="6" t="n"/>
-      <c r="G144" s="6" t="n"/>
-      <c r="H144" s="6" t="n"/>
-      <c r="I144" s="6" t="n"/>
-      <c r="J144" s="6" t="n"/>
-      <c r="K144" s="6" t="n"/>
-    </row>
-    <row r="145" ht="13" customHeight="1">
-      <c r="A145" s="17" t="inlineStr">
+      <c r="B149" s="6" t="n"/>
+      <c r="C149" s="6" t="n"/>
+      <c r="D149" s="6" t="n"/>
+      <c r="E149" s="6" t="n"/>
+      <c r="F149" s="6" t="n"/>
+      <c r="G149" s="6" t="n"/>
+      <c r="H149" s="6" t="n"/>
+      <c r="I149" s="6" t="n"/>
+      <c r="J149" s="6" t="n"/>
+      <c r="K149" s="6" t="n"/>
+    </row>
+    <row r="150" ht="13" customHeight="1">
+      <c r="A150" s="17" t="inlineStr">
         <is>
           <t>•  SARI zeminli 'demir çapı veya profil tipi' hücreleri, proje toplamını tutturmak üzere yapılan dağıtımı gösterir.</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="33" customHeight="1">
-      <c r="A146" s="17" t="inlineStr">
+    <row r="151" ht="33" customHeight="1">
+      <c r="A151" s="17" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok temellerinin donatı TOPLAMLARI betonarme paftasındaki METRAJ tablosundan aynen alınmıştır (blok başına ø6-12 = 4.159,89 kg, ø14-50 = 7.287,50 kg). Bu toplamlar eleman bazında dağıtılmış, dağıtılamayan kısım açıkça 'proje METRAJ tablosunu tamamlayan pay' satırı olarak gösterilmiştir. Genel toplamlar proje tablosuyla birebir tutmaktadır.</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="17" t="inlineStr">
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="17" t="inlineStr">
         <is>
           <t>•  ÇELİK TAŞIYICI SİSTEM STATİK ÇELİK PROJESİNDEN ALINMIŞTIR. Profiller SHS 150x150x6 (kolon, ana kiriş, boyuna kiriş), RHS 100x50x3 (çatı aşığı, yan aşık, kuşak) ve SHS 100x100x4 (çapraz); malzeme S235JR. Çerçeve geometrisi projedeki gibidir: aks açıklıkları 3,75 + 6,00 + 3,80 = 13,55 m, kolon üstü +2,84, mahya +4,34.</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="13" customHeight="1">
-      <c r="A148" s="17" t="inlineStr">
+    <row r="153" ht="13" customHeight="1">
+      <c r="A153" s="17" t="inlineStr">
         <is>
           <t>•  Gübre çukuru ve müştemilat donatısı, projedeki METRAJ tablolarından ve eleman hacmi x birim donatı oranı (kg/m³) esasıyla hesaplanmıştır.</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="17" t="inlineStr">
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="17" t="inlineStr">
         <is>
           <t>•  Birim ağırlıklar (ton/m): ø8 0,000395 · ø10 0,000617 · ø12 0,000888 · ø14 0,001210 · ø16 0,001580 · ø20 0,002470 · HEA 200 0,0423 · HEA 260 0,0541 · IPE 270 0,0361 · Z 200x70x2,5 0,00900 · L 70x70x7 0,00738.</t>
         </is>
@@ -22007,23 +22284,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A135:K135"/>
     <mergeCell ref="A149:K149"/>
-    <mergeCell ref="A145:K145"/>
+    <mergeCell ref="A143:K143"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A130:K130"/>
-    <mergeCell ref="A147:K147"/>
-    <mergeCell ref="A148:K148"/>
+    <mergeCell ref="A153:K153"/>
+    <mergeCell ref="A154:K154"/>
+    <mergeCell ref="A128:K128"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A152:K152"/>
     <mergeCell ref="A52:K52"/>
     <mergeCell ref="A99:K99"/>
     <mergeCell ref="A117:K117"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A123:K123"/>
-    <mergeCell ref="A138:K138"/>
+    <mergeCell ref="A151:K151"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A150:K150"/>
     <mergeCell ref="A110:K110"/>
-    <mergeCell ref="A146:K146"/>
-    <mergeCell ref="A144:K144"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/belgeler/IPARD_EVRAKLARI.xlsx
+++ b/belgeler/IPARD_EVRAKLARI.xlsx
@@ -14831,7 +14831,7 @@
     <row r="415" ht="20" customHeight="1">
       <c r="A415" s="18" t="inlineStr">
         <is>
-          <t>Yapı/Bina Adı: FOSEPTIK</t>
+          <t>Yapı/Bina Adı: FOSEPTİK</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15113,7 @@
     <row r="427" ht="20" customHeight="1">
       <c r="A427" s="18" t="inlineStr">
         <is>
-          <t>Yapı/Bina Adı: YEM SILOSU BETONARME KAIDELERI</t>
+          <t>Yapı/Bina Adı: YEM SİLOSU BETONARME KAİDELERİ</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
     <row r="497" ht="20" customHeight="1">
       <c r="A497" s="18" t="inlineStr">
         <is>
-          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
+          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESİ VE SAHA ALTYAPISI</t>
         </is>
       </c>
     </row>
@@ -21410,7 +21410,7 @@
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>Yapı/Bina Adı: YEM SILOSU BETONARME KAIDELERI</t>
+          <t>Yapı/Bina Adı: YEM SİLOSU BETONARME KAİDELERİ</t>
         </is>
       </c>
     </row>
@@ -22087,7 +22087,7 @@
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESI VE SAHA ALTYAPISI</t>
+          <t>Yapı/Bina Adı: ÇEVRE DÜZENLEMESİ VE SAHA ALTYAPISI</t>
         </is>
       </c>
     </row>
